--- a/outputs/SA_curtailment.xlsx
+++ b/outputs/SA_curtailment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V49"/>
+  <dimension ref="A1:X49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -481,6 +481,8 @@
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -531,65 +533,75 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Actual FY23-24</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Actual FY24-25</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>ELI Near Term</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ELI Med Term</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>FY24-25</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>FY25-26</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>FY26-27 (Draft)</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Curt FY1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Curt FY2</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Curt FY3</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Curt Avg</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Offl FY1</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Offl FY2</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Offl FY3</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Offl Avg</t>
         </is>
@@ -631,25 +643,31 @@
         <v>24.75</v>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="5" t="inlineStr"/>
-      <c r="K2" s="5" t="inlineStr"/>
-      <c r="L2" s="5" t="n">
+      <c r="J2" s="5" t="n">
+        <v>0.3222683455189714</v>
+      </c>
+      <c r="K2" s="5" t="n">
+        <v>0.2755625039739843</v>
+      </c>
+      <c r="L2" s="5" t="inlineStr"/>
+      <c r="M2" s="5" t="inlineStr"/>
+      <c r="N2" s="5" t="n">
         <v>1.0025</v>
       </c>
-      <c r="M2" s="5" t="n">
+      <c r="O2" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="N2" s="5" t="n">
+      <c r="P2" s="5" t="n">
         <v>1.0034</v>
       </c>
-      <c r="O2" s="6" t="inlineStr"/>
-      <c r="P2" s="6" t="inlineStr"/>
       <c r="Q2" s="6" t="inlineStr"/>
       <c r="R2" s="6" t="inlineStr"/>
       <c r="S2" s="6" t="inlineStr"/>
       <c r="T2" s="6" t="inlineStr"/>
       <c r="U2" s="6" t="inlineStr"/>
       <c r="V2" s="6" t="inlineStr"/>
+      <c r="W2" s="6" t="inlineStr"/>
+      <c r="X2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -689,23 +707,25 @@
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="5" t="inlineStr"/>
       <c r="K3" s="5" t="inlineStr"/>
-      <c r="L3" s="5" t="n">
+      <c r="L3" s="5" t="inlineStr"/>
+      <c r="M3" s="5" t="inlineStr"/>
+      <c r="N3" s="5" t="n">
         <v>1.0025</v>
       </c>
-      <c r="M3" s="5" t="n">
+      <c r="O3" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="N3" s="5" t="n">
+      <c r="P3" s="5" t="n">
         <v>1.0034</v>
       </c>
-      <c r="O3" s="6" t="inlineStr"/>
-      <c r="P3" s="6" t="inlineStr"/>
       <c r="Q3" s="6" t="inlineStr"/>
       <c r="R3" s="6" t="inlineStr"/>
       <c r="S3" s="6" t="inlineStr"/>
       <c r="T3" s="6" t="inlineStr"/>
       <c r="U3" s="6" t="inlineStr"/>
       <c r="V3" s="6" t="inlineStr"/>
+      <c r="W3" s="6" t="inlineStr"/>
+      <c r="X3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -745,23 +765,25 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
-      <c r="L4" s="5" t="n">
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="n">
         <v>1.0025</v>
       </c>
-      <c r="M4" s="5" t="n">
+      <c r="O4" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="N4" s="5" t="n">
+      <c r="P4" s="5" t="n">
         <v>1.0034</v>
       </c>
-      <c r="O4" s="6" t="inlineStr"/>
-      <c r="P4" s="6" t="inlineStr"/>
       <c r="Q4" s="6" t="inlineStr"/>
       <c r="R4" s="6" t="inlineStr"/>
       <c r="S4" s="6" t="inlineStr"/>
       <c r="T4" s="6" t="inlineStr"/>
       <c r="U4" s="6" t="inlineStr"/>
       <c r="V4" s="6" t="inlineStr"/>
+      <c r="W4" s="6" t="inlineStr"/>
+      <c r="X4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -799,25 +821,31 @@
         <v>8.25</v>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
-      <c r="L5" s="5" t="n">
+      <c r="J5" s="5" t="n">
+        <v>0.2483229876673971</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>0.1843730537306586</v>
+      </c>
+      <c r="L5" s="5" t="inlineStr"/>
+      <c r="M5" s="5" t="inlineStr"/>
+      <c r="N5" s="5" t="n">
         <v>1.0004</v>
       </c>
-      <c r="M5" s="5" t="n">
+      <c r="O5" s="5" t="n">
         <v>0.9999</v>
       </c>
-      <c r="N5" s="5" t="n">
+      <c r="P5" s="5" t="n">
         <v>1.0002</v>
       </c>
-      <c r="O5" s="6" t="inlineStr"/>
-      <c r="P5" s="6" t="inlineStr"/>
       <c r="Q5" s="6" t="inlineStr"/>
       <c r="R5" s="6" t="inlineStr"/>
       <c r="S5" s="6" t="inlineStr"/>
       <c r="T5" s="6" t="inlineStr"/>
       <c r="U5" s="6" t="inlineStr"/>
       <c r="V5" s="6" t="inlineStr"/>
+      <c r="W5" s="6" t="inlineStr"/>
+      <c r="X5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -862,26 +890,26 @@
         <v>132</v>
       </c>
       <c r="J6" s="5" t="n">
+        <v>0.2260441150541987</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>0.3551752959427892</v>
+      </c>
+      <c r="L6" s="5" t="n">
         <v>0.501077617843089</v>
       </c>
-      <c r="K6" s="5" t="n">
+      <c r="M6" s="5" t="n">
         <v>0.212860651220515</v>
       </c>
-      <c r="L6" s="5" t="n">
+      <c r="N6" s="5" t="n">
         <v>0.9565</v>
       </c>
-      <c r="M6" s="5" t="n">
+      <c r="O6" s="5" t="n">
         <v>0.9725</v>
       </c>
-      <c r="N6" s="5" t="n">
+      <c r="P6" s="5" t="n">
         <v>0.9698</v>
       </c>
-      <c r="O6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q6" s="6" t="n">
         <v>0</v>
       </c>
@@ -889,15 +917,21 @@
         <v>0</v>
       </c>
       <c r="S6" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="T6" s="6" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="U6" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="V6" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="W6" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="X6" s="6" t="n">
         <v>0.07333333333333335</v>
       </c>
     </row>
@@ -944,26 +978,26 @@
         <v>132</v>
       </c>
       <c r="J7" s="5" t="n">
+        <v>0.1877237381087118</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>0.2949469219730214</v>
+      </c>
+      <c r="L7" s="5" t="n">
         <v>0.501077617843089</v>
       </c>
-      <c r="K7" s="5" t="n">
+      <c r="M7" s="5" t="n">
         <v>0.212860651220515</v>
       </c>
-      <c r="L7" s="5" t="n">
+      <c r="N7" s="5" t="n">
         <v>0.9565</v>
       </c>
-      <c r="M7" s="5" t="n">
+      <c r="O7" s="5" t="n">
         <v>0.9725</v>
       </c>
-      <c r="N7" s="5" t="n">
+      <c r="P7" s="5" t="n">
         <v>0.9698</v>
       </c>
-      <c r="O7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
       </c>
@@ -971,15 +1005,21 @@
         <v>0</v>
       </c>
       <c r="S7" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="T7" s="6" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="U7" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="V7" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="W7" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="X7" s="6" t="n">
         <v>0.07333333333333335</v>
       </c>
     </row>
@@ -1021,23 +1061,25 @@
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="5" t="inlineStr"/>
       <c r="K8" s="5" t="inlineStr"/>
-      <c r="L8" s="5" t="n">
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="n">
         <v>1.0025</v>
       </c>
-      <c r="M8" s="5" t="n">
+      <c r="O8" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="N8" s="5" t="n">
+      <c r="P8" s="5" t="n">
         <v>1.0034</v>
       </c>
-      <c r="O8" s="6" t="inlineStr"/>
-      <c r="P8" s="6" t="inlineStr"/>
       <c r="Q8" s="6" t="inlineStr"/>
       <c r="R8" s="6" t="inlineStr"/>
       <c r="S8" s="6" t="inlineStr"/>
       <c r="T8" s="6" t="inlineStr"/>
       <c r="U8" s="6" t="inlineStr"/>
       <c r="V8" s="6" t="inlineStr"/>
+      <c r="W8" s="6" t="inlineStr"/>
+      <c r="X8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1077,23 +1119,25 @@
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="5" t="inlineStr"/>
       <c r="K9" s="5" t="inlineStr"/>
-      <c r="L9" s="5" t="n">
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="n">
         <v>1.0025</v>
       </c>
-      <c r="M9" s="5" t="n">
+      <c r="O9" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="N9" s="5" t="n">
+      <c r="P9" s="5" t="n">
         <v>1.0034</v>
       </c>
-      <c r="O9" s="6" t="inlineStr"/>
-      <c r="P9" s="6" t="inlineStr"/>
       <c r="Q9" s="6" t="inlineStr"/>
       <c r="R9" s="6" t="inlineStr"/>
       <c r="S9" s="6" t="inlineStr"/>
       <c r="T9" s="6" t="inlineStr"/>
       <c r="U9" s="6" t="inlineStr"/>
       <c r="V9" s="6" t="inlineStr"/>
+      <c r="W9" s="6" t="inlineStr"/>
+      <c r="X9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1138,28 +1182,34 @@
         <v>66</v>
       </c>
       <c r="J10" s="5" t="n">
+        <v>0.2369581649793167</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>0.2553599837400992</v>
+      </c>
+      <c r="L10" s="5" t="n">
         <v>0.511388342191138</v>
       </c>
-      <c r="K10" s="5" t="n">
+      <c r="M10" s="5" t="n">
         <v>0.22265637813532</v>
       </c>
-      <c r="L10" s="5" t="n">
+      <c r="N10" s="5" t="n">
         <v>1.0043</v>
       </c>
-      <c r="M10" s="5" t="n">
+      <c r="O10" s="5" t="n">
         <v>1.0024</v>
       </c>
-      <c r="N10" s="5" t="n">
+      <c r="P10" s="5" t="n">
         <v>1.0022</v>
       </c>
-      <c r="O10" s="6" t="inlineStr"/>
-      <c r="P10" s="6" t="inlineStr"/>
       <c r="Q10" s="6" t="inlineStr"/>
       <c r="R10" s="6" t="inlineStr"/>
       <c r="S10" s="6" t="inlineStr"/>
       <c r="T10" s="6" t="inlineStr"/>
       <c r="U10" s="6" t="inlineStr"/>
       <c r="V10" s="6" t="inlineStr"/>
+      <c r="W10" s="6" t="inlineStr"/>
+      <c r="X10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1204,26 +1254,26 @@
         <v>3.3</v>
       </c>
       <c r="J11" s="5" t="n">
+        <v>0.233601468490469</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>0.215574037292203</v>
+      </c>
+      <c r="L11" s="5" t="n">
         <v>0.510590381447813</v>
       </c>
-      <c r="K11" s="5" t="n">
+      <c r="M11" s="5" t="n">
         <v>0.225784053085401</v>
       </c>
-      <c r="L11" s="5" t="n">
+      <c r="N11" s="5" t="n">
         <v>0.9926</v>
       </c>
-      <c r="M11" s="5" t="n">
+      <c r="O11" s="5" t="n">
         <v>1.0257</v>
       </c>
-      <c r="N11" s="5" t="n">
+      <c r="P11" s="5" t="n">
         <v>1.0132</v>
       </c>
-      <c r="O11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
       </c>
@@ -1240,6 +1290,12 @@
         <v>0</v>
       </c>
       <c r="V11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1286,26 +1342,26 @@
         <v>3.3</v>
       </c>
       <c r="J12" s="5" t="n">
+        <v>0.233601468490469</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>0.215574037292203</v>
+      </c>
+      <c r="L12" s="5" t="n">
         <v>0.510590381447813</v>
       </c>
-      <c r="K12" s="5" t="n">
+      <c r="M12" s="5" t="n">
         <v>0.225784053085401</v>
       </c>
-      <c r="L12" s="5" t="n">
+      <c r="N12" s="5" t="n">
         <v>0.9926</v>
       </c>
-      <c r="M12" s="5" t="n">
+      <c r="O12" s="5" t="n">
         <v>1.0257</v>
       </c>
-      <c r="N12" s="5" t="n">
+      <c r="P12" s="5" t="n">
         <v>1.0132</v>
       </c>
-      <c r="O12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
       </c>
@@ -1322,6 +1378,12 @@
         <v>0</v>
       </c>
       <c r="V12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1368,26 +1430,26 @@
         <v>3.3</v>
       </c>
       <c r="J13" s="5" t="n">
+        <v>0.2443246485498652</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>0.183277695807331</v>
+      </c>
+      <c r="L13" s="5" t="n">
         <v>0.510590381447813</v>
       </c>
-      <c r="K13" s="5" t="n">
+      <c r="M13" s="5" t="n">
         <v>0.225784053085401</v>
       </c>
-      <c r="L13" s="5" t="n">
+      <c r="N13" s="5" t="n">
         <v>0.9802</v>
       </c>
-      <c r="M13" s="5" t="n">
+      <c r="O13" s="5" t="n">
         <v>1.0252</v>
       </c>
-      <c r="N13" s="5" t="n">
+      <c r="P13" s="5" t="n">
         <v>1.0135</v>
       </c>
-      <c r="O13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
       </c>
@@ -1404,6 +1466,12 @@
         <v>0</v>
       </c>
       <c r="V13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1450,26 +1518,26 @@
         <v>33</v>
       </c>
       <c r="J14" s="5" t="n">
+        <v>0.1329824757126514</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>0.3248435729394352</v>
+      </c>
+      <c r="L14" s="5" t="n">
         <v>0.510590381447813</v>
       </c>
-      <c r="K14" s="5" t="n">
+      <c r="M14" s="5" t="n">
         <v>0.225784053085401</v>
       </c>
-      <c r="L14" s="5" t="n">
+      <c r="N14" s="5" t="n">
         <v>0.9937</v>
       </c>
-      <c r="M14" s="5" t="n">
+      <c r="O14" s="5" t="n">
         <v>0.9932</v>
       </c>
-      <c r="N14" s="5" t="n">
+      <c r="P14" s="5" t="n">
         <v>0.9955000000000001</v>
       </c>
-      <c r="O14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q14" s="6" t="n">
         <v>0</v>
       </c>
@@ -1477,10 +1545,10 @@
         <v>0</v>
       </c>
       <c r="S14" s="6" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="T14" s="6" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="U14" s="6" t="n">
         <v>0.16</v>
@@ -1488,6 +1556,12 @@
       <c r="V14" s="6" t="n">
         <v>0.16</v>
       </c>
+      <c r="W14" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="X14" s="6" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1532,26 +1606,26 @@
         <v>3.3</v>
       </c>
       <c r="J15" s="5" t="n">
+        <v>0.1341216632110691</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>0.2753352654629494</v>
+      </c>
+      <c r="L15" s="5" t="n">
         <v>0.65425629128861</v>
       </c>
-      <c r="K15" s="5" t="n">
+      <c r="M15" s="5" t="n">
         <v>0.512670422089759</v>
       </c>
-      <c r="L15" s="5" t="n">
+      <c r="N15" s="5" t="n">
         <v>0.9759</v>
       </c>
-      <c r="M15" s="5" t="n">
+      <c r="O15" s="5" t="n">
         <v>1.0146</v>
       </c>
-      <c r="N15" s="5" t="n">
+      <c r="P15" s="5" t="n">
         <v>0.966</v>
       </c>
-      <c r="O15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q15" s="6" t="n">
         <v>0</v>
       </c>
@@ -1559,10 +1633,10 @@
         <v>0</v>
       </c>
       <c r="S15" s="6" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="T15" s="6" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>0.16</v>
@@ -1570,6 +1644,12 @@
       <c r="V15" s="6" t="n">
         <v>0.16</v>
       </c>
+      <c r="W15" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="X15" s="6" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1614,26 +1694,26 @@
         <v>3.3</v>
       </c>
       <c r="J16" s="5" t="n">
+        <v>0.1186603136108224</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>0.2706607556452453</v>
+      </c>
+      <c r="L16" s="5" t="n">
         <v>0.65425629128861</v>
       </c>
-      <c r="K16" s="5" t="n">
+      <c r="M16" s="5" t="n">
         <v>0.512670422089759</v>
       </c>
-      <c r="L16" s="5" t="n">
+      <c r="N16" s="5" t="n">
         <v>0.9766</v>
       </c>
-      <c r="M16" s="5" t="n">
+      <c r="O16" s="5" t="n">
         <v>1.003</v>
       </c>
-      <c r="N16" s="5" t="n">
+      <c r="P16" s="5" t="n">
         <v>0.9723000000000001</v>
       </c>
-      <c r="O16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q16" s="6" t="n">
         <v>0</v>
       </c>
@@ -1641,10 +1721,10 @@
         <v>0</v>
       </c>
       <c r="S16" s="6" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="T16" s="6" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="U16" s="6" t="n">
         <v>0.16</v>
@@ -1652,6 +1732,12 @@
       <c r="V16" s="6" t="n">
         <v>0.16</v>
       </c>
+      <c r="W16" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="X16" s="6" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1696,26 +1782,26 @@
         <v>3.3</v>
       </c>
       <c r="J17" s="5" t="n">
+        <v>0.1075421523838416</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>0.1479399367177207</v>
+      </c>
+      <c r="L17" s="5" t="n">
         <v>0.65425629128861</v>
       </c>
-      <c r="K17" s="5" t="n">
+      <c r="M17" s="5" t="n">
         <v>0.512670422089759</v>
       </c>
-      <c r="L17" s="5" t="n">
+      <c r="N17" s="5" t="n">
         <v>0.9787</v>
       </c>
-      <c r="M17" s="5" t="n">
+      <c r="O17" s="5" t="n">
         <v>0.9897</v>
       </c>
-      <c r="N17" s="5" t="n">
+      <c r="P17" s="5" t="n">
         <v>0.9766</v>
       </c>
-      <c r="O17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q17" s="6" t="n">
         <v>0</v>
       </c>
@@ -1723,10 +1809,10 @@
         <v>0</v>
       </c>
       <c r="S17" s="6" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="T17" s="6" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="U17" s="6" t="n">
         <v>0.16</v>
@@ -1734,6 +1820,12 @@
       <c r="V17" s="6" t="n">
         <v>0.16</v>
       </c>
+      <c r="W17" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="X17" s="6" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1778,26 +1870,26 @@
         <v>3.3</v>
       </c>
       <c r="J18" s="5" t="n">
+        <v>0.1251631989034748</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>0.233198203822338</v>
+      </c>
+      <c r="L18" s="5" t="n">
         <v>0.65425629128861</v>
       </c>
-      <c r="K18" s="5" t="n">
+      <c r="M18" s="5" t="n">
         <v>0.512670422089759</v>
       </c>
-      <c r="L18" s="5" t="n">
+      <c r="N18" s="5" t="n">
         <v>0.9751</v>
       </c>
-      <c r="M18" s="5" t="n">
+      <c r="O18" s="5" t="n">
         <v>0.9837</v>
       </c>
-      <c r="N18" s="5" t="n">
+      <c r="P18" s="5" t="n">
         <v>0.9781</v>
       </c>
-      <c r="O18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
       </c>
@@ -1805,10 +1897,10 @@
         <v>0</v>
       </c>
       <c r="S18" s="6" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="T18" s="6" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="U18" s="6" t="n">
         <v>0.16</v>
@@ -1816,6 +1908,12 @@
       <c r="V18" s="6" t="n">
         <v>0.16</v>
       </c>
+      <c r="W18" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="X18" s="6" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1860,26 +1958,26 @@
         <v>11</v>
       </c>
       <c r="J19" s="5" t="n">
+        <v>0.2396658493615177</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>0.2613261383795547</v>
+      </c>
+      <c r="L19" s="5" t="n">
         <v>0.510590381447813</v>
       </c>
-      <c r="K19" s="5" t="n">
+      <c r="M19" s="5" t="n">
         <v>0.225784053085401</v>
       </c>
-      <c r="L19" s="5" t="n">
+      <c r="N19" s="5" t="n">
         <v>0.9993</v>
       </c>
-      <c r="M19" s="5" t="n">
+      <c r="O19" s="5" t="n">
         <v>1.0127</v>
       </c>
-      <c r="N19" s="5" t="n">
+      <c r="P19" s="5" t="n">
         <v>1.0106</v>
       </c>
-      <c r="O19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
       </c>
@@ -1896,6 +1994,12 @@
         <v>0</v>
       </c>
       <c r="V19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1942,26 +2046,26 @@
         <v>11</v>
       </c>
       <c r="J20" s="5" t="n">
+        <v>0.2396658493615177</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>0.2613261383795547</v>
+      </c>
+      <c r="L20" s="5" t="n">
         <v>0.510590381447813</v>
       </c>
-      <c r="K20" s="5" t="n">
+      <c r="M20" s="5" t="n">
         <v>0.225784053085401</v>
       </c>
-      <c r="L20" s="5" t="n">
+      <c r="N20" s="5" t="n">
         <v>0.9993</v>
       </c>
-      <c r="M20" s="5" t="n">
+      <c r="O20" s="5" t="n">
         <v>1.0127</v>
       </c>
-      <c r="N20" s="5" t="n">
+      <c r="P20" s="5" t="n">
         <v>1.0106</v>
       </c>
-      <c r="O20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
       </c>
@@ -1978,6 +2082,12 @@
         <v>0</v>
       </c>
       <c r="V20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2024,26 +2134,26 @@
         <v>275</v>
       </c>
       <c r="J21" s="5" t="n">
+        <v>0.1972627642475195</v>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>0.4012166584184587</v>
+      </c>
+      <c r="L21" s="5" t="n">
         <v>0.501077617843089</v>
       </c>
-      <c r="K21" s="5" t="n">
+      <c r="M21" s="5" t="n">
         <v>0.212860651220515</v>
       </c>
-      <c r="L21" s="5" t="n">
+      <c r="N21" s="5" t="n">
         <v>0.9608</v>
       </c>
-      <c r="M21" s="5" t="n">
+      <c r="O21" s="5" t="n">
         <v>0.9735</v>
       </c>
-      <c r="N21" s="5" t="n">
+      <c r="P21" s="5" t="n">
         <v>0.9709</v>
       </c>
-      <c r="O21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
       </c>
@@ -2051,15 +2161,21 @@
         <v>0</v>
       </c>
       <c r="S21" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="T21" s="6" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="U21" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="V21" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="W21" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="X21" s="6" t="n">
         <v>0.07333333333333335</v>
       </c>
     </row>
@@ -2106,28 +2222,34 @@
         <v>132</v>
       </c>
       <c r="J22" s="5" t="n">
+        <v>0.2449284253072609</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>0.3166893979467619</v>
+      </c>
+      <c r="L22" s="5" t="n">
         <v>0.511370986967519</v>
       </c>
-      <c r="K22" s="5" t="n">
+      <c r="M22" s="5" t="n">
         <v>0.22945882760626</v>
       </c>
-      <c r="L22" s="5" t="n">
+      <c r="N22" s="5" t="n">
         <v>1.0102</v>
       </c>
-      <c r="M22" s="5" t="n">
+      <c r="O22" s="5" t="n">
         <v>0.9945000000000001</v>
       </c>
-      <c r="N22" s="5" t="n">
+      <c r="P22" s="5" t="n">
         <v>0.9963</v>
       </c>
-      <c r="O22" s="6" t="inlineStr"/>
-      <c r="P22" s="6" t="inlineStr"/>
       <c r="Q22" s="6" t="inlineStr"/>
       <c r="R22" s="6" t="inlineStr"/>
       <c r="S22" s="6" t="inlineStr"/>
       <c r="T22" s="6" t="inlineStr"/>
       <c r="U22" s="6" t="inlineStr"/>
       <c r="V22" s="6" t="inlineStr"/>
+      <c r="W22" s="6" t="inlineStr"/>
+      <c r="X22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2172,28 +2294,34 @@
         <v>132</v>
       </c>
       <c r="J23" s="5" t="n">
+        <v>0.2720339427313853</v>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>0.383961084072671</v>
+      </c>
+      <c r="L23" s="5" t="n">
         <v>0.511370986967519</v>
       </c>
-      <c r="K23" s="5" t="n">
+      <c r="M23" s="5" t="n">
         <v>0.22945882760626</v>
       </c>
-      <c r="L23" s="5" t="n">
+      <c r="N23" s="5" t="n">
         <v>1.009</v>
       </c>
-      <c r="M23" s="5" t="n">
+      <c r="O23" s="5" t="n">
         <v>0.9952</v>
       </c>
-      <c r="N23" s="5" t="n">
+      <c r="P23" s="5" t="n">
         <v>0.9967</v>
       </c>
-      <c r="O23" s="6" t="inlineStr"/>
-      <c r="P23" s="6" t="inlineStr"/>
       <c r="Q23" s="6" t="inlineStr"/>
       <c r="R23" s="6" t="inlineStr"/>
       <c r="S23" s="6" t="inlineStr"/>
       <c r="T23" s="6" t="inlineStr"/>
       <c r="U23" s="6" t="inlineStr"/>
       <c r="V23" s="6" t="inlineStr"/>
+      <c r="W23" s="6" t="inlineStr"/>
+      <c r="X23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2231,25 +2359,31 @@
         <v>46</v>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
-      <c r="L24" s="5" t="n">
+      <c r="J24" s="5" t="n">
+        <v>0.1837838121931059</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>0.2611513523019278</v>
+      </c>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="n">
         <v>0.9755</v>
       </c>
-      <c r="M24" s="5" t="n">
+      <c r="O24" s="5" t="n">
         <v>0.9333</v>
       </c>
-      <c r="N24" s="5" t="n">
+      <c r="P24" s="5" t="n">
         <v>0.9458</v>
       </c>
-      <c r="O24" s="6" t="inlineStr"/>
-      <c r="P24" s="6" t="inlineStr"/>
       <c r="Q24" s="6" t="inlineStr"/>
       <c r="R24" s="6" t="inlineStr"/>
       <c r="S24" s="6" t="inlineStr"/>
       <c r="T24" s="6" t="inlineStr"/>
       <c r="U24" s="6" t="inlineStr"/>
       <c r="V24" s="6" t="inlineStr"/>
+      <c r="W24" s="6" t="inlineStr"/>
+      <c r="X24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2287,25 +2421,31 @@
         <v>66</v>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="5" t="inlineStr"/>
-      <c r="K25" s="5" t="inlineStr"/>
-      <c r="L25" s="5" t="n">
+      <c r="J25" s="5" t="n">
+        <v>0.1487965707958214</v>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>0.05183812537020938</v>
+      </c>
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="n">
         <v>0.9308999999999999</v>
       </c>
-      <c r="M25" s="5" t="n">
+      <c r="O25" s="5" t="n">
         <v>0.9467</v>
       </c>
-      <c r="N25" s="5" t="n">
+      <c r="P25" s="5" t="n">
         <v>0.9408</v>
       </c>
-      <c r="O25" s="6" t="inlineStr"/>
-      <c r="P25" s="6" t="inlineStr"/>
       <c r="Q25" s="6" t="inlineStr"/>
       <c r="R25" s="6" t="inlineStr"/>
       <c r="S25" s="6" t="inlineStr"/>
       <c r="T25" s="6" t="inlineStr"/>
       <c r="U25" s="6" t="inlineStr"/>
       <c r="V25" s="6" t="inlineStr"/>
+      <c r="W25" s="6" t="inlineStr"/>
+      <c r="X25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2343,25 +2483,31 @@
         <v>57</v>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="5" t="inlineStr"/>
-      <c r="K26" s="5" t="inlineStr"/>
-      <c r="L26" s="5" t="n">
+      <c r="J26" s="5" t="n">
+        <v>0.01165648634818117</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>0.004972497428635703</v>
+      </c>
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="n">
         <v>0.9486</v>
       </c>
-      <c r="M26" s="5" t="n">
+      <c r="O26" s="5" t="n">
         <v>0.9604</v>
       </c>
-      <c r="N26" s="5" t="n">
+      <c r="P26" s="5" t="n">
         <v>0.9605</v>
       </c>
-      <c r="O26" s="6" t="inlineStr"/>
-      <c r="P26" s="6" t="inlineStr"/>
       <c r="Q26" s="6" t="inlineStr"/>
       <c r="R26" s="6" t="inlineStr"/>
       <c r="S26" s="6" t="inlineStr"/>
       <c r="T26" s="6" t="inlineStr"/>
       <c r="U26" s="6" t="inlineStr"/>
       <c r="V26" s="6" t="inlineStr"/>
+      <c r="W26" s="6" t="inlineStr"/>
+      <c r="X26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2399,25 +2545,31 @@
         <v>209</v>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="5" t="inlineStr"/>
-      <c r="K27" s="5" t="inlineStr"/>
-      <c r="L27" s="5" t="n">
+      <c r="J27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>0.179641601485183</v>
+      </c>
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="n">
         <v>0.9643</v>
       </c>
-      <c r="M27" s="5" t="n">
+      <c r="O27" s="5" t="n">
         <v>0.9697</v>
       </c>
-      <c r="N27" s="5" t="n">
+      <c r="P27" s="5" t="n">
         <v>0.9711</v>
       </c>
-      <c r="O27" s="6" t="inlineStr"/>
-      <c r="P27" s="6" t="inlineStr"/>
       <c r="Q27" s="6" t="inlineStr"/>
       <c r="R27" s="6" t="inlineStr"/>
       <c r="S27" s="6" t="inlineStr"/>
       <c r="T27" s="6" t="inlineStr"/>
       <c r="U27" s="6" t="inlineStr"/>
       <c r="V27" s="6" t="inlineStr"/>
+      <c r="W27" s="6" t="inlineStr"/>
+      <c r="X27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2455,25 +2607,31 @@
         <v>203</v>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
-      <c r="L28" s="5" t="n">
+      <c r="J28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>0.1555674430999341</v>
+      </c>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="n">
         <v>0.9641</v>
       </c>
-      <c r="M28" s="5" t="n">
+      <c r="O28" s="5" t="n">
         <v>0.9689</v>
       </c>
-      <c r="N28" s="5" t="n">
+      <c r="P28" s="5" t="n">
         <v>0.971</v>
       </c>
-      <c r="O28" s="6" t="inlineStr"/>
-      <c r="P28" s="6" t="inlineStr"/>
       <c r="Q28" s="6" t="inlineStr"/>
       <c r="R28" s="6" t="inlineStr"/>
       <c r="S28" s="6" t="inlineStr"/>
       <c r="T28" s="6" t="inlineStr"/>
       <c r="U28" s="6" t="inlineStr"/>
       <c r="V28" s="6" t="inlineStr"/>
+      <c r="W28" s="6" t="inlineStr"/>
+      <c r="X28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2511,25 +2669,31 @@
         <v>94.5</v>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
-      <c r="L29" s="5" t="n">
+      <c r="J29" s="5" t="n">
+        <v>0.09029871973567261</v>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>0.1208463990083658</v>
+      </c>
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="n">
         <v>0.9565</v>
       </c>
-      <c r="M29" s="5" t="n">
+      <c r="O29" s="5" t="n">
         <v>0.9663</v>
       </c>
-      <c r="N29" s="5" t="n">
+      <c r="P29" s="5" t="n">
         <v>0.9635</v>
       </c>
-      <c r="O29" s="6" t="inlineStr"/>
-      <c r="P29" s="6" t="inlineStr"/>
       <c r="Q29" s="6" t="inlineStr"/>
       <c r="R29" s="6" t="inlineStr"/>
       <c r="S29" s="6" t="inlineStr"/>
       <c r="T29" s="6" t="inlineStr"/>
       <c r="U29" s="6" t="inlineStr"/>
       <c r="V29" s="6" t="inlineStr"/>
+      <c r="W29" s="6" t="inlineStr"/>
+      <c r="X29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2567,25 +2731,31 @@
         <v>71.40000000000001</v>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
-      <c r="L30" s="5" t="n">
+      <c r="J30" s="5" t="n">
+        <v>0.1002715806472839</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>0.1083613761067723</v>
+      </c>
+      <c r="L30" s="5" t="inlineStr"/>
+      <c r="M30" s="5" t="inlineStr"/>
+      <c r="N30" s="5" t="n">
         <v>0.9526</v>
       </c>
-      <c r="M30" s="5" t="n">
+      <c r="O30" s="5" t="n">
         <v>0.9608</v>
       </c>
-      <c r="N30" s="5" t="n">
+      <c r="P30" s="5" t="n">
         <v>0.962</v>
       </c>
-      <c r="O30" s="6" t="inlineStr"/>
-      <c r="P30" s="6" t="inlineStr"/>
       <c r="Q30" s="6" t="inlineStr"/>
       <c r="R30" s="6" t="inlineStr"/>
       <c r="S30" s="6" t="inlineStr"/>
       <c r="T30" s="6" t="inlineStr"/>
       <c r="U30" s="6" t="inlineStr"/>
       <c r="V30" s="6" t="inlineStr"/>
+      <c r="W30" s="6" t="inlineStr"/>
+      <c r="X30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2623,25 +2793,31 @@
         <v>102.4</v>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="5" t="inlineStr"/>
-      <c r="K31" s="5" t="inlineStr"/>
-      <c r="L31" s="5" t="n">
+      <c r="J31" s="5" t="n">
+        <v>0.007476326214591267</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>0.0009835058684714015</v>
+      </c>
+      <c r="L31" s="5" t="inlineStr"/>
+      <c r="M31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="n">
         <v>0.9423</v>
       </c>
-      <c r="M31" s="5" t="n">
+      <c r="O31" s="5" t="n">
         <v>0.956</v>
       </c>
-      <c r="N31" s="5" t="n">
+      <c r="P31" s="5" t="n">
         <v>0.9538</v>
       </c>
-      <c r="O31" s="6" t="inlineStr"/>
-      <c r="P31" s="6" t="inlineStr"/>
       <c r="Q31" s="6" t="inlineStr"/>
       <c r="R31" s="6" t="inlineStr"/>
       <c r="S31" s="6" t="inlineStr"/>
       <c r="T31" s="6" t="inlineStr"/>
       <c r="U31" s="6" t="inlineStr"/>
       <c r="V31" s="6" t="inlineStr"/>
+      <c r="W31" s="6" t="inlineStr"/>
+      <c r="X31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2679,25 +2855,31 @@
         <v>102.4</v>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="5" t="inlineStr"/>
-      <c r="K32" s="5" t="inlineStr"/>
-      <c r="L32" s="5" t="n">
+      <c r="J32" s="5" t="n">
+        <v>0.004042184103801194</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="5" t="inlineStr"/>
+      <c r="M32" s="5" t="inlineStr"/>
+      <c r="N32" s="5" t="n">
         <v>0.9423</v>
       </c>
-      <c r="M32" s="5" t="n">
+      <c r="O32" s="5" t="n">
         <v>0.956</v>
       </c>
-      <c r="N32" s="5" t="n">
+      <c r="P32" s="5" t="n">
         <v>0.9538</v>
       </c>
-      <c r="O32" s="6" t="inlineStr"/>
-      <c r="P32" s="6" t="inlineStr"/>
       <c r="Q32" s="6" t="inlineStr"/>
       <c r="R32" s="6" t="inlineStr"/>
       <c r="S32" s="6" t="inlineStr"/>
       <c r="T32" s="6" t="inlineStr"/>
       <c r="U32" s="6" t="inlineStr"/>
       <c r="V32" s="6" t="inlineStr"/>
+      <c r="W32" s="6" t="inlineStr"/>
+      <c r="X32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2735,25 +2917,31 @@
         <v>112</v>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="5" t="inlineStr"/>
-      <c r="K33" s="5" t="inlineStr"/>
-      <c r="L33" s="5" t="n">
+      <c r="J33" s="5" t="n">
+        <v>0.00666136667720707</v>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="5" t="inlineStr"/>
+      <c r="M33" s="5" t="inlineStr"/>
+      <c r="N33" s="5" t="n">
         <v>0.9423</v>
       </c>
-      <c r="M33" s="5" t="n">
+      <c r="O33" s="5" t="n">
         <v>0.956</v>
       </c>
-      <c r="N33" s="5" t="n">
+      <c r="P33" s="5" t="n">
         <v>0.9538</v>
       </c>
-      <c r="O33" s="6" t="inlineStr"/>
-      <c r="P33" s="6" t="inlineStr"/>
       <c r="Q33" s="6" t="inlineStr"/>
       <c r="R33" s="6" t="inlineStr"/>
       <c r="S33" s="6" t="inlineStr"/>
       <c r="T33" s="6" t="inlineStr"/>
       <c r="U33" s="6" t="inlineStr"/>
       <c r="V33" s="6" t="inlineStr"/>
+      <c r="W33" s="6" t="inlineStr"/>
+      <c r="X33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2791,25 +2979,31 @@
         <v>159</v>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="5" t="inlineStr"/>
-      <c r="K34" s="5" t="inlineStr"/>
-      <c r="L34" s="5" t="n">
+      <c r="J34" s="5" t="n">
+        <v>0.1078900067150126</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>0.2000408936031856</v>
+      </c>
+      <c r="L34" s="5" t="inlineStr"/>
+      <c r="M34" s="5" t="inlineStr"/>
+      <c r="N34" s="5" t="n">
         <v>0.9709</v>
       </c>
-      <c r="M34" s="5" t="n">
+      <c r="O34" s="5" t="n">
         <v>0.9297</v>
       </c>
-      <c r="N34" s="5" t="n">
+      <c r="P34" s="5" t="n">
         <v>0.9389999999999999</v>
       </c>
-      <c r="O34" s="6" t="inlineStr"/>
-      <c r="P34" s="6" t="inlineStr"/>
       <c r="Q34" s="6" t="inlineStr"/>
       <c r="R34" s="6" t="inlineStr"/>
       <c r="S34" s="6" t="inlineStr"/>
       <c r="T34" s="6" t="inlineStr"/>
       <c r="U34" s="6" t="inlineStr"/>
       <c r="V34" s="6" t="inlineStr"/>
+      <c r="W34" s="6" t="inlineStr"/>
+      <c r="X34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2847,25 +3041,31 @@
         <v>39</v>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="5" t="inlineStr"/>
-      <c r="K35" s="5" t="inlineStr"/>
-      <c r="L35" s="5" t="n">
+      <c r="J35" s="5" t="n">
+        <v>0.2044227016730216</v>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>0.265181802157253</v>
+      </c>
+      <c r="L35" s="5" t="inlineStr"/>
+      <c r="M35" s="5" t="inlineStr"/>
+      <c r="N35" s="5" t="n">
         <v>0.9709</v>
       </c>
-      <c r="M35" s="5" t="n">
+      <c r="O35" s="5" t="n">
         <v>0.9297</v>
       </c>
-      <c r="N35" s="5" t="n">
+      <c r="P35" s="5" t="n">
         <v>0.9389999999999999</v>
       </c>
-      <c r="O35" s="6" t="inlineStr"/>
-      <c r="P35" s="6" t="inlineStr"/>
       <c r="Q35" s="6" t="inlineStr"/>
       <c r="R35" s="6" t="inlineStr"/>
       <c r="S35" s="6" t="inlineStr"/>
       <c r="T35" s="6" t="inlineStr"/>
       <c r="U35" s="6" t="inlineStr"/>
       <c r="V35" s="6" t="inlineStr"/>
+      <c r="W35" s="6" t="inlineStr"/>
+      <c r="X35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2903,25 +3103,31 @@
         <v>80.5</v>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="5" t="inlineStr"/>
-      <c r="K36" s="5" t="inlineStr"/>
-      <c r="L36" s="5" t="n">
+      <c r="J36" s="5" t="n">
+        <v>0.2050709857686178</v>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>0.2636993184442319</v>
+      </c>
+      <c r="L36" s="5" t="inlineStr"/>
+      <c r="M36" s="5" t="inlineStr"/>
+      <c r="N36" s="5" t="n">
         <v>0.9709</v>
       </c>
-      <c r="M36" s="5" t="n">
+      <c r="O36" s="5" t="n">
         <v>0.9297</v>
       </c>
-      <c r="N36" s="5" t="n">
+      <c r="P36" s="5" t="n">
         <v>0.9389999999999999</v>
       </c>
-      <c r="O36" s="6" t="inlineStr"/>
-      <c r="P36" s="6" t="inlineStr"/>
       <c r="Q36" s="6" t="inlineStr"/>
       <c r="R36" s="6" t="inlineStr"/>
       <c r="S36" s="6" t="inlineStr"/>
       <c r="T36" s="6" t="inlineStr"/>
       <c r="U36" s="6" t="inlineStr"/>
       <c r="V36" s="6" t="inlineStr"/>
+      <c r="W36" s="6" t="inlineStr"/>
+      <c r="X36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2959,25 +3165,31 @@
         <v>126</v>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="5" t="inlineStr"/>
-      <c r="K37" s="5" t="inlineStr"/>
-      <c r="L37" s="5" t="n">
+      <c r="J37" s="5" t="n">
+        <v>0.100240841468152</v>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>0.1457829031037056</v>
+      </c>
+      <c r="L37" s="5" t="inlineStr"/>
+      <c r="M37" s="5" t="inlineStr"/>
+      <c r="N37" s="5" t="n">
         <v>0.9576</v>
       </c>
-      <c r="M37" s="5" t="n">
+      <c r="O37" s="5" t="n">
         <v>0.9689</v>
       </c>
-      <c r="N37" s="5" t="n">
+      <c r="P37" s="5" t="n">
         <v>0.9661999999999999</v>
       </c>
-      <c r="O37" s="6" t="inlineStr"/>
-      <c r="P37" s="6" t="inlineStr"/>
       <c r="Q37" s="6" t="inlineStr"/>
       <c r="R37" s="6" t="inlineStr"/>
       <c r="S37" s="6" t="inlineStr"/>
       <c r="T37" s="6" t="inlineStr"/>
       <c r="U37" s="6" t="inlineStr"/>
       <c r="V37" s="6" t="inlineStr"/>
+      <c r="W37" s="6" t="inlineStr"/>
+      <c r="X37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3015,25 +3227,31 @@
         <v>86</v>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="5" t="inlineStr"/>
-      <c r="K38" s="5" t="inlineStr"/>
-      <c r="L38" s="5" t="n">
+      <c r="J38" s="5" t="n">
+        <v>0.1132112008880745</v>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>0.165330135848075</v>
+      </c>
+      <c r="L38" s="5" t="inlineStr"/>
+      <c r="M38" s="5" t="inlineStr"/>
+      <c r="N38" s="5" t="n">
         <v>0.9576</v>
       </c>
-      <c r="M38" s="5" t="n">
+      <c r="O38" s="5" t="n">
         <v>0.9689</v>
       </c>
-      <c r="N38" s="5" t="n">
+      <c r="P38" s="5" t="n">
         <v>0.9661999999999999</v>
       </c>
-      <c r="O38" s="6" t="inlineStr"/>
-      <c r="P38" s="6" t="inlineStr"/>
       <c r="Q38" s="6" t="inlineStr"/>
       <c r="R38" s="6" t="inlineStr"/>
       <c r="S38" s="6" t="inlineStr"/>
       <c r="T38" s="6" t="inlineStr"/>
       <c r="U38" s="6" t="inlineStr"/>
       <c r="V38" s="6" t="inlineStr"/>
+      <c r="W38" s="6" t="inlineStr"/>
+      <c r="X38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3071,25 +3289,31 @@
         <v>70</v>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="5" t="inlineStr"/>
-      <c r="K39" s="5" t="inlineStr"/>
-      <c r="L39" s="5" t="n">
+      <c r="J39" s="5" t="n">
+        <v>0.1951479456045728</v>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>0.3052119364643321</v>
+      </c>
+      <c r="L39" s="5" t="inlineStr"/>
+      <c r="M39" s="5" t="inlineStr"/>
+      <c r="N39" s="5" t="n">
         <v>0.9162</v>
       </c>
-      <c r="M39" s="5" t="n">
+      <c r="O39" s="5" t="n">
         <v>0.9403</v>
       </c>
-      <c r="N39" s="5" t="n">
+      <c r="P39" s="5" t="n">
         <v>0.9379</v>
       </c>
-      <c r="O39" s="6" t="inlineStr"/>
-      <c r="P39" s="6" t="inlineStr"/>
       <c r="Q39" s="6" t="inlineStr"/>
       <c r="R39" s="6" t="inlineStr"/>
       <c r="S39" s="6" t="inlineStr"/>
       <c r="T39" s="6" t="inlineStr"/>
       <c r="U39" s="6" t="inlineStr"/>
       <c r="V39" s="6" t="inlineStr"/>
+      <c r="W39" s="6" t="inlineStr"/>
+      <c r="X39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3127,25 +3351,31 @@
         <v>132.3</v>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="5" t="inlineStr"/>
-      <c r="K40" s="5" t="inlineStr"/>
-      <c r="L40" s="5" t="n">
+      <c r="J40" s="5" t="n">
+        <v>0.07862107896860038</v>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>0.1223251897635215</v>
+      </c>
+      <c r="L40" s="5" t="inlineStr"/>
+      <c r="M40" s="5" t="inlineStr"/>
+      <c r="N40" s="5" t="n">
         <v>0.9467</v>
       </c>
-      <c r="M40" s="5" t="n">
+      <c r="O40" s="5" t="n">
         <v>0.9579</v>
       </c>
-      <c r="N40" s="5" t="n">
+      <c r="P40" s="5" t="n">
         <v>0.9583</v>
       </c>
-      <c r="O40" s="6" t="inlineStr"/>
-      <c r="P40" s="6" t="inlineStr"/>
       <c r="Q40" s="6" t="inlineStr"/>
       <c r="R40" s="6" t="inlineStr"/>
       <c r="S40" s="6" t="inlineStr"/>
       <c r="T40" s="6" t="inlineStr"/>
       <c r="U40" s="6" t="inlineStr"/>
       <c r="V40" s="6" t="inlineStr"/>
+      <c r="W40" s="6" t="inlineStr"/>
+      <c r="X40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3183,25 +3413,31 @@
         <v>210</v>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="5" t="inlineStr"/>
-      <c r="K41" s="5" t="inlineStr"/>
-      <c r="L41" s="5" t="n">
+      <c r="J41" s="5" t="n">
+        <v>0.09378566692877877</v>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>0.1999025312540723</v>
+      </c>
+      <c r="L41" s="5" t="inlineStr"/>
+      <c r="M41" s="5" t="inlineStr"/>
+      <c r="N41" s="5" t="n">
         <v>0.9608</v>
       </c>
-      <c r="M41" s="5" t="n">
+      <c r="O41" s="5" t="n">
         <v>0.9735</v>
       </c>
-      <c r="N41" s="5" t="n">
+      <c r="P41" s="5" t="n">
         <v>0.9709</v>
       </c>
-      <c r="O41" s="6" t="inlineStr"/>
-      <c r="P41" s="6" t="inlineStr"/>
       <c r="Q41" s="6" t="inlineStr"/>
       <c r="R41" s="6" t="inlineStr"/>
       <c r="S41" s="6" t="inlineStr"/>
       <c r="T41" s="6" t="inlineStr"/>
       <c r="U41" s="6" t="inlineStr"/>
       <c r="V41" s="6" t="inlineStr"/>
+      <c r="W41" s="6" t="inlineStr"/>
+      <c r="X41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3239,25 +3475,31 @@
         <v>126</v>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="5" t="inlineStr"/>
-      <c r="K42" s="5" t="inlineStr"/>
-      <c r="L42" s="5" t="n">
+      <c r="J42" s="5" t="n">
+        <v>0.006173969971481119</v>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>0.003504366906944112</v>
+      </c>
+      <c r="L42" s="5" t="inlineStr"/>
+      <c r="M42" s="5" t="inlineStr"/>
+      <c r="N42" s="5" t="n">
         <v>0.9613</v>
       </c>
-      <c r="M42" s="5" t="n">
+      <c r="O42" s="5" t="n">
         <v>0.9695</v>
       </c>
-      <c r="N42" s="5" t="n">
+      <c r="P42" s="5" t="n">
         <v>0.9694</v>
       </c>
-      <c r="O42" s="6" t="inlineStr"/>
-      <c r="P42" s="6" t="inlineStr"/>
       <c r="Q42" s="6" t="inlineStr"/>
       <c r="R42" s="6" t="inlineStr"/>
       <c r="S42" s="6" t="inlineStr"/>
       <c r="T42" s="6" t="inlineStr"/>
       <c r="U42" s="6" t="inlineStr"/>
       <c r="V42" s="6" t="inlineStr"/>
+      <c r="W42" s="6" t="inlineStr"/>
+      <c r="X42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3295,25 +3537,31 @@
         <v>144</v>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="5" t="inlineStr"/>
-      <c r="K43" s="5" t="inlineStr"/>
-      <c r="L43" s="5" t="n">
+      <c r="J43" s="5" t="n">
+        <v>0.009571326064233943</v>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="5" t="inlineStr"/>
+      <c r="M43" s="5" t="inlineStr"/>
+      <c r="N43" s="5" t="n">
         <v>0.9613</v>
       </c>
-      <c r="M43" s="5" t="n">
+      <c r="O43" s="5" t="n">
         <v>0.9695</v>
       </c>
-      <c r="N43" s="5" t="n">
+      <c r="P43" s="5" t="n">
         <v>0.9694</v>
       </c>
-      <c r="O43" s="6" t="inlineStr"/>
-      <c r="P43" s="6" t="inlineStr"/>
       <c r="Q43" s="6" t="inlineStr"/>
       <c r="R43" s="6" t="inlineStr"/>
       <c r="S43" s="6" t="inlineStr"/>
       <c r="T43" s="6" t="inlineStr"/>
       <c r="U43" s="6" t="inlineStr"/>
       <c r="V43" s="6" t="inlineStr"/>
+      <c r="W43" s="6" t="inlineStr"/>
+      <c r="X43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3351,25 +3599,31 @@
         <v>99</v>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="5" t="inlineStr"/>
-      <c r="K44" s="5" t="inlineStr"/>
-      <c r="L44" s="5" t="n">
+      <c r="J44" s="5" t="n">
+        <v>0.1117765711557074</v>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>0.186319094139723</v>
+      </c>
+      <c r="L44" s="5" t="inlineStr"/>
+      <c r="M44" s="5" t="inlineStr"/>
+      <c r="N44" s="5" t="n">
         <v>0.8932</v>
       </c>
-      <c r="M44" s="5" t="n">
+      <c r="O44" s="5" t="n">
         <v>0.9157</v>
       </c>
-      <c r="N44" s="5" t="n">
+      <c r="P44" s="5" t="n">
         <v>0.9112</v>
       </c>
-      <c r="O44" s="6" t="inlineStr"/>
-      <c r="P44" s="6" t="inlineStr"/>
       <c r="Q44" s="6" t="inlineStr"/>
       <c r="R44" s="6" t="inlineStr"/>
       <c r="S44" s="6" t="inlineStr"/>
       <c r="T44" s="6" t="inlineStr"/>
       <c r="U44" s="6" t="inlineStr"/>
       <c r="V44" s="6" t="inlineStr"/>
+      <c r="W44" s="6" t="inlineStr"/>
+      <c r="X44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3407,25 +3661,31 @@
         <v>34.5</v>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="5" t="inlineStr"/>
-      <c r="K45" s="5" t="inlineStr"/>
-      <c r="L45" s="5" t="n">
+      <c r="J45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="5" t="inlineStr"/>
+      <c r="M45" s="5" t="inlineStr"/>
+      <c r="N45" s="5" t="n">
         <v>1.0025</v>
       </c>
-      <c r="M45" s="5" t="n">
+      <c r="O45" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="N45" s="5" t="n">
+      <c r="P45" s="5" t="n">
         <v>1.0034</v>
       </c>
-      <c r="O45" s="6" t="inlineStr"/>
-      <c r="P45" s="6" t="inlineStr"/>
       <c r="Q45" s="6" t="inlineStr"/>
       <c r="R45" s="6" t="inlineStr"/>
       <c r="S45" s="6" t="inlineStr"/>
       <c r="T45" s="6" t="inlineStr"/>
       <c r="U45" s="6" t="inlineStr"/>
       <c r="V45" s="6" t="inlineStr"/>
+      <c r="W45" s="6" t="inlineStr"/>
+      <c r="X45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3463,25 +3723,31 @@
         <v>52.5</v>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="5" t="inlineStr"/>
-      <c r="K46" s="5" t="inlineStr"/>
-      <c r="L46" s="5" t="n">
+      <c r="J46" s="5" t="n">
+        <v>0.1104986454982489</v>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>0.08860136051521761</v>
+      </c>
+      <c r="L46" s="5" t="inlineStr"/>
+      <c r="M46" s="5" t="inlineStr"/>
+      <c r="N46" s="5" t="n">
         <v>0.9467</v>
       </c>
-      <c r="M46" s="5" t="n">
+      <c r="O46" s="5" t="n">
         <v>0.9579</v>
       </c>
-      <c r="N46" s="5" t="n">
+      <c r="P46" s="5" t="n">
         <v>0.9583</v>
       </c>
-      <c r="O46" s="6" t="inlineStr"/>
-      <c r="P46" s="6" t="inlineStr"/>
       <c r="Q46" s="6" t="inlineStr"/>
       <c r="R46" s="6" t="inlineStr"/>
       <c r="S46" s="6" t="inlineStr"/>
       <c r="T46" s="6" t="inlineStr"/>
       <c r="U46" s="6" t="inlineStr"/>
       <c r="V46" s="6" t="inlineStr"/>
+      <c r="W46" s="6" t="inlineStr"/>
+      <c r="X46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3519,25 +3785,31 @@
         <v>130.8</v>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="5" t="inlineStr"/>
-      <c r="K47" s="5" t="inlineStr"/>
-      <c r="L47" s="5" t="n">
+      <c r="J47" s="5" t="n">
+        <v>0.0231798012669201</v>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>0.02046415405566893</v>
+      </c>
+      <c r="L47" s="5" t="inlineStr"/>
+      <c r="M47" s="5" t="inlineStr"/>
+      <c r="N47" s="5" t="n">
         <v>0.9547</v>
       </c>
-      <c r="M47" s="5" t="n">
+      <c r="O47" s="5" t="n">
         <v>0.9624</v>
       </c>
-      <c r="N47" s="5" t="n">
+      <c r="P47" s="5" t="n">
         <v>0.9611</v>
       </c>
-      <c r="O47" s="6" t="inlineStr"/>
-      <c r="P47" s="6" t="inlineStr"/>
       <c r="Q47" s="6" t="inlineStr"/>
       <c r="R47" s="6" t="inlineStr"/>
       <c r="S47" s="6" t="inlineStr"/>
       <c r="T47" s="6" t="inlineStr"/>
       <c r="U47" s="6" t="inlineStr"/>
       <c r="V47" s="6" t="inlineStr"/>
+      <c r="W47" s="6" t="inlineStr"/>
+      <c r="X47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3575,25 +3847,31 @@
         <v>90.75</v>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="5" t="inlineStr"/>
-      <c r="K48" s="5" t="inlineStr"/>
-      <c r="L48" s="5" t="n">
+      <c r="J48" s="5" t="n">
+        <v>0.09149797011929861</v>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>0.1685558219338047</v>
+      </c>
+      <c r="L48" s="5" t="inlineStr"/>
+      <c r="M48" s="5" t="inlineStr"/>
+      <c r="N48" s="5" t="n">
         <v>0.8179</v>
       </c>
-      <c r="M48" s="5" t="n">
+      <c r="O48" s="5" t="n">
         <v>0.8456</v>
       </c>
-      <c r="N48" s="5" t="n">
+      <c r="P48" s="5" t="n">
         <v>0.844</v>
       </c>
-      <c r="O48" s="6" t="inlineStr"/>
-      <c r="P48" s="6" t="inlineStr"/>
       <c r="Q48" s="6" t="inlineStr"/>
       <c r="R48" s="6" t="inlineStr"/>
       <c r="S48" s="6" t="inlineStr"/>
       <c r="T48" s="6" t="inlineStr"/>
       <c r="U48" s="6" t="inlineStr"/>
       <c r="V48" s="6" t="inlineStr"/>
+      <c r="W48" s="6" t="inlineStr"/>
+      <c r="X48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3631,25 +3909,31 @@
         <v>122</v>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="5" t="inlineStr"/>
-      <c r="K49" s="5" t="inlineStr"/>
-      <c r="L49" s="5" t="n">
+      <c r="J49" s="5" t="n">
+        <v>0.1018185649768411</v>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>0.04324399718648553</v>
+      </c>
+      <c r="L49" s="5" t="inlineStr"/>
+      <c r="M49" s="5" t="inlineStr"/>
+      <c r="N49" s="5" t="n">
         <v>0.9498</v>
       </c>
-      <c r="M49" s="5" t="n">
+      <c r="O49" s="5" t="n">
         <v>0.9601</v>
       </c>
-      <c r="N49" s="5" t="n">
+      <c r="P49" s="5" t="n">
         <v>0.9605</v>
       </c>
-      <c r="O49" s="6" t="inlineStr"/>
-      <c r="P49" s="6" t="inlineStr"/>
       <c r="Q49" s="6" t="inlineStr"/>
       <c r="R49" s="6" t="inlineStr"/>
       <c r="S49" s="6" t="inlineStr"/>
       <c r="T49" s="6" t="inlineStr"/>
       <c r="U49" s="6" t="inlineStr"/>
       <c r="V49" s="6" t="inlineStr"/>
+      <c r="W49" s="6" t="inlineStr"/>
+      <c r="X49" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3662,7 +3946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U49"/>
+  <dimension ref="A1:W49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3686,6 +3970,8 @@
     <col width="14" customWidth="1" min="19" max="19"/>
     <col width="14" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3716,80 +4002,90 @@
       </c>
       <c r="F1" s="7" t="inlineStr">
         <is>
+          <t>CURTAILMENT_ACTUAL_FY23-24</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>CURTAILMENT_ACTUAL_FY24-25</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
           <t>ELI_CURTAILMENT_NEAR</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>ELI_CURTAILMENT_MED</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>ISP_CURTAILMENT_FY1</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>ISP_CURTAILMENT_FY1_LABEL</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>ISP_CURTAILMENT_FY2</t>
         </is>
       </c>
-      <c r="K1" s="7" t="inlineStr">
+      <c r="M1" s="7" t="inlineStr">
         <is>
           <t>ISP_CURTAILMENT_FY2_LABEL</t>
         </is>
       </c>
-      <c r="L1" s="7" t="inlineStr">
+      <c r="N1" s="7" t="inlineStr">
         <is>
           <t>ISP_CURTAILMENT_FY3</t>
         </is>
       </c>
-      <c r="M1" s="7" t="inlineStr">
+      <c r="O1" s="7" t="inlineStr">
         <is>
           <t>ISP_CURTAILMENT_FY3_LABEL</t>
         </is>
       </c>
-      <c r="N1" s="7" t="inlineStr">
+      <c r="P1" s="7" t="inlineStr">
         <is>
           <t>ISP_CURTAILMENT_AVG</t>
         </is>
       </c>
-      <c r="O1" s="7" t="inlineStr">
+      <c r="Q1" s="7" t="inlineStr">
         <is>
           <t>ISP_OFFLOADING_FY1</t>
         </is>
       </c>
-      <c r="P1" s="7" t="inlineStr">
+      <c r="R1" s="7" t="inlineStr">
         <is>
           <t>ISP_OFFLOADING_FY1_LABEL</t>
         </is>
       </c>
-      <c r="Q1" s="7" t="inlineStr">
+      <c r="S1" s="7" t="inlineStr">
         <is>
           <t>ISP_OFFLOADING_FY2</t>
         </is>
       </c>
-      <c r="R1" s="7" t="inlineStr">
+      <c r="T1" s="7" t="inlineStr">
         <is>
           <t>ISP_OFFLOADING_FY2_LABEL</t>
         </is>
       </c>
-      <c r="S1" s="7" t="inlineStr">
+      <c r="U1" s="7" t="inlineStr">
         <is>
           <t>ISP_OFFLOADING_FY3</t>
         </is>
       </c>
-      <c r="T1" s="7" t="inlineStr">
+      <c r="V1" s="7" t="inlineStr">
         <is>
           <t>ISP_OFFLOADING_FY3_LABEL</t>
         </is>
       </c>
-      <c r="U1" s="7" t="inlineStr">
+      <c r="W1" s="7" t="inlineStr">
         <is>
           <t>ISP_OFFLOADING_AVG</t>
         </is>
@@ -3815,46 +4111,52 @@
       <c r="E2" s="5" t="n">
         <v>1.0034</v>
       </c>
-      <c r="F2" s="5" t="inlineStr"/>
-      <c r="G2" s="5" t="inlineStr"/>
+      <c r="F2" s="5" t="n">
+        <v>0.3222683455189714</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>0.2755625039739843</v>
+      </c>
       <c r="H2" s="5" t="inlineStr"/>
-      <c r="I2" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I2" s="5" t="inlineStr"/>
       <c r="J2" s="5" t="inlineStr"/>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr"/>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N2" s="5" t="inlineStr"/>
-      <c r="O2" s="5" t="inlineStr"/>
-      <c r="P2" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
       <c r="Q2" s="5" t="inlineStr"/>
       <c r="R2" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S2" s="5" t="inlineStr"/>
       <c r="T2" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U2" s="5" t="inlineStr"/>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
@@ -3879,43 +4181,45 @@
       <c r="F3" s="5" t="inlineStr"/>
       <c r="G3" s="5" t="inlineStr"/>
       <c r="H3" s="5" t="inlineStr"/>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I3" s="5" t="inlineStr"/>
       <c r="J3" s="5" t="inlineStr"/>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr"/>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N3" s="5" t="inlineStr"/>
-      <c r="O3" s="5" t="inlineStr"/>
-      <c r="P3" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr"/>
       <c r="Q3" s="5" t="inlineStr"/>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr"/>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr"/>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
@@ -3940,43 +4244,45 @@
       <c r="F4" s="5" t="inlineStr"/>
       <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr"/>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr"/>
-      <c r="O4" s="5" t="inlineStr"/>
-      <c r="P4" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr"/>
       <c r="Q4" s="5" t="inlineStr"/>
       <c r="R4" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S4" s="5" t="inlineStr"/>
       <c r="T4" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U4" s="5" t="inlineStr"/>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -3998,46 +4304,52 @@
       <c r="E5" s="5" t="n">
         <v>1.0002</v>
       </c>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="n">
+        <v>0.2483229876673971</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0.1843730537306586</v>
+      </c>
       <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I5" s="5" t="inlineStr"/>
       <c r="J5" s="5" t="inlineStr"/>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr"/>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N5" s="5" t="inlineStr"/>
-      <c r="O5" s="5" t="inlineStr"/>
-      <c r="P5" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="inlineStr"/>
       <c r="Q5" s="5" t="inlineStr"/>
       <c r="R5" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S5" s="5" t="inlineStr"/>
       <c r="T5" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U5" s="5" t="inlineStr"/>
+      <c r="V5" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -4060,25 +4372,23 @@
         <v>0.9698</v>
       </c>
       <c r="F6" s="5" t="n">
+        <v>0.2260441150541987</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.3551752959427892</v>
+      </c>
+      <c r="H6" s="5" t="n">
         <v>0.501077617843089</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="I6" s="5" t="n">
         <v>0.212860651220515</v>
       </c>
-      <c r="H6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L6" s="5" t="n">
@@ -4086,37 +4396,45 @@
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O6" s="5" t="n">
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="5" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="P6" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q6" s="5" t="n">
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S6" s="5" t="n">
         <v>0.08</v>
       </c>
-      <c r="R6" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S6" s="5" t="n">
+      <c r="T6" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U6" s="5" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="T6" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U6" s="5" t="n">
+      <c r="V6" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W6" s="5" t="n">
         <v>0.07333333333333335</v>
       </c>
     </row>
@@ -4141,25 +4459,23 @@
         <v>0.9698</v>
       </c>
       <c r="F7" s="5" t="n">
+        <v>0.1877237381087118</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0.2949469219730214</v>
+      </c>
+      <c r="H7" s="5" t="n">
         <v>0.501077617843089</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="I7" s="5" t="n">
         <v>0.212860651220515</v>
       </c>
-      <c r="H7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L7" s="5" t="n">
@@ -4167,37 +4483,45 @@
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N7" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O7" s="5" t="n">
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="5" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="P7" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q7" s="5" t="n">
+      <c r="R7" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S7" s="5" t="n">
         <v>0.08</v>
       </c>
-      <c r="R7" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S7" s="5" t="n">
+      <c r="T7" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U7" s="5" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="T7" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U7" s="5" t="n">
+      <c r="V7" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W7" s="5" t="n">
         <v>0.07333333333333335</v>
       </c>
     </row>
@@ -4224,43 +4548,45 @@
       <c r="F8" s="5" t="inlineStr"/>
       <c r="G8" s="5" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I8" s="5" t="inlineStr"/>
       <c r="J8" s="5" t="inlineStr"/>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr"/>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N8" s="5" t="inlineStr"/>
-      <c r="O8" s="5" t="inlineStr"/>
-      <c r="P8" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P8" s="5" t="inlineStr"/>
       <c r="Q8" s="5" t="inlineStr"/>
       <c r="R8" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S8" s="5" t="inlineStr"/>
       <c r="T8" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U8" s="5" t="inlineStr"/>
+      <c r="V8" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -4285,43 +4611,45 @@
       <c r="F9" s="5" t="inlineStr"/>
       <c r="G9" s="5" t="inlineStr"/>
       <c r="H9" s="5" t="inlineStr"/>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I9" s="5" t="inlineStr"/>
       <c r="J9" s="5" t="inlineStr"/>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr"/>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N9" s="5" t="inlineStr"/>
-      <c r="O9" s="5" t="inlineStr"/>
-      <c r="P9" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P9" s="5" t="inlineStr"/>
       <c r="Q9" s="5" t="inlineStr"/>
       <c r="R9" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S9" s="5" t="inlineStr"/>
       <c r="T9" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U9" s="5" t="inlineStr"/>
+      <c r="V9" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -4344,49 +4672,55 @@
         <v>1.0022</v>
       </c>
       <c r="F10" s="5" t="n">
+        <v>0.2369581649793167</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.2553599837400992</v>
+      </c>
+      <c r="H10" s="5" t="n">
         <v>0.511388342191138</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="I10" s="5" t="n">
         <v>0.22265637813532</v>
-      </c>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
       </c>
       <c r="J10" s="5" t="inlineStr"/>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr"/>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N10" s="5" t="inlineStr"/>
-      <c r="O10" s="5" t="inlineStr"/>
-      <c r="P10" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P10" s="5" t="inlineStr"/>
       <c r="Q10" s="5" t="inlineStr"/>
       <c r="R10" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S10" s="5" t="inlineStr"/>
       <c r="T10" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U10" s="5" t="inlineStr"/>
+      <c r="V10" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -4409,25 +4743,23 @@
         <v>1.0132</v>
       </c>
       <c r="F11" s="5" t="n">
+        <v>0.233601468490469</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0.215574037292203</v>
+      </c>
+      <c r="H11" s="5" t="n">
         <v>0.510590381447813</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="I11" s="5" t="n">
         <v>0.225784053085401</v>
       </c>
-      <c r="H11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L11" s="5" t="n">
@@ -4435,26 +4767,26 @@
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N11" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P11" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R11" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S11" s="5" t="n">
@@ -4462,10 +4794,18 @@
       </c>
       <c r="T11" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W11" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4490,25 +4830,23 @@
         <v>1.0132</v>
       </c>
       <c r="F12" s="5" t="n">
+        <v>0.233601468490469</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.215574037292203</v>
+      </c>
+      <c r="H12" s="5" t="n">
         <v>0.510590381447813</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="I12" s="5" t="n">
         <v>0.225784053085401</v>
       </c>
-      <c r="H12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L12" s="5" t="n">
@@ -4516,26 +4854,26 @@
       </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N12" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P12" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R12" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S12" s="5" t="n">
@@ -4543,10 +4881,18 @@
       </c>
       <c r="T12" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W12" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4571,25 +4917,23 @@
         <v>1.0135</v>
       </c>
       <c r="F13" s="5" t="n">
+        <v>0.2443246485498652</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0.183277695807331</v>
+      </c>
+      <c r="H13" s="5" t="n">
         <v>0.510590381447813</v>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="I13" s="5" t="n">
         <v>0.225784053085401</v>
       </c>
-      <c r="H13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L13" s="5" t="n">
@@ -4597,26 +4941,26 @@
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P13" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R13" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S13" s="5" t="n">
@@ -4624,10 +4968,18 @@
       </c>
       <c r="T13" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W13" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4652,25 +5004,23 @@
         <v>0.9955000000000001</v>
       </c>
       <c r="F14" s="5" t="n">
+        <v>0.1329824757126514</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0.3248435729394352</v>
+      </c>
+      <c r="H14" s="5" t="n">
         <v>0.510590381447813</v>
       </c>
-      <c r="G14" s="5" t="n">
+      <c r="I14" s="5" t="n">
         <v>0.225784053085401</v>
       </c>
-      <c r="H14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L14" s="5" t="n">
@@ -4678,26 +5028,26 @@
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N14" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O14" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="P14" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P14" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>0.16</v>
       </c>
       <c r="R14" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S14" s="5" t="n">
@@ -4705,12 +5055,20 @@
       </c>
       <c r="T14" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U14" s="5" t="n">
         <v>0.16</v>
       </c>
+      <c r="V14" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W14" s="5" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
@@ -4733,25 +5091,23 @@
         <v>0.966</v>
       </c>
       <c r="F15" s="5" t="n">
+        <v>0.1341216632110691</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0.2753352654629494</v>
+      </c>
+      <c r="H15" s="5" t="n">
         <v>0.65425629128861</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="I15" s="5" t="n">
         <v>0.512670422089759</v>
       </c>
-      <c r="H15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L15" s="5" t="n">
@@ -4759,26 +5115,26 @@
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N15" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O15" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="P15" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P15" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>0.16</v>
       </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S15" s="5" t="n">
@@ -4786,12 +5142,20 @@
       </c>
       <c r="T15" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U15" s="5" t="n">
         <v>0.16</v>
       </c>
+      <c r="V15" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W15" s="5" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
@@ -4814,25 +5178,23 @@
         <v>0.9723000000000001</v>
       </c>
       <c r="F16" s="5" t="n">
+        <v>0.1186603136108224</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.2706607556452453</v>
+      </c>
+      <c r="H16" s="5" t="n">
         <v>0.65425629128861</v>
       </c>
-      <c r="G16" s="5" t="n">
+      <c r="I16" s="5" t="n">
         <v>0.512670422089759</v>
       </c>
-      <c r="H16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L16" s="5" t="n">
@@ -4840,26 +5202,26 @@
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N16" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O16" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="P16" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P16" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0.16</v>
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S16" s="5" t="n">
@@ -4867,12 +5229,20 @@
       </c>
       <c r="T16" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U16" s="5" t="n">
         <v>0.16</v>
       </c>
+      <c r="V16" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W16" s="5" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -4895,25 +5265,23 @@
         <v>0.9766</v>
       </c>
       <c r="F17" s="5" t="n">
+        <v>0.1075421523838416</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.1479399367177207</v>
+      </c>
+      <c r="H17" s="5" t="n">
         <v>0.65425629128861</v>
       </c>
-      <c r="G17" s="5" t="n">
+      <c r="I17" s="5" t="n">
         <v>0.512670422089759</v>
       </c>
-      <c r="H17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L17" s="5" t="n">
@@ -4921,26 +5289,26 @@
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N17" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O17" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="P17" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P17" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0.16</v>
       </c>
       <c r="R17" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S17" s="5" t="n">
@@ -4948,12 +5316,20 @@
       </c>
       <c r="T17" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U17" s="5" t="n">
         <v>0.16</v>
       </c>
+      <c r="V17" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W17" s="5" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -4976,25 +5352,23 @@
         <v>0.9781</v>
       </c>
       <c r="F18" s="5" t="n">
+        <v>0.1251631989034748</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.233198203822338</v>
+      </c>
+      <c r="H18" s="5" t="n">
         <v>0.65425629128861</v>
       </c>
-      <c r="G18" s="5" t="n">
+      <c r="I18" s="5" t="n">
         <v>0.512670422089759</v>
       </c>
-      <c r="H18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L18" s="5" t="n">
@@ -5002,26 +5376,26 @@
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N18" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O18" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="P18" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
+      <c r="O18" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P18" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0.16</v>
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S18" s="5" t="n">
@@ -5029,12 +5403,20 @@
       </c>
       <c r="T18" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U18" s="5" t="n">
         <v>0.16</v>
       </c>
+      <c r="V18" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W18" s="5" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
@@ -5057,25 +5439,23 @@
         <v>1.0106</v>
       </c>
       <c r="F19" s="5" t="n">
+        <v>0.2396658493615177</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0.2613261383795547</v>
+      </c>
+      <c r="H19" s="5" t="n">
         <v>0.510590381447813</v>
       </c>
-      <c r="G19" s="5" t="n">
+      <c r="I19" s="5" t="n">
         <v>0.225784053085401</v>
       </c>
-      <c r="H19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L19" s="5" t="n">
@@ -5083,26 +5463,26 @@
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
+      <c r="O19" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P19" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S19" s="5" t="n">
@@ -5110,10 +5490,18 @@
       </c>
       <c r="T19" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W19" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5138,25 +5526,23 @@
         <v>1.0106</v>
       </c>
       <c r="F20" s="5" t="n">
+        <v>0.2396658493615177</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0.2613261383795547</v>
+      </c>
+      <c r="H20" s="5" t="n">
         <v>0.510590381447813</v>
       </c>
-      <c r="G20" s="5" t="n">
+      <c r="I20" s="5" t="n">
         <v>0.225784053085401</v>
       </c>
-      <c r="H20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L20" s="5" t="n">
@@ -5164,26 +5550,26 @@
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N20" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
+      <c r="O20" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P20" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S20" s="5" t="n">
@@ -5191,10 +5577,18 @@
       </c>
       <c r="T20" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W20" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5219,25 +5613,23 @@
         <v>0.9709</v>
       </c>
       <c r="F21" s="5" t="n">
+        <v>0.1972627642475195</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0.4012166584184587</v>
+      </c>
+      <c r="H21" s="5" t="n">
         <v>0.501077617843089</v>
       </c>
-      <c r="G21" s="5" t="n">
+      <c r="I21" s="5" t="n">
         <v>0.212860651220515</v>
       </c>
-      <c r="H21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
       <c r="J21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L21" s="5" t="n">
@@ -5245,37 +5637,45 @@
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N21" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O21" s="5" t="n">
+      <c r="O21" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="5" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="P21" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q21" s="5" t="n">
+      <c r="R21" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S21" s="5" t="n">
         <v>0.08</v>
       </c>
-      <c r="R21" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S21" s="5" t="n">
+      <c r="T21" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U21" s="5" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="T21" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U21" s="5" t="n">
+      <c r="V21" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W21" s="5" t="n">
         <v>0.07333333333333335</v>
       </c>
     </row>
@@ -5300,49 +5700,55 @@
         <v>0.9963</v>
       </c>
       <c r="F22" s="5" t="n">
+        <v>0.2449284253072609</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.3166893979467619</v>
+      </c>
+      <c r="H22" s="5" t="n">
         <v>0.511370986967519</v>
       </c>
-      <c r="G22" s="5" t="n">
+      <c r="I22" s="5" t="n">
         <v>0.22945882760626</v>
-      </c>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
       </c>
       <c r="J22" s="5" t="inlineStr"/>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr"/>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr"/>
-      <c r="O22" s="5" t="inlineStr"/>
-      <c r="P22" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O22" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P22" s="5" t="inlineStr"/>
       <c r="Q22" s="5" t="inlineStr"/>
       <c r="R22" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S22" s="5" t="inlineStr"/>
       <c r="T22" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U22" s="5" t="inlineStr"/>
+      <c r="V22" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -5365,49 +5771,55 @@
         <v>0.9967</v>
       </c>
       <c r="F23" s="5" t="n">
+        <v>0.2720339427313853</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0.383961084072671</v>
+      </c>
+      <c r="H23" s="5" t="n">
         <v>0.511370986967519</v>
       </c>
-      <c r="G23" s="5" t="n">
+      <c r="I23" s="5" t="n">
         <v>0.22945882760626</v>
-      </c>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
       </c>
       <c r="J23" s="5" t="inlineStr"/>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr"/>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N23" s="5" t="inlineStr"/>
-      <c r="O23" s="5" t="inlineStr"/>
-      <c r="P23" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O23" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P23" s="5" t="inlineStr"/>
       <c r="Q23" s="5" t="inlineStr"/>
       <c r="R23" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S23" s="5" t="inlineStr"/>
       <c r="T23" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U23" s="5" t="inlineStr"/>
+      <c r="V23" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -5429,46 +5841,52 @@
       <c r="E24" s="5" t="n">
         <v>0.9458</v>
       </c>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="n">
+        <v>0.1837838121931059</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.2611513523019278</v>
+      </c>
       <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I24" s="5" t="inlineStr"/>
       <c r="J24" s="5" t="inlineStr"/>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr"/>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N24" s="5" t="inlineStr"/>
-      <c r="O24" s="5" t="inlineStr"/>
-      <c r="P24" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O24" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P24" s="5" t="inlineStr"/>
       <c r="Q24" s="5" t="inlineStr"/>
       <c r="R24" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S24" s="5" t="inlineStr"/>
       <c r="T24" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U24" s="5" t="inlineStr"/>
+      <c r="V24" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -5490,46 +5908,52 @@
       <c r="E25" s="5" t="n">
         <v>0.9408</v>
       </c>
-      <c r="F25" s="5" t="inlineStr"/>
-      <c r="G25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="n">
+        <v>0.1487965707958214</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.05183812537020938</v>
+      </c>
       <c r="H25" s="5" t="inlineStr"/>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I25" s="5" t="inlineStr"/>
       <c r="J25" s="5" t="inlineStr"/>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr"/>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N25" s="5" t="inlineStr"/>
-      <c r="O25" s="5" t="inlineStr"/>
-      <c r="P25" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O25" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P25" s="5" t="inlineStr"/>
       <c r="Q25" s="5" t="inlineStr"/>
       <c r="R25" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S25" s="5" t="inlineStr"/>
       <c r="T25" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U25" s="5" t="inlineStr"/>
+      <c r="V25" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
@@ -5551,46 +5975,52 @@
       <c r="E26" s="5" t="n">
         <v>0.9605</v>
       </c>
-      <c r="F26" s="5" t="inlineStr"/>
-      <c r="G26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="n">
+        <v>0.01165648634818117</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0.004972497428635703</v>
+      </c>
       <c r="H26" s="5" t="inlineStr"/>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I26" s="5" t="inlineStr"/>
       <c r="J26" s="5" t="inlineStr"/>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr"/>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N26" s="5" t="inlineStr"/>
-      <c r="O26" s="5" t="inlineStr"/>
-      <c r="P26" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O26" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P26" s="5" t="inlineStr"/>
       <c r="Q26" s="5" t="inlineStr"/>
       <c r="R26" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr"/>
       <c r="T26" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U26" s="5" t="inlineStr"/>
+      <c r="V26" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -5612,46 +6042,52 @@
       <c r="E27" s="5" t="n">
         <v>0.9711</v>
       </c>
-      <c r="F27" s="5" t="inlineStr"/>
-      <c r="G27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0.179641601485183</v>
+      </c>
       <c r="H27" s="5" t="inlineStr"/>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I27" s="5" t="inlineStr"/>
       <c r="J27" s="5" t="inlineStr"/>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr"/>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N27" s="5" t="inlineStr"/>
-      <c r="O27" s="5" t="inlineStr"/>
-      <c r="P27" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O27" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P27" s="5" t="inlineStr"/>
       <c r="Q27" s="5" t="inlineStr"/>
       <c r="R27" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S27" s="5" t="inlineStr"/>
       <c r="T27" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U27" s="5" t="inlineStr"/>
+      <c r="V27" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -5673,46 +6109,52 @@
       <c r="E28" s="5" t="n">
         <v>0.971</v>
       </c>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0.1555674430999341</v>
+      </c>
       <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I28" s="5" t="inlineStr"/>
       <c r="J28" s="5" t="inlineStr"/>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr"/>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N28" s="5" t="inlineStr"/>
-      <c r="O28" s="5" t="inlineStr"/>
-      <c r="P28" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O28" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P28" s="5" t="inlineStr"/>
       <c r="Q28" s="5" t="inlineStr"/>
       <c r="R28" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S28" s="5" t="inlineStr"/>
       <c r="T28" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U28" s="5" t="inlineStr"/>
+      <c r="V28" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
@@ -5734,46 +6176,52 @@
       <c r="E29" s="5" t="n">
         <v>0.9635</v>
       </c>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="n">
+        <v>0.09029871973567261</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0.1208463990083658</v>
+      </c>
       <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I29" s="5" t="inlineStr"/>
       <c r="J29" s="5" t="inlineStr"/>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr"/>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N29" s="5" t="inlineStr"/>
-      <c r="O29" s="5" t="inlineStr"/>
-      <c r="P29" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O29" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P29" s="5" t="inlineStr"/>
       <c r="Q29" s="5" t="inlineStr"/>
       <c r="R29" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S29" s="5" t="inlineStr"/>
       <c r="T29" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U29" s="5" t="inlineStr"/>
+      <c r="V29" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -5795,46 +6243,52 @@
       <c r="E30" s="5" t="n">
         <v>0.962</v>
       </c>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="n">
+        <v>0.1002715806472839</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.1083613761067723</v>
+      </c>
       <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I30" s="5" t="inlineStr"/>
       <c r="J30" s="5" t="inlineStr"/>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr"/>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr"/>
-      <c r="O30" s="5" t="inlineStr"/>
-      <c r="P30" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O30" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P30" s="5" t="inlineStr"/>
       <c r="Q30" s="5" t="inlineStr"/>
       <c r="R30" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S30" s="5" t="inlineStr"/>
       <c r="T30" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U30" s="5" t="inlineStr"/>
+      <c r="V30" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
@@ -5856,46 +6310,52 @@
       <c r="E31" s="5" t="n">
         <v>0.9538</v>
       </c>
-      <c r="F31" s="5" t="inlineStr"/>
-      <c r="G31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="n">
+        <v>0.007476326214591267</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0.0009835058684714015</v>
+      </c>
       <c r="H31" s="5" t="inlineStr"/>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I31" s="5" t="inlineStr"/>
       <c r="J31" s="5" t="inlineStr"/>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr"/>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N31" s="5" t="inlineStr"/>
-      <c r="O31" s="5" t="inlineStr"/>
-      <c r="P31" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O31" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P31" s="5" t="inlineStr"/>
       <c r="Q31" s="5" t="inlineStr"/>
       <c r="R31" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S31" s="5" t="inlineStr"/>
       <c r="T31" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U31" s="5" t="inlineStr"/>
+      <c r="V31" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
@@ -5917,46 +6377,52 @@
       <c r="E32" s="5" t="n">
         <v>0.9538</v>
       </c>
-      <c r="F32" s="5" t="inlineStr"/>
-      <c r="G32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="n">
+        <v>0.004042184103801194</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="H32" s="5" t="inlineStr"/>
-      <c r="I32" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I32" s="5" t="inlineStr"/>
       <c r="J32" s="5" t="inlineStr"/>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr"/>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N32" s="5" t="inlineStr"/>
-      <c r="O32" s="5" t="inlineStr"/>
-      <c r="P32" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O32" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P32" s="5" t="inlineStr"/>
       <c r="Q32" s="5" t="inlineStr"/>
       <c r="R32" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S32" s="5" t="inlineStr"/>
       <c r="T32" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U32" s="5" t="inlineStr"/>
+      <c r="V32" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
@@ -5978,46 +6444,52 @@
       <c r="E33" s="5" t="n">
         <v>0.9538</v>
       </c>
-      <c r="F33" s="5" t="inlineStr"/>
-      <c r="G33" s="5" t="inlineStr"/>
+      <c r="F33" s="5" t="n">
+        <v>0.00666136667720707</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="H33" s="5" t="inlineStr"/>
-      <c r="I33" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I33" s="5" t="inlineStr"/>
       <c r="J33" s="5" t="inlineStr"/>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr"/>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N33" s="5" t="inlineStr"/>
-      <c r="O33" s="5" t="inlineStr"/>
-      <c r="P33" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O33" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P33" s="5" t="inlineStr"/>
       <c r="Q33" s="5" t="inlineStr"/>
       <c r="R33" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S33" s="5" t="inlineStr"/>
       <c r="T33" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U33" s="5" t="inlineStr"/>
+      <c r="V33" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
@@ -6039,46 +6511,52 @@
       <c r="E34" s="5" t="n">
         <v>0.9389999999999999</v>
       </c>
-      <c r="F34" s="5" t="inlineStr"/>
-      <c r="G34" s="5" t="inlineStr"/>
+      <c r="F34" s="5" t="n">
+        <v>0.1078900067150126</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0.2000408936031856</v>
+      </c>
       <c r="H34" s="5" t="inlineStr"/>
-      <c r="I34" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I34" s="5" t="inlineStr"/>
       <c r="J34" s="5" t="inlineStr"/>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr"/>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N34" s="5" t="inlineStr"/>
-      <c r="O34" s="5" t="inlineStr"/>
-      <c r="P34" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O34" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P34" s="5" t="inlineStr"/>
       <c r="Q34" s="5" t="inlineStr"/>
       <c r="R34" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S34" s="5" t="inlineStr"/>
       <c r="T34" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U34" s="5" t="inlineStr"/>
+      <c r="V34" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
@@ -6100,46 +6578,52 @@
       <c r="E35" s="5" t="n">
         <v>0.9389999999999999</v>
       </c>
-      <c r="F35" s="5" t="inlineStr"/>
-      <c r="G35" s="5" t="inlineStr"/>
+      <c r="F35" s="5" t="n">
+        <v>0.2044227016730216</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0.265181802157253</v>
+      </c>
       <c r="H35" s="5" t="inlineStr"/>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I35" s="5" t="inlineStr"/>
       <c r="J35" s="5" t="inlineStr"/>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr"/>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N35" s="5" t="inlineStr"/>
-      <c r="O35" s="5" t="inlineStr"/>
-      <c r="P35" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O35" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P35" s="5" t="inlineStr"/>
       <c r="Q35" s="5" t="inlineStr"/>
       <c r="R35" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S35" s="5" t="inlineStr"/>
       <c r="T35" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U35" s="5" t="inlineStr"/>
+      <c r="V35" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
@@ -6161,46 +6645,52 @@
       <c r="E36" s="5" t="n">
         <v>0.9389999999999999</v>
       </c>
-      <c r="F36" s="5" t="inlineStr"/>
-      <c r="G36" s="5" t="inlineStr"/>
+      <c r="F36" s="5" t="n">
+        <v>0.2050709857686178</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0.2636993184442319</v>
+      </c>
       <c r="H36" s="5" t="inlineStr"/>
-      <c r="I36" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I36" s="5" t="inlineStr"/>
       <c r="J36" s="5" t="inlineStr"/>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr"/>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N36" s="5" t="inlineStr"/>
-      <c r="O36" s="5" t="inlineStr"/>
-      <c r="P36" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O36" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P36" s="5" t="inlineStr"/>
       <c r="Q36" s="5" t="inlineStr"/>
       <c r="R36" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S36" s="5" t="inlineStr"/>
       <c r="T36" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U36" s="5" t="inlineStr"/>
+      <c r="V36" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
@@ -6222,46 +6712,52 @@
       <c r="E37" s="5" t="n">
         <v>0.9661999999999999</v>
       </c>
-      <c r="F37" s="5" t="inlineStr"/>
-      <c r="G37" s="5" t="inlineStr"/>
+      <c r="F37" s="5" t="n">
+        <v>0.100240841468152</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0.1457829031037056</v>
+      </c>
       <c r="H37" s="5" t="inlineStr"/>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I37" s="5" t="inlineStr"/>
       <c r="J37" s="5" t="inlineStr"/>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr"/>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N37" s="5" t="inlineStr"/>
-      <c r="O37" s="5" t="inlineStr"/>
-      <c r="P37" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O37" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P37" s="5" t="inlineStr"/>
       <c r="Q37" s="5" t="inlineStr"/>
       <c r="R37" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S37" s="5" t="inlineStr"/>
       <c r="T37" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U37" s="5" t="inlineStr"/>
+      <c r="V37" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
@@ -6283,46 +6779,52 @@
       <c r="E38" s="5" t="n">
         <v>0.9661999999999999</v>
       </c>
-      <c r="F38" s="5" t="inlineStr"/>
-      <c r="G38" s="5" t="inlineStr"/>
+      <c r="F38" s="5" t="n">
+        <v>0.1132112008880745</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0.165330135848075</v>
+      </c>
       <c r="H38" s="5" t="inlineStr"/>
-      <c r="I38" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I38" s="5" t="inlineStr"/>
       <c r="J38" s="5" t="inlineStr"/>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr"/>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N38" s="5" t="inlineStr"/>
-      <c r="O38" s="5" t="inlineStr"/>
-      <c r="P38" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O38" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P38" s="5" t="inlineStr"/>
       <c r="Q38" s="5" t="inlineStr"/>
       <c r="R38" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S38" s="5" t="inlineStr"/>
       <c r="T38" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U38" s="5" t="inlineStr"/>
+      <c r="V38" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
@@ -6344,46 +6846,52 @@
       <c r="E39" s="5" t="n">
         <v>0.9379</v>
       </c>
-      <c r="F39" s="5" t="inlineStr"/>
-      <c r="G39" s="5" t="inlineStr"/>
+      <c r="F39" s="5" t="n">
+        <v>0.1951479456045728</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0.3052119364643321</v>
+      </c>
       <c r="H39" s="5" t="inlineStr"/>
-      <c r="I39" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I39" s="5" t="inlineStr"/>
       <c r="J39" s="5" t="inlineStr"/>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr"/>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N39" s="5" t="inlineStr"/>
-      <c r="O39" s="5" t="inlineStr"/>
-      <c r="P39" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O39" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P39" s="5" t="inlineStr"/>
       <c r="Q39" s="5" t="inlineStr"/>
       <c r="R39" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S39" s="5" t="inlineStr"/>
       <c r="T39" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U39" s="5" t="inlineStr"/>
+      <c r="V39" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
@@ -6405,46 +6913,52 @@
       <c r="E40" s="5" t="n">
         <v>0.9583</v>
       </c>
-      <c r="F40" s="5" t="inlineStr"/>
-      <c r="G40" s="5" t="inlineStr"/>
+      <c r="F40" s="5" t="n">
+        <v>0.07862107896860038</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0.1223251897635215</v>
+      </c>
       <c r="H40" s="5" t="inlineStr"/>
-      <c r="I40" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I40" s="5" t="inlineStr"/>
       <c r="J40" s="5" t="inlineStr"/>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr"/>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N40" s="5" t="inlineStr"/>
-      <c r="O40" s="5" t="inlineStr"/>
-      <c r="P40" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O40" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P40" s="5" t="inlineStr"/>
       <c r="Q40" s="5" t="inlineStr"/>
       <c r="R40" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S40" s="5" t="inlineStr"/>
       <c r="T40" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U40" s="5" t="inlineStr"/>
+      <c r="V40" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
@@ -6466,46 +6980,52 @@
       <c r="E41" s="5" t="n">
         <v>0.9709</v>
       </c>
-      <c r="F41" s="5" t="inlineStr"/>
-      <c r="G41" s="5" t="inlineStr"/>
+      <c r="F41" s="5" t="n">
+        <v>0.09378566692877877</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.1999025312540723</v>
+      </c>
       <c r="H41" s="5" t="inlineStr"/>
-      <c r="I41" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I41" s="5" t="inlineStr"/>
       <c r="J41" s="5" t="inlineStr"/>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr"/>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N41" s="5" t="inlineStr"/>
-      <c r="O41" s="5" t="inlineStr"/>
-      <c r="P41" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O41" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P41" s="5" t="inlineStr"/>
       <c r="Q41" s="5" t="inlineStr"/>
       <c r="R41" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S41" s="5" t="inlineStr"/>
       <c r="T41" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U41" s="5" t="inlineStr"/>
+      <c r="V41" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
@@ -6527,46 +7047,52 @@
       <c r="E42" s="5" t="n">
         <v>0.9694</v>
       </c>
-      <c r="F42" s="5" t="inlineStr"/>
-      <c r="G42" s="5" t="inlineStr"/>
+      <c r="F42" s="5" t="n">
+        <v>0.006173969971481119</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0.003504366906944112</v>
+      </c>
       <c r="H42" s="5" t="inlineStr"/>
-      <c r="I42" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I42" s="5" t="inlineStr"/>
       <c r="J42" s="5" t="inlineStr"/>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr"/>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N42" s="5" t="inlineStr"/>
-      <c r="O42" s="5" t="inlineStr"/>
-      <c r="P42" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O42" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P42" s="5" t="inlineStr"/>
       <c r="Q42" s="5" t="inlineStr"/>
       <c r="R42" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S42" s="5" t="inlineStr"/>
       <c r="T42" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U42" s="5" t="inlineStr"/>
+      <c r="V42" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
@@ -6588,46 +7114,52 @@
       <c r="E43" s="5" t="n">
         <v>0.9694</v>
       </c>
-      <c r="F43" s="5" t="inlineStr"/>
-      <c r="G43" s="5" t="inlineStr"/>
+      <c r="F43" s="5" t="n">
+        <v>0.009571326064233943</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="H43" s="5" t="inlineStr"/>
-      <c r="I43" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I43" s="5" t="inlineStr"/>
       <c r="J43" s="5" t="inlineStr"/>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr"/>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N43" s="5" t="inlineStr"/>
-      <c r="O43" s="5" t="inlineStr"/>
-      <c r="P43" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O43" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P43" s="5" t="inlineStr"/>
       <c r="Q43" s="5" t="inlineStr"/>
       <c r="R43" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S43" s="5" t="inlineStr"/>
       <c r="T43" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U43" s="5" t="inlineStr"/>
+      <c r="V43" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
@@ -6649,46 +7181,52 @@
       <c r="E44" s="5" t="n">
         <v>0.9112</v>
       </c>
-      <c r="F44" s="5" t="inlineStr"/>
-      <c r="G44" s="5" t="inlineStr"/>
+      <c r="F44" s="5" t="n">
+        <v>0.1117765711557074</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0.186319094139723</v>
+      </c>
       <c r="H44" s="5" t="inlineStr"/>
-      <c r="I44" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I44" s="5" t="inlineStr"/>
       <c r="J44" s="5" t="inlineStr"/>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr"/>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N44" s="5" t="inlineStr"/>
-      <c r="O44" s="5" t="inlineStr"/>
-      <c r="P44" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O44" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P44" s="5" t="inlineStr"/>
       <c r="Q44" s="5" t="inlineStr"/>
       <c r="R44" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S44" s="5" t="inlineStr"/>
       <c r="T44" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U44" s="5" t="inlineStr"/>
+      <c r="V44" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W44" s="5" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
@@ -6710,46 +7248,52 @@
       <c r="E45" s="5" t="n">
         <v>1.0034</v>
       </c>
-      <c r="F45" s="5" t="inlineStr"/>
-      <c r="G45" s="5" t="inlineStr"/>
+      <c r="F45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="H45" s="5" t="inlineStr"/>
-      <c r="I45" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I45" s="5" t="inlineStr"/>
       <c r="J45" s="5" t="inlineStr"/>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr"/>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N45" s="5" t="inlineStr"/>
-      <c r="O45" s="5" t="inlineStr"/>
-      <c r="P45" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O45" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P45" s="5" t="inlineStr"/>
       <c r="Q45" s="5" t="inlineStr"/>
       <c r="R45" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S45" s="5" t="inlineStr"/>
       <c r="T45" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U45" s="5" t="inlineStr"/>
+      <c r="V45" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
@@ -6771,46 +7315,52 @@
       <c r="E46" s="5" t="n">
         <v>0.9583</v>
       </c>
-      <c r="F46" s="5" t="inlineStr"/>
-      <c r="G46" s="5" t="inlineStr"/>
+      <c r="F46" s="5" t="n">
+        <v>0.1104986454982489</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0.08860136051521761</v>
+      </c>
       <c r="H46" s="5" t="inlineStr"/>
-      <c r="I46" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I46" s="5" t="inlineStr"/>
       <c r="J46" s="5" t="inlineStr"/>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L46" s="5" t="inlineStr"/>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N46" s="5" t="inlineStr"/>
-      <c r="O46" s="5" t="inlineStr"/>
-      <c r="P46" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O46" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P46" s="5" t="inlineStr"/>
       <c r="Q46" s="5" t="inlineStr"/>
       <c r="R46" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S46" s="5" t="inlineStr"/>
       <c r="T46" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U46" s="5" t="inlineStr"/>
+      <c r="V46" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
@@ -6832,46 +7382,52 @@
       <c r="E47" s="5" t="n">
         <v>0.9611</v>
       </c>
-      <c r="F47" s="5" t="inlineStr"/>
-      <c r="G47" s="5" t="inlineStr"/>
+      <c r="F47" s="5" t="n">
+        <v>0.0231798012669201</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0.02046415405566893</v>
+      </c>
       <c r="H47" s="5" t="inlineStr"/>
-      <c r="I47" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I47" s="5" t="inlineStr"/>
       <c r="J47" s="5" t="inlineStr"/>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr"/>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N47" s="5" t="inlineStr"/>
-      <c r="O47" s="5" t="inlineStr"/>
-      <c r="P47" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O47" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P47" s="5" t="inlineStr"/>
       <c r="Q47" s="5" t="inlineStr"/>
       <c r="R47" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S47" s="5" t="inlineStr"/>
       <c r="T47" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U47" s="5" t="inlineStr"/>
+      <c r="V47" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
@@ -6893,46 +7449,52 @@
       <c r="E48" s="5" t="n">
         <v>0.844</v>
       </c>
-      <c r="F48" s="5" t="inlineStr"/>
-      <c r="G48" s="5" t="inlineStr"/>
+      <c r="F48" s="5" t="n">
+        <v>0.09149797011929861</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.1685558219338047</v>
+      </c>
       <c r="H48" s="5" t="inlineStr"/>
-      <c r="I48" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I48" s="5" t="inlineStr"/>
       <c r="J48" s="5" t="inlineStr"/>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L48" s="5" t="inlineStr"/>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N48" s="5" t="inlineStr"/>
-      <c r="O48" s="5" t="inlineStr"/>
-      <c r="P48" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O48" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P48" s="5" t="inlineStr"/>
       <c r="Q48" s="5" t="inlineStr"/>
       <c r="R48" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S48" s="5" t="inlineStr"/>
       <c r="T48" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U48" s="5" t="inlineStr"/>
+      <c r="V48" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W48" s="5" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
@@ -6954,46 +7516,52 @@
       <c r="E49" s="5" t="n">
         <v>0.9605</v>
       </c>
-      <c r="F49" s="5" t="inlineStr"/>
-      <c r="G49" s="5" t="inlineStr"/>
+      <c r="F49" s="5" t="n">
+        <v>0.1018185649768411</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.04324399718648553</v>
+      </c>
       <c r="H49" s="5" t="inlineStr"/>
-      <c r="I49" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I49" s="5" t="inlineStr"/>
       <c r="J49" s="5" t="inlineStr"/>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr"/>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N49" s="5" t="inlineStr"/>
-      <c r="O49" s="5" t="inlineStr"/>
-      <c r="P49" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O49" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P49" s="5" t="inlineStr"/>
       <c r="Q49" s="5" t="inlineStr"/>
       <c r="R49" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S49" s="5" t="inlineStr"/>
       <c r="T49" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U49" s="5" t="inlineStr"/>
+      <c r="V49" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W49" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C49">
@@ -7224,6 +7792,30 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="V2:V49">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W2:W49">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/SA_curtailment.xlsx
+++ b/outputs/SA_curtailment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -67,7 +67,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -82,9 +82,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -456,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X49"/>
+  <dimension ref="A1:P49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -475,14 +472,6 @@
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="12" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -566,46 +555,6 @@
           <t>FY26-27 (Draft)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Curt FY1</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Curt FY2</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Curt FY3</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Curt Avg</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Offl FY1</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Offl FY2</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Offl FY3</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Offl Avg</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -644,10 +593,10 @@
       </c>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="5" t="n">
-        <v>0.3222683455189714</v>
+        <v>0.2903</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>0.2755625039739843</v>
+        <v>0.256</v>
       </c>
       <c r="L2" s="5" t="inlineStr"/>
       <c r="M2" s="5" t="inlineStr"/>
@@ -660,14 +609,6 @@
       <c r="P2" s="5" t="n">
         <v>1.0034</v>
       </c>
-      <c r="Q2" s="6" t="inlineStr"/>
-      <c r="R2" s="6" t="inlineStr"/>
-      <c r="S2" s="6" t="inlineStr"/>
-      <c r="T2" s="6" t="inlineStr"/>
-      <c r="U2" s="6" t="inlineStr"/>
-      <c r="V2" s="6" t="inlineStr"/>
-      <c r="W2" s="6" t="inlineStr"/>
-      <c r="X2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -718,14 +659,6 @@
       <c r="P3" s="5" t="n">
         <v>1.0034</v>
       </c>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
-      <c r="V3" s="6" t="inlineStr"/>
-      <c r="W3" s="6" t="inlineStr"/>
-      <c r="X3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -776,14 +709,6 @@
       <c r="P4" s="5" t="n">
         <v>1.0034</v>
       </c>
-      <c r="Q4" s="6" t="inlineStr"/>
-      <c r="R4" s="6" t="inlineStr"/>
-      <c r="S4" s="6" t="inlineStr"/>
-      <c r="T4" s="6" t="inlineStr"/>
-      <c r="U4" s="6" t="inlineStr"/>
-      <c r="V4" s="6" t="inlineStr"/>
-      <c r="W4" s="6" t="inlineStr"/>
-      <c r="X4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -821,11 +746,9 @@
         <v>8.25</v>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="5" t="n">
-        <v>0.2483229876673971</v>
-      </c>
+      <c r="J5" s="5" t="inlineStr"/>
       <c r="K5" s="5" t="n">
-        <v>0.1843730537306586</v>
+        <v>0.1726</v>
       </c>
       <c r="L5" s="5" t="inlineStr"/>
       <c r="M5" s="5" t="inlineStr"/>
@@ -838,14 +761,6 @@
       <c r="P5" s="5" t="n">
         <v>1.0002</v>
       </c>
-      <c r="Q5" s="6" t="inlineStr"/>
-      <c r="R5" s="6" t="inlineStr"/>
-      <c r="S5" s="6" t="inlineStr"/>
-      <c r="T5" s="6" t="inlineStr"/>
-      <c r="U5" s="6" t="inlineStr"/>
-      <c r="V5" s="6" t="inlineStr"/>
-      <c r="W5" s="6" t="inlineStr"/>
-      <c r="X5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -890,10 +805,10 @@
         <v>132</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0.2260441150541987</v>
+        <v>0.2073</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>0.3551752959427892</v>
+        <v>0.3235</v>
       </c>
       <c r="L6" s="5" t="n">
         <v>0.501077617843089</v>
@@ -910,30 +825,6 @@
       <c r="P6" s="5" t="n">
         <v>0.9698</v>
       </c>
-      <c r="Q6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="V6" s="6" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="W6" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="X6" s="6" t="n">
-        <v>0.07333333333333335</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -978,10 +869,10 @@
         <v>132</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>0.1877237381087118</v>
+        <v>0.1744</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>0.2949469219730214</v>
+        <v>0.2766</v>
       </c>
       <c r="L7" s="5" t="n">
         <v>0.501077617843089</v>
@@ -997,30 +888,6 @@
       </c>
       <c r="P7" s="5" t="n">
         <v>0.9698</v>
-      </c>
-      <c r="Q7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="V7" s="6" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="W7" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="X7" s="6" t="n">
-        <v>0.07333333333333335</v>
       </c>
     </row>
     <row r="8">
@@ -1072,14 +939,6 @@
       <c r="P8" s="5" t="n">
         <v>1.0034</v>
       </c>
-      <c r="Q8" s="6" t="inlineStr"/>
-      <c r="R8" s="6" t="inlineStr"/>
-      <c r="S8" s="6" t="inlineStr"/>
-      <c r="T8" s="6" t="inlineStr"/>
-      <c r="U8" s="6" t="inlineStr"/>
-      <c r="V8" s="6" t="inlineStr"/>
-      <c r="W8" s="6" t="inlineStr"/>
-      <c r="X8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1130,14 +989,6 @@
       <c r="P9" s="5" t="n">
         <v>1.0034</v>
       </c>
-      <c r="Q9" s="6" t="inlineStr"/>
-      <c r="R9" s="6" t="inlineStr"/>
-      <c r="S9" s="6" t="inlineStr"/>
-      <c r="T9" s="6" t="inlineStr"/>
-      <c r="U9" s="6" t="inlineStr"/>
-      <c r="V9" s="6" t="inlineStr"/>
-      <c r="W9" s="6" t="inlineStr"/>
-      <c r="X9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1182,10 +1033,10 @@
         <v>66</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0.2369581649793167</v>
+        <v>0.2225</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>0.2553599837400992</v>
+        <v>0.2415</v>
       </c>
       <c r="L10" s="5" t="n">
         <v>0.511388342191138</v>
@@ -1202,14 +1053,6 @@
       <c r="P10" s="5" t="n">
         <v>1.0022</v>
       </c>
-      <c r="Q10" s="6" t="inlineStr"/>
-      <c r="R10" s="6" t="inlineStr"/>
-      <c r="S10" s="6" t="inlineStr"/>
-      <c r="T10" s="6" t="inlineStr"/>
-      <c r="U10" s="6" t="inlineStr"/>
-      <c r="V10" s="6" t="inlineStr"/>
-      <c r="W10" s="6" t="inlineStr"/>
-      <c r="X10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1254,10 +1097,10 @@
         <v>3.3</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>0.233601468490469</v>
+        <v>0.2199</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>0.215574037292203</v>
+        <v>0.2007</v>
       </c>
       <c r="L11" s="5" t="n">
         <v>0.510590381447813</v>
@@ -1274,30 +1117,6 @@
       <c r="P11" s="5" t="n">
         <v>1.0132</v>
       </c>
-      <c r="Q11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" s="6" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1342,10 +1161,10 @@
         <v>3.3</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.233601468490469</v>
+        <v>0.2199</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>0.215574037292203</v>
+        <v>0.2007</v>
       </c>
       <c r="L12" s="5" t="n">
         <v>0.510590381447813</v>
@@ -1362,30 +1181,6 @@
       <c r="P12" s="5" t="n">
         <v>1.0132</v>
       </c>
-      <c r="Q12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" s="6" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1430,11 +1225,9 @@
         <v>3.3</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.2443246485498652</v>
-      </c>
-      <c r="K13" s="5" t="n">
-        <v>0.183277695807331</v>
-      </c>
+        <v>0.2291</v>
+      </c>
+      <c r="K13" s="5" t="inlineStr"/>
       <c r="L13" s="5" t="n">
         <v>0.510590381447813</v>
       </c>
@@ -1450,30 +1243,6 @@
       <c r="P13" s="5" t="n">
         <v>1.0135</v>
       </c>
-      <c r="Q13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" s="6" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1512,16 +1281,14 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>37</v>
+        <v>29.99</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="J14" s="5" t="n">
-        <v>0.1329824757126514</v>
-      </c>
+      <c r="J14" s="5" t="inlineStr"/>
       <c r="K14" s="5" t="n">
-        <v>0.3248435729394352</v>
+        <v>0.3012</v>
       </c>
       <c r="L14" s="5" t="n">
         <v>0.510590381447813</v>
@@ -1538,30 +1305,6 @@
       <c r="P14" s="5" t="n">
         <v>0.9955000000000001</v>
       </c>
-      <c r="Q14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="V14" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="W14" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="X14" s="6" t="n">
-        <v>0.16</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1606,10 +1349,10 @@
         <v>3.3</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>0.1341216632110691</v>
+        <v>0.1286</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>0.2753352654629494</v>
+        <v>0.2462</v>
       </c>
       <c r="L15" s="5" t="n">
         <v>0.65425629128861</v>
@@ -1626,30 +1369,6 @@
       <c r="P15" s="5" t="n">
         <v>0.966</v>
       </c>
-      <c r="Q15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="V15" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="W15" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="X15" s="6" t="n">
-        <v>0.16</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1694,10 +1413,10 @@
         <v>3.3</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0.1186603136108224</v>
+        <v>0.1131</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0.2706607556452453</v>
+        <v>0.2411</v>
       </c>
       <c r="L16" s="5" t="n">
         <v>0.65425629128861</v>
@@ -1714,30 +1433,6 @@
       <c r="P16" s="5" t="n">
         <v>0.9723000000000001</v>
       </c>
-      <c r="Q16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="V16" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="W16" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="X16" s="6" t="n">
-        <v>0.16</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1782,10 +1477,10 @@
         <v>3.3</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0.1075421523838416</v>
+        <v>0.0897</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>0.1479399367177207</v>
+        <v>0.1273</v>
       </c>
       <c r="L17" s="5" t="n">
         <v>0.65425629128861</v>
@@ -1802,30 +1497,6 @@
       <c r="P17" s="5" t="n">
         <v>0.9766</v>
       </c>
-      <c r="Q17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="V17" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="W17" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="X17" s="6" t="n">
-        <v>0.16</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1870,10 +1541,10 @@
         <v>3.3</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>0.1251631989034748</v>
+        <v>0.1184</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>0.233198203822338</v>
+        <v>0.2031</v>
       </c>
       <c r="L18" s="5" t="n">
         <v>0.65425629128861</v>
@@ -1890,30 +1561,6 @@
       <c r="P18" s="5" t="n">
         <v>0.9781</v>
       </c>
-      <c r="Q18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="V18" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="W18" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="X18" s="6" t="n">
-        <v>0.16</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1958,10 +1605,10 @@
         <v>11</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>0.2396658493615177</v>
+        <v>0.2268</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>0.2613261383795547</v>
+        <v>0.2284</v>
       </c>
       <c r="L19" s="5" t="n">
         <v>0.510590381447813</v>
@@ -1978,30 +1625,6 @@
       <c r="P19" s="5" t="n">
         <v>1.0106</v>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" s="6" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2046,10 +1669,10 @@
         <v>11</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>0.2396658493615177</v>
+        <v>0.2268</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>0.2613261383795547</v>
+        <v>0.2284</v>
       </c>
       <c r="L20" s="5" t="n">
         <v>0.510590381447813</v>
@@ -2066,30 +1689,6 @@
       <c r="P20" s="5" t="n">
         <v>1.0106</v>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" s="6" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2128,16 +1727,16 @@
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>99</v>
+        <v>79.2</v>
       </c>
       <c r="I21" s="2" t="n">
         <v>275</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>0.1972627642475195</v>
+        <v>0.1842</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>0.4012166584184587</v>
+        <v>0.3589</v>
       </c>
       <c r="L21" s="5" t="n">
         <v>0.501077617843089</v>
@@ -2154,30 +1753,6 @@
       <c r="P21" s="5" t="n">
         <v>0.9709</v>
       </c>
-      <c r="Q21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="V21" s="6" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="W21" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="X21" s="6" t="n">
-        <v>0.07333333333333335</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2222,10 +1797,10 @@
         <v>132</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>0.2449284253072609</v>
+        <v>0.1987</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>0.3166893979467619</v>
+        <v>0.2973</v>
       </c>
       <c r="L22" s="5" t="n">
         <v>0.511370986967519</v>
@@ -2242,14 +1817,6 @@
       <c r="P22" s="5" t="n">
         <v>0.9963</v>
       </c>
-      <c r="Q22" s="6" t="inlineStr"/>
-      <c r="R22" s="6" t="inlineStr"/>
-      <c r="S22" s="6" t="inlineStr"/>
-      <c r="T22" s="6" t="inlineStr"/>
-      <c r="U22" s="6" t="inlineStr"/>
-      <c r="V22" s="6" t="inlineStr"/>
-      <c r="W22" s="6" t="inlineStr"/>
-      <c r="X22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2294,10 +1861,10 @@
         <v>132</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>0.2720339427313853</v>
+        <v>0.2394</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>0.383961084072671</v>
+        <v>0.3511</v>
       </c>
       <c r="L23" s="5" t="n">
         <v>0.511370986967519</v>
@@ -2314,14 +1881,6 @@
       <c r="P23" s="5" t="n">
         <v>0.9967</v>
       </c>
-      <c r="Q23" s="6" t="inlineStr"/>
-      <c r="R23" s="6" t="inlineStr"/>
-      <c r="S23" s="6" t="inlineStr"/>
-      <c r="T23" s="6" t="inlineStr"/>
-      <c r="U23" s="6" t="inlineStr"/>
-      <c r="V23" s="6" t="inlineStr"/>
-      <c r="W23" s="6" t="inlineStr"/>
-      <c r="X23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2360,10 +1919,10 @@
       </c>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="5" t="n">
-        <v>0.1837838121931059</v>
+        <v>0.1746</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>0.2611513523019278</v>
+        <v>0.254</v>
       </c>
       <c r="L24" s="5" t="inlineStr"/>
       <c r="M24" s="5" t="inlineStr"/>
@@ -2376,14 +1935,6 @@
       <c r="P24" s="5" t="n">
         <v>0.9458</v>
       </c>
-      <c r="Q24" s="6" t="inlineStr"/>
-      <c r="R24" s="6" t="inlineStr"/>
-      <c r="S24" s="6" t="inlineStr"/>
-      <c r="T24" s="6" t="inlineStr"/>
-      <c r="U24" s="6" t="inlineStr"/>
-      <c r="V24" s="6" t="inlineStr"/>
-      <c r="W24" s="6" t="inlineStr"/>
-      <c r="X24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2422,10 +1973,10 @@
       </c>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="5" t="n">
-        <v>0.1487965707958214</v>
+        <v>0.1389</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>0.05183812537020938</v>
+        <v>0.0515</v>
       </c>
       <c r="L25" s="5" t="inlineStr"/>
       <c r="M25" s="5" t="inlineStr"/>
@@ -2438,14 +1989,6 @@
       <c r="P25" s="5" t="n">
         <v>0.9408</v>
       </c>
-      <c r="Q25" s="6" t="inlineStr"/>
-      <c r="R25" s="6" t="inlineStr"/>
-      <c r="S25" s="6" t="inlineStr"/>
-      <c r="T25" s="6" t="inlineStr"/>
-      <c r="U25" s="6" t="inlineStr"/>
-      <c r="V25" s="6" t="inlineStr"/>
-      <c r="W25" s="6" t="inlineStr"/>
-      <c r="X25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2484,10 +2027,10 @@
       </c>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="5" t="n">
-        <v>0.01165648634818117</v>
+        <v>0.0134</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>0.004972497428635703</v>
+        <v>0.0062</v>
       </c>
       <c r="L26" s="5" t="inlineStr"/>
       <c r="M26" s="5" t="inlineStr"/>
@@ -2500,14 +2043,6 @@
       <c r="P26" s="5" t="n">
         <v>0.9605</v>
       </c>
-      <c r="Q26" s="6" t="inlineStr"/>
-      <c r="R26" s="6" t="inlineStr"/>
-      <c r="S26" s="6" t="inlineStr"/>
-      <c r="T26" s="6" t="inlineStr"/>
-      <c r="U26" s="6" t="inlineStr"/>
-      <c r="V26" s="6" t="inlineStr"/>
-      <c r="W26" s="6" t="inlineStr"/>
-      <c r="X26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2545,11 +2080,9 @@
         <v>209</v>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J27" s="5" t="inlineStr"/>
       <c r="K27" s="5" t="n">
-        <v>0.179641601485183</v>
+        <v>0.176</v>
       </c>
       <c r="L27" s="5" t="inlineStr"/>
       <c r="M27" s="5" t="inlineStr"/>
@@ -2562,14 +2095,6 @@
       <c r="P27" s="5" t="n">
         <v>0.9711</v>
       </c>
-      <c r="Q27" s="6" t="inlineStr"/>
-      <c r="R27" s="6" t="inlineStr"/>
-      <c r="S27" s="6" t="inlineStr"/>
-      <c r="T27" s="6" t="inlineStr"/>
-      <c r="U27" s="6" t="inlineStr"/>
-      <c r="V27" s="6" t="inlineStr"/>
-      <c r="W27" s="6" t="inlineStr"/>
-      <c r="X27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2607,12 +2132,8 @@
         <v>203</v>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="5" t="n">
-        <v>0.1555674430999341</v>
-      </c>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr"/>
       <c r="L28" s="5" t="inlineStr"/>
       <c r="M28" s="5" t="inlineStr"/>
       <c r="N28" s="5" t="n">
@@ -2624,14 +2145,6 @@
       <c r="P28" s="5" t="n">
         <v>0.971</v>
       </c>
-      <c r="Q28" s="6" t="inlineStr"/>
-      <c r="R28" s="6" t="inlineStr"/>
-      <c r="S28" s="6" t="inlineStr"/>
-      <c r="T28" s="6" t="inlineStr"/>
-      <c r="U28" s="6" t="inlineStr"/>
-      <c r="V28" s="6" t="inlineStr"/>
-      <c r="W28" s="6" t="inlineStr"/>
-      <c r="X28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2670,10 +2183,10 @@
       </c>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="5" t="n">
-        <v>0.09029871973567261</v>
+        <v>0.0813</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>0.1208463990083658</v>
+        <v>0.1169</v>
       </c>
       <c r="L29" s="5" t="inlineStr"/>
       <c r="M29" s="5" t="inlineStr"/>
@@ -2686,14 +2199,6 @@
       <c r="P29" s="5" t="n">
         <v>0.9635</v>
       </c>
-      <c r="Q29" s="6" t="inlineStr"/>
-      <c r="R29" s="6" t="inlineStr"/>
-      <c r="S29" s="6" t="inlineStr"/>
-      <c r="T29" s="6" t="inlineStr"/>
-      <c r="U29" s="6" t="inlineStr"/>
-      <c r="V29" s="6" t="inlineStr"/>
-      <c r="W29" s="6" t="inlineStr"/>
-      <c r="X29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2732,10 +2237,10 @@
       </c>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="5" t="n">
-        <v>0.1002715806472839</v>
+        <v>0.0914</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>0.1083613761067723</v>
+        <v>0.1053</v>
       </c>
       <c r="L30" s="5" t="inlineStr"/>
       <c r="M30" s="5" t="inlineStr"/>
@@ -2748,14 +2253,6 @@
       <c r="P30" s="5" t="n">
         <v>0.962</v>
       </c>
-      <c r="Q30" s="6" t="inlineStr"/>
-      <c r="R30" s="6" t="inlineStr"/>
-      <c r="S30" s="6" t="inlineStr"/>
-      <c r="T30" s="6" t="inlineStr"/>
-      <c r="U30" s="6" t="inlineStr"/>
-      <c r="V30" s="6" t="inlineStr"/>
-      <c r="W30" s="6" t="inlineStr"/>
-      <c r="X30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2794,10 +2291,10 @@
       </c>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="5" t="n">
-        <v>0.007476326214591267</v>
+        <v>0.0092</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>0.0009835058684714015</v>
+        <v>0.0033</v>
       </c>
       <c r="L31" s="5" t="inlineStr"/>
       <c r="M31" s="5" t="inlineStr"/>
@@ -2810,14 +2307,6 @@
       <c r="P31" s="5" t="n">
         <v>0.9538</v>
       </c>
-      <c r="Q31" s="6" t="inlineStr"/>
-      <c r="R31" s="6" t="inlineStr"/>
-      <c r="S31" s="6" t="inlineStr"/>
-      <c r="T31" s="6" t="inlineStr"/>
-      <c r="U31" s="6" t="inlineStr"/>
-      <c r="V31" s="6" t="inlineStr"/>
-      <c r="W31" s="6" t="inlineStr"/>
-      <c r="X31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2856,10 +2345,10 @@
       </c>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="5" t="n">
-        <v>0.004042184103801194</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>0</v>
+        <v>0.0038</v>
       </c>
       <c r="L32" s="5" t="inlineStr"/>
       <c r="M32" s="5" t="inlineStr"/>
@@ -2872,14 +2361,6 @@
       <c r="P32" s="5" t="n">
         <v>0.9538</v>
       </c>
-      <c r="Q32" s="6" t="inlineStr"/>
-      <c r="R32" s="6" t="inlineStr"/>
-      <c r="S32" s="6" t="inlineStr"/>
-      <c r="T32" s="6" t="inlineStr"/>
-      <c r="U32" s="6" t="inlineStr"/>
-      <c r="V32" s="6" t="inlineStr"/>
-      <c r="W32" s="6" t="inlineStr"/>
-      <c r="X32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2918,10 +2399,10 @@
       </c>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="5" t="n">
-        <v>0.00666136667720707</v>
+        <v>0.0092</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>0</v>
+        <v>0.0027</v>
       </c>
       <c r="L33" s="5" t="inlineStr"/>
       <c r="M33" s="5" t="inlineStr"/>
@@ -2934,14 +2415,6 @@
       <c r="P33" s="5" t="n">
         <v>0.9538</v>
       </c>
-      <c r="Q33" s="6" t="inlineStr"/>
-      <c r="R33" s="6" t="inlineStr"/>
-      <c r="S33" s="6" t="inlineStr"/>
-      <c r="T33" s="6" t="inlineStr"/>
-      <c r="U33" s="6" t="inlineStr"/>
-      <c r="V33" s="6" t="inlineStr"/>
-      <c r="W33" s="6" t="inlineStr"/>
-      <c r="X33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2980,10 +2453,10 @@
       </c>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="5" t="n">
-        <v>0.1078900067150126</v>
+        <v>0.1058</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>0.2000408936031856</v>
+        <v>0.1941</v>
       </c>
       <c r="L34" s="5" t="inlineStr"/>
       <c r="M34" s="5" t="inlineStr"/>
@@ -2996,14 +2469,6 @@
       <c r="P34" s="5" t="n">
         <v>0.9389999999999999</v>
       </c>
-      <c r="Q34" s="6" t="inlineStr"/>
-      <c r="R34" s="6" t="inlineStr"/>
-      <c r="S34" s="6" t="inlineStr"/>
-      <c r="T34" s="6" t="inlineStr"/>
-      <c r="U34" s="6" t="inlineStr"/>
-      <c r="V34" s="6" t="inlineStr"/>
-      <c r="W34" s="6" t="inlineStr"/>
-      <c r="X34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -3042,10 +2507,10 @@
       </c>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="5" t="n">
-        <v>0.2044227016730216</v>
+        <v>0.1939</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>0.265181802157253</v>
+        <v>0.2514</v>
       </c>
       <c r="L35" s="5" t="inlineStr"/>
       <c r="M35" s="5" t="inlineStr"/>
@@ -3058,14 +2523,6 @@
       <c r="P35" s="5" t="n">
         <v>0.9389999999999999</v>
       </c>
-      <c r="Q35" s="6" t="inlineStr"/>
-      <c r="R35" s="6" t="inlineStr"/>
-      <c r="S35" s="6" t="inlineStr"/>
-      <c r="T35" s="6" t="inlineStr"/>
-      <c r="U35" s="6" t="inlineStr"/>
-      <c r="V35" s="6" t="inlineStr"/>
-      <c r="W35" s="6" t="inlineStr"/>
-      <c r="X35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -3104,10 +2561,10 @@
       </c>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="5" t="n">
-        <v>0.2050709857686178</v>
+        <v>0.1878</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>0.2636993184442319</v>
+        <v>0.2535</v>
       </c>
       <c r="L36" s="5" t="inlineStr"/>
       <c r="M36" s="5" t="inlineStr"/>
@@ -3120,14 +2577,6 @@
       <c r="P36" s="5" t="n">
         <v>0.9389999999999999</v>
       </c>
-      <c r="Q36" s="6" t="inlineStr"/>
-      <c r="R36" s="6" t="inlineStr"/>
-      <c r="S36" s="6" t="inlineStr"/>
-      <c r="T36" s="6" t="inlineStr"/>
-      <c r="U36" s="6" t="inlineStr"/>
-      <c r="V36" s="6" t="inlineStr"/>
-      <c r="W36" s="6" t="inlineStr"/>
-      <c r="X36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -3166,10 +2615,10 @@
       </c>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="5" t="n">
-        <v>0.100240841468152</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>0.1457829031037056</v>
+        <v>0.1438</v>
       </c>
       <c r="L37" s="5" t="inlineStr"/>
       <c r="M37" s="5" t="inlineStr"/>
@@ -3182,14 +2631,6 @@
       <c r="P37" s="5" t="n">
         <v>0.9661999999999999</v>
       </c>
-      <c r="Q37" s="6" t="inlineStr"/>
-      <c r="R37" s="6" t="inlineStr"/>
-      <c r="S37" s="6" t="inlineStr"/>
-      <c r="T37" s="6" t="inlineStr"/>
-      <c r="U37" s="6" t="inlineStr"/>
-      <c r="V37" s="6" t="inlineStr"/>
-      <c r="W37" s="6" t="inlineStr"/>
-      <c r="X37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3228,10 +2669,10 @@
       </c>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="5" t="n">
-        <v>0.1132112008880745</v>
+        <v>0.1085</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>0.165330135848075</v>
+        <v>0.1628</v>
       </c>
       <c r="L38" s="5" t="inlineStr"/>
       <c r="M38" s="5" t="inlineStr"/>
@@ -3244,14 +2685,6 @@
       <c r="P38" s="5" t="n">
         <v>0.9661999999999999</v>
       </c>
-      <c r="Q38" s="6" t="inlineStr"/>
-      <c r="R38" s="6" t="inlineStr"/>
-      <c r="S38" s="6" t="inlineStr"/>
-      <c r="T38" s="6" t="inlineStr"/>
-      <c r="U38" s="6" t="inlineStr"/>
-      <c r="V38" s="6" t="inlineStr"/>
-      <c r="W38" s="6" t="inlineStr"/>
-      <c r="X38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3290,10 +2723,10 @@
       </c>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="5" t="n">
-        <v>0.1951479456045728</v>
+        <v>0.1885</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>0.3052119364643321</v>
+        <v>0.287</v>
       </c>
       <c r="L39" s="5" t="inlineStr"/>
       <c r="M39" s="5" t="inlineStr"/>
@@ -3306,14 +2739,6 @@
       <c r="P39" s="5" t="n">
         <v>0.9379</v>
       </c>
-      <c r="Q39" s="6" t="inlineStr"/>
-      <c r="R39" s="6" t="inlineStr"/>
-      <c r="S39" s="6" t="inlineStr"/>
-      <c r="T39" s="6" t="inlineStr"/>
-      <c r="U39" s="6" t="inlineStr"/>
-      <c r="V39" s="6" t="inlineStr"/>
-      <c r="W39" s="6" t="inlineStr"/>
-      <c r="X39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3352,10 +2777,10 @@
       </c>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="5" t="n">
-        <v>0.07862107896860038</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>0.1223251897635215</v>
+        <v>0.1193</v>
       </c>
       <c r="L40" s="5" t="inlineStr"/>
       <c r="M40" s="5" t="inlineStr"/>
@@ -3368,14 +2793,6 @@
       <c r="P40" s="5" t="n">
         <v>0.9583</v>
       </c>
-      <c r="Q40" s="6" t="inlineStr"/>
-      <c r="R40" s="6" t="inlineStr"/>
-      <c r="S40" s="6" t="inlineStr"/>
-      <c r="T40" s="6" t="inlineStr"/>
-      <c r="U40" s="6" t="inlineStr"/>
-      <c r="V40" s="6" t="inlineStr"/>
-      <c r="W40" s="6" t="inlineStr"/>
-      <c r="X40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3414,10 +2831,10 @@
       </c>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="5" t="n">
-        <v>0.09378566692877877</v>
+        <v>0.0914</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>0.1999025312540723</v>
+        <v>0.1943</v>
       </c>
       <c r="L41" s="5" t="inlineStr"/>
       <c r="M41" s="5" t="inlineStr"/>
@@ -3430,14 +2847,6 @@
       <c r="P41" s="5" t="n">
         <v>0.9709</v>
       </c>
-      <c r="Q41" s="6" t="inlineStr"/>
-      <c r="R41" s="6" t="inlineStr"/>
-      <c r="S41" s="6" t="inlineStr"/>
-      <c r="T41" s="6" t="inlineStr"/>
-      <c r="U41" s="6" t="inlineStr"/>
-      <c r="V41" s="6" t="inlineStr"/>
-      <c r="W41" s="6" t="inlineStr"/>
-      <c r="X41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3476,10 +2885,10 @@
       </c>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="5" t="n">
-        <v>0.006173969971481119</v>
+        <v>0.0071</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>0.003504366906944112</v>
+        <v>0.0037</v>
       </c>
       <c r="L42" s="5" t="inlineStr"/>
       <c r="M42" s="5" t="inlineStr"/>
@@ -3492,14 +2901,6 @@
       <c r="P42" s="5" t="n">
         <v>0.9694</v>
       </c>
-      <c r="Q42" s="6" t="inlineStr"/>
-      <c r="R42" s="6" t="inlineStr"/>
-      <c r="S42" s="6" t="inlineStr"/>
-      <c r="T42" s="6" t="inlineStr"/>
-      <c r="U42" s="6" t="inlineStr"/>
-      <c r="V42" s="6" t="inlineStr"/>
-      <c r="W42" s="6" t="inlineStr"/>
-      <c r="X42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3538,10 +2939,10 @@
       </c>
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="5" t="n">
-        <v>0.009571326064233943</v>
+        <v>0.0101</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>0</v>
+        <v>0.0026</v>
       </c>
       <c r="L43" s="5" t="inlineStr"/>
       <c r="M43" s="5" t="inlineStr"/>
@@ -3554,14 +2955,6 @@
       <c r="P43" s="5" t="n">
         <v>0.9694</v>
       </c>
-      <c r="Q43" s="6" t="inlineStr"/>
-      <c r="R43" s="6" t="inlineStr"/>
-      <c r="S43" s="6" t="inlineStr"/>
-      <c r="T43" s="6" t="inlineStr"/>
-      <c r="U43" s="6" t="inlineStr"/>
-      <c r="V43" s="6" t="inlineStr"/>
-      <c r="W43" s="6" t="inlineStr"/>
-      <c r="X43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3600,10 +2993,10 @@
       </c>
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="5" t="n">
-        <v>0.1117765711557074</v>
+        <v>0.1075</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>0.186319094139723</v>
+        <v>0.1825</v>
       </c>
       <c r="L44" s="5" t="inlineStr"/>
       <c r="M44" s="5" t="inlineStr"/>
@@ -3616,14 +3009,6 @@
       <c r="P44" s="5" t="n">
         <v>0.9112</v>
       </c>
-      <c r="Q44" s="6" t="inlineStr"/>
-      <c r="R44" s="6" t="inlineStr"/>
-      <c r="S44" s="6" t="inlineStr"/>
-      <c r="T44" s="6" t="inlineStr"/>
-      <c r="U44" s="6" t="inlineStr"/>
-      <c r="V44" s="6" t="inlineStr"/>
-      <c r="W44" s="6" t="inlineStr"/>
-      <c r="X44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3678,14 +3063,6 @@
       <c r="P45" s="5" t="n">
         <v>1.0034</v>
       </c>
-      <c r="Q45" s="6" t="inlineStr"/>
-      <c r="R45" s="6" t="inlineStr"/>
-      <c r="S45" s="6" t="inlineStr"/>
-      <c r="T45" s="6" t="inlineStr"/>
-      <c r="U45" s="6" t="inlineStr"/>
-      <c r="V45" s="6" t="inlineStr"/>
-      <c r="W45" s="6" t="inlineStr"/>
-      <c r="X45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3724,10 +3101,10 @@
       </c>
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="5" t="n">
-        <v>0.1104986454982489</v>
+        <v>0.1016</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>0.08860136051521761</v>
+        <v>0.0847</v>
       </c>
       <c r="L46" s="5" t="inlineStr"/>
       <c r="M46" s="5" t="inlineStr"/>
@@ -3740,14 +3117,6 @@
       <c r="P46" s="5" t="n">
         <v>0.9583</v>
       </c>
-      <c r="Q46" s="6" t="inlineStr"/>
-      <c r="R46" s="6" t="inlineStr"/>
-      <c r="S46" s="6" t="inlineStr"/>
-      <c r="T46" s="6" t="inlineStr"/>
-      <c r="U46" s="6" t="inlineStr"/>
-      <c r="V46" s="6" t="inlineStr"/>
-      <c r="W46" s="6" t="inlineStr"/>
-      <c r="X46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3786,10 +3155,10 @@
       </c>
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="5" t="n">
-        <v>0.0231798012669201</v>
+        <v>0.0239</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>0.02046415405566893</v>
+        <v>0.0203</v>
       </c>
       <c r="L47" s="5" t="inlineStr"/>
       <c r="M47" s="5" t="inlineStr"/>
@@ -3802,14 +3171,6 @@
       <c r="P47" s="5" t="n">
         <v>0.9611</v>
       </c>
-      <c r="Q47" s="6" t="inlineStr"/>
-      <c r="R47" s="6" t="inlineStr"/>
-      <c r="S47" s="6" t="inlineStr"/>
-      <c r="T47" s="6" t="inlineStr"/>
-      <c r="U47" s="6" t="inlineStr"/>
-      <c r="V47" s="6" t="inlineStr"/>
-      <c r="W47" s="6" t="inlineStr"/>
-      <c r="X47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3848,10 +3209,10 @@
       </c>
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="5" t="n">
-        <v>0.09149797011929861</v>
+        <v>0.0871</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>0.1685558219338047</v>
+        <v>0.1598</v>
       </c>
       <c r="L48" s="5" t="inlineStr"/>
       <c r="M48" s="5" t="inlineStr"/>
@@ -3864,14 +3225,6 @@
       <c r="P48" s="5" t="n">
         <v>0.844</v>
       </c>
-      <c r="Q48" s="6" t="inlineStr"/>
-      <c r="R48" s="6" t="inlineStr"/>
-      <c r="S48" s="6" t="inlineStr"/>
-      <c r="T48" s="6" t="inlineStr"/>
-      <c r="U48" s="6" t="inlineStr"/>
-      <c r="V48" s="6" t="inlineStr"/>
-      <c r="W48" s="6" t="inlineStr"/>
-      <c r="X48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3910,10 +3263,10 @@
       </c>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="5" t="n">
-        <v>0.1018185649768411</v>
+        <v>0.0941</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>0.04324399718648553</v>
+        <v>0.0426</v>
       </c>
       <c r="L49" s="5" t="inlineStr"/>
       <c r="M49" s="5" t="inlineStr"/>
@@ -3926,14 +3279,6 @@
       <c r="P49" s="5" t="n">
         <v>0.9605</v>
       </c>
-      <c r="Q49" s="6" t="inlineStr"/>
-      <c r="R49" s="6" t="inlineStr"/>
-      <c r="S49" s="6" t="inlineStr"/>
-      <c r="T49" s="6" t="inlineStr"/>
-      <c r="U49" s="6" t="inlineStr"/>
-      <c r="V49" s="6" t="inlineStr"/>
-      <c r="W49" s="6" t="inlineStr"/>
-      <c r="X49" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3946,7 +3291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W49"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3958,146 +3303,62 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>DUID</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Fuel</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>MLF_FY24-25</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>MLF_FY25-26</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>MLF_FY26-27 (Draft)</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>CURTAILMENT_ACTUAL_FY23-24</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>CURTAILMENT_ACTUAL_FY24-25</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>ELI_CURTAILMENT_NEAR</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>ELI_CURTAILMENT_MED</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY1</t>
-        </is>
-      </c>
-      <c r="K1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY1_LABEL</t>
-        </is>
-      </c>
-      <c r="L1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY2</t>
-        </is>
-      </c>
-      <c r="M1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY2_LABEL</t>
-        </is>
-      </c>
-      <c r="N1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY3</t>
-        </is>
-      </c>
-      <c r="O1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY3_LABEL</t>
-        </is>
-      </c>
-      <c r="P1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_AVG</t>
-        </is>
-      </c>
-      <c r="Q1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY1</t>
-        </is>
-      </c>
-      <c r="R1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY1_LABEL</t>
-        </is>
-      </c>
-      <c r="S1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY2</t>
-        </is>
-      </c>
-      <c r="T1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY2_LABEL</t>
-        </is>
-      </c>
-      <c r="U1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY3</t>
-        </is>
-      </c>
-      <c r="V1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY3_LABEL</t>
-        </is>
-      </c>
-      <c r="W1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_AVG</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>ADPPV1</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4112,59 +3373,21 @@
         <v>1.0034</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>0.3222683455189714</v>
+        <v>0.2903</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.2755625039739843</v>
+        <v>0.256</v>
       </c>
       <c r="H2" s="5" t="inlineStr"/>
       <c r="I2" s="5" t="inlineStr"/>
-      <c r="J2" s="5" t="inlineStr"/>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="inlineStr"/>
-      <c r="M2" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N2" s="5" t="inlineStr"/>
-      <c r="O2" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P2" s="5" t="inlineStr"/>
-      <c r="Q2" s="5" t="inlineStr"/>
-      <c r="R2" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S2" s="5" t="inlineStr"/>
-      <c r="T2" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U2" s="5" t="inlineStr"/>
-      <c r="V2" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>ADPPV2</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4182,52 +3405,14 @@
       <c r="G3" s="5" t="inlineStr"/>
       <c r="H3" s="5" t="inlineStr"/>
       <c r="I3" s="5" t="inlineStr"/>
-      <c r="J3" s="5" t="inlineStr"/>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="inlineStr"/>
-      <c r="M3" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N3" s="5" t="inlineStr"/>
-      <c r="O3" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P3" s="5" t="inlineStr"/>
-      <c r="Q3" s="5" t="inlineStr"/>
-      <c r="R3" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S3" s="5" t="inlineStr"/>
-      <c r="T3" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U3" s="5" t="inlineStr"/>
-      <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>ADPPV3</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4245,52 +3430,14 @@
       <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="inlineStr"/>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N4" s="5" t="inlineStr"/>
-      <c r="O4" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="5" t="inlineStr"/>
-      <c r="R4" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S4" s="5" t="inlineStr"/>
-      <c r="T4" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U4" s="5" t="inlineStr"/>
-      <c r="V4" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>BOWWPV1</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4304,60 +3451,20 @@
       <c r="E5" s="5" t="n">
         <v>1.0002</v>
       </c>
-      <c r="F5" s="5" t="n">
-        <v>0.2483229876673971</v>
-      </c>
+      <c r="F5" s="5" t="inlineStr"/>
       <c r="G5" s="5" t="n">
-        <v>0.1843730537306586</v>
+        <v>0.1726</v>
       </c>
       <c r="H5" s="5" t="inlineStr"/>
       <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="inlineStr"/>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N5" s="5" t="inlineStr"/>
-      <c r="O5" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P5" s="5" t="inlineStr"/>
-      <c r="Q5" s="5" t="inlineStr"/>
-      <c r="R5" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S5" s="5" t="inlineStr"/>
-      <c r="T5" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U5" s="5" t="inlineStr"/>
-      <c r="V5" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>BNGSF1</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4372,10 +3479,10 @@
         <v>0.9698</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.2260441150541987</v>
+        <v>0.2073</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.3551752959427892</v>
+        <v>0.3235</v>
       </c>
       <c r="H6" s="5" t="n">
         <v>0.501077617843089</v>
@@ -4383,68 +3490,14 @@
       <c r="I6" s="5" t="n">
         <v>0.212860651220515</v>
       </c>
-      <c r="J6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="R6" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S6" s="5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="T6" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U6" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="V6" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W6" s="5" t="n">
-        <v>0.07333333333333335</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>BNGSF2</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4459,10 +3512,10 @@
         <v>0.9698</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.1877237381087118</v>
+        <v>0.1744</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.2949469219730214</v>
+        <v>0.2766</v>
       </c>
       <c r="H7" s="5" t="n">
         <v>0.501077617843089</v>
@@ -4470,68 +3523,14 @@
       <c r="I7" s="5" t="n">
         <v>0.212860651220515</v>
       </c>
-      <c r="J7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="R7" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S7" s="5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="T7" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U7" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="V7" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W7" s="5" t="n">
-        <v>0.07333333333333335</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>CBWWPV1</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4549,52 +3548,14 @@
       <c r="G8" s="5" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="5" t="inlineStr"/>
-      <c r="J8" s="5" t="inlineStr"/>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="inlineStr"/>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N8" s="5" t="inlineStr"/>
-      <c r="O8" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P8" s="5" t="inlineStr"/>
-      <c r="Q8" s="5" t="inlineStr"/>
-      <c r="R8" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S8" s="5" t="inlineStr"/>
-      <c r="T8" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U8" s="5" t="inlineStr"/>
-      <c r="V8" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>CBWWPV2</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4612,52 +3573,14 @@
       <c r="G9" s="5" t="inlineStr"/>
       <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="5" t="inlineStr"/>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr"/>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N9" s="5" t="inlineStr"/>
-      <c r="O9" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P9" s="5" t="inlineStr"/>
-      <c r="Q9" s="5" t="inlineStr"/>
-      <c r="R9" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S9" s="5" t="inlineStr"/>
-      <c r="T9" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U9" s="5" t="inlineStr"/>
-      <c r="V9" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>HVWWPV1</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4672,10 +3595,10 @@
         <v>1.0022</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.2369581649793167</v>
+        <v>0.2225</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.2553599837400992</v>
+        <v>0.2415</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>0.511388342191138</v>
@@ -4683,52 +3606,14 @@
       <c r="I10" s="5" t="n">
         <v>0.22265637813532</v>
       </c>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="inlineStr"/>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N10" s="5" t="inlineStr"/>
-      <c r="O10" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P10" s="5" t="inlineStr"/>
-      <c r="Q10" s="5" t="inlineStr"/>
-      <c r="R10" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S10" s="5" t="inlineStr"/>
-      <c r="T10" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U10" s="5" t="inlineStr"/>
-      <c r="V10" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>MAPS2PV1</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4743,10 +3628,10 @@
         <v>1.0132</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.233601468490469</v>
+        <v>0.2199</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.215574037292203</v>
+        <v>0.2007</v>
       </c>
       <c r="H11" s="5" t="n">
         <v>0.510590381447813</v>
@@ -4754,68 +3639,14 @@
       <c r="I11" s="5" t="n">
         <v>0.225784053085401</v>
       </c>
-      <c r="J11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W11" s="5" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>MAPS2PV1</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4830,10 +3661,10 @@
         <v>1.0132</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.233601468490469</v>
+        <v>0.2199</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.215574037292203</v>
+        <v>0.2007</v>
       </c>
       <c r="H12" s="5" t="n">
         <v>0.510590381447813</v>
@@ -4841,68 +3672,14 @@
       <c r="I12" s="5" t="n">
         <v>0.225784053085401</v>
       </c>
-      <c r="J12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W12" s="5" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>MAPS3PV1</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4917,79 +3694,23 @@
         <v>1.0135</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.2443246485498652</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>0.183277695807331</v>
-      </c>
+        <v>0.2291</v>
+      </c>
+      <c r="G13" s="5" t="inlineStr"/>
       <c r="H13" s="5" t="n">
         <v>0.510590381447813</v>
       </c>
       <c r="I13" s="5" t="n">
         <v>0.225784053085401</v>
       </c>
-      <c r="J13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W13" s="5" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>MANNSF2</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5003,11 +3724,9 @@
       <c r="E14" s="5" t="n">
         <v>0.9955000000000001</v>
       </c>
-      <c r="F14" s="5" t="n">
-        <v>0.1329824757126514</v>
-      </c>
+      <c r="F14" s="5" t="inlineStr"/>
       <c r="G14" s="5" t="n">
-        <v>0.3248435729394352</v>
+        <v>0.3012</v>
       </c>
       <c r="H14" s="5" t="n">
         <v>0.510590381447813</v>
@@ -5015,68 +3734,14 @@
       <c r="I14" s="5" t="n">
         <v>0.225784053085401</v>
       </c>
-      <c r="J14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="R14" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S14" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="T14" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U14" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="V14" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W14" s="5" t="n">
-        <v>0.16</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>MWPS1PV1</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5091,10 +3756,10 @@
         <v>0.966</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.1341216632110691</v>
+        <v>0.1286</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.2753352654629494</v>
+        <v>0.2462</v>
       </c>
       <c r="H15" s="5" t="n">
         <v>0.65425629128861</v>
@@ -5102,68 +3767,14 @@
       <c r="I15" s="5" t="n">
         <v>0.512670422089759</v>
       </c>
-      <c r="J15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="R15" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S15" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="T15" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U15" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="V15" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W15" s="5" t="n">
-        <v>0.16</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>MWPS2PV1</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5178,10 +3789,10 @@
         <v>0.9723000000000001</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.1186603136108224</v>
+        <v>0.1131</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.2706607556452453</v>
+        <v>0.2411</v>
       </c>
       <c r="H16" s="5" t="n">
         <v>0.65425629128861</v>
@@ -5189,68 +3800,14 @@
       <c r="I16" s="5" t="n">
         <v>0.512670422089759</v>
       </c>
-      <c r="J16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="R16" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S16" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="T16" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U16" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="V16" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W16" s="5" t="n">
-        <v>0.16</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>MWPS3PV1</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5265,10 +3822,10 @@
         <v>0.9766</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.1075421523838416</v>
+        <v>0.0897</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.1479399367177207</v>
+        <v>0.1273</v>
       </c>
       <c r="H17" s="5" t="n">
         <v>0.65425629128861</v>
@@ -5276,68 +3833,14 @@
       <c r="I17" s="5" t="n">
         <v>0.512670422089759</v>
       </c>
-      <c r="J17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="R17" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S17" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="T17" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U17" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="V17" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W17" s="5" t="n">
-        <v>0.16</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>MWPS4PV1</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5352,10 +3855,10 @@
         <v>0.9781</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.1251631989034748</v>
+        <v>0.1184</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.233198203822338</v>
+        <v>0.2031</v>
       </c>
       <c r="H18" s="5" t="n">
         <v>0.65425629128861</v>
@@ -5363,68 +3866,14 @@
       <c r="I18" s="5" t="n">
         <v>0.512670422089759</v>
       </c>
-      <c r="J18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="R18" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S18" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="T18" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U18" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="V18" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W18" s="5" t="n">
-        <v>0.16</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>MBPS2PV1</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5439,10 +3888,10 @@
         <v>1.0106</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.2396658493615177</v>
+        <v>0.2268</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.2613261383795547</v>
+        <v>0.2284</v>
       </c>
       <c r="H19" s="5" t="n">
         <v>0.510590381447813</v>
@@ -5450,68 +3899,14 @@
       <c r="I19" s="5" t="n">
         <v>0.225784053085401</v>
       </c>
-      <c r="J19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W19" s="5" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>MBPS2PV1</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5526,10 +3921,10 @@
         <v>1.0106</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.2396658493615177</v>
+        <v>0.2268</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.2613261383795547</v>
+        <v>0.2284</v>
       </c>
       <c r="H20" s="5" t="n">
         <v>0.510590381447813</v>
@@ -5537,68 +3932,14 @@
       <c r="I20" s="5" t="n">
         <v>0.225784053085401</v>
       </c>
-      <c r="J20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W20" s="5" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>PAREPS1</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5613,10 +3954,10 @@
         <v>0.9709</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.1972627642475195</v>
+        <v>0.1842</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.4012166584184587</v>
+        <v>0.3589</v>
       </c>
       <c r="H21" s="5" t="n">
         <v>0.501077617843089</v>
@@ -5624,68 +3965,14 @@
       <c r="I21" s="5" t="n">
         <v>0.212860651220515</v>
       </c>
-      <c r="J21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="R21" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S21" s="5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="T21" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U21" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="V21" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W21" s="5" t="n">
-        <v>0.07333333333333335</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>TB2SF1</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5700,10 +3987,10 @@
         <v>0.9963</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.2449284253072609</v>
+        <v>0.1987</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.3166893979467619</v>
+        <v>0.2973</v>
       </c>
       <c r="H22" s="5" t="n">
         <v>0.511370986967519</v>
@@ -5711,52 +3998,14 @@
       <c r="I22" s="5" t="n">
         <v>0.22945882760626</v>
       </c>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L22" s="5" t="inlineStr"/>
-      <c r="M22" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N22" s="5" t="inlineStr"/>
-      <c r="O22" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P22" s="5" t="inlineStr"/>
-      <c r="Q22" s="5" t="inlineStr"/>
-      <c r="R22" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S22" s="5" t="inlineStr"/>
-      <c r="T22" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U22" s="5" t="inlineStr"/>
-      <c r="V22" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>TBSF1</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5771,10 +4020,10 @@
         <v>0.9967</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.2720339427313853</v>
+        <v>0.2394</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.383961084072671</v>
+        <v>0.3511</v>
       </c>
       <c r="H23" s="5" t="n">
         <v>0.511370986967519</v>
@@ -5782,52 +4031,14 @@
       <c r="I23" s="5" t="n">
         <v>0.22945882760626</v>
       </c>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr"/>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N23" s="5" t="inlineStr"/>
-      <c r="O23" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P23" s="5" t="inlineStr"/>
-      <c r="Q23" s="5" t="inlineStr"/>
-      <c r="R23" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S23" s="5" t="inlineStr"/>
-      <c r="T23" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U23" s="5" t="inlineStr"/>
-      <c r="V23" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>CNUNDAWF</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5842,59 +4053,21 @@
         <v>0.9458</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.1837838121931059</v>
+        <v>0.1746</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.2611513523019278</v>
+        <v>0.254</v>
       </c>
       <c r="H24" s="5" t="inlineStr"/>
       <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L24" s="5" t="inlineStr"/>
-      <c r="M24" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N24" s="5" t="inlineStr"/>
-      <c r="O24" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P24" s="5" t="inlineStr"/>
-      <c r="Q24" s="5" t="inlineStr"/>
-      <c r="R24" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S24" s="5" t="inlineStr"/>
-      <c r="T24" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U24" s="5" t="inlineStr"/>
-      <c r="V24" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>CATHROCK</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5909,59 +4082,21 @@
         <v>0.9408</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>0.1487965707958214</v>
+        <v>0.1389</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.05183812537020938</v>
+        <v>0.0515</v>
       </c>
       <c r="H25" s="5" t="inlineStr"/>
       <c r="I25" s="5" t="inlineStr"/>
-      <c r="J25" s="5" t="inlineStr"/>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr"/>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N25" s="5" t="inlineStr"/>
-      <c r="O25" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P25" s="5" t="inlineStr"/>
-      <c r="Q25" s="5" t="inlineStr"/>
-      <c r="R25" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S25" s="5" t="inlineStr"/>
-      <c r="T25" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U25" s="5" t="inlineStr"/>
-      <c r="V25" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>CLEMGPWF</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5976,59 +4111,21 @@
         <v>0.9605</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>0.01165648634818117</v>
+        <v>0.0134</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.004972497428635703</v>
+        <v>0.0062</v>
       </c>
       <c r="H26" s="5" t="inlineStr"/>
       <c r="I26" s="5" t="inlineStr"/>
-      <c r="J26" s="5" t="inlineStr"/>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L26" s="5" t="inlineStr"/>
-      <c r="M26" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N26" s="5" t="inlineStr"/>
-      <c r="O26" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P26" s="5" t="inlineStr"/>
-      <c r="Q26" s="5" t="inlineStr"/>
-      <c r="R26" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S26" s="5" t="inlineStr"/>
-      <c r="T26" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U26" s="5" t="inlineStr"/>
-      <c r="V26" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>GSWF1A</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6042,60 +4139,20 @@
       <c r="E27" s="5" t="n">
         <v>0.9711</v>
       </c>
-      <c r="F27" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="F27" s="5" t="inlineStr"/>
       <c r="G27" s="5" t="n">
-        <v>0.179641601485183</v>
+        <v>0.176</v>
       </c>
       <c r="H27" s="5" t="inlineStr"/>
       <c r="I27" s="5" t="inlineStr"/>
-      <c r="J27" s="5" t="inlineStr"/>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr"/>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N27" s="5" t="inlineStr"/>
-      <c r="O27" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P27" s="5" t="inlineStr"/>
-      <c r="Q27" s="5" t="inlineStr"/>
-      <c r="R27" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S27" s="5" t="inlineStr"/>
-      <c r="T27" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U27" s="5" t="inlineStr"/>
-      <c r="V27" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>GSWF1B1</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6109,60 +4166,18 @@
       <c r="E28" s="5" t="n">
         <v>0.971</v>
       </c>
-      <c r="F28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>0.1555674430999341</v>
-      </c>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
       <c r="H28" s="5" t="inlineStr"/>
       <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L28" s="5" t="inlineStr"/>
-      <c r="M28" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N28" s="5" t="inlineStr"/>
-      <c r="O28" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P28" s="5" t="inlineStr"/>
-      <c r="Q28" s="5" t="inlineStr"/>
-      <c r="R28" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S28" s="5" t="inlineStr"/>
-      <c r="T28" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U28" s="5" t="inlineStr"/>
-      <c r="V28" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>HALLWF1</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6177,59 +4192,21 @@
         <v>0.9635</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0.09029871973567261</v>
+        <v>0.0813</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.1208463990083658</v>
+        <v>0.1169</v>
       </c>
       <c r="H29" s="5" t="inlineStr"/>
       <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L29" s="5" t="inlineStr"/>
-      <c r="M29" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N29" s="5" t="inlineStr"/>
-      <c r="O29" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P29" s="5" t="inlineStr"/>
-      <c r="Q29" s="5" t="inlineStr"/>
-      <c r="R29" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S29" s="5" t="inlineStr"/>
-      <c r="T29" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U29" s="5" t="inlineStr"/>
-      <c r="V29" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>HALLWF2</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6244,59 +4221,21 @@
         <v>0.962</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.1002715806472839</v>
+        <v>0.0914</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.1083613761067723</v>
+        <v>0.1053</v>
       </c>
       <c r="H30" s="5" t="inlineStr"/>
       <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L30" s="5" t="inlineStr"/>
-      <c r="M30" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N30" s="5" t="inlineStr"/>
-      <c r="O30" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P30" s="5" t="inlineStr"/>
-      <c r="Q30" s="5" t="inlineStr"/>
-      <c r="R30" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S30" s="5" t="inlineStr"/>
-      <c r="T30" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U30" s="5" t="inlineStr"/>
-      <c r="V30" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>HDWF1</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6311,59 +4250,21 @@
         <v>0.9538</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>0.007476326214591267</v>
+        <v>0.0092</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0009835058684714015</v>
+        <v>0.0033</v>
       </c>
       <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="5" t="inlineStr"/>
-      <c r="J31" s="5" t="inlineStr"/>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L31" s="5" t="inlineStr"/>
-      <c r="M31" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N31" s="5" t="inlineStr"/>
-      <c r="O31" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P31" s="5" t="inlineStr"/>
-      <c r="Q31" s="5" t="inlineStr"/>
-      <c r="R31" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S31" s="5" t="inlineStr"/>
-      <c r="T31" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U31" s="5" t="inlineStr"/>
-      <c r="V31" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>HDWF2</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6378,59 +4279,21 @@
         <v>0.9538</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>0.004042184103801194</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0</v>
+        <v>0.0038</v>
       </c>
       <c r="H32" s="5" t="inlineStr"/>
       <c r="I32" s="5" t="inlineStr"/>
-      <c r="J32" s="5" t="inlineStr"/>
-      <c r="K32" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L32" s="5" t="inlineStr"/>
-      <c r="M32" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N32" s="5" t="inlineStr"/>
-      <c r="O32" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P32" s="5" t="inlineStr"/>
-      <c r="Q32" s="5" t="inlineStr"/>
-      <c r="R32" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S32" s="5" t="inlineStr"/>
-      <c r="T32" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U32" s="5" t="inlineStr"/>
-      <c r="V32" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>HDWF3</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6445,59 +4308,21 @@
         <v>0.9538</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>0.00666136667720707</v>
+        <v>0.0092</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0</v>
+        <v>0.0027</v>
       </c>
       <c r="H33" s="5" t="inlineStr"/>
       <c r="I33" s="5" t="inlineStr"/>
-      <c r="J33" s="5" t="inlineStr"/>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L33" s="5" t="inlineStr"/>
-      <c r="M33" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N33" s="5" t="inlineStr"/>
-      <c r="O33" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P33" s="5" t="inlineStr"/>
-      <c r="Q33" s="5" t="inlineStr"/>
-      <c r="R33" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S33" s="5" t="inlineStr"/>
-      <c r="T33" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U33" s="5" t="inlineStr"/>
-      <c r="V33" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>LKBONNY2</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6512,59 +4337,21 @@
         <v>0.9389999999999999</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.1078900067150126</v>
+        <v>0.1058</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.2000408936031856</v>
+        <v>0.1941</v>
       </c>
       <c r="H34" s="5" t="inlineStr"/>
       <c r="I34" s="5" t="inlineStr"/>
-      <c r="J34" s="5" t="inlineStr"/>
-      <c r="K34" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L34" s="5" t="inlineStr"/>
-      <c r="M34" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N34" s="5" t="inlineStr"/>
-      <c r="O34" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P34" s="5" t="inlineStr"/>
-      <c r="Q34" s="5" t="inlineStr"/>
-      <c r="R34" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S34" s="5" t="inlineStr"/>
-      <c r="T34" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U34" s="5" t="inlineStr"/>
-      <c r="V34" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>LKBONNY3</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6579,59 +4366,21 @@
         <v>0.9389999999999999</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>0.2044227016730216</v>
+        <v>0.1939</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.265181802157253</v>
+        <v>0.2514</v>
       </c>
       <c r="H35" s="5" t="inlineStr"/>
       <c r="I35" s="5" t="inlineStr"/>
-      <c r="J35" s="5" t="inlineStr"/>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L35" s="5" t="inlineStr"/>
-      <c r="M35" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N35" s="5" t="inlineStr"/>
-      <c r="O35" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P35" s="5" t="inlineStr"/>
-      <c r="Q35" s="5" t="inlineStr"/>
-      <c r="R35" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S35" s="5" t="inlineStr"/>
-      <c r="T35" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U35" s="5" t="inlineStr"/>
-      <c r="V35" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>LKBONNY1</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6646,59 +4395,21 @@
         <v>0.9389999999999999</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0.2050709857686178</v>
+        <v>0.1878</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.2636993184442319</v>
+        <v>0.2535</v>
       </c>
       <c r="H36" s="5" t="inlineStr"/>
       <c r="I36" s="5" t="inlineStr"/>
-      <c r="J36" s="5" t="inlineStr"/>
-      <c r="K36" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L36" s="5" t="inlineStr"/>
-      <c r="M36" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N36" s="5" t="inlineStr"/>
-      <c r="O36" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P36" s="5" t="inlineStr"/>
-      <c r="Q36" s="5" t="inlineStr"/>
-      <c r="R36" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S36" s="5" t="inlineStr"/>
-      <c r="T36" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U36" s="5" t="inlineStr"/>
-      <c r="V36" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>LGAPWF1</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6713,59 +4424,21 @@
         <v>0.9661999999999999</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>0.100240841468152</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.1457829031037056</v>
+        <v>0.1438</v>
       </c>
       <c r="H37" s="5" t="inlineStr"/>
       <c r="I37" s="5" t="inlineStr"/>
-      <c r="J37" s="5" t="inlineStr"/>
-      <c r="K37" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L37" s="5" t="inlineStr"/>
-      <c r="M37" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N37" s="5" t="inlineStr"/>
-      <c r="O37" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P37" s="5" t="inlineStr"/>
-      <c r="Q37" s="5" t="inlineStr"/>
-      <c r="R37" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S37" s="5" t="inlineStr"/>
-      <c r="T37" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U37" s="5" t="inlineStr"/>
-      <c r="V37" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>LGAPWF2</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6780,59 +4453,21 @@
         <v>0.9661999999999999</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0.1132112008880745</v>
+        <v>0.1085</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.165330135848075</v>
+        <v>0.1628</v>
       </c>
       <c r="H38" s="5" t="inlineStr"/>
       <c r="I38" s="5" t="inlineStr"/>
-      <c r="J38" s="5" t="inlineStr"/>
-      <c r="K38" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L38" s="5" t="inlineStr"/>
-      <c r="M38" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N38" s="5" t="inlineStr"/>
-      <c r="O38" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P38" s="5" t="inlineStr"/>
-      <c r="Q38" s="5" t="inlineStr"/>
-      <c r="R38" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S38" s="5" t="inlineStr"/>
-      <c r="T38" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U38" s="5" t="inlineStr"/>
-      <c r="V38" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>MTMILLAR</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6847,59 +4482,21 @@
         <v>0.9379</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>0.1951479456045728</v>
+        <v>0.1885</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.3052119364643321</v>
+        <v>0.287</v>
       </c>
       <c r="H39" s="5" t="inlineStr"/>
       <c r="I39" s="5" t="inlineStr"/>
-      <c r="J39" s="5" t="inlineStr"/>
-      <c r="K39" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L39" s="5" t="inlineStr"/>
-      <c r="M39" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N39" s="5" t="inlineStr"/>
-      <c r="O39" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P39" s="5" t="inlineStr"/>
-      <c r="Q39" s="5" t="inlineStr"/>
-      <c r="R39" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S39" s="5" t="inlineStr"/>
-      <c r="T39" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U39" s="5" t="inlineStr"/>
-      <c r="V39" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>NBHWF1</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6914,59 +4511,21 @@
         <v>0.9583</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>0.07862107896860038</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.1223251897635215</v>
+        <v>0.1193</v>
       </c>
       <c r="H40" s="5" t="inlineStr"/>
       <c r="I40" s="5" t="inlineStr"/>
-      <c r="J40" s="5" t="inlineStr"/>
-      <c r="K40" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L40" s="5" t="inlineStr"/>
-      <c r="M40" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N40" s="5" t="inlineStr"/>
-      <c r="O40" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P40" s="5" t="inlineStr"/>
-      <c r="Q40" s="5" t="inlineStr"/>
-      <c r="R40" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S40" s="5" t="inlineStr"/>
-      <c r="T40" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U40" s="5" t="inlineStr"/>
-      <c r="V40" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>PAREPW1</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6981,59 +4540,21 @@
         <v>0.9709</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>0.09378566692877877</v>
+        <v>0.0914</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.1999025312540723</v>
+        <v>0.1943</v>
       </c>
       <c r="H41" s="5" t="inlineStr"/>
       <c r="I41" s="5" t="inlineStr"/>
-      <c r="J41" s="5" t="inlineStr"/>
-      <c r="K41" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L41" s="5" t="inlineStr"/>
-      <c r="M41" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N41" s="5" t="inlineStr"/>
-      <c r="O41" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P41" s="5" t="inlineStr"/>
-      <c r="Q41" s="5" t="inlineStr"/>
-      <c r="R41" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S41" s="5" t="inlineStr"/>
-      <c r="T41" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U41" s="5" t="inlineStr"/>
-      <c r="V41" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>SNOWSTH1</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -7048,59 +4569,21 @@
         <v>0.9694</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.006173969971481119</v>
+        <v>0.0071</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.003504366906944112</v>
+        <v>0.0037</v>
       </c>
       <c r="H42" s="5" t="inlineStr"/>
       <c r="I42" s="5" t="inlineStr"/>
-      <c r="J42" s="5" t="inlineStr"/>
-      <c r="K42" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L42" s="5" t="inlineStr"/>
-      <c r="M42" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N42" s="5" t="inlineStr"/>
-      <c r="O42" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P42" s="5" t="inlineStr"/>
-      <c r="Q42" s="5" t="inlineStr"/>
-      <c r="R42" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S42" s="5" t="inlineStr"/>
-      <c r="T42" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U42" s="5" t="inlineStr"/>
-      <c r="V42" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>SNOWNTH1</t>
         </is>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -7115,59 +4598,21 @@
         <v>0.9694</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>0.009571326064233943</v>
+        <v>0.0101</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0</v>
+        <v>0.0026</v>
       </c>
       <c r="H43" s="5" t="inlineStr"/>
       <c r="I43" s="5" t="inlineStr"/>
-      <c r="J43" s="5" t="inlineStr"/>
-      <c r="K43" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L43" s="5" t="inlineStr"/>
-      <c r="M43" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N43" s="5" t="inlineStr"/>
-      <c r="O43" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P43" s="5" t="inlineStr"/>
-      <c r="Q43" s="5" t="inlineStr"/>
-      <c r="R43" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S43" s="5" t="inlineStr"/>
-      <c r="T43" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U43" s="5" t="inlineStr"/>
-      <c r="V43" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>SNOWTWN1</t>
         </is>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -7182,59 +4627,21 @@
         <v>0.9112</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.1117765711557074</v>
+        <v>0.1075</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.186319094139723</v>
+        <v>0.1825</v>
       </c>
       <c r="H44" s="5" t="inlineStr"/>
       <c r="I44" s="5" t="inlineStr"/>
-      <c r="J44" s="5" t="inlineStr"/>
-      <c r="K44" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L44" s="5" t="inlineStr"/>
-      <c r="M44" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N44" s="5" t="inlineStr"/>
-      <c r="O44" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P44" s="5" t="inlineStr"/>
-      <c r="Q44" s="5" t="inlineStr"/>
-      <c r="R44" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S44" s="5" t="inlineStr"/>
-      <c r="T44" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U44" s="5" t="inlineStr"/>
-      <c r="V44" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W44" s="5" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="inlineStr">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>STARHLWF</t>
         </is>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -7256,52 +4663,14 @@
       </c>
       <c r="H45" s="5" t="inlineStr"/>
       <c r="I45" s="5" t="inlineStr"/>
-      <c r="J45" s="5" t="inlineStr"/>
-      <c r="K45" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L45" s="5" t="inlineStr"/>
-      <c r="M45" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N45" s="5" t="inlineStr"/>
-      <c r="O45" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P45" s="5" t="inlineStr"/>
-      <c r="Q45" s="5" t="inlineStr"/>
-      <c r="R45" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S45" s="5" t="inlineStr"/>
-      <c r="T45" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U45" s="5" t="inlineStr"/>
-      <c r="V45" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>BLUFF1</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -7316,59 +4685,21 @@
         <v>0.9583</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.1104986454982489</v>
+        <v>0.1016</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.08860136051521761</v>
+        <v>0.0847</v>
       </c>
       <c r="H46" s="5" t="inlineStr"/>
       <c r="I46" s="5" t="inlineStr"/>
-      <c r="J46" s="5" t="inlineStr"/>
-      <c r="K46" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L46" s="5" t="inlineStr"/>
-      <c r="M46" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N46" s="5" t="inlineStr"/>
-      <c r="O46" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P46" s="5" t="inlineStr"/>
-      <c r="Q46" s="5" t="inlineStr"/>
-      <c r="R46" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S46" s="5" t="inlineStr"/>
-      <c r="T46" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U46" s="5" t="inlineStr"/>
-      <c r="V46" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="8" t="inlineStr">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>WATERLWF</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -7383,59 +4714,21 @@
         <v>0.9611</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>0.0231798012669201</v>
+        <v>0.0239</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.02046415405566893</v>
+        <v>0.0203</v>
       </c>
       <c r="H47" s="5" t="inlineStr"/>
       <c r="I47" s="5" t="inlineStr"/>
-      <c r="J47" s="5" t="inlineStr"/>
-      <c r="K47" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L47" s="5" t="inlineStr"/>
-      <c r="M47" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N47" s="5" t="inlineStr"/>
-      <c r="O47" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P47" s="5" t="inlineStr"/>
-      <c r="Q47" s="5" t="inlineStr"/>
-      <c r="R47" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S47" s="5" t="inlineStr"/>
-      <c r="T47" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U47" s="5" t="inlineStr"/>
-      <c r="V47" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="8" t="inlineStr">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>WPWF</t>
         </is>
       </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -7450,59 +4743,21 @@
         <v>0.844</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>0.09149797011929861</v>
+        <v>0.0871</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.1685558219338047</v>
+        <v>0.1598</v>
       </c>
       <c r="H48" s="5" t="inlineStr"/>
       <c r="I48" s="5" t="inlineStr"/>
-      <c r="J48" s="5" t="inlineStr"/>
-      <c r="K48" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L48" s="5" t="inlineStr"/>
-      <c r="M48" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N48" s="5" t="inlineStr"/>
-      <c r="O48" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P48" s="5" t="inlineStr"/>
-      <c r="Q48" s="5" t="inlineStr"/>
-      <c r="R48" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S48" s="5" t="inlineStr"/>
-      <c r="T48" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U48" s="5" t="inlineStr"/>
-      <c r="V48" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W48" s="5" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>WGWF1</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -7517,51 +4772,13 @@
         <v>0.9605</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>0.1018185649768411</v>
+        <v>0.0941</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.04324399718648553</v>
+        <v>0.0426</v>
       </c>
       <c r="H49" s="5" t="inlineStr"/>
       <c r="I49" s="5" t="inlineStr"/>
-      <c r="J49" s="5" t="inlineStr"/>
-      <c r="K49" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L49" s="5" t="inlineStr"/>
-      <c r="M49" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N49" s="5" t="inlineStr"/>
-      <c r="O49" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P49" s="5" t="inlineStr"/>
-      <c r="Q49" s="5" t="inlineStr"/>
-      <c r="R49" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S49" s="5" t="inlineStr"/>
-      <c r="T49" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U49" s="5" t="inlineStr"/>
-      <c r="V49" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W49" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C49">
@@ -7648,174 +4865,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J49">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K49">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L49">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M49">
-    <cfRule type="colorScale" priority="11">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N49">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O49">
-    <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P49">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q49">
-    <cfRule type="colorScale" priority="15">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R49">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S49">
-    <cfRule type="colorScale" priority="17">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T49">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U49">
-    <cfRule type="colorScale" priority="19">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V49">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="W2:W49">
-    <cfRule type="colorScale" priority="21">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/SA_curtailment.xlsx
+++ b/outputs/SA_curtailment.xlsx
@@ -67,7 +67,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -82,6 +82,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -453,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P49"/>
+  <dimension ref="A1:X49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -472,6 +475,14 @@
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -555,6 +566,46 @@
           <t>FY26-27 (Draft)</t>
         </is>
       </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Curt FY1</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Curt FY2</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Curt FY3</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Curt Avg</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Offl FY1</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Offl FY2</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Offl FY3</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Offl Avg</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -609,6 +660,14 @@
       <c r="P2" s="5" t="n">
         <v>1.0034</v>
       </c>
+      <c r="Q2" s="6" t="inlineStr"/>
+      <c r="R2" s="6" t="inlineStr"/>
+      <c r="S2" s="6" t="inlineStr"/>
+      <c r="T2" s="6" t="inlineStr"/>
+      <c r="U2" s="6" t="inlineStr"/>
+      <c r="V2" s="6" t="inlineStr"/>
+      <c r="W2" s="6" t="inlineStr"/>
+      <c r="X2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -659,6 +718,14 @@
       <c r="P3" s="5" t="n">
         <v>1.0034</v>
       </c>
+      <c r="Q3" s="6" t="inlineStr"/>
+      <c r="R3" s="6" t="inlineStr"/>
+      <c r="S3" s="6" t="inlineStr"/>
+      <c r="T3" s="6" t="inlineStr"/>
+      <c r="U3" s="6" t="inlineStr"/>
+      <c r="V3" s="6" t="inlineStr"/>
+      <c r="W3" s="6" t="inlineStr"/>
+      <c r="X3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -709,6 +776,14 @@
       <c r="P4" s="5" t="n">
         <v>1.0034</v>
       </c>
+      <c r="Q4" s="6" t="inlineStr"/>
+      <c r="R4" s="6" t="inlineStr"/>
+      <c r="S4" s="6" t="inlineStr"/>
+      <c r="T4" s="6" t="inlineStr"/>
+      <c r="U4" s="6" t="inlineStr"/>
+      <c r="V4" s="6" t="inlineStr"/>
+      <c r="W4" s="6" t="inlineStr"/>
+      <c r="X4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -761,6 +836,14 @@
       <c r="P5" s="5" t="n">
         <v>1.0002</v>
       </c>
+      <c r="Q5" s="6" t="inlineStr"/>
+      <c r="R5" s="6" t="inlineStr"/>
+      <c r="S5" s="6" t="inlineStr"/>
+      <c r="T5" s="6" t="inlineStr"/>
+      <c r="U5" s="6" t="inlineStr"/>
+      <c r="V5" s="6" t="inlineStr"/>
+      <c r="W5" s="6" t="inlineStr"/>
+      <c r="X5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -825,6 +908,30 @@
       <c r="P6" s="5" t="n">
         <v>0.9698</v>
       </c>
+      <c r="Q6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="V6" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="W6" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="X6" s="6" t="n">
+        <v>0.07333333333333335</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -888,6 +995,30 @@
       </c>
       <c r="P7" s="5" t="n">
         <v>0.9698</v>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="V7" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="W7" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="X7" s="6" t="n">
+        <v>0.07333333333333335</v>
       </c>
     </row>
     <row r="8">
@@ -939,6 +1070,14 @@
       <c r="P8" s="5" t="n">
         <v>1.0034</v>
       </c>
+      <c r="Q8" s="6" t="inlineStr"/>
+      <c r="R8" s="6" t="inlineStr"/>
+      <c r="S8" s="6" t="inlineStr"/>
+      <c r="T8" s="6" t="inlineStr"/>
+      <c r="U8" s="6" t="inlineStr"/>
+      <c r="V8" s="6" t="inlineStr"/>
+      <c r="W8" s="6" t="inlineStr"/>
+      <c r="X8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -989,6 +1128,14 @@
       <c r="P9" s="5" t="n">
         <v>1.0034</v>
       </c>
+      <c r="Q9" s="6" t="inlineStr"/>
+      <c r="R9" s="6" t="inlineStr"/>
+      <c r="S9" s="6" t="inlineStr"/>
+      <c r="T9" s="6" t="inlineStr"/>
+      <c r="U9" s="6" t="inlineStr"/>
+      <c r="V9" s="6" t="inlineStr"/>
+      <c r="W9" s="6" t="inlineStr"/>
+      <c r="X9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1053,6 +1200,14 @@
       <c r="P10" s="5" t="n">
         <v>1.0022</v>
       </c>
+      <c r="Q10" s="6" t="inlineStr"/>
+      <c r="R10" s="6" t="inlineStr"/>
+      <c r="S10" s="6" t="inlineStr"/>
+      <c r="T10" s="6" t="inlineStr"/>
+      <c r="U10" s="6" t="inlineStr"/>
+      <c r="V10" s="6" t="inlineStr"/>
+      <c r="W10" s="6" t="inlineStr"/>
+      <c r="X10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1117,6 +1272,30 @@
       <c r="P11" s="5" t="n">
         <v>1.0132</v>
       </c>
+      <c r="Q11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1180,6 +1359,30 @@
       </c>
       <c r="P12" s="5" t="n">
         <v>1.0132</v>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1243,6 +1446,30 @@
       <c r="P13" s="5" t="n">
         <v>1.0135</v>
       </c>
+      <c r="Q13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1305,6 +1532,30 @@
       <c r="P14" s="5" t="n">
         <v>0.9955000000000001</v>
       </c>
+      <c r="Q14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="V14" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W14" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="X14" s="6" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1369,6 +1620,30 @@
       <c r="P15" s="5" t="n">
         <v>0.966</v>
       </c>
+      <c r="Q15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="V15" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W15" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="X15" s="6" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1433,6 +1708,30 @@
       <c r="P16" s="5" t="n">
         <v>0.9723000000000001</v>
       </c>
+      <c r="Q16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="V16" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W16" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="X16" s="6" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1497,6 +1796,30 @@
       <c r="P17" s="5" t="n">
         <v>0.9766</v>
       </c>
+      <c r="Q17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="V17" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W17" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="X17" s="6" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1561,6 +1884,30 @@
       <c r="P18" s="5" t="n">
         <v>0.9781</v>
       </c>
+      <c r="Q18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="V18" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W18" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="X18" s="6" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1625,6 +1972,30 @@
       <c r="P19" s="5" t="n">
         <v>1.0106</v>
       </c>
+      <c r="Q19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1689,6 +2060,30 @@
       <c r="P20" s="5" t="n">
         <v>1.0106</v>
       </c>
+      <c r="Q20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1753,6 +2148,30 @@
       <c r="P21" s="5" t="n">
         <v>0.9709</v>
       </c>
+      <c r="Q21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="V21" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="W21" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="X21" s="6" t="n">
+        <v>0.07333333333333335</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1817,6 +2236,14 @@
       <c r="P22" s="5" t="n">
         <v>0.9963</v>
       </c>
+      <c r="Q22" s="6" t="inlineStr"/>
+      <c r="R22" s="6" t="inlineStr"/>
+      <c r="S22" s="6" t="inlineStr"/>
+      <c r="T22" s="6" t="inlineStr"/>
+      <c r="U22" s="6" t="inlineStr"/>
+      <c r="V22" s="6" t="inlineStr"/>
+      <c r="W22" s="6" t="inlineStr"/>
+      <c r="X22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1881,6 +2308,14 @@
       <c r="P23" s="5" t="n">
         <v>0.9967</v>
       </c>
+      <c r="Q23" s="6" t="inlineStr"/>
+      <c r="R23" s="6" t="inlineStr"/>
+      <c r="S23" s="6" t="inlineStr"/>
+      <c r="T23" s="6" t="inlineStr"/>
+      <c r="U23" s="6" t="inlineStr"/>
+      <c r="V23" s="6" t="inlineStr"/>
+      <c r="W23" s="6" t="inlineStr"/>
+      <c r="X23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1935,6 +2370,14 @@
       <c r="P24" s="5" t="n">
         <v>0.9458</v>
       </c>
+      <c r="Q24" s="6" t="inlineStr"/>
+      <c r="R24" s="6" t="inlineStr"/>
+      <c r="S24" s="6" t="inlineStr"/>
+      <c r="T24" s="6" t="inlineStr"/>
+      <c r="U24" s="6" t="inlineStr"/>
+      <c r="V24" s="6" t="inlineStr"/>
+      <c r="W24" s="6" t="inlineStr"/>
+      <c r="X24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1989,6 +2432,14 @@
       <c r="P25" s="5" t="n">
         <v>0.9408</v>
       </c>
+      <c r="Q25" s="6" t="inlineStr"/>
+      <c r="R25" s="6" t="inlineStr"/>
+      <c r="S25" s="6" t="inlineStr"/>
+      <c r="T25" s="6" t="inlineStr"/>
+      <c r="U25" s="6" t="inlineStr"/>
+      <c r="V25" s="6" t="inlineStr"/>
+      <c r="W25" s="6" t="inlineStr"/>
+      <c r="X25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2043,6 +2494,14 @@
       <c r="P26" s="5" t="n">
         <v>0.9605</v>
       </c>
+      <c r="Q26" s="6" t="inlineStr"/>
+      <c r="R26" s="6" t="inlineStr"/>
+      <c r="S26" s="6" t="inlineStr"/>
+      <c r="T26" s="6" t="inlineStr"/>
+      <c r="U26" s="6" t="inlineStr"/>
+      <c r="V26" s="6" t="inlineStr"/>
+      <c r="W26" s="6" t="inlineStr"/>
+      <c r="X26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2095,6 +2554,14 @@
       <c r="P27" s="5" t="n">
         <v>0.9711</v>
       </c>
+      <c r="Q27" s="6" t="inlineStr"/>
+      <c r="R27" s="6" t="inlineStr"/>
+      <c r="S27" s="6" t="inlineStr"/>
+      <c r="T27" s="6" t="inlineStr"/>
+      <c r="U27" s="6" t="inlineStr"/>
+      <c r="V27" s="6" t="inlineStr"/>
+      <c r="W27" s="6" t="inlineStr"/>
+      <c r="X27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2145,6 +2612,14 @@
       <c r="P28" s="5" t="n">
         <v>0.971</v>
       </c>
+      <c r="Q28" s="6" t="inlineStr"/>
+      <c r="R28" s="6" t="inlineStr"/>
+      <c r="S28" s="6" t="inlineStr"/>
+      <c r="T28" s="6" t="inlineStr"/>
+      <c r="U28" s="6" t="inlineStr"/>
+      <c r="V28" s="6" t="inlineStr"/>
+      <c r="W28" s="6" t="inlineStr"/>
+      <c r="X28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2199,6 +2674,14 @@
       <c r="P29" s="5" t="n">
         <v>0.9635</v>
       </c>
+      <c r="Q29" s="6" t="inlineStr"/>
+      <c r="R29" s="6" t="inlineStr"/>
+      <c r="S29" s="6" t="inlineStr"/>
+      <c r="T29" s="6" t="inlineStr"/>
+      <c r="U29" s="6" t="inlineStr"/>
+      <c r="V29" s="6" t="inlineStr"/>
+      <c r="W29" s="6" t="inlineStr"/>
+      <c r="X29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2253,6 +2736,14 @@
       <c r="P30" s="5" t="n">
         <v>0.962</v>
       </c>
+      <c r="Q30" s="6" t="inlineStr"/>
+      <c r="R30" s="6" t="inlineStr"/>
+      <c r="S30" s="6" t="inlineStr"/>
+      <c r="T30" s="6" t="inlineStr"/>
+      <c r="U30" s="6" t="inlineStr"/>
+      <c r="V30" s="6" t="inlineStr"/>
+      <c r="W30" s="6" t="inlineStr"/>
+      <c r="X30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2307,6 +2798,14 @@
       <c r="P31" s="5" t="n">
         <v>0.9538</v>
       </c>
+      <c r="Q31" s="6" t="inlineStr"/>
+      <c r="R31" s="6" t="inlineStr"/>
+      <c r="S31" s="6" t="inlineStr"/>
+      <c r="T31" s="6" t="inlineStr"/>
+      <c r="U31" s="6" t="inlineStr"/>
+      <c r="V31" s="6" t="inlineStr"/>
+      <c r="W31" s="6" t="inlineStr"/>
+      <c r="X31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2361,6 +2860,14 @@
       <c r="P32" s="5" t="n">
         <v>0.9538</v>
       </c>
+      <c r="Q32" s="6" t="inlineStr"/>
+      <c r="R32" s="6" t="inlineStr"/>
+      <c r="S32" s="6" t="inlineStr"/>
+      <c r="T32" s="6" t="inlineStr"/>
+      <c r="U32" s="6" t="inlineStr"/>
+      <c r="V32" s="6" t="inlineStr"/>
+      <c r="W32" s="6" t="inlineStr"/>
+      <c r="X32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2415,6 +2922,14 @@
       <c r="P33" s="5" t="n">
         <v>0.9538</v>
       </c>
+      <c r="Q33" s="6" t="inlineStr"/>
+      <c r="R33" s="6" t="inlineStr"/>
+      <c r="S33" s="6" t="inlineStr"/>
+      <c r="T33" s="6" t="inlineStr"/>
+      <c r="U33" s="6" t="inlineStr"/>
+      <c r="V33" s="6" t="inlineStr"/>
+      <c r="W33" s="6" t="inlineStr"/>
+      <c r="X33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2469,6 +2984,14 @@
       <c r="P34" s="5" t="n">
         <v>0.9389999999999999</v>
       </c>
+      <c r="Q34" s="6" t="inlineStr"/>
+      <c r="R34" s="6" t="inlineStr"/>
+      <c r="S34" s="6" t="inlineStr"/>
+      <c r="T34" s="6" t="inlineStr"/>
+      <c r="U34" s="6" t="inlineStr"/>
+      <c r="V34" s="6" t="inlineStr"/>
+      <c r="W34" s="6" t="inlineStr"/>
+      <c r="X34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2523,6 +3046,14 @@
       <c r="P35" s="5" t="n">
         <v>0.9389999999999999</v>
       </c>
+      <c r="Q35" s="6" t="inlineStr"/>
+      <c r="R35" s="6" t="inlineStr"/>
+      <c r="S35" s="6" t="inlineStr"/>
+      <c r="T35" s="6" t="inlineStr"/>
+      <c r="U35" s="6" t="inlineStr"/>
+      <c r="V35" s="6" t="inlineStr"/>
+      <c r="W35" s="6" t="inlineStr"/>
+      <c r="X35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2577,6 +3108,14 @@
       <c r="P36" s="5" t="n">
         <v>0.9389999999999999</v>
       </c>
+      <c r="Q36" s="6" t="inlineStr"/>
+      <c r="R36" s="6" t="inlineStr"/>
+      <c r="S36" s="6" t="inlineStr"/>
+      <c r="T36" s="6" t="inlineStr"/>
+      <c r="U36" s="6" t="inlineStr"/>
+      <c r="V36" s="6" t="inlineStr"/>
+      <c r="W36" s="6" t="inlineStr"/>
+      <c r="X36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2631,6 +3170,14 @@
       <c r="P37" s="5" t="n">
         <v>0.9661999999999999</v>
       </c>
+      <c r="Q37" s="6" t="inlineStr"/>
+      <c r="R37" s="6" t="inlineStr"/>
+      <c r="S37" s="6" t="inlineStr"/>
+      <c r="T37" s="6" t="inlineStr"/>
+      <c r="U37" s="6" t="inlineStr"/>
+      <c r="V37" s="6" t="inlineStr"/>
+      <c r="W37" s="6" t="inlineStr"/>
+      <c r="X37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2685,6 +3232,14 @@
       <c r="P38" s="5" t="n">
         <v>0.9661999999999999</v>
       </c>
+      <c r="Q38" s="6" t="inlineStr"/>
+      <c r="R38" s="6" t="inlineStr"/>
+      <c r="S38" s="6" t="inlineStr"/>
+      <c r="T38" s="6" t="inlineStr"/>
+      <c r="U38" s="6" t="inlineStr"/>
+      <c r="V38" s="6" t="inlineStr"/>
+      <c r="W38" s="6" t="inlineStr"/>
+      <c r="X38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2739,6 +3294,14 @@
       <c r="P39" s="5" t="n">
         <v>0.9379</v>
       </c>
+      <c r="Q39" s="6" t="inlineStr"/>
+      <c r="R39" s="6" t="inlineStr"/>
+      <c r="S39" s="6" t="inlineStr"/>
+      <c r="T39" s="6" t="inlineStr"/>
+      <c r="U39" s="6" t="inlineStr"/>
+      <c r="V39" s="6" t="inlineStr"/>
+      <c r="W39" s="6" t="inlineStr"/>
+      <c r="X39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2793,6 +3356,14 @@
       <c r="P40" s="5" t="n">
         <v>0.9583</v>
       </c>
+      <c r="Q40" s="6" t="inlineStr"/>
+      <c r="R40" s="6" t="inlineStr"/>
+      <c r="S40" s="6" t="inlineStr"/>
+      <c r="T40" s="6" t="inlineStr"/>
+      <c r="U40" s="6" t="inlineStr"/>
+      <c r="V40" s="6" t="inlineStr"/>
+      <c r="W40" s="6" t="inlineStr"/>
+      <c r="X40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2847,6 +3418,14 @@
       <c r="P41" s="5" t="n">
         <v>0.9709</v>
       </c>
+      <c r="Q41" s="6" t="inlineStr"/>
+      <c r="R41" s="6" t="inlineStr"/>
+      <c r="S41" s="6" t="inlineStr"/>
+      <c r="T41" s="6" t="inlineStr"/>
+      <c r="U41" s="6" t="inlineStr"/>
+      <c r="V41" s="6" t="inlineStr"/>
+      <c r="W41" s="6" t="inlineStr"/>
+      <c r="X41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2901,6 +3480,14 @@
       <c r="P42" s="5" t="n">
         <v>0.9694</v>
       </c>
+      <c r="Q42" s="6" t="inlineStr"/>
+      <c r="R42" s="6" t="inlineStr"/>
+      <c r="S42" s="6" t="inlineStr"/>
+      <c r="T42" s="6" t="inlineStr"/>
+      <c r="U42" s="6" t="inlineStr"/>
+      <c r="V42" s="6" t="inlineStr"/>
+      <c r="W42" s="6" t="inlineStr"/>
+      <c r="X42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2955,6 +3542,14 @@
       <c r="P43" s="5" t="n">
         <v>0.9694</v>
       </c>
+      <c r="Q43" s="6" t="inlineStr"/>
+      <c r="R43" s="6" t="inlineStr"/>
+      <c r="S43" s="6" t="inlineStr"/>
+      <c r="T43" s="6" t="inlineStr"/>
+      <c r="U43" s="6" t="inlineStr"/>
+      <c r="V43" s="6" t="inlineStr"/>
+      <c r="W43" s="6" t="inlineStr"/>
+      <c r="X43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3009,6 +3604,14 @@
       <c r="P44" s="5" t="n">
         <v>0.9112</v>
       </c>
+      <c r="Q44" s="6" t="inlineStr"/>
+      <c r="R44" s="6" t="inlineStr"/>
+      <c r="S44" s="6" t="inlineStr"/>
+      <c r="T44" s="6" t="inlineStr"/>
+      <c r="U44" s="6" t="inlineStr"/>
+      <c r="V44" s="6" t="inlineStr"/>
+      <c r="W44" s="6" t="inlineStr"/>
+      <c r="X44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3063,6 +3666,14 @@
       <c r="P45" s="5" t="n">
         <v>1.0034</v>
       </c>
+      <c r="Q45" s="6" t="inlineStr"/>
+      <c r="R45" s="6" t="inlineStr"/>
+      <c r="S45" s="6" t="inlineStr"/>
+      <c r="T45" s="6" t="inlineStr"/>
+      <c r="U45" s="6" t="inlineStr"/>
+      <c r="V45" s="6" t="inlineStr"/>
+      <c r="W45" s="6" t="inlineStr"/>
+      <c r="X45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3117,6 +3728,14 @@
       <c r="P46" s="5" t="n">
         <v>0.9583</v>
       </c>
+      <c r="Q46" s="6" t="inlineStr"/>
+      <c r="R46" s="6" t="inlineStr"/>
+      <c r="S46" s="6" t="inlineStr"/>
+      <c r="T46" s="6" t="inlineStr"/>
+      <c r="U46" s="6" t="inlineStr"/>
+      <c r="V46" s="6" t="inlineStr"/>
+      <c r="W46" s="6" t="inlineStr"/>
+      <c r="X46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3171,6 +3790,14 @@
       <c r="P47" s="5" t="n">
         <v>0.9611</v>
       </c>
+      <c r="Q47" s="6" t="inlineStr"/>
+      <c r="R47" s="6" t="inlineStr"/>
+      <c r="S47" s="6" t="inlineStr"/>
+      <c r="T47" s="6" t="inlineStr"/>
+      <c r="U47" s="6" t="inlineStr"/>
+      <c r="V47" s="6" t="inlineStr"/>
+      <c r="W47" s="6" t="inlineStr"/>
+      <c r="X47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3225,6 +3852,14 @@
       <c r="P48" s="5" t="n">
         <v>0.844</v>
       </c>
+      <c r="Q48" s="6" t="inlineStr"/>
+      <c r="R48" s="6" t="inlineStr"/>
+      <c r="S48" s="6" t="inlineStr"/>
+      <c r="T48" s="6" t="inlineStr"/>
+      <c r="U48" s="6" t="inlineStr"/>
+      <c r="V48" s="6" t="inlineStr"/>
+      <c r="W48" s="6" t="inlineStr"/>
+      <c r="X48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3279,6 +3914,14 @@
       <c r="P49" s="5" t="n">
         <v>0.9605</v>
       </c>
+      <c r="Q49" s="6" t="inlineStr"/>
+      <c r="R49" s="6" t="inlineStr"/>
+      <c r="S49" s="6" t="inlineStr"/>
+      <c r="T49" s="6" t="inlineStr"/>
+      <c r="U49" s="6" t="inlineStr"/>
+      <c r="V49" s="6" t="inlineStr"/>
+      <c r="W49" s="6" t="inlineStr"/>
+      <c r="X49" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3291,7 +3934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:W49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3303,62 +3946,146 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>DUID</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Fuel</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>MLF_FY24-25</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>MLF_FY25-26</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>MLF_FY26-27 (Draft)</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>CURTAILMENT_ACTUAL_FY23-24</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>CURTAILMENT_ACTUAL_FY24-25</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>ELI_CURTAILMENT_NEAR</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>ELI_CURTAILMENT_MED</t>
         </is>
       </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY1</t>
+        </is>
+      </c>
+      <c r="K1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY1_LABEL</t>
+        </is>
+      </c>
+      <c r="L1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY2</t>
+        </is>
+      </c>
+      <c r="M1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY2_LABEL</t>
+        </is>
+      </c>
+      <c r="N1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY3</t>
+        </is>
+      </c>
+      <c r="O1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY3_LABEL</t>
+        </is>
+      </c>
+      <c r="P1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_AVG</t>
+        </is>
+      </c>
+      <c r="Q1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY1</t>
+        </is>
+      </c>
+      <c r="R1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY1_LABEL</t>
+        </is>
+      </c>
+      <c r="S1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY2</t>
+        </is>
+      </c>
+      <c r="T1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY2_LABEL</t>
+        </is>
+      </c>
+      <c r="U1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY3</t>
+        </is>
+      </c>
+      <c r="V1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY3_LABEL</t>
+        </is>
+      </c>
+      <c r="W1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_AVG</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>ADPPV1</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3380,14 +4107,52 @@
       </c>
       <c r="H2" s="5" t="inlineStr"/>
       <c r="I2" s="5" t="inlineStr"/>
+      <c r="J2" s="5" t="inlineStr"/>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr"/>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr"/>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr"/>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="inlineStr"/>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>ADPPV2</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3405,14 +4170,52 @@
       <c r="G3" s="5" t="inlineStr"/>
       <c r="H3" s="5" t="inlineStr"/>
       <c r="I3" s="5" t="inlineStr"/>
+      <c r="J3" s="5" t="inlineStr"/>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr"/>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr"/>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr"/>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="inlineStr"/>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>ADPPV3</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3430,14 +4233,52 @@
       <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="inlineStr"/>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>BOWWPV1</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3457,14 +4298,52 @@
       </c>
       <c r="H5" s="5" t="inlineStr"/>
       <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="5" t="inlineStr"/>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr"/>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr"/>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="inlineStr"/>
+      <c r="Q5" s="5" t="inlineStr"/>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S5" s="5" t="inlineStr"/>
+      <c r="T5" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U5" s="5" t="inlineStr"/>
+      <c r="V5" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>BNGSF1</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3490,14 +4369,68 @@
       <c r="I6" s="5" t="n">
         <v>0.212860651220515</v>
       </c>
+      <c r="J6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S6" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T6" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U6" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="V6" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W6" s="5" t="n">
+        <v>0.07333333333333335</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>BNGSF2</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3523,14 +4456,68 @@
       <c r="I7" s="5" t="n">
         <v>0.212860651220515</v>
       </c>
+      <c r="J7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="R7" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S7" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T7" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U7" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="V7" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W7" s="5" t="n">
+        <v>0.07333333333333335</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>CBWWPV1</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3548,14 +4535,52 @@
       <c r="G8" s="5" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P8" s="5" t="inlineStr"/>
+      <c r="Q8" s="5" t="inlineStr"/>
+      <c r="R8" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S8" s="5" t="inlineStr"/>
+      <c r="T8" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U8" s="5" t="inlineStr"/>
+      <c r="V8" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>CBWWPV2</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3573,14 +4598,52 @@
       <c r="G9" s="5" t="inlineStr"/>
       <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P9" s="5" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr"/>
+      <c r="R9" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S9" s="5" t="inlineStr"/>
+      <c r="T9" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U9" s="5" t="inlineStr"/>
+      <c r="V9" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>HVWWPV1</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3606,14 +4669,52 @@
       <c r="I10" s="5" t="n">
         <v>0.22265637813532</v>
       </c>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P10" s="5" t="inlineStr"/>
+      <c r="Q10" s="5" t="inlineStr"/>
+      <c r="R10" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S10" s="5" t="inlineStr"/>
+      <c r="T10" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U10" s="5" t="inlineStr"/>
+      <c r="V10" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>MAPS2PV1</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3639,14 +4740,68 @@
       <c r="I11" s="5" t="n">
         <v>0.225784053085401</v>
       </c>
+      <c r="J11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W11" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>MAPS2PV1</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3672,14 +4827,68 @@
       <c r="I12" s="5" t="n">
         <v>0.225784053085401</v>
       </c>
+      <c r="J12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W12" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>MAPS3PV1</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3703,14 +4912,68 @@
       <c r="I13" s="5" t="n">
         <v>0.225784053085401</v>
       </c>
+      <c r="J13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W13" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>MANNSF2</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3734,14 +4997,68 @@
       <c r="I14" s="5" t="n">
         <v>0.225784053085401</v>
       </c>
+      <c r="J14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="R14" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S14" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="T14" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U14" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="V14" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W14" s="5" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>MWPS1PV1</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3767,14 +5084,68 @@
       <c r="I15" s="5" t="n">
         <v>0.512670422089759</v>
       </c>
+      <c r="J15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="R15" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S15" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="T15" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U15" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="V15" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W15" s="5" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>MWPS2PV1</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3800,14 +5171,68 @@
       <c r="I16" s="5" t="n">
         <v>0.512670422089759</v>
       </c>
+      <c r="J16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="R16" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S16" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="T16" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U16" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="V16" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W16" s="5" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>MWPS3PV1</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3833,14 +5258,68 @@
       <c r="I17" s="5" t="n">
         <v>0.512670422089759</v>
       </c>
+      <c r="J17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="R17" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S17" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="T17" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U17" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="V17" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W17" s="5" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>MWPS4PV1</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3866,14 +5345,68 @@
       <c r="I18" s="5" t="n">
         <v>0.512670422089759</v>
       </c>
+      <c r="J18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="R18" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S18" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="T18" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U18" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="V18" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W18" s="5" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>MBPS2PV1</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3899,14 +5432,68 @@
       <c r="I19" s="5" t="n">
         <v>0.225784053085401</v>
       </c>
+      <c r="J19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W19" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>MBPS2PV1</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3932,14 +5519,68 @@
       <c r="I20" s="5" t="n">
         <v>0.225784053085401</v>
       </c>
+      <c r="J20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W20" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>PAREPS1</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3965,14 +5606,68 @@
       <c r="I21" s="5" t="n">
         <v>0.212860651220515</v>
       </c>
+      <c r="J21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="R21" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S21" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T21" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U21" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="V21" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W21" s="5" t="n">
+        <v>0.07333333333333335</v>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>TB2SF1</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3998,14 +5693,52 @@
       <c r="I22" s="5" t="n">
         <v>0.22945882760626</v>
       </c>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P22" s="5" t="inlineStr"/>
+      <c r="Q22" s="5" t="inlineStr"/>
+      <c r="R22" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S22" s="5" t="inlineStr"/>
+      <c r="T22" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U22" s="5" t="inlineStr"/>
+      <c r="V22" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>TBSF1</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4031,14 +5764,52 @@
       <c r="I23" s="5" t="n">
         <v>0.22945882760626</v>
       </c>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P23" s="5" t="inlineStr"/>
+      <c r="Q23" s="5" t="inlineStr"/>
+      <c r="R23" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S23" s="5" t="inlineStr"/>
+      <c r="T23" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U23" s="5" t="inlineStr"/>
+      <c r="V23" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>CNUNDAWF</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4060,14 +5831,52 @@
       </c>
       <c r="H24" s="5" t="inlineStr"/>
       <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N24" s="5" t="inlineStr"/>
+      <c r="O24" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P24" s="5" t="inlineStr"/>
+      <c r="Q24" s="5" t="inlineStr"/>
+      <c r="R24" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S24" s="5" t="inlineStr"/>
+      <c r="T24" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U24" s="5" t="inlineStr"/>
+      <c r="V24" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>CATHROCK</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4089,14 +5898,52 @@
       </c>
       <c r="H25" s="5" t="inlineStr"/>
       <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P25" s="5" t="inlineStr"/>
+      <c r="Q25" s="5" t="inlineStr"/>
+      <c r="R25" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S25" s="5" t="inlineStr"/>
+      <c r="T25" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U25" s="5" t="inlineStr"/>
+      <c r="V25" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>CLEMGPWF</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4118,14 +5965,52 @@
       </c>
       <c r="H26" s="5" t="inlineStr"/>
       <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P26" s="5" t="inlineStr"/>
+      <c r="Q26" s="5" t="inlineStr"/>
+      <c r="R26" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S26" s="5" t="inlineStr"/>
+      <c r="T26" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U26" s="5" t="inlineStr"/>
+      <c r="V26" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>GSWF1A</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4145,14 +6030,52 @@
       </c>
       <c r="H27" s="5" t="inlineStr"/>
       <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P27" s="5" t="inlineStr"/>
+      <c r="Q27" s="5" t="inlineStr"/>
+      <c r="R27" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S27" s="5" t="inlineStr"/>
+      <c r="T27" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U27" s="5" t="inlineStr"/>
+      <c r="V27" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>GSWF1B1</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4170,14 +6093,52 @@
       <c r="G28" s="5" t="inlineStr"/>
       <c r="H28" s="5" t="inlineStr"/>
       <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P28" s="5" t="inlineStr"/>
+      <c r="Q28" s="5" t="inlineStr"/>
+      <c r="R28" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S28" s="5" t="inlineStr"/>
+      <c r="T28" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U28" s="5" t="inlineStr"/>
+      <c r="V28" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>HALLWF1</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4199,14 +6160,52 @@
       </c>
       <c r="H29" s="5" t="inlineStr"/>
       <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P29" s="5" t="inlineStr"/>
+      <c r="Q29" s="5" t="inlineStr"/>
+      <c r="R29" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S29" s="5" t="inlineStr"/>
+      <c r="T29" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U29" s="5" t="inlineStr"/>
+      <c r="V29" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>HALLWF2</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4228,14 +6227,52 @@
       </c>
       <c r="H30" s="5" t="inlineStr"/>
       <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr"/>
+      <c r="M30" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N30" s="5" t="inlineStr"/>
+      <c r="O30" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P30" s="5" t="inlineStr"/>
+      <c r="Q30" s="5" t="inlineStr"/>
+      <c r="R30" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S30" s="5" t="inlineStr"/>
+      <c r="T30" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U30" s="5" t="inlineStr"/>
+      <c r="V30" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>HDWF1</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4257,14 +6294,52 @@
       </c>
       <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr"/>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr"/>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N31" s="5" t="inlineStr"/>
+      <c r="O31" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P31" s="5" t="inlineStr"/>
+      <c r="Q31" s="5" t="inlineStr"/>
+      <c r="R31" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S31" s="5" t="inlineStr"/>
+      <c r="T31" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U31" s="5" t="inlineStr"/>
+      <c r="V31" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>HDWF2</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4286,14 +6361,52 @@
       </c>
       <c r="H32" s="5" t="inlineStr"/>
       <c r="I32" s="5" t="inlineStr"/>
+      <c r="J32" s="5" t="inlineStr"/>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr"/>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N32" s="5" t="inlineStr"/>
+      <c r="O32" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P32" s="5" t="inlineStr"/>
+      <c r="Q32" s="5" t="inlineStr"/>
+      <c r="R32" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S32" s="5" t="inlineStr"/>
+      <c r="T32" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U32" s="5" t="inlineStr"/>
+      <c r="V32" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>HDWF3</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4315,14 +6428,52 @@
       </c>
       <c r="H33" s="5" t="inlineStr"/>
       <c r="I33" s="5" t="inlineStr"/>
+      <c r="J33" s="5" t="inlineStr"/>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr"/>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N33" s="5" t="inlineStr"/>
+      <c r="O33" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P33" s="5" t="inlineStr"/>
+      <c r="Q33" s="5" t="inlineStr"/>
+      <c r="R33" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S33" s="5" t="inlineStr"/>
+      <c r="T33" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U33" s="5" t="inlineStr"/>
+      <c r="V33" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>LKBONNY2</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4344,14 +6495,52 @@
       </c>
       <c r="H34" s="5" t="inlineStr"/>
       <c r="I34" s="5" t="inlineStr"/>
+      <c r="J34" s="5" t="inlineStr"/>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr"/>
+      <c r="M34" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N34" s="5" t="inlineStr"/>
+      <c r="O34" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P34" s="5" t="inlineStr"/>
+      <c r="Q34" s="5" t="inlineStr"/>
+      <c r="R34" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S34" s="5" t="inlineStr"/>
+      <c r="T34" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U34" s="5" t="inlineStr"/>
+      <c r="V34" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>LKBONNY3</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4373,14 +6562,52 @@
       </c>
       <c r="H35" s="5" t="inlineStr"/>
       <c r="I35" s="5" t="inlineStr"/>
+      <c r="J35" s="5" t="inlineStr"/>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr"/>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N35" s="5" t="inlineStr"/>
+      <c r="O35" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P35" s="5" t="inlineStr"/>
+      <c r="Q35" s="5" t="inlineStr"/>
+      <c r="R35" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S35" s="5" t="inlineStr"/>
+      <c r="T35" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U35" s="5" t="inlineStr"/>
+      <c r="V35" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>LKBONNY1</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4402,14 +6629,52 @@
       </c>
       <c r="H36" s="5" t="inlineStr"/>
       <c r="I36" s="5" t="inlineStr"/>
+      <c r="J36" s="5" t="inlineStr"/>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="inlineStr"/>
+      <c r="M36" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N36" s="5" t="inlineStr"/>
+      <c r="O36" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P36" s="5" t="inlineStr"/>
+      <c r="Q36" s="5" t="inlineStr"/>
+      <c r="R36" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S36" s="5" t="inlineStr"/>
+      <c r="T36" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U36" s="5" t="inlineStr"/>
+      <c r="V36" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>LGAPWF1</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4431,14 +6696,52 @@
       </c>
       <c r="H37" s="5" t="inlineStr"/>
       <c r="I37" s="5" t="inlineStr"/>
+      <c r="J37" s="5" t="inlineStr"/>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr"/>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N37" s="5" t="inlineStr"/>
+      <c r="O37" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P37" s="5" t="inlineStr"/>
+      <c r="Q37" s="5" t="inlineStr"/>
+      <c r="R37" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S37" s="5" t="inlineStr"/>
+      <c r="T37" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U37" s="5" t="inlineStr"/>
+      <c r="V37" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>LGAPWF2</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4460,14 +6763,52 @@
       </c>
       <c r="H38" s="5" t="inlineStr"/>
       <c r="I38" s="5" t="inlineStr"/>
+      <c r="J38" s="5" t="inlineStr"/>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="inlineStr"/>
+      <c r="M38" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N38" s="5" t="inlineStr"/>
+      <c r="O38" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P38" s="5" t="inlineStr"/>
+      <c r="Q38" s="5" t="inlineStr"/>
+      <c r="R38" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S38" s="5" t="inlineStr"/>
+      <c r="T38" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U38" s="5" t="inlineStr"/>
+      <c r="V38" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="inlineStr">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>MTMILLAR</t>
         </is>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4489,14 +6830,52 @@
       </c>
       <c r="H39" s="5" t="inlineStr"/>
       <c r="I39" s="5" t="inlineStr"/>
+      <c r="J39" s="5" t="inlineStr"/>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr"/>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N39" s="5" t="inlineStr"/>
+      <c r="O39" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P39" s="5" t="inlineStr"/>
+      <c r="Q39" s="5" t="inlineStr"/>
+      <c r="R39" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S39" s="5" t="inlineStr"/>
+      <c r="T39" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U39" s="5" t="inlineStr"/>
+      <c r="V39" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="7" t="inlineStr">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>NBHWF1</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4518,14 +6897,52 @@
       </c>
       <c r="H40" s="5" t="inlineStr"/>
       <c r="I40" s="5" t="inlineStr"/>
+      <c r="J40" s="5" t="inlineStr"/>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="inlineStr"/>
+      <c r="M40" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N40" s="5" t="inlineStr"/>
+      <c r="O40" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P40" s="5" t="inlineStr"/>
+      <c r="Q40" s="5" t="inlineStr"/>
+      <c r="R40" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S40" s="5" t="inlineStr"/>
+      <c r="T40" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U40" s="5" t="inlineStr"/>
+      <c r="V40" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="7" t="inlineStr">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>PAREPW1</t>
         </is>
       </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4547,14 +6964,52 @@
       </c>
       <c r="H41" s="5" t="inlineStr"/>
       <c r="I41" s="5" t="inlineStr"/>
+      <c r="J41" s="5" t="inlineStr"/>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr"/>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N41" s="5" t="inlineStr"/>
+      <c r="O41" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P41" s="5" t="inlineStr"/>
+      <c r="Q41" s="5" t="inlineStr"/>
+      <c r="R41" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S41" s="5" t="inlineStr"/>
+      <c r="T41" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U41" s="5" t="inlineStr"/>
+      <c r="V41" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>SNOWSTH1</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4576,14 +7031,52 @@
       </c>
       <c r="H42" s="5" t="inlineStr"/>
       <c r="I42" s="5" t="inlineStr"/>
+      <c r="J42" s="5" t="inlineStr"/>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="inlineStr"/>
+      <c r="M42" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N42" s="5" t="inlineStr"/>
+      <c r="O42" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P42" s="5" t="inlineStr"/>
+      <c r="Q42" s="5" t="inlineStr"/>
+      <c r="R42" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S42" s="5" t="inlineStr"/>
+      <c r="T42" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U42" s="5" t="inlineStr"/>
+      <c r="V42" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="7" t="inlineStr">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>SNOWNTH1</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4605,14 +7098,52 @@
       </c>
       <c r="H43" s="5" t="inlineStr"/>
       <c r="I43" s="5" t="inlineStr"/>
+      <c r="J43" s="5" t="inlineStr"/>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr"/>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N43" s="5" t="inlineStr"/>
+      <c r="O43" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P43" s="5" t="inlineStr"/>
+      <c r="Q43" s="5" t="inlineStr"/>
+      <c r="R43" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S43" s="5" t="inlineStr"/>
+      <c r="T43" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U43" s="5" t="inlineStr"/>
+      <c r="V43" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="7" t="inlineStr">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>SNOWTWN1</t>
         </is>
       </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="B44" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4634,14 +7165,52 @@
       </c>
       <c r="H44" s="5" t="inlineStr"/>
       <c r="I44" s="5" t="inlineStr"/>
+      <c r="J44" s="5" t="inlineStr"/>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr"/>
+      <c r="M44" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N44" s="5" t="inlineStr"/>
+      <c r="O44" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P44" s="5" t="inlineStr"/>
+      <c r="Q44" s="5" t="inlineStr"/>
+      <c r="R44" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S44" s="5" t="inlineStr"/>
+      <c r="T44" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U44" s="5" t="inlineStr"/>
+      <c r="V44" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W44" s="5" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="7" t="inlineStr">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>STARHLWF</t>
         </is>
       </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4663,14 +7232,52 @@
       </c>
       <c r="H45" s="5" t="inlineStr"/>
       <c r="I45" s="5" t="inlineStr"/>
+      <c r="J45" s="5" t="inlineStr"/>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr"/>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N45" s="5" t="inlineStr"/>
+      <c r="O45" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P45" s="5" t="inlineStr"/>
+      <c r="Q45" s="5" t="inlineStr"/>
+      <c r="R45" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S45" s="5" t="inlineStr"/>
+      <c r="T45" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U45" s="5" t="inlineStr"/>
+      <c r="V45" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="7" t="inlineStr">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>BLUFF1</t>
         </is>
       </c>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="B46" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4692,14 +7299,52 @@
       </c>
       <c r="H46" s="5" t="inlineStr"/>
       <c r="I46" s="5" t="inlineStr"/>
+      <c r="J46" s="5" t="inlineStr"/>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr"/>
+      <c r="M46" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N46" s="5" t="inlineStr"/>
+      <c r="O46" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P46" s="5" t="inlineStr"/>
+      <c r="Q46" s="5" t="inlineStr"/>
+      <c r="R46" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S46" s="5" t="inlineStr"/>
+      <c r="T46" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U46" s="5" t="inlineStr"/>
+      <c r="V46" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="7" t="inlineStr">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>WATERLWF</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4721,14 +7366,52 @@
       </c>
       <c r="H47" s="5" t="inlineStr"/>
       <c r="I47" s="5" t="inlineStr"/>
+      <c r="J47" s="5" t="inlineStr"/>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr"/>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N47" s="5" t="inlineStr"/>
+      <c r="O47" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P47" s="5" t="inlineStr"/>
+      <c r="Q47" s="5" t="inlineStr"/>
+      <c r="R47" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S47" s="5" t="inlineStr"/>
+      <c r="T47" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U47" s="5" t="inlineStr"/>
+      <c r="V47" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="inlineStr">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>WPWF</t>
         </is>
       </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B48" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4750,14 +7433,52 @@
       </c>
       <c r="H48" s="5" t="inlineStr"/>
       <c r="I48" s="5" t="inlineStr"/>
+      <c r="J48" s="5" t="inlineStr"/>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L48" s="5" t="inlineStr"/>
+      <c r="M48" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N48" s="5" t="inlineStr"/>
+      <c r="O48" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P48" s="5" t="inlineStr"/>
+      <c r="Q48" s="5" t="inlineStr"/>
+      <c r="R48" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S48" s="5" t="inlineStr"/>
+      <c r="T48" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U48" s="5" t="inlineStr"/>
+      <c r="V48" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W48" s="5" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="inlineStr">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>WGWF1</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="B49" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4779,6 +7500,44 @@
       </c>
       <c r="H49" s="5" t="inlineStr"/>
       <c r="I49" s="5" t="inlineStr"/>
+      <c r="J49" s="5" t="inlineStr"/>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr"/>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N49" s="5" t="inlineStr"/>
+      <c r="O49" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P49" s="5" t="inlineStr"/>
+      <c r="Q49" s="5" t="inlineStr"/>
+      <c r="R49" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S49" s="5" t="inlineStr"/>
+      <c r="T49" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U49" s="5" t="inlineStr"/>
+      <c r="V49" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W49" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C49">
@@ -4865,6 +7624,174 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J49">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K49">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L49">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M49">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:N49">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O2:O49">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P49">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q2:Q49">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R49">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S2:S49">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T2:T49">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U2:U49">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V2:V49">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W2:W49">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/SA_curtailment.xlsx
+++ b/outputs/SA_curtailment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X49"/>
+  <dimension ref="A1:X47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1300,12 +1300,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>MAPS2PV1</t>
+          <t>MAPS3PV1</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Mannum - Adelaide Pipeline Pumping Station No 2, PV Units 1-6</t>
+          <t>Mannum - Adelaide Pipeline Pumping Station No 3, PV Units 1-6</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1340,11 +1340,9 @@
         <v>3.3</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.2199</v>
-      </c>
-      <c r="K12" s="5" t="n">
-        <v>0.2007</v>
-      </c>
+        <v>0.2291</v>
+      </c>
+      <c r="K12" s="5" t="inlineStr"/>
       <c r="L12" s="5" t="n">
         <v>0.510590381447813</v>
       </c>
@@ -1352,13 +1350,13 @@
         <v>0.225784053085401</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>0.9926</v>
+        <v>0.9802</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>1.0257</v>
+        <v>1.0252</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>1.0132</v>
+        <v>1.0135</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1388,12 +1386,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>MAPS3PV1</t>
+          <t>MANNSF2</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Mannum - Adelaide Pipeline Pumping Station No 3, PV Units 1-6</t>
+          <t>Mannum 2 Solar Farm</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1413,7 +1411,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>South East South Australia</t>
+          <t>Riverland</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1422,15 +1420,15 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>16.5</v>
+        <v>29.99</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J13" s="5" t="n">
-        <v>0.2291</v>
-      </c>
-      <c r="K13" s="5" t="inlineStr"/>
+        <v>33</v>
+      </c>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="n">
+        <v>0.3012</v>
+      </c>
       <c r="L13" s="5" t="n">
         <v>0.510590381447813</v>
       </c>
@@ -1438,13 +1436,13 @@
         <v>0.225784053085401</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>0.9802</v>
+        <v>0.9937</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>1.0252</v>
+        <v>0.9932</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>1.0135</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1459,27 +1457,27 @@
         <v>0</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="X13" s="6" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>MANNSF2</t>
+          <t>MWPS1PV1</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Mannum 2 Solar Farm</t>
+          <t>Morgan-Whyalla Pipeline Pumping Station No 1</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1489,7 +1487,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Mobilong</t>
+          <t>Waterloo</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1508,29 +1506,31 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>29.99</v>
+        <v>5.5</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J14" s="5" t="inlineStr"/>
+        <v>3.3</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>0.1286</v>
+      </c>
       <c r="K14" s="5" t="n">
-        <v>0.3012</v>
+        <v>0.2462</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>0.510590381447813</v>
+        <v>0.65425629128861</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>0.225784053085401</v>
+        <v>0.512670422089759</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>0.9937</v>
+        <v>0.9759</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>0.9932</v>
+        <v>1.0146</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>0.9955000000000001</v>
+        <v>0.966</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>0</v>
@@ -1560,12 +1560,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>MWPS1PV1</t>
+          <t>MWPS2PV1</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Morgan-Whyalla Pipeline Pumping Station No 1</t>
+          <t>Morgan-Whyalla Pipeline Pumping Station No 2</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1600,10 +1600,10 @@
         <v>3.3</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>0.1286</v>
+        <v>0.1131</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>0.2462</v>
+        <v>0.2411</v>
       </c>
       <c r="L15" s="5" t="n">
         <v>0.65425629128861</v>
@@ -1612,13 +1612,13 @@
         <v>0.512670422089759</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>0.9759</v>
+        <v>0.9766</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>1.0146</v>
+        <v>1.003</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>0.966</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="Q15" s="6" t="n">
         <v>0</v>
@@ -1648,12 +1648,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>MWPS2PV1</t>
+          <t>MWPS3PV1</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Morgan-Whyalla Pipeline Pumping Station No 2</t>
+          <t>Morgan-Whyalla Pipeline Pumping Station No 3</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1682,16 +1682,16 @@
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="I16" s="2" t="n">
         <v>3.3</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0.1131</v>
+        <v>0.0897</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0.2411</v>
+        <v>0.1273</v>
       </c>
       <c r="L16" s="5" t="n">
         <v>0.65425629128861</v>
@@ -1700,13 +1700,13 @@
         <v>0.512670422089759</v>
       </c>
       <c r="N16" s="5" t="n">
+        <v>0.9787</v>
+      </c>
+      <c r="O16" s="5" t="n">
+        <v>0.9897</v>
+      </c>
+      <c r="P16" s="5" t="n">
         <v>0.9766</v>
-      </c>
-      <c r="O16" s="5" t="n">
-        <v>1.003</v>
-      </c>
-      <c r="P16" s="5" t="n">
-        <v>0.9723000000000001</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>0</v>
@@ -1736,12 +1736,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>MWPS3PV1</t>
+          <t>MWPS4PV1</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Morgan-Whyalla Pipeline Pumping Station No 3</t>
+          <t>Morgan-Whyalla Pipeline Pumping Station No 4</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1770,16 +1770,16 @@
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="I17" s="2" t="n">
         <v>3.3</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0.0897</v>
+        <v>0.1184</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>0.1273</v>
+        <v>0.2031</v>
       </c>
       <c r="L17" s="5" t="n">
         <v>0.65425629128861</v>
@@ -1788,13 +1788,13 @@
         <v>0.512670422089759</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>0.9787</v>
+        <v>0.9751</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>0.9897</v>
+        <v>0.9837</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>0.9766</v>
+        <v>0.9781</v>
       </c>
       <c r="Q17" s="6" t="n">
         <v>0</v>
@@ -1824,12 +1824,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>MWPS4PV1</t>
+          <t>MBPS2PV1</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Morgan-Whyalla Pipeline Pumping Station No 4</t>
+          <t>Murray Bridge-Onkaparinga Pipeline Pumping Station No 2</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Waterloo</t>
+          <t>Mobilong</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Riverland</t>
+          <t>South East South Australia</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1858,31 +1858,31 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>5.5</v>
+        <v>13.75</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>3.3</v>
+        <v>11</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>0.1184</v>
+        <v>0.2268</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>0.2031</v>
+        <v>0.2284</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>0.65425629128861</v>
+        <v>0.510590381447813</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>0.512670422089759</v>
+        <v>0.225784053085401</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>0.9751</v>
+        <v>0.9993</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>0.9837</v>
+        <v>1.0127</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>0.9781</v>
+        <v>1.0106</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1897,27 +1897,27 @@
         <v>0</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="X18" s="6" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>MBPS2PV1</t>
+          <t>PAREPS1</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Murray Bridge-Onkaparinga Pipeline Pumping Station No 2</t>
+          <t>Port Augusta Renewable Energy Park</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Mobilong</t>
+          <t>Davenport</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>South East South Australia</t>
+          <t>Northern South Australia</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1946,31 +1946,31 @@
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>13.75</v>
+        <v>79.2</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>11</v>
+        <v>275</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>0.2268</v>
+        <v>0.1842</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>0.2284</v>
+        <v>0.3589</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>0.510590381447813</v>
+        <v>0.501077617843089</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>0.225784053085401</v>
+        <v>0.212860651220515</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>0.9993</v>
+        <v>0.9608</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>1.0127</v>
+        <v>0.9735</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>1.0106</v>
+        <v>0.9709</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -1985,27 +1985,27 @@
         <v>0</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V19" s="6" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="W19" s="6" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="X19" s="6" t="n">
-        <v>0</v>
+        <v>0.07333333333333335</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>MBPS2PV1</t>
+          <t>TB2SF1</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Murray Bridge-Onkaparinga Pipeline Pumping Station No 2</t>
+          <t>Tailem Bend 2 Hybrid Renewable Power Station</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Mobilong</t>
+          <t>Tailem Bend</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>South East South Australia</t>
+          <t>Non-REZ</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2034,66 +2034,50 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>13.75</v>
+        <v>105</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>11</v>
+        <v>132</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>0.2268</v>
+        <v>0.1987</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>0.2284</v>
+        <v>0.2973</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>0.510590381447813</v>
+        <v>0.511370986967519</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>0.225784053085401</v>
+        <v>0.22945882760626</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>0.9993</v>
+        <v>1.0102</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>1.0127</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>1.0106</v>
-      </c>
-      <c r="Q20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" s="6" t="n">
-        <v>0</v>
-      </c>
+        <v>0.9963</v>
+      </c>
+      <c r="Q20" s="6" t="inlineStr"/>
+      <c r="R20" s="6" t="inlineStr"/>
+      <c r="S20" s="6" t="inlineStr"/>
+      <c r="T20" s="6" t="inlineStr"/>
+      <c r="U20" s="6" t="inlineStr"/>
+      <c r="V20" s="6" t="inlineStr"/>
+      <c r="W20" s="6" t="inlineStr"/>
+      <c r="X20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>PAREPS1</t>
+          <t>TBSF1</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Port Augusta Renewable Energy Park</t>
+          <t>Tailem Bend Solar Project 1</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2103,17 +2087,17 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Davenport</t>
+          <t>Tailem Bend</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Northern South Australia</t>
+          <t>Non-REZ</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2122,78 +2106,58 @@
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>79.2</v>
+        <v>108</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>275</v>
+        <v>132</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>0.1842</v>
+        <v>0.2394</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>0.3589</v>
+        <v>0.3511</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>0.501077617843089</v>
+        <v>0.511370986967519</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>0.212860651220515</v>
+        <v>0.22945882760626</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>0.9608</v>
+        <v>1.009</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>0.9735</v>
+        <v>0.9952</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>0.9709</v>
-      </c>
-      <c r="Q21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="V21" s="6" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="W21" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="X21" s="6" t="n">
-        <v>0.07333333333333335</v>
-      </c>
+        <v>0.9967</v>
+      </c>
+      <c r="Q21" s="6" t="inlineStr"/>
+      <c r="R21" s="6" t="inlineStr"/>
+      <c r="S21" s="6" t="inlineStr"/>
+      <c r="T21" s="6" t="inlineStr"/>
+      <c r="U21" s="6" t="inlineStr"/>
+      <c r="V21" s="6" t="inlineStr"/>
+      <c r="W21" s="6" t="inlineStr"/>
+      <c r="X21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>TB2SF1</t>
+          <t>CNUNDAWF</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Tailem Bend 2 Hybrid Renewable Power Station</t>
+          <t>Canunda Wind Farm</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Solar</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Tailem Bend</t>
-        </is>
-      </c>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
           <t>N</t>
@@ -2210,31 +2174,25 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>105</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>132</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="5" t="n">
-        <v>0.1987</v>
+        <v>0.1746</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>0.2973</v>
-      </c>
-      <c r="L22" s="5" t="n">
-        <v>0.511370986967519</v>
-      </c>
-      <c r="M22" s="5" t="n">
-        <v>0.22945882760626</v>
-      </c>
+        <v>0.254</v>
+      </c>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr"/>
       <c r="N22" s="5" t="n">
-        <v>1.0102</v>
+        <v>0.9755</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>0.9945000000000001</v>
+        <v>0.9333</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>0.9963</v>
+        <v>0.9458</v>
       </c>
       <c r="Q22" s="6" t="inlineStr"/>
       <c r="R22" s="6" t="inlineStr"/>
@@ -2248,24 +2206,20 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>TBSF1</t>
+          <t>CATHROCK</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Tailem Bend Solar Project 1</t>
+          <t>Cathedral Rocks</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Solar</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>Tailem Bend</t>
-        </is>
-      </c>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr"/>
       <c r="E23" s="2" t="inlineStr">
         <is>
           <t>N</t>
@@ -2282,31 +2236,25 @@
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>108</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>132</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="5" t="n">
-        <v>0.2394</v>
+        <v>0.1389</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>0.3511</v>
-      </c>
-      <c r="L23" s="5" t="n">
-        <v>0.511370986967519</v>
-      </c>
-      <c r="M23" s="5" t="n">
-        <v>0.22945882760626</v>
-      </c>
+        <v>0.0515</v>
+      </c>
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr"/>
       <c r="N23" s="5" t="n">
-        <v>1.009</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>0.9952</v>
+        <v>0.9467</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>0.9967</v>
+        <v>0.9408</v>
       </c>
       <c r="Q23" s="6" t="inlineStr"/>
       <c r="R23" s="6" t="inlineStr"/>
@@ -2320,12 +2268,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>CNUNDAWF</t>
+          <t>CLEMGPWF</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Canunda Wind Farm</t>
+          <t>Clements Gap Wind Farm</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2350,25 +2298,25 @@
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="5" t="n">
-        <v>0.1746</v>
+        <v>0.0134</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>0.254</v>
+        <v>0.0062</v>
       </c>
       <c r="L24" s="5" t="inlineStr"/>
       <c r="M24" s="5" t="inlineStr"/>
       <c r="N24" s="5" t="n">
-        <v>0.9755</v>
+        <v>0.9486</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>0.9333</v>
+        <v>0.9604</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>0.9458</v>
+        <v>0.9605</v>
       </c>
       <c r="Q24" s="6" t="inlineStr"/>
       <c r="R24" s="6" t="inlineStr"/>
@@ -2382,12 +2330,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>CATHROCK</t>
+          <t>GSWF1A</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Cathedral Rocks</t>
+          <t>Goyder South Wind Farm 1A</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2412,25 +2360,23 @@
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>66</v>
+        <v>209</v>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="5" t="n">
-        <v>0.1389</v>
-      </c>
+      <c r="J25" s="5" t="inlineStr"/>
       <c r="K25" s="5" t="n">
-        <v>0.0515</v>
+        <v>0.176</v>
       </c>
       <c r="L25" s="5" t="inlineStr"/>
       <c r="M25" s="5" t="inlineStr"/>
       <c r="N25" s="5" t="n">
-        <v>0.9308999999999999</v>
+        <v>0.9643</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>0.9467</v>
+        <v>0.9697</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>0.9408</v>
+        <v>0.9711</v>
       </c>
       <c r="Q25" s="6" t="inlineStr"/>
       <c r="R25" s="6" t="inlineStr"/>
@@ -2444,12 +2390,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>CLEMGPWF</t>
+          <t>GSWF1B1</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Clements Gap Wind Farm</t>
+          <t>Goyder South Wind Farm 1B</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2474,25 +2420,21 @@
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>57</v>
+        <v>203</v>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="5" t="n">
-        <v>0.0134</v>
-      </c>
-      <c r="K26" s="5" t="n">
-        <v>0.0062</v>
-      </c>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
       <c r="L26" s="5" t="inlineStr"/>
       <c r="M26" s="5" t="inlineStr"/>
       <c r="N26" s="5" t="n">
-        <v>0.9486</v>
+        <v>0.9641</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>0.9604</v>
+        <v>0.9689</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>0.9605</v>
+        <v>0.971</v>
       </c>
       <c r="Q26" s="6" t="inlineStr"/>
       <c r="R26" s="6" t="inlineStr"/>
@@ -2506,12 +2448,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GSWF1A</t>
+          <t>HALLWF1</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Goyder South Wind Farm 1A</t>
+          <t>Hallett 1 Wind Farm</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2536,23 +2478,25 @@
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>209</v>
+        <v>94.5</v>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="n">
+        <v>0.0813</v>
+      </c>
       <c r="K27" s="5" t="n">
-        <v>0.176</v>
+        <v>0.1169</v>
       </c>
       <c r="L27" s="5" t="inlineStr"/>
       <c r="M27" s="5" t="inlineStr"/>
       <c r="N27" s="5" t="n">
-        <v>0.9643</v>
+        <v>0.9565</v>
       </c>
       <c r="O27" s="5" t="n">
-        <v>0.9697</v>
+        <v>0.9663</v>
       </c>
       <c r="P27" s="5" t="n">
-        <v>0.9711</v>
+        <v>0.9635</v>
       </c>
       <c r="Q27" s="6" t="inlineStr"/>
       <c r="R27" s="6" t="inlineStr"/>
@@ -2566,12 +2510,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GSWF1B1</t>
+          <t>HALLWF2</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Goyder South Wind Farm 1B</t>
+          <t>Hallett 2 Wind Farm</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2596,21 +2540,25 @@
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>203</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="n">
+        <v>0.0914</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>0.1053</v>
+      </c>
       <c r="L28" s="5" t="inlineStr"/>
       <c r="M28" s="5" t="inlineStr"/>
       <c r="N28" s="5" t="n">
-        <v>0.9641</v>
+        <v>0.9526</v>
       </c>
       <c r="O28" s="5" t="n">
-        <v>0.9689</v>
+        <v>0.9608</v>
       </c>
       <c r="P28" s="5" t="n">
-        <v>0.971</v>
+        <v>0.962</v>
       </c>
       <c r="Q28" s="6" t="inlineStr"/>
       <c r="R28" s="6" t="inlineStr"/>
@@ -2624,12 +2572,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>HALLWF1</t>
+          <t>HDWF1</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Hallett 1 Wind Farm</t>
+          <t>Hornsdale Wind Farm</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2654,25 +2602,25 @@
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>94.5</v>
+        <v>102.4</v>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="5" t="n">
-        <v>0.0813</v>
+        <v>0.0092</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>0.1169</v>
+        <v>0.0033</v>
       </c>
       <c r="L29" s="5" t="inlineStr"/>
       <c r="M29" s="5" t="inlineStr"/>
       <c r="N29" s="5" t="n">
-        <v>0.9565</v>
+        <v>0.9423</v>
       </c>
       <c r="O29" s="5" t="n">
-        <v>0.9663</v>
+        <v>0.956</v>
       </c>
       <c r="P29" s="5" t="n">
-        <v>0.9635</v>
+        <v>0.9538</v>
       </c>
       <c r="Q29" s="6" t="inlineStr"/>
       <c r="R29" s="6" t="inlineStr"/>
@@ -2686,12 +2634,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>HALLWF2</t>
+          <t>HDWF2</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Hallett 2 Wind Farm</t>
+          <t>Hornsdale Wind Farm 2</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2716,25 +2664,25 @@
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>71.40000000000001</v>
+        <v>102.4</v>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="5" t="n">
-        <v>0.0914</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>0.1053</v>
+        <v>0.0038</v>
       </c>
       <c r="L30" s="5" t="inlineStr"/>
       <c r="M30" s="5" t="inlineStr"/>
       <c r="N30" s="5" t="n">
-        <v>0.9526</v>
+        <v>0.9423</v>
       </c>
       <c r="O30" s="5" t="n">
-        <v>0.9608</v>
+        <v>0.956</v>
       </c>
       <c r="P30" s="5" t="n">
-        <v>0.962</v>
+        <v>0.9538</v>
       </c>
       <c r="Q30" s="6" t="inlineStr"/>
       <c r="R30" s="6" t="inlineStr"/>
@@ -2748,12 +2696,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>HDWF1</t>
+          <t>HDWF3</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Hornsdale Wind Farm</t>
+          <t>Hornsdale Wind Farm 3</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2778,14 +2726,14 @@
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>102.4</v>
+        <v>112</v>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="5" t="n">
         <v>0.0092</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0027</v>
       </c>
       <c r="L31" s="5" t="inlineStr"/>
       <c r="M31" s="5" t="inlineStr"/>
@@ -2810,12 +2758,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>HDWF2</t>
+          <t>LKBONNY2</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Hornsdale Wind Farm 2</t>
+          <t>Lake Bonney Stage 2 Windfarm</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2840,25 +2788,25 @@
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>102.4</v>
+        <v>159</v>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.1058</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.1941</v>
       </c>
       <c r="L32" s="5" t="inlineStr"/>
       <c r="M32" s="5" t="inlineStr"/>
       <c r="N32" s="5" t="n">
-        <v>0.9423</v>
+        <v>0.9709</v>
       </c>
       <c r="O32" s="5" t="n">
-        <v>0.956</v>
+        <v>0.9297</v>
       </c>
       <c r="P32" s="5" t="n">
-        <v>0.9538</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="Q32" s="6" t="inlineStr"/>
       <c r="R32" s="6" t="inlineStr"/>
@@ -2872,12 +2820,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>HDWF3</t>
+          <t>LKBONNY3</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Hornsdale Wind Farm 3</t>
+          <t>Lake Bonney Stage 3 Wind Farm</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2902,25 +2850,25 @@
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>112</v>
+        <v>39</v>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="5" t="n">
-        <v>0.0092</v>
+        <v>0.1939</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>0.0027</v>
+        <v>0.2514</v>
       </c>
       <c r="L33" s="5" t="inlineStr"/>
       <c r="M33" s="5" t="inlineStr"/>
       <c r="N33" s="5" t="n">
-        <v>0.9423</v>
+        <v>0.9709</v>
       </c>
       <c r="O33" s="5" t="n">
-        <v>0.956</v>
+        <v>0.9297</v>
       </c>
       <c r="P33" s="5" t="n">
-        <v>0.9538</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="Q33" s="6" t="inlineStr"/>
       <c r="R33" s="6" t="inlineStr"/>
@@ -2934,12 +2882,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>LKBONNY2</t>
+          <t>LKBONNY1</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Lake Bonney Stage 2 Windfarm</t>
+          <t>Lake Bonney Wind Farm Stage 1</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2964,14 +2912,14 @@
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>159</v>
+        <v>80.5</v>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="5" t="n">
-        <v>0.1058</v>
+        <v>0.1878</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>0.1941</v>
+        <v>0.2535</v>
       </c>
       <c r="L34" s="5" t="inlineStr"/>
       <c r="M34" s="5" t="inlineStr"/>
@@ -2996,12 +2944,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>LKBONNY3</t>
+          <t>LGAPWF1</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Lake Bonney Stage 3 Wind Farm</t>
+          <t>Lincoln Gap Wind Farm</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3026,25 +2974,25 @@
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>39</v>
+        <v>126</v>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="5" t="n">
-        <v>0.1939</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>0.2514</v>
+        <v>0.1438</v>
       </c>
       <c r="L35" s="5" t="inlineStr"/>
       <c r="M35" s="5" t="inlineStr"/>
       <c r="N35" s="5" t="n">
-        <v>0.9709</v>
+        <v>0.9576</v>
       </c>
       <c r="O35" s="5" t="n">
-        <v>0.9297</v>
+        <v>0.9689</v>
       </c>
       <c r="P35" s="5" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="Q35" s="6" t="inlineStr"/>
       <c r="R35" s="6" t="inlineStr"/>
@@ -3058,12 +3006,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>LKBONNY1</t>
+          <t>LGAPWF2</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Lake Bonney Wind Farm Stage 1</t>
+          <t>Lincoln Gap Wind Farm</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3088,25 +3036,25 @@
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>80.5</v>
+        <v>86</v>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="5" t="n">
-        <v>0.1878</v>
+        <v>0.1085</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>0.2535</v>
+        <v>0.1628</v>
       </c>
       <c r="L36" s="5" t="inlineStr"/>
       <c r="M36" s="5" t="inlineStr"/>
       <c r="N36" s="5" t="n">
-        <v>0.9709</v>
+        <v>0.9576</v>
       </c>
       <c r="O36" s="5" t="n">
-        <v>0.9297</v>
+        <v>0.9689</v>
       </c>
       <c r="P36" s="5" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="Q36" s="6" t="inlineStr"/>
       <c r="R36" s="6" t="inlineStr"/>
@@ -3120,12 +3068,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>LGAPWF1</t>
+          <t>MTMILLAR</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Lincoln Gap Wind Farm</t>
+          <t>Mt Millar Wind Farm</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3150,25 +3098,25 @@
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="5" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.1885</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>0.1438</v>
+        <v>0.287</v>
       </c>
       <c r="L37" s="5" t="inlineStr"/>
       <c r="M37" s="5" t="inlineStr"/>
       <c r="N37" s="5" t="n">
-        <v>0.9576</v>
+        <v>0.9162</v>
       </c>
       <c r="O37" s="5" t="n">
-        <v>0.9689</v>
+        <v>0.9403</v>
       </c>
       <c r="P37" s="5" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.9379</v>
       </c>
       <c r="Q37" s="6" t="inlineStr"/>
       <c r="R37" s="6" t="inlineStr"/>
@@ -3182,12 +3130,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>LGAPWF2</t>
+          <t>NBHWF1</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Lincoln Gap Wind Farm</t>
+          <t>North Brown Hill Wind Farm</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3212,25 +3160,25 @@
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>86</v>
+        <v>132.3</v>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="5" t="n">
-        <v>0.1085</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>0.1628</v>
+        <v>0.1193</v>
       </c>
       <c r="L38" s="5" t="inlineStr"/>
       <c r="M38" s="5" t="inlineStr"/>
       <c r="N38" s="5" t="n">
-        <v>0.9576</v>
+        <v>0.9467</v>
       </c>
       <c r="O38" s="5" t="n">
-        <v>0.9689</v>
+        <v>0.9579</v>
       </c>
       <c r="P38" s="5" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.9583</v>
       </c>
       <c r="Q38" s="6" t="inlineStr"/>
       <c r="R38" s="6" t="inlineStr"/>
@@ -3244,12 +3192,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>MTMILLAR</t>
+          <t>PAREPW1</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Mt Millar Wind Farm</t>
+          <t>Port Augusta Renewable Energy Park</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3274,25 +3222,25 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>70</v>
+        <v>210</v>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="5" t="n">
-        <v>0.1885</v>
+        <v>0.0914</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>0.287</v>
+        <v>0.1943</v>
       </c>
       <c r="L39" s="5" t="inlineStr"/>
       <c r="M39" s="5" t="inlineStr"/>
       <c r="N39" s="5" t="n">
-        <v>0.9162</v>
+        <v>0.9608</v>
       </c>
       <c r="O39" s="5" t="n">
-        <v>0.9403</v>
+        <v>0.9735</v>
       </c>
       <c r="P39" s="5" t="n">
-        <v>0.9379</v>
+        <v>0.9709</v>
       </c>
       <c r="Q39" s="6" t="inlineStr"/>
       <c r="R39" s="6" t="inlineStr"/>
@@ -3306,12 +3254,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>NBHWF1</t>
+          <t>SNOWSTH1</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>North Brown Hill Wind Farm</t>
+          <t>Snowtown South Wind Farm</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3336,25 +3284,25 @@
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>132.3</v>
+        <v>126</v>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="5" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.0071</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>0.1193</v>
+        <v>0.0037</v>
       </c>
       <c r="L40" s="5" t="inlineStr"/>
       <c r="M40" s="5" t="inlineStr"/>
       <c r="N40" s="5" t="n">
-        <v>0.9467</v>
+        <v>0.9613</v>
       </c>
       <c r="O40" s="5" t="n">
-        <v>0.9579</v>
+        <v>0.9695</v>
       </c>
       <c r="P40" s="5" t="n">
-        <v>0.9583</v>
+        <v>0.9694</v>
       </c>
       <c r="Q40" s="6" t="inlineStr"/>
       <c r="R40" s="6" t="inlineStr"/>
@@ -3368,12 +3316,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>PAREPW1</t>
+          <t>SNOWNTH1</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Port Augusta Renewable Energy Park</t>
+          <t>Snowtown Wind Farm Stage 2 North</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3398,25 +3346,25 @@
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>210</v>
+        <v>144</v>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="5" t="n">
-        <v>0.0914</v>
+        <v>0.0101</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>0.1943</v>
+        <v>0.0026</v>
       </c>
       <c r="L41" s="5" t="inlineStr"/>
       <c r="M41" s="5" t="inlineStr"/>
       <c r="N41" s="5" t="n">
-        <v>0.9608</v>
+        <v>0.9613</v>
       </c>
       <c r="O41" s="5" t="n">
-        <v>0.9735</v>
+        <v>0.9695</v>
       </c>
       <c r="P41" s="5" t="n">
-        <v>0.9709</v>
+        <v>0.9694</v>
       </c>
       <c r="Q41" s="6" t="inlineStr"/>
       <c r="R41" s="6" t="inlineStr"/>
@@ -3430,12 +3378,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>SNOWSTH1</t>
+          <t>SNOWTWN1</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Snowtown South Wind Farm</t>
+          <t>Snowtown Wind Farm Units 1 And 47</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3460,25 +3408,25 @@
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.1075</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>0.0037</v>
+        <v>0.1825</v>
       </c>
       <c r="L42" s="5" t="inlineStr"/>
       <c r="M42" s="5" t="inlineStr"/>
       <c r="N42" s="5" t="n">
-        <v>0.9613</v>
+        <v>0.8932</v>
       </c>
       <c r="O42" s="5" t="n">
-        <v>0.9695</v>
+        <v>0.9157</v>
       </c>
       <c r="P42" s="5" t="n">
-        <v>0.9694</v>
+        <v>0.9112</v>
       </c>
       <c r="Q42" s="6" t="inlineStr"/>
       <c r="R42" s="6" t="inlineStr"/>
@@ -3492,12 +3440,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>SNOWNTH1</t>
+          <t>STARHLWF</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Snowtown Wind Farm Stage 2 North</t>
+          <t>Starfish Hill Wind Farm</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3522,25 +3470,25 @@
         </is>
       </c>
       <c r="H43" s="4" t="n">
-        <v>144</v>
+        <v>34.5</v>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="5" t="n">
-        <v>0.0101</v>
+        <v>0</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>0.0026</v>
+        <v>0</v>
       </c>
       <c r="L43" s="5" t="inlineStr"/>
       <c r="M43" s="5" t="inlineStr"/>
       <c r="N43" s="5" t="n">
-        <v>0.9613</v>
+        <v>1.0025</v>
       </c>
       <c r="O43" s="5" t="n">
-        <v>0.9695</v>
+        <v>1.0037</v>
       </c>
       <c r="P43" s="5" t="n">
-        <v>0.9694</v>
+        <v>1.0034</v>
       </c>
       <c r="Q43" s="6" t="inlineStr"/>
       <c r="R43" s="6" t="inlineStr"/>
@@ -3554,12 +3502,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>SNOWTWN1</t>
+          <t>BLUFF1</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Snowtown Wind Farm Units 1 And 47</t>
+          <t>The Bluff Wind Farm</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3584,25 +3532,25 @@
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>99</v>
+        <v>52.5</v>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="5" t="n">
-        <v>0.1075</v>
+        <v>0.1016</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>0.1825</v>
+        <v>0.0847</v>
       </c>
       <c r="L44" s="5" t="inlineStr"/>
       <c r="M44" s="5" t="inlineStr"/>
       <c r="N44" s="5" t="n">
-        <v>0.8932</v>
+        <v>0.9467</v>
       </c>
       <c r="O44" s="5" t="n">
-        <v>0.9157</v>
+        <v>0.9579</v>
       </c>
       <c r="P44" s="5" t="n">
-        <v>0.9112</v>
+        <v>0.9583</v>
       </c>
       <c r="Q44" s="6" t="inlineStr"/>
       <c r="R44" s="6" t="inlineStr"/>
@@ -3616,12 +3564,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>STARHLWF</t>
+          <t>WATERLWF</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Starfish Hill Wind Farm</t>
+          <t>Waterloo Wind Farm</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3646,25 +3594,25 @@
         </is>
       </c>
       <c r="H45" s="4" t="n">
-        <v>34.5</v>
+        <v>130.8</v>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="5" t="n">
-        <v>0</v>
+        <v>0.0239</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>0</v>
+        <v>0.0203</v>
       </c>
       <c r="L45" s="5" t="inlineStr"/>
       <c r="M45" s="5" t="inlineStr"/>
       <c r="N45" s="5" t="n">
-        <v>1.0025</v>
+        <v>0.9547</v>
       </c>
       <c r="O45" s="5" t="n">
-        <v>1.0037</v>
+        <v>0.9624</v>
       </c>
       <c r="P45" s="5" t="n">
-        <v>1.0034</v>
+        <v>0.9611</v>
       </c>
       <c r="Q45" s="6" t="inlineStr"/>
       <c r="R45" s="6" t="inlineStr"/>
@@ -3678,12 +3626,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>BLUFF1</t>
+          <t>WPWF</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>The Bluff Wind Farm</t>
+          <t>Wattle Point Wind Farm</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3708,25 +3656,25 @@
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>52.5</v>
+        <v>90.75</v>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="5" t="n">
-        <v>0.1016</v>
+        <v>0.0871</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>0.0847</v>
+        <v>0.1598</v>
       </c>
       <c r="L46" s="5" t="inlineStr"/>
       <c r="M46" s="5" t="inlineStr"/>
       <c r="N46" s="5" t="n">
-        <v>0.9467</v>
+        <v>0.8179</v>
       </c>
       <c r="O46" s="5" t="n">
-        <v>0.9579</v>
+        <v>0.8456</v>
       </c>
       <c r="P46" s="5" t="n">
-        <v>0.9583</v>
+        <v>0.844</v>
       </c>
       <c r="Q46" s="6" t="inlineStr"/>
       <c r="R46" s="6" t="inlineStr"/>
@@ -3740,12 +3688,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>WATERLWF</t>
+          <t>WGWF1</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Waterloo Wind Farm</t>
+          <t>Willogoleche Wind Farm</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3770,25 +3718,25 @@
         </is>
       </c>
       <c r="H47" s="4" t="n">
-        <v>130.8</v>
+        <v>122</v>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="5" t="n">
-        <v>0.0239</v>
+        <v>0.0941</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>0.0203</v>
+        <v>0.0426</v>
       </c>
       <c r="L47" s="5" t="inlineStr"/>
       <c r="M47" s="5" t="inlineStr"/>
       <c r="N47" s="5" t="n">
-        <v>0.9547</v>
+        <v>0.9498</v>
       </c>
       <c r="O47" s="5" t="n">
-        <v>0.9624</v>
+        <v>0.9601</v>
       </c>
       <c r="P47" s="5" t="n">
-        <v>0.9611</v>
+        <v>0.9605</v>
       </c>
       <c r="Q47" s="6" t="inlineStr"/>
       <c r="R47" s="6" t="inlineStr"/>
@@ -3798,130 +3746,6 @@
       <c r="V47" s="6" t="inlineStr"/>
       <c r="W47" s="6" t="inlineStr"/>
       <c r="X47" s="6" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>WPWF</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>Wattle Point Wind Farm</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Wind</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr"/>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="n">
-        <v>90.75</v>
-      </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="5" t="n">
-        <v>0.0871</v>
-      </c>
-      <c r="K48" s="5" t="n">
-        <v>0.1598</v>
-      </c>
-      <c r="L48" s="5" t="inlineStr"/>
-      <c r="M48" s="5" t="inlineStr"/>
-      <c r="N48" s="5" t="n">
-        <v>0.8179</v>
-      </c>
-      <c r="O48" s="5" t="n">
-        <v>0.8456</v>
-      </c>
-      <c r="P48" s="5" t="n">
-        <v>0.844</v>
-      </c>
-      <c r="Q48" s="6" t="inlineStr"/>
-      <c r="R48" s="6" t="inlineStr"/>
-      <c r="S48" s="6" t="inlineStr"/>
-      <c r="T48" s="6" t="inlineStr"/>
-      <c r="U48" s="6" t="inlineStr"/>
-      <c r="V48" s="6" t="inlineStr"/>
-      <c r="W48" s="6" t="inlineStr"/>
-      <c r="X48" s="6" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>WGWF1</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>Willogoleche Wind Farm</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Wind</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr"/>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="H49" s="4" t="n">
-        <v>122</v>
-      </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="5" t="n">
-        <v>0.0941</v>
-      </c>
-      <c r="K49" s="5" t="n">
-        <v>0.0426</v>
-      </c>
-      <c r="L49" s="5" t="inlineStr"/>
-      <c r="M49" s="5" t="inlineStr"/>
-      <c r="N49" s="5" t="n">
-        <v>0.9498</v>
-      </c>
-      <c r="O49" s="5" t="n">
-        <v>0.9601</v>
-      </c>
-      <c r="P49" s="5" t="n">
-        <v>0.9605</v>
-      </c>
-      <c r="Q49" s="6" t="inlineStr"/>
-      <c r="R49" s="6" t="inlineStr"/>
-      <c r="S49" s="6" t="inlineStr"/>
-      <c r="T49" s="6" t="inlineStr"/>
-      <c r="U49" s="6" t="inlineStr"/>
-      <c r="V49" s="6" t="inlineStr"/>
-      <c r="W49" s="6" t="inlineStr"/>
-      <c r="X49" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3934,7 +3758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W49"/>
+  <dimension ref="A1:W47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4798,7 +4622,7 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>MAPS2PV1</t>
+          <t>MAPS3PV1</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
@@ -4807,20 +4631,18 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0.9926</v>
+        <v>0.9802</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>1.0257</v>
+        <v>1.0252</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>1.0132</v>
+        <v>1.0135</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.2199</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>0.2007</v>
-      </c>
+        <v>0.2291</v>
+      </c>
+      <c r="G12" s="5" t="inlineStr"/>
       <c r="H12" s="5" t="n">
         <v>0.510590381447813</v>
       </c>
@@ -4885,7 +4707,7 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>MAPS3PV1</t>
+          <t>MANNSF2</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -4894,18 +4716,18 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.9802</v>
+        <v>0.9937</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1.0252</v>
+        <v>0.9932</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1.0135</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>0.2291</v>
-      </c>
-      <c r="G13" s="5" t="inlineStr"/>
+        <v>0.9955000000000001</v>
+      </c>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="n">
+        <v>0.3012</v>
+      </c>
       <c r="H13" s="5" t="n">
         <v>0.510590381447813</v>
       </c>
@@ -4940,7 +4762,7 @@
         <v>0</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="R13" s="5" t="inlineStr">
         <is>
@@ -4948,7 +4770,7 @@
         </is>
       </c>
       <c r="S13" s="5" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="T13" s="5" t="inlineStr">
         <is>
@@ -4956,7 +4778,7 @@
         </is>
       </c>
       <c r="U13" s="5" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="V13" s="5" t="inlineStr">
         <is>
@@ -4964,13 +4786,13 @@
         </is>
       </c>
       <c r="W13" s="5" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>MANNSF2</t>
+          <t>MWPS1PV1</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
@@ -4979,23 +4801,25 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0.9937</v>
+        <v>0.9759</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>0.9932</v>
+        <v>1.0146</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.9955000000000001</v>
-      </c>
-      <c r="F14" s="5" t="inlineStr"/>
+        <v>0.966</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>0.1286</v>
+      </c>
       <c r="G14" s="5" t="n">
-        <v>0.3012</v>
+        <v>0.2462</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>0.510590381447813</v>
+        <v>0.65425629128861</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0.225784053085401</v>
+        <v>0.512670422089759</v>
       </c>
       <c r="J14" s="5" t="n">
         <v>0</v>
@@ -5055,7 +4879,7 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>MWPS1PV1</t>
+          <t>MWPS2PV1</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
@@ -5064,19 +4888,19 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0.9759</v>
+        <v>0.9766</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1.0146</v>
+        <v>1.003</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.966</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.1286</v>
+        <v>0.1131</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.2462</v>
+        <v>0.2411</v>
       </c>
       <c r="H15" s="5" t="n">
         <v>0.65425629128861</v>
@@ -5142,7 +4966,7 @@
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>MWPS2PV1</t>
+          <t>MWPS3PV1</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -5151,19 +4975,19 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
+        <v>0.9787</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.9897</v>
+      </c>
+      <c r="E16" s="5" t="n">
         <v>0.9766</v>
       </c>
-      <c r="D16" s="5" t="n">
-        <v>1.003</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>0.9723000000000001</v>
-      </c>
       <c r="F16" s="5" t="n">
-        <v>0.1131</v>
+        <v>0.0897</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.2411</v>
+        <v>0.1273</v>
       </c>
       <c r="H16" s="5" t="n">
         <v>0.65425629128861</v>
@@ -5229,7 +5053,7 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>MWPS3PV1</t>
+          <t>MWPS4PV1</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -5238,19 +5062,19 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>0.9787</v>
+        <v>0.9751</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0.9897</v>
+        <v>0.9837</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.9766</v>
+        <v>0.9781</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.0897</v>
+        <v>0.1184</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.1273</v>
+        <v>0.2031</v>
       </c>
       <c r="H17" s="5" t="n">
         <v>0.65425629128861</v>
@@ -5316,7 +5140,7 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>MWPS4PV1</t>
+          <t>MBPS2PV1</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -5325,25 +5149,25 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.9751</v>
+        <v>0.9993</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>0.9837</v>
+        <v>1.0127</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.9781</v>
+        <v>1.0106</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.1184</v>
+        <v>0.2268</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.2031</v>
+        <v>0.2284</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>0.65425629128861</v>
+        <v>0.510590381447813</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>0.512670422089759</v>
+        <v>0.225784053085401</v>
       </c>
       <c r="J18" s="5" t="n">
         <v>0</v>
@@ -5373,7 +5197,7 @@
         <v>0</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
@@ -5381,7 +5205,7 @@
         </is>
       </c>
       <c r="S18" s="5" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="T18" s="5" t="inlineStr">
         <is>
@@ -5389,7 +5213,7 @@
         </is>
       </c>
       <c r="U18" s="5" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="V18" s="5" t="inlineStr">
         <is>
@@ -5397,13 +5221,13 @@
         </is>
       </c>
       <c r="W18" s="5" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>MBPS2PV1</t>
+          <t>PAREPS1</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -5412,25 +5236,25 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>0.9993</v>
+        <v>0.9608</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1.0127</v>
+        <v>0.9735</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1.0106</v>
+        <v>0.9709</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.2268</v>
+        <v>0.1842</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.2284</v>
+        <v>0.3589</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>0.510590381447813</v>
+        <v>0.501077617843089</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>0.225784053085401</v>
+        <v>0.212860651220515</v>
       </c>
       <c r="J19" s="5" t="n">
         <v>0</v>
@@ -5460,7 +5284,7 @@
         <v>0</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R19" s="5" t="inlineStr">
         <is>
@@ -5468,7 +5292,7 @@
         </is>
       </c>
       <c r="S19" s="5" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="T19" s="5" t="inlineStr">
         <is>
@@ -5476,7 +5300,7 @@
         </is>
       </c>
       <c r="U19" s="5" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V19" s="5" t="inlineStr">
         <is>
@@ -5484,13 +5308,13 @@
         </is>
       </c>
       <c r="W19" s="5" t="n">
-        <v>0</v>
+        <v>0.07333333333333335</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>MBPS2PV1</t>
+          <t>TB2SF1</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -5499,85 +5323,69 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>0.9993</v>
+        <v>1.0102</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>1.0127</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>1.0106</v>
+        <v>0.9963</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.2268</v>
+        <v>0.1987</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.2284</v>
+        <v>0.2973</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>0.510590381447813</v>
+        <v>0.511370986967519</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>0.225784053085401</v>
-      </c>
-      <c r="J20" s="5" t="n">
-        <v>0</v>
-      </c>
+        <v>0.22945882760626</v>
+      </c>
+      <c r="J20" s="5" t="inlineStr"/>
       <c r="K20" s="5" t="inlineStr">
         <is>
           <t>25-26</t>
         </is>
       </c>
-      <c r="L20" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="L20" s="5" t="inlineStr"/>
       <c r="M20" s="5" t="inlineStr">
         <is>
           <t>26-27</t>
         </is>
       </c>
-      <c r="N20" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N20" s="5" t="inlineStr"/>
       <c r="O20" s="5" t="inlineStr">
         <is>
           <t>27-28</t>
         </is>
       </c>
-      <c r="P20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="P20" s="5" t="inlineStr"/>
+      <c r="Q20" s="5" t="inlineStr"/>
       <c r="R20" s="5" t="inlineStr">
         <is>
           <t>25-26</t>
         </is>
       </c>
-      <c r="S20" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="S20" s="5" t="inlineStr"/>
       <c r="T20" s="5" t="inlineStr">
         <is>
           <t>26-27</t>
         </is>
       </c>
-      <c r="U20" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="U20" s="5" t="inlineStr"/>
       <c r="V20" s="5" t="inlineStr">
         <is>
           <t>27-28</t>
         </is>
       </c>
-      <c r="W20" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="W20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>PAREPS1</t>
+          <t>TBSF1</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -5586,113 +5394,93 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0.9608</v>
+        <v>1.009</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>0.9735</v>
+        <v>0.9952</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0.9709</v>
+        <v>0.9967</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.1842</v>
+        <v>0.2394</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.3589</v>
+        <v>0.3511</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>0.501077617843089</v>
+        <v>0.511370986967519</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>0.212860651220515</v>
-      </c>
-      <c r="J21" s="5" t="n">
-        <v>0</v>
-      </c>
+        <v>0.22945882760626</v>
+      </c>
+      <c r="J21" s="5" t="inlineStr"/>
       <c r="K21" s="5" t="inlineStr">
         <is>
           <t>25-26</t>
         </is>
       </c>
-      <c r="L21" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="L21" s="5" t="inlineStr"/>
       <c r="M21" s="5" t="inlineStr">
         <is>
           <t>26-27</t>
         </is>
       </c>
-      <c r="N21" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N21" s="5" t="inlineStr"/>
       <c r="O21" s="5" t="inlineStr">
         <is>
           <t>27-28</t>
         </is>
       </c>
-      <c r="P21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
+      <c r="P21" s="5" t="inlineStr"/>
+      <c r="Q21" s="5" t="inlineStr"/>
       <c r="R21" s="5" t="inlineStr">
         <is>
           <t>25-26</t>
         </is>
       </c>
-      <c r="S21" s="5" t="n">
-        <v>0.08</v>
-      </c>
+      <c r="S21" s="5" t="inlineStr"/>
       <c r="T21" s="5" t="inlineStr">
         <is>
           <t>26-27</t>
         </is>
       </c>
-      <c r="U21" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
+      <c r="U21" s="5" t="inlineStr"/>
       <c r="V21" s="5" t="inlineStr">
         <is>
           <t>27-28</t>
         </is>
       </c>
-      <c r="W21" s="5" t="n">
-        <v>0.07333333333333335</v>
-      </c>
+      <c r="W21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>TB2SF1</t>
+          <t>CNUNDAWF</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>1.0102</v>
+        <v>0.9755</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>0.9945000000000001</v>
+        <v>0.9333</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.9963</v>
+        <v>0.9458</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.1987</v>
+        <v>0.1746</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.2973</v>
-      </c>
-      <c r="H22" s="5" t="n">
-        <v>0.511370986967519</v>
-      </c>
-      <c r="I22" s="5" t="n">
-        <v>0.22945882760626</v>
-      </c>
+        <v>0.254</v>
+      </c>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
       <c r="J22" s="5" t="inlineStr"/>
       <c r="K22" s="5" t="inlineStr">
         <is>
@@ -5735,35 +5523,31 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>TBSF1</t>
+          <t>CATHROCK</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>1.009</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>0.9952</v>
+        <v>0.9467</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0.9967</v>
+        <v>0.9408</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.2394</v>
+        <v>0.1389</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.3511</v>
-      </c>
-      <c r="H23" s="5" t="n">
-        <v>0.511370986967519</v>
-      </c>
-      <c r="I23" s="5" t="n">
-        <v>0.22945882760626</v>
-      </c>
+        <v>0.0515</v>
+      </c>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
       <c r="J23" s="5" t="inlineStr"/>
       <c r="K23" s="5" t="inlineStr">
         <is>
@@ -5806,7 +5590,7 @@
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>CNUNDAWF</t>
+          <t>CLEMGPWF</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -5815,19 +5599,19 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>0.9755</v>
+        <v>0.9486</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>0.9333</v>
+        <v>0.9604</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0.9458</v>
+        <v>0.9605</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.1746</v>
+        <v>0.0134</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.254</v>
+        <v>0.0062</v>
       </c>
       <c r="H24" s="5" t="inlineStr"/>
       <c r="I24" s="5" t="inlineStr"/>
@@ -5873,7 +5657,7 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>CATHROCK</t>
+          <t>GSWF1A</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -5882,19 +5666,17 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>0.9308999999999999</v>
+        <v>0.9643</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>0.9467</v>
+        <v>0.9697</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0.9408</v>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>0.1389</v>
-      </c>
+        <v>0.9711</v>
+      </c>
+      <c r="F25" s="5" t="inlineStr"/>
       <c r="G25" s="5" t="n">
-        <v>0.0515</v>
+        <v>0.176</v>
       </c>
       <c r="H25" s="5" t="inlineStr"/>
       <c r="I25" s="5" t="inlineStr"/>
@@ -5940,7 +5722,7 @@
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>CLEMGPWF</t>
+          <t>GSWF1B1</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -5949,20 +5731,16 @@
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>0.9486</v>
+        <v>0.9641</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>0.9604</v>
+        <v>0.9689</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>0.9605</v>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>0.0134</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>0.0062</v>
-      </c>
+        <v>0.971</v>
+      </c>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
       <c r="H26" s="5" t="inlineStr"/>
       <c r="I26" s="5" t="inlineStr"/>
       <c r="J26" s="5" t="inlineStr"/>
@@ -6007,7 +5785,7 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>GSWF1A</t>
+          <t>HALLWF1</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -6016,17 +5794,19 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>0.9643</v>
+        <v>0.9565</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>0.9697</v>
+        <v>0.9663</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>0.9711</v>
-      </c>
-      <c r="F27" s="5" t="inlineStr"/>
+        <v>0.9635</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>0.0813</v>
+      </c>
       <c r="G27" s="5" t="n">
-        <v>0.176</v>
+        <v>0.1169</v>
       </c>
       <c r="H27" s="5" t="inlineStr"/>
       <c r="I27" s="5" t="inlineStr"/>
@@ -6072,7 +5852,7 @@
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>GSWF1B1</t>
+          <t>HALLWF2</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -6081,16 +5861,20 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>0.9641</v>
+        <v>0.9526</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>0.9689</v>
+        <v>0.9608</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0.971</v>
-      </c>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
+        <v>0.962</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0.0914</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0.1053</v>
+      </c>
       <c r="H28" s="5" t="inlineStr"/>
       <c r="I28" s="5" t="inlineStr"/>
       <c r="J28" s="5" t="inlineStr"/>
@@ -6135,7 +5919,7 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>HALLWF1</t>
+          <t>HDWF1</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -6144,19 +5928,19 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>0.9565</v>
+        <v>0.9423</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>0.9663</v>
+        <v>0.956</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0.9635</v>
+        <v>0.9538</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0.0813</v>
+        <v>0.0092</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.1169</v>
+        <v>0.0033</v>
       </c>
       <c r="H29" s="5" t="inlineStr"/>
       <c r="I29" s="5" t="inlineStr"/>
@@ -6202,7 +5986,7 @@
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>HALLWF2</t>
+          <t>HDWF2</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -6211,19 +5995,19 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>0.9526</v>
+        <v>0.9423</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>0.9608</v>
+        <v>0.956</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0.962</v>
+        <v>0.9538</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.0914</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.1053</v>
+        <v>0.0038</v>
       </c>
       <c r="H30" s="5" t="inlineStr"/>
       <c r="I30" s="5" t="inlineStr"/>
@@ -6269,7 +6053,7 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>HDWF1</t>
+          <t>HDWF3</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -6290,7 +6074,7 @@
         <v>0.0092</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0027</v>
       </c>
       <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="5" t="inlineStr"/>
@@ -6336,7 +6120,7 @@
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>HDWF2</t>
+          <t>LKBONNY2</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -6345,19 +6129,19 @@
         </is>
       </c>
       <c r="C32" s="5" t="n">
-        <v>0.9423</v>
+        <v>0.9709</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>0.956</v>
+        <v>0.9297</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>0.9538</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.1058</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.1941</v>
       </c>
       <c r="H32" s="5" t="inlineStr"/>
       <c r="I32" s="5" t="inlineStr"/>
@@ -6403,7 +6187,7 @@
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>HDWF3</t>
+          <t>LKBONNY3</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -6412,19 +6196,19 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>0.9423</v>
+        <v>0.9709</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>0.956</v>
+        <v>0.9297</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0.9538</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>0.0092</v>
+        <v>0.1939</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0027</v>
+        <v>0.2514</v>
       </c>
       <c r="H33" s="5" t="inlineStr"/>
       <c r="I33" s="5" t="inlineStr"/>
@@ -6470,7 +6254,7 @@
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>LKBONNY2</t>
+          <t>LKBONNY1</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -6488,10 +6272,10 @@
         <v>0.9389999999999999</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.1058</v>
+        <v>0.1878</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.1941</v>
+        <v>0.2535</v>
       </c>
       <c r="H34" s="5" t="inlineStr"/>
       <c r="I34" s="5" t="inlineStr"/>
@@ -6537,7 +6321,7 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>LKBONNY3</t>
+          <t>LGAPWF1</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -6546,19 +6330,19 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>0.9709</v>
+        <v>0.9576</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>0.9297</v>
+        <v>0.9689</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>0.1939</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.2514</v>
+        <v>0.1438</v>
       </c>
       <c r="H35" s="5" t="inlineStr"/>
       <c r="I35" s="5" t="inlineStr"/>
@@ -6604,7 +6388,7 @@
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>LKBONNY1</t>
+          <t>LGAPWF2</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
@@ -6613,19 +6397,19 @@
         </is>
       </c>
       <c r="C36" s="5" t="n">
-        <v>0.9709</v>
+        <v>0.9576</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>0.9297</v>
+        <v>0.9689</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0.1878</v>
+        <v>0.1085</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.2535</v>
+        <v>0.1628</v>
       </c>
       <c r="H36" s="5" t="inlineStr"/>
       <c r="I36" s="5" t="inlineStr"/>
@@ -6671,7 +6455,7 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>LGAPWF1</t>
+          <t>MTMILLAR</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -6680,19 +6464,19 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>0.9576</v>
+        <v>0.9162</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>0.9689</v>
+        <v>0.9403</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.9379</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.1885</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.1438</v>
+        <v>0.287</v>
       </c>
       <c r="H37" s="5" t="inlineStr"/>
       <c r="I37" s="5" t="inlineStr"/>
@@ -6738,7 +6522,7 @@
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>LGAPWF2</t>
+          <t>NBHWF1</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
@@ -6747,19 +6531,19 @@
         </is>
       </c>
       <c r="C38" s="5" t="n">
-        <v>0.9576</v>
+        <v>0.9467</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>0.9689</v>
+        <v>0.9579</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.9583</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0.1085</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.1628</v>
+        <v>0.1193</v>
       </c>
       <c r="H38" s="5" t="inlineStr"/>
       <c r="I38" s="5" t="inlineStr"/>
@@ -6805,7 +6589,7 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>MTMILLAR</t>
+          <t>PAREPW1</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
@@ -6814,19 +6598,19 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>0.9162</v>
+        <v>0.9608</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>0.9403</v>
+        <v>0.9735</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>0.9379</v>
+        <v>0.9709</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>0.1885</v>
+        <v>0.0914</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.287</v>
+        <v>0.1943</v>
       </c>
       <c r="H39" s="5" t="inlineStr"/>
       <c r="I39" s="5" t="inlineStr"/>
@@ -6872,7 +6656,7 @@
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>NBHWF1</t>
+          <t>SNOWSTH1</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
@@ -6881,19 +6665,19 @@
         </is>
       </c>
       <c r="C40" s="5" t="n">
-        <v>0.9467</v>
+        <v>0.9613</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>0.9579</v>
+        <v>0.9695</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>0.9583</v>
+        <v>0.9694</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.0071</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.1193</v>
+        <v>0.0037</v>
       </c>
       <c r="H40" s="5" t="inlineStr"/>
       <c r="I40" s="5" t="inlineStr"/>
@@ -6939,7 +6723,7 @@
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>PAREPW1</t>
+          <t>SNOWNTH1</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
@@ -6948,19 +6732,19 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>0.9608</v>
+        <v>0.9613</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>0.9735</v>
+        <v>0.9695</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>0.9709</v>
+        <v>0.9694</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>0.0914</v>
+        <v>0.0101</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.1943</v>
+        <v>0.0026</v>
       </c>
       <c r="H41" s="5" t="inlineStr"/>
       <c r="I41" s="5" t="inlineStr"/>
@@ -7006,7 +6790,7 @@
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>SNOWSTH1</t>
+          <t>SNOWTWN1</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
@@ -7015,19 +6799,19 @@
         </is>
       </c>
       <c r="C42" s="5" t="n">
-        <v>0.9613</v>
+        <v>0.8932</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>0.9695</v>
+        <v>0.9157</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0.9694</v>
+        <v>0.9112</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.1075</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0037</v>
+        <v>0.1825</v>
       </c>
       <c r="H42" s="5" t="inlineStr"/>
       <c r="I42" s="5" t="inlineStr"/>
@@ -7073,7 +6857,7 @@
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>SNOWNTH1</t>
+          <t>STARHLWF</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
@@ -7082,19 +6866,19 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>0.9613</v>
+        <v>1.0025</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>0.9695</v>
+        <v>1.0037</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0.9694</v>
+        <v>1.0034</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>0.0101</v>
+        <v>0</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0026</v>
+        <v>0</v>
       </c>
       <c r="H43" s="5" t="inlineStr"/>
       <c r="I43" s="5" t="inlineStr"/>
@@ -7140,7 +6924,7 @@
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>SNOWTWN1</t>
+          <t>BLUFF1</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
@@ -7149,19 +6933,19 @@
         </is>
       </c>
       <c r="C44" s="5" t="n">
-        <v>0.8932</v>
+        <v>0.9467</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>0.9157</v>
+        <v>0.9579</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0.9112</v>
+        <v>0.9583</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.1075</v>
+        <v>0.1016</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.1825</v>
+        <v>0.0847</v>
       </c>
       <c r="H44" s="5" t="inlineStr"/>
       <c r="I44" s="5" t="inlineStr"/>
@@ -7207,7 +6991,7 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>STARHLWF</t>
+          <t>WATERLWF</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
@@ -7216,19 +7000,19 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>1.0025</v>
+        <v>0.9547</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>1.0037</v>
+        <v>0.9624</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>1.0034</v>
+        <v>0.9611</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>0</v>
+        <v>0.0239</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0</v>
+        <v>0.0203</v>
       </c>
       <c r="H45" s="5" t="inlineStr"/>
       <c r="I45" s="5" t="inlineStr"/>
@@ -7274,7 +7058,7 @@
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>BLUFF1</t>
+          <t>WPWF</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
@@ -7283,19 +7067,19 @@
         </is>
       </c>
       <c r="C46" s="5" t="n">
-        <v>0.9467</v>
+        <v>0.8179</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>0.9579</v>
+        <v>0.8456</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>0.9583</v>
+        <v>0.844</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.1016</v>
+        <v>0.0871</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0847</v>
+        <v>0.1598</v>
       </c>
       <c r="H46" s="5" t="inlineStr"/>
       <c r="I46" s="5" t="inlineStr"/>
@@ -7341,7 +7125,7 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>WATERLWF</t>
+          <t>WGWF1</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
@@ -7350,19 +7134,19 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>0.9547</v>
+        <v>0.9498</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>0.9624</v>
+        <v>0.9601</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0.9611</v>
+        <v>0.9605</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>0.0239</v>
+        <v>0.0941</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0203</v>
+        <v>0.0426</v>
       </c>
       <c r="H47" s="5" t="inlineStr"/>
       <c r="I47" s="5" t="inlineStr"/>
@@ -7405,142 +7189,8 @@
       </c>
       <c r="W47" s="5" t="inlineStr"/>
     </row>
-    <row r="48">
-      <c r="A48" s="8" t="inlineStr">
-        <is>
-          <t>WPWF</t>
-        </is>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>Wind</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="n">
-        <v>0.8179</v>
-      </c>
-      <c r="D48" s="5" t="n">
-        <v>0.8456</v>
-      </c>
-      <c r="E48" s="5" t="n">
-        <v>0.844</v>
-      </c>
-      <c r="F48" s="5" t="n">
-        <v>0.0871</v>
-      </c>
-      <c r="G48" s="5" t="n">
-        <v>0.1598</v>
-      </c>
-      <c r="H48" s="5" t="inlineStr"/>
-      <c r="I48" s="5" t="inlineStr"/>
-      <c r="J48" s="5" t="inlineStr"/>
-      <c r="K48" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L48" s="5" t="inlineStr"/>
-      <c r="M48" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N48" s="5" t="inlineStr"/>
-      <c r="O48" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P48" s="5" t="inlineStr"/>
-      <c r="Q48" s="5" t="inlineStr"/>
-      <c r="R48" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S48" s="5" t="inlineStr"/>
-      <c r="T48" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U48" s="5" t="inlineStr"/>
-      <c r="V48" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W48" s="5" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="8" t="inlineStr">
-        <is>
-          <t>WGWF1</t>
-        </is>
-      </c>
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>Wind</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="n">
-        <v>0.9498</v>
-      </c>
-      <c r="D49" s="5" t="n">
-        <v>0.9601</v>
-      </c>
-      <c r="E49" s="5" t="n">
-        <v>0.9605</v>
-      </c>
-      <c r="F49" s="5" t="n">
-        <v>0.0941</v>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>0.0426</v>
-      </c>
-      <c r="H49" s="5" t="inlineStr"/>
-      <c r="I49" s="5" t="inlineStr"/>
-      <c r="J49" s="5" t="inlineStr"/>
-      <c r="K49" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L49" s="5" t="inlineStr"/>
-      <c r="M49" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N49" s="5" t="inlineStr"/>
-      <c r="O49" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P49" s="5" t="inlineStr"/>
-      <c r="Q49" s="5" t="inlineStr"/>
-      <c r="R49" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S49" s="5" t="inlineStr"/>
-      <c r="T49" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U49" s="5" t="inlineStr"/>
-      <c r="V49" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W49" s="5" t="inlineStr"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C49">
+  <conditionalFormatting sqref="C2:C47">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -7552,7 +7202,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D49">
+  <conditionalFormatting sqref="D2:D47">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -7564,7 +7214,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E49">
+  <conditionalFormatting sqref="E2:E47">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -7576,7 +7226,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F49">
+  <conditionalFormatting sqref="F2:F47">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -7588,7 +7238,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G49">
+  <conditionalFormatting sqref="G2:G47">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -7600,7 +7250,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H49">
+  <conditionalFormatting sqref="H2:H47">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -7612,7 +7262,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I49">
+  <conditionalFormatting sqref="I2:I47">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -7624,7 +7274,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J49">
+  <conditionalFormatting sqref="J2:J47">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -7636,7 +7286,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K49">
+  <conditionalFormatting sqref="K2:K47">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -7648,7 +7298,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L49">
+  <conditionalFormatting sqref="L2:L47">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -7660,7 +7310,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M49">
+  <conditionalFormatting sqref="M2:M47">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -7672,7 +7322,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N49">
+  <conditionalFormatting sqref="N2:N47">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -7684,7 +7334,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O49">
+  <conditionalFormatting sqref="O2:O47">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -7696,7 +7346,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P49">
+  <conditionalFormatting sqref="P2:P47">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
@@ -7708,7 +7358,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q49">
+  <conditionalFormatting sqref="Q2:Q47">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -7720,7 +7370,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R49">
+  <conditionalFormatting sqref="R2:R47">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
@@ -7732,7 +7382,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S49">
+  <conditionalFormatting sqref="S2:S47">
     <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="min"/>
@@ -7744,7 +7394,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T49">
+  <conditionalFormatting sqref="T2:T47">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="min"/>
@@ -7756,7 +7406,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U49">
+  <conditionalFormatting sqref="U2:U47">
     <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="min"/>
@@ -7768,7 +7418,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V49">
+  <conditionalFormatting sqref="V2:V47">
     <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="min"/>
@@ -7780,7 +7430,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W2:W49">
+  <conditionalFormatting sqref="W2:W47">
     <cfRule type="colorScale" priority="21">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/SA_curtailment.xlsx
+++ b/outputs/SA_curtailment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/outputs/SA_curtailment.xlsx
+++ b/outputs/SA_curtailment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X47"/>
+  <dimension ref="A1:W47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -482,7 +482,6 @@
     <col width="12" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="12" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -553,55 +552,50 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>FY24-25</t>
+          <t>FY25-26</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>FY25-26</t>
+          <t>FY26-27</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>FY26-27 (Draft)</t>
+          <t>Curt FY1</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Curt FY1</t>
+          <t>Curt FY2</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Curt FY2</t>
+          <t>Curt FY3</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Curt FY3</t>
+          <t>Curt Avg</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Curt Avg</t>
+          <t>Offl FY1</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Offl FY1</t>
+          <t>Offl FY2</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Offl FY2</t>
+          <t>Offl FY3</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Offl FY3</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Offl Avg</t>
         </is>
@@ -652,14 +646,12 @@
       <c r="L2" s="5" t="inlineStr"/>
       <c r="M2" s="5" t="inlineStr"/>
       <c r="N2" s="5" t="n">
-        <v>1.0025</v>
+        <v>1.0037</v>
       </c>
       <c r="O2" s="5" t="n">
-        <v>1.0037</v>
-      </c>
-      <c r="P2" s="5" t="n">
-        <v>1.0034</v>
-      </c>
+        <v>1.0033</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr"/>
       <c r="Q2" s="6" t="inlineStr"/>
       <c r="R2" s="6" t="inlineStr"/>
       <c r="S2" s="6" t="inlineStr"/>
@@ -667,7 +659,6 @@
       <c r="U2" s="6" t="inlineStr"/>
       <c r="V2" s="6" t="inlineStr"/>
       <c r="W2" s="6" t="inlineStr"/>
-      <c r="X2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -710,14 +701,12 @@
       <c r="L3" s="5" t="inlineStr"/>
       <c r="M3" s="5" t="inlineStr"/>
       <c r="N3" s="5" t="n">
-        <v>1.0025</v>
+        <v>1.0037</v>
       </c>
       <c r="O3" s="5" t="n">
-        <v>1.0037</v>
-      </c>
-      <c r="P3" s="5" t="n">
-        <v>1.0034</v>
-      </c>
+        <v>1.0033</v>
+      </c>
+      <c r="P3" s="6" t="inlineStr"/>
       <c r="Q3" s="6" t="inlineStr"/>
       <c r="R3" s="6" t="inlineStr"/>
       <c r="S3" s="6" t="inlineStr"/>
@@ -725,7 +714,6 @@
       <c r="U3" s="6" t="inlineStr"/>
       <c r="V3" s="6" t="inlineStr"/>
       <c r="W3" s="6" t="inlineStr"/>
-      <c r="X3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -768,14 +756,12 @@
       <c r="L4" s="5" t="inlineStr"/>
       <c r="M4" s="5" t="inlineStr"/>
       <c r="N4" s="5" t="n">
-        <v>1.0025</v>
+        <v>1.0037</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>1.0037</v>
-      </c>
-      <c r="P4" s="5" t="n">
-        <v>1.0034</v>
-      </c>
+        <v>1.0033</v>
+      </c>
+      <c r="P4" s="6" t="inlineStr"/>
       <c r="Q4" s="6" t="inlineStr"/>
       <c r="R4" s="6" t="inlineStr"/>
       <c r="S4" s="6" t="inlineStr"/>
@@ -783,7 +769,6 @@
       <c r="U4" s="6" t="inlineStr"/>
       <c r="V4" s="6" t="inlineStr"/>
       <c r="W4" s="6" t="inlineStr"/>
-      <c r="X4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -828,14 +813,12 @@
       <c r="L5" s="5" t="inlineStr"/>
       <c r="M5" s="5" t="inlineStr"/>
       <c r="N5" s="5" t="n">
-        <v>1.0004</v>
+        <v>0.9999</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>0.9999</v>
-      </c>
-      <c r="P5" s="5" t="n">
         <v>1.0002</v>
       </c>
+      <c r="P5" s="6" t="inlineStr"/>
       <c r="Q5" s="6" t="inlineStr"/>
       <c r="R5" s="6" t="inlineStr"/>
       <c r="S5" s="6" t="inlineStr"/>
@@ -843,7 +826,6 @@
       <c r="U5" s="6" t="inlineStr"/>
       <c r="V5" s="6" t="inlineStr"/>
       <c r="W5" s="6" t="inlineStr"/>
-      <c r="X5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -900,13 +882,13 @@
         <v>0.212860651220515</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>0.9565</v>
+        <v>0.9725</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>0.9725</v>
-      </c>
-      <c r="P6" s="5" t="n">
-        <v>0.9698</v>
+        <v>0.9703000000000001</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>0</v>
@@ -918,18 +900,15 @@
         <v>0</v>
       </c>
       <c r="T6" s="6" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="U6" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="V6" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="V6" s="6" t="n">
-        <v>0.08</v>
-      </c>
       <c r="W6" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="X6" s="6" t="n">
         <v>0.07333333333333335</v>
       </c>
     </row>
@@ -988,13 +967,13 @@
         <v>0.212860651220515</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>0.9565</v>
+        <v>0.9725</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>0.9725</v>
-      </c>
-      <c r="P7" s="5" t="n">
-        <v>0.9698</v>
+        <v>0.9703000000000001</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1006,18 +985,15 @@
         <v>0</v>
       </c>
       <c r="T7" s="6" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="U7" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="V7" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="V7" s="6" t="n">
-        <v>0.08</v>
-      </c>
       <c r="W7" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="X7" s="6" t="n">
         <v>0.07333333333333335</v>
       </c>
     </row>
@@ -1062,14 +1038,12 @@
       <c r="L8" s="5" t="inlineStr"/>
       <c r="M8" s="5" t="inlineStr"/>
       <c r="N8" s="5" t="n">
-        <v>1.0025</v>
+        <v>1.0037</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>1.0037</v>
-      </c>
-      <c r="P8" s="5" t="n">
-        <v>1.0034</v>
-      </c>
+        <v>1.0033</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr"/>
       <c r="Q8" s="6" t="inlineStr"/>
       <c r="R8" s="6" t="inlineStr"/>
       <c r="S8" s="6" t="inlineStr"/>
@@ -1077,7 +1051,6 @@
       <c r="U8" s="6" t="inlineStr"/>
       <c r="V8" s="6" t="inlineStr"/>
       <c r="W8" s="6" t="inlineStr"/>
-      <c r="X8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1120,14 +1093,12 @@
       <c r="L9" s="5" t="inlineStr"/>
       <c r="M9" s="5" t="inlineStr"/>
       <c r="N9" s="5" t="n">
-        <v>1.0025</v>
+        <v>1.0037</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>1.0037</v>
-      </c>
-      <c r="P9" s="5" t="n">
-        <v>1.0034</v>
-      </c>
+        <v>1.0033</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr"/>
       <c r="Q9" s="6" t="inlineStr"/>
       <c r="R9" s="6" t="inlineStr"/>
       <c r="S9" s="6" t="inlineStr"/>
@@ -1135,7 +1106,6 @@
       <c r="U9" s="6" t="inlineStr"/>
       <c r="V9" s="6" t="inlineStr"/>
       <c r="W9" s="6" t="inlineStr"/>
-      <c r="X9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1192,14 +1162,12 @@
         <v>0.22265637813532</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>1.0043</v>
+        <v>1.0024</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>1.0024</v>
-      </c>
-      <c r="P10" s="5" t="n">
         <v>1.0022</v>
       </c>
+      <c r="P10" s="6" t="inlineStr"/>
       <c r="Q10" s="6" t="inlineStr"/>
       <c r="R10" s="6" t="inlineStr"/>
       <c r="S10" s="6" t="inlineStr"/>
@@ -1207,7 +1175,6 @@
       <c r="U10" s="6" t="inlineStr"/>
       <c r="V10" s="6" t="inlineStr"/>
       <c r="W10" s="6" t="inlineStr"/>
-      <c r="X10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1264,13 +1231,13 @@
         <v>0.225784053085401</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>0.9926</v>
+        <v>1.0257</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>1.0257</v>
-      </c>
-      <c r="P11" s="5" t="n">
-        <v>1.0132</v>
+        <v>1.0134</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1291,9 +1258,6 @@
         <v>0</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1350,13 +1314,13 @@
         <v>0.225784053085401</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>0.9802</v>
+        <v>1.0252</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>1.0252</v>
-      </c>
-      <c r="P12" s="5" t="n">
-        <v>1.0135</v>
+        <v>1.0137</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1377,9 +1341,6 @@
         <v>0</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1436,13 +1397,13 @@
         <v>0.225784053085401</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>0.9937</v>
+        <v>0.9932</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>0.9932</v>
-      </c>
-      <c r="P13" s="5" t="n">
-        <v>0.9955000000000001</v>
+        <v>0.9959</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1454,7 +1415,7 @@
         <v>0</v>
       </c>
       <c r="T13" s="6" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="U13" s="6" t="n">
         <v>0.16</v>
@@ -1465,9 +1426,6 @@
       <c r="W13" s="6" t="n">
         <v>0.16</v>
       </c>
-      <c r="X13" s="6" t="n">
-        <v>0.16</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1524,13 +1482,13 @@
         <v>0.512670422089759</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>0.9759</v>
+        <v>1.0146</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>1.0146</v>
-      </c>
-      <c r="P14" s="5" t="n">
-        <v>0.966</v>
+        <v>0.9540999999999999</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>0</v>
@@ -1542,7 +1500,7 @@
         <v>0</v>
       </c>
       <c r="T14" s="6" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="U14" s="6" t="n">
         <v>0.16</v>
@@ -1553,9 +1511,6 @@
       <c r="W14" s="6" t="n">
         <v>0.16</v>
       </c>
-      <c r="X14" s="6" t="n">
-        <v>0.16</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1612,13 +1567,13 @@
         <v>0.512670422089759</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>0.9766</v>
+        <v>1.003</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>1.003</v>
-      </c>
-      <c r="P15" s="5" t="n">
-        <v>0.9723000000000001</v>
+        <v>0.9664</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q15" s="6" t="n">
         <v>0</v>
@@ -1630,7 +1585,7 @@
         <v>0</v>
       </c>
       <c r="T15" s="6" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>0.16</v>
@@ -1641,9 +1596,6 @@
       <c r="W15" s="6" t="n">
         <v>0.16</v>
       </c>
-      <c r="X15" s="6" t="n">
-        <v>0.16</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1700,13 +1652,13 @@
         <v>0.512670422089759</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>0.9787</v>
+        <v>0.9897</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>0.9897</v>
-      </c>
-      <c r="P16" s="5" t="n">
-        <v>0.9766</v>
+        <v>0.9741</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>0</v>
@@ -1718,7 +1670,7 @@
         <v>0</v>
       </c>
       <c r="T16" s="6" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="U16" s="6" t="n">
         <v>0.16</v>
@@ -1729,9 +1681,6 @@
       <c r="W16" s="6" t="n">
         <v>0.16</v>
       </c>
-      <c r="X16" s="6" t="n">
-        <v>0.16</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1788,13 +1737,13 @@
         <v>0.512670422089759</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>0.9751</v>
+        <v>0.9837</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>0.9837</v>
-      </c>
-      <c r="P17" s="5" t="n">
-        <v>0.9781</v>
+        <v>0.9772999999999999</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q17" s="6" t="n">
         <v>0</v>
@@ -1806,7 +1755,7 @@
         <v>0</v>
       </c>
       <c r="T17" s="6" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="U17" s="6" t="n">
         <v>0.16</v>
@@ -1817,9 +1766,6 @@
       <c r="W17" s="6" t="n">
         <v>0.16</v>
       </c>
-      <c r="X17" s="6" t="n">
-        <v>0.16</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1876,13 +1822,13 @@
         <v>0.225784053085401</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>0.9993</v>
+        <v>1.0127</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>1.0127</v>
-      </c>
-      <c r="P18" s="5" t="n">
-        <v>1.0106</v>
+        <v>1.011</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1903,9 +1849,6 @@
         <v>0</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1964,14 +1907,14 @@
         <v>0.212860651220515</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>0.9608</v>
+        <v>0.9735</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>0.9735</v>
-      </c>
-      <c r="P19" s="5" t="n">
         <v>0.9709</v>
       </c>
+      <c r="P19" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
       </c>
@@ -1982,18 +1925,15 @@
         <v>0</v>
       </c>
       <c r="T19" s="6" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="U19" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="V19" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="V19" s="6" t="n">
-        <v>0.08</v>
-      </c>
       <c r="W19" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="X19" s="6" t="n">
         <v>0.07333333333333335</v>
       </c>
     </row>
@@ -2052,14 +1992,12 @@
         <v>0.22945882760626</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>1.0102</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>0.9945000000000001</v>
-      </c>
-      <c r="P20" s="5" t="n">
-        <v>0.9963</v>
-      </c>
+        <v>0.9968</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr"/>
       <c r="Q20" s="6" t="inlineStr"/>
       <c r="R20" s="6" t="inlineStr"/>
       <c r="S20" s="6" t="inlineStr"/>
@@ -2067,7 +2005,6 @@
       <c r="U20" s="6" t="inlineStr"/>
       <c r="V20" s="6" t="inlineStr"/>
       <c r="W20" s="6" t="inlineStr"/>
-      <c r="X20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2124,14 +2061,12 @@
         <v>0.22945882760626</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>1.009</v>
+        <v>0.9952</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>0.9952</v>
-      </c>
-      <c r="P21" s="5" t="n">
-        <v>0.9967</v>
-      </c>
+        <v>0.9978</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr"/>
       <c r="Q21" s="6" t="inlineStr"/>
       <c r="R21" s="6" t="inlineStr"/>
       <c r="S21" s="6" t="inlineStr"/>
@@ -2139,7 +2074,6 @@
       <c r="U21" s="6" t="inlineStr"/>
       <c r="V21" s="6" t="inlineStr"/>
       <c r="W21" s="6" t="inlineStr"/>
-      <c r="X21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2186,14 +2120,12 @@
       <c r="L22" s="5" t="inlineStr"/>
       <c r="M22" s="5" t="inlineStr"/>
       <c r="N22" s="5" t="n">
-        <v>0.9755</v>
+        <v>0.9333</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>0.9333</v>
-      </c>
-      <c r="P22" s="5" t="n">
-        <v>0.9458</v>
-      </c>
+        <v>0.9527</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr"/>
       <c r="Q22" s="6" t="inlineStr"/>
       <c r="R22" s="6" t="inlineStr"/>
       <c r="S22" s="6" t="inlineStr"/>
@@ -2201,7 +2133,6 @@
       <c r="U22" s="6" t="inlineStr"/>
       <c r="V22" s="6" t="inlineStr"/>
       <c r="W22" s="6" t="inlineStr"/>
-      <c r="X22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2248,14 +2179,12 @@
       <c r="L23" s="5" t="inlineStr"/>
       <c r="M23" s="5" t="inlineStr"/>
       <c r="N23" s="5" t="n">
-        <v>0.9308999999999999</v>
+        <v>0.9467</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>0.9467</v>
-      </c>
-      <c r="P23" s="5" t="n">
-        <v>0.9408</v>
-      </c>
+        <v>0.9417</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr"/>
       <c r="Q23" s="6" t="inlineStr"/>
       <c r="R23" s="6" t="inlineStr"/>
       <c r="S23" s="6" t="inlineStr"/>
@@ -2263,7 +2192,6 @@
       <c r="U23" s="6" t="inlineStr"/>
       <c r="V23" s="6" t="inlineStr"/>
       <c r="W23" s="6" t="inlineStr"/>
-      <c r="X23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2310,14 +2238,12 @@
       <c r="L24" s="5" t="inlineStr"/>
       <c r="M24" s="5" t="inlineStr"/>
       <c r="N24" s="5" t="n">
-        <v>0.9486</v>
+        <v>0.9604</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>0.9604</v>
-      </c>
-      <c r="P24" s="5" t="n">
-        <v>0.9605</v>
-      </c>
+        <v>0.9614</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr"/>
       <c r="Q24" s="6" t="inlineStr"/>
       <c r="R24" s="6" t="inlineStr"/>
       <c r="S24" s="6" t="inlineStr"/>
@@ -2325,7 +2251,6 @@
       <c r="U24" s="6" t="inlineStr"/>
       <c r="V24" s="6" t="inlineStr"/>
       <c r="W24" s="6" t="inlineStr"/>
-      <c r="X24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2370,14 +2295,12 @@
       <c r="L25" s="5" t="inlineStr"/>
       <c r="M25" s="5" t="inlineStr"/>
       <c r="N25" s="5" t="n">
-        <v>0.9643</v>
+        <v>0.9697</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>0.9697</v>
-      </c>
-      <c r="P25" s="5" t="n">
-        <v>0.9711</v>
-      </c>
+        <v>0.9687</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr"/>
       <c r="Q25" s="6" t="inlineStr"/>
       <c r="R25" s="6" t="inlineStr"/>
       <c r="S25" s="6" t="inlineStr"/>
@@ -2385,7 +2308,6 @@
       <c r="U25" s="6" t="inlineStr"/>
       <c r="V25" s="6" t="inlineStr"/>
       <c r="W25" s="6" t="inlineStr"/>
-      <c r="X25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2428,14 +2350,12 @@
       <c r="L26" s="5" t="inlineStr"/>
       <c r="M26" s="5" t="inlineStr"/>
       <c r="N26" s="5" t="n">
-        <v>0.9641</v>
+        <v>0.9689</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>0.9689</v>
-      </c>
-      <c r="P26" s="5" t="n">
-        <v>0.971</v>
-      </c>
+        <v>0.9687</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr"/>
       <c r="Q26" s="6" t="inlineStr"/>
       <c r="R26" s="6" t="inlineStr"/>
       <c r="S26" s="6" t="inlineStr"/>
@@ -2443,7 +2363,6 @@
       <c r="U26" s="6" t="inlineStr"/>
       <c r="V26" s="6" t="inlineStr"/>
       <c r="W26" s="6" t="inlineStr"/>
-      <c r="X26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2490,14 +2409,12 @@
       <c r="L27" s="5" t="inlineStr"/>
       <c r="M27" s="5" t="inlineStr"/>
       <c r="N27" s="5" t="n">
-        <v>0.9565</v>
+        <v>0.9663</v>
       </c>
       <c r="O27" s="5" t="n">
-        <v>0.9663</v>
-      </c>
-      <c r="P27" s="5" t="n">
-        <v>0.9635</v>
-      </c>
+        <v>0.9628</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr"/>
       <c r="Q27" s="6" t="inlineStr"/>
       <c r="R27" s="6" t="inlineStr"/>
       <c r="S27" s="6" t="inlineStr"/>
@@ -2505,7 +2422,6 @@
       <c r="U27" s="6" t="inlineStr"/>
       <c r="V27" s="6" t="inlineStr"/>
       <c r="W27" s="6" t="inlineStr"/>
-      <c r="X27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2552,14 +2468,12 @@
       <c r="L28" s="5" t="inlineStr"/>
       <c r="M28" s="5" t="inlineStr"/>
       <c r="N28" s="5" t="n">
-        <v>0.9526</v>
+        <v>0.9608</v>
       </c>
       <c r="O28" s="5" t="n">
-        <v>0.9608</v>
-      </c>
-      <c r="P28" s="5" t="n">
-        <v>0.962</v>
-      </c>
+        <v>0.9606</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr"/>
       <c r="Q28" s="6" t="inlineStr"/>
       <c r="R28" s="6" t="inlineStr"/>
       <c r="S28" s="6" t="inlineStr"/>
@@ -2567,7 +2481,6 @@
       <c r="U28" s="6" t="inlineStr"/>
       <c r="V28" s="6" t="inlineStr"/>
       <c r="W28" s="6" t="inlineStr"/>
-      <c r="X28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2614,14 +2527,12 @@
       <c r="L29" s="5" t="inlineStr"/>
       <c r="M29" s="5" t="inlineStr"/>
       <c r="N29" s="5" t="n">
-        <v>0.9423</v>
+        <v>0.956</v>
       </c>
       <c r="O29" s="5" t="n">
-        <v>0.956</v>
-      </c>
-      <c r="P29" s="5" t="n">
-        <v>0.9538</v>
-      </c>
+        <v>0.9533</v>
+      </c>
+      <c r="P29" s="6" t="inlineStr"/>
       <c r="Q29" s="6" t="inlineStr"/>
       <c r="R29" s="6" t="inlineStr"/>
       <c r="S29" s="6" t="inlineStr"/>
@@ -2629,7 +2540,6 @@
       <c r="U29" s="6" t="inlineStr"/>
       <c r="V29" s="6" t="inlineStr"/>
       <c r="W29" s="6" t="inlineStr"/>
-      <c r="X29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2676,14 +2586,12 @@
       <c r="L30" s="5" t="inlineStr"/>
       <c r="M30" s="5" t="inlineStr"/>
       <c r="N30" s="5" t="n">
-        <v>0.9423</v>
+        <v>0.956</v>
       </c>
       <c r="O30" s="5" t="n">
-        <v>0.956</v>
-      </c>
-      <c r="P30" s="5" t="n">
-        <v>0.9538</v>
-      </c>
+        <v>0.9533</v>
+      </c>
+      <c r="P30" s="6" t="inlineStr"/>
       <c r="Q30" s="6" t="inlineStr"/>
       <c r="R30" s="6" t="inlineStr"/>
       <c r="S30" s="6" t="inlineStr"/>
@@ -2691,7 +2599,6 @@
       <c r="U30" s="6" t="inlineStr"/>
       <c r="V30" s="6" t="inlineStr"/>
       <c r="W30" s="6" t="inlineStr"/>
-      <c r="X30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2738,14 +2645,12 @@
       <c r="L31" s="5" t="inlineStr"/>
       <c r="M31" s="5" t="inlineStr"/>
       <c r="N31" s="5" t="n">
-        <v>0.9423</v>
+        <v>0.956</v>
       </c>
       <c r="O31" s="5" t="n">
-        <v>0.956</v>
-      </c>
-      <c r="P31" s="5" t="n">
-        <v>0.9538</v>
-      </c>
+        <v>0.9533</v>
+      </c>
+      <c r="P31" s="6" t="inlineStr"/>
       <c r="Q31" s="6" t="inlineStr"/>
       <c r="R31" s="6" t="inlineStr"/>
       <c r="S31" s="6" t="inlineStr"/>
@@ -2753,7 +2658,6 @@
       <c r="U31" s="6" t="inlineStr"/>
       <c r="V31" s="6" t="inlineStr"/>
       <c r="W31" s="6" t="inlineStr"/>
-      <c r="X31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2800,14 +2704,12 @@
       <c r="L32" s="5" t="inlineStr"/>
       <c r="M32" s="5" t="inlineStr"/>
       <c r="N32" s="5" t="n">
-        <v>0.9709</v>
+        <v>0.9297</v>
       </c>
       <c r="O32" s="5" t="n">
-        <v>0.9297</v>
-      </c>
-      <c r="P32" s="5" t="n">
-        <v>0.9389999999999999</v>
-      </c>
+        <v>0.9468</v>
+      </c>
+      <c r="P32" s="6" t="inlineStr"/>
       <c r="Q32" s="6" t="inlineStr"/>
       <c r="R32" s="6" t="inlineStr"/>
       <c r="S32" s="6" t="inlineStr"/>
@@ -2815,7 +2717,6 @@
       <c r="U32" s="6" t="inlineStr"/>
       <c r="V32" s="6" t="inlineStr"/>
       <c r="W32" s="6" t="inlineStr"/>
-      <c r="X32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2862,14 +2763,12 @@
       <c r="L33" s="5" t="inlineStr"/>
       <c r="M33" s="5" t="inlineStr"/>
       <c r="N33" s="5" t="n">
-        <v>0.9709</v>
+        <v>0.9297</v>
       </c>
       <c r="O33" s="5" t="n">
-        <v>0.9297</v>
-      </c>
-      <c r="P33" s="5" t="n">
-        <v>0.9389999999999999</v>
-      </c>
+        <v>0.9468</v>
+      </c>
+      <c r="P33" s="6" t="inlineStr"/>
       <c r="Q33" s="6" t="inlineStr"/>
       <c r="R33" s="6" t="inlineStr"/>
       <c r="S33" s="6" t="inlineStr"/>
@@ -2877,7 +2776,6 @@
       <c r="U33" s="6" t="inlineStr"/>
       <c r="V33" s="6" t="inlineStr"/>
       <c r="W33" s="6" t="inlineStr"/>
-      <c r="X33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2924,14 +2822,12 @@
       <c r="L34" s="5" t="inlineStr"/>
       <c r="M34" s="5" t="inlineStr"/>
       <c r="N34" s="5" t="n">
-        <v>0.9709</v>
+        <v>0.9297</v>
       </c>
       <c r="O34" s="5" t="n">
-        <v>0.9297</v>
-      </c>
-      <c r="P34" s="5" t="n">
-        <v>0.9389999999999999</v>
-      </c>
+        <v>0.9468</v>
+      </c>
+      <c r="P34" s="6" t="inlineStr"/>
       <c r="Q34" s="6" t="inlineStr"/>
       <c r="R34" s="6" t="inlineStr"/>
       <c r="S34" s="6" t="inlineStr"/>
@@ -2939,7 +2835,6 @@
       <c r="U34" s="6" t="inlineStr"/>
       <c r="V34" s="6" t="inlineStr"/>
       <c r="W34" s="6" t="inlineStr"/>
-      <c r="X34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2986,14 +2881,12 @@
       <c r="L35" s="5" t="inlineStr"/>
       <c r="M35" s="5" t="inlineStr"/>
       <c r="N35" s="5" t="n">
-        <v>0.9576</v>
+        <v>0.9689</v>
       </c>
       <c r="O35" s="5" t="n">
-        <v>0.9689</v>
-      </c>
-      <c r="P35" s="5" t="n">
-        <v>0.9661999999999999</v>
-      </c>
+        <v>0.9661</v>
+      </c>
+      <c r="P35" s="6" t="inlineStr"/>
       <c r="Q35" s="6" t="inlineStr"/>
       <c r="R35" s="6" t="inlineStr"/>
       <c r="S35" s="6" t="inlineStr"/>
@@ -3001,7 +2894,6 @@
       <c r="U35" s="6" t="inlineStr"/>
       <c r="V35" s="6" t="inlineStr"/>
       <c r="W35" s="6" t="inlineStr"/>
-      <c r="X35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -3048,14 +2940,12 @@
       <c r="L36" s="5" t="inlineStr"/>
       <c r="M36" s="5" t="inlineStr"/>
       <c r="N36" s="5" t="n">
-        <v>0.9576</v>
+        <v>0.9689</v>
       </c>
       <c r="O36" s="5" t="n">
-        <v>0.9689</v>
-      </c>
-      <c r="P36" s="5" t="n">
-        <v>0.9661999999999999</v>
-      </c>
+        <v>0.9661</v>
+      </c>
+      <c r="P36" s="6" t="inlineStr"/>
       <c r="Q36" s="6" t="inlineStr"/>
       <c r="R36" s="6" t="inlineStr"/>
       <c r="S36" s="6" t="inlineStr"/>
@@ -3063,7 +2953,6 @@
       <c r="U36" s="6" t="inlineStr"/>
       <c r="V36" s="6" t="inlineStr"/>
       <c r="W36" s="6" t="inlineStr"/>
-      <c r="X36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -3110,14 +2999,12 @@
       <c r="L37" s="5" t="inlineStr"/>
       <c r="M37" s="5" t="inlineStr"/>
       <c r="N37" s="5" t="n">
-        <v>0.9162</v>
+        <v>0.9403</v>
       </c>
       <c r="O37" s="5" t="n">
-        <v>0.9403</v>
-      </c>
-      <c r="P37" s="5" t="n">
-        <v>0.9379</v>
-      </c>
+        <v>0.9387</v>
+      </c>
+      <c r="P37" s="6" t="inlineStr"/>
       <c r="Q37" s="6" t="inlineStr"/>
       <c r="R37" s="6" t="inlineStr"/>
       <c r="S37" s="6" t="inlineStr"/>
@@ -3125,7 +3012,6 @@
       <c r="U37" s="6" t="inlineStr"/>
       <c r="V37" s="6" t="inlineStr"/>
       <c r="W37" s="6" t="inlineStr"/>
-      <c r="X37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3172,14 +3058,12 @@
       <c r="L38" s="5" t="inlineStr"/>
       <c r="M38" s="5" t="inlineStr"/>
       <c r="N38" s="5" t="n">
-        <v>0.9467</v>
+        <v>0.9579</v>
       </c>
       <c r="O38" s="5" t="n">
-        <v>0.9579</v>
-      </c>
-      <c r="P38" s="5" t="n">
-        <v>0.9583</v>
-      </c>
+        <v>0.9572000000000001</v>
+      </c>
+      <c r="P38" s="6" t="inlineStr"/>
       <c r="Q38" s="6" t="inlineStr"/>
       <c r="R38" s="6" t="inlineStr"/>
       <c r="S38" s="6" t="inlineStr"/>
@@ -3187,7 +3071,6 @@
       <c r="U38" s="6" t="inlineStr"/>
       <c r="V38" s="6" t="inlineStr"/>
       <c r="W38" s="6" t="inlineStr"/>
-      <c r="X38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3234,14 +3117,12 @@
       <c r="L39" s="5" t="inlineStr"/>
       <c r="M39" s="5" t="inlineStr"/>
       <c r="N39" s="5" t="n">
-        <v>0.9608</v>
+        <v>0.9735</v>
       </c>
       <c r="O39" s="5" t="n">
-        <v>0.9735</v>
-      </c>
-      <c r="P39" s="5" t="n">
         <v>0.9709</v>
       </c>
+      <c r="P39" s="6" t="inlineStr"/>
       <c r="Q39" s="6" t="inlineStr"/>
       <c r="R39" s="6" t="inlineStr"/>
       <c r="S39" s="6" t="inlineStr"/>
@@ -3249,7 +3130,6 @@
       <c r="U39" s="6" t="inlineStr"/>
       <c r="V39" s="6" t="inlineStr"/>
       <c r="W39" s="6" t="inlineStr"/>
-      <c r="X39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3296,14 +3176,12 @@
       <c r="L40" s="5" t="inlineStr"/>
       <c r="M40" s="5" t="inlineStr"/>
       <c r="N40" s="5" t="n">
-        <v>0.9613</v>
+        <v>0.9695</v>
       </c>
       <c r="O40" s="5" t="n">
-        <v>0.9695</v>
-      </c>
-      <c r="P40" s="5" t="n">
-        <v>0.9694</v>
-      </c>
+        <v>0.9699</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr"/>
       <c r="Q40" s="6" t="inlineStr"/>
       <c r="R40" s="6" t="inlineStr"/>
       <c r="S40" s="6" t="inlineStr"/>
@@ -3311,7 +3189,6 @@
       <c r="U40" s="6" t="inlineStr"/>
       <c r="V40" s="6" t="inlineStr"/>
       <c r="W40" s="6" t="inlineStr"/>
-      <c r="X40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3358,14 +3235,12 @@
       <c r="L41" s="5" t="inlineStr"/>
       <c r="M41" s="5" t="inlineStr"/>
       <c r="N41" s="5" t="n">
-        <v>0.9613</v>
+        <v>0.9695</v>
       </c>
       <c r="O41" s="5" t="n">
-        <v>0.9695</v>
-      </c>
-      <c r="P41" s="5" t="n">
-        <v>0.9694</v>
-      </c>
+        <v>0.9699</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr"/>
       <c r="Q41" s="6" t="inlineStr"/>
       <c r="R41" s="6" t="inlineStr"/>
       <c r="S41" s="6" t="inlineStr"/>
@@ -3373,7 +3248,6 @@
       <c r="U41" s="6" t="inlineStr"/>
       <c r="V41" s="6" t="inlineStr"/>
       <c r="W41" s="6" t="inlineStr"/>
-      <c r="X41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3420,14 +3294,12 @@
       <c r="L42" s="5" t="inlineStr"/>
       <c r="M42" s="5" t="inlineStr"/>
       <c r="N42" s="5" t="n">
-        <v>0.8932</v>
+        <v>0.9157</v>
       </c>
       <c r="O42" s="5" t="n">
-        <v>0.9157</v>
-      </c>
-      <c r="P42" s="5" t="n">
-        <v>0.9112</v>
-      </c>
+        <v>0.9132</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr"/>
       <c r="Q42" s="6" t="inlineStr"/>
       <c r="R42" s="6" t="inlineStr"/>
       <c r="S42" s="6" t="inlineStr"/>
@@ -3435,7 +3307,6 @@
       <c r="U42" s="6" t="inlineStr"/>
       <c r="V42" s="6" t="inlineStr"/>
       <c r="W42" s="6" t="inlineStr"/>
-      <c r="X42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3482,14 +3353,12 @@
       <c r="L43" s="5" t="inlineStr"/>
       <c r="M43" s="5" t="inlineStr"/>
       <c r="N43" s="5" t="n">
-        <v>1.0025</v>
+        <v>1.0037</v>
       </c>
       <c r="O43" s="5" t="n">
-        <v>1.0037</v>
-      </c>
-      <c r="P43" s="5" t="n">
-        <v>1.0034</v>
-      </c>
+        <v>1.0033</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr"/>
       <c r="Q43" s="6" t="inlineStr"/>
       <c r="R43" s="6" t="inlineStr"/>
       <c r="S43" s="6" t="inlineStr"/>
@@ -3497,7 +3366,6 @@
       <c r="U43" s="6" t="inlineStr"/>
       <c r="V43" s="6" t="inlineStr"/>
       <c r="W43" s="6" t="inlineStr"/>
-      <c r="X43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3544,14 +3412,12 @@
       <c r="L44" s="5" t="inlineStr"/>
       <c r="M44" s="5" t="inlineStr"/>
       <c r="N44" s="5" t="n">
-        <v>0.9467</v>
+        <v>0.9579</v>
       </c>
       <c r="O44" s="5" t="n">
-        <v>0.9579</v>
-      </c>
-      <c r="P44" s="5" t="n">
-        <v>0.9583</v>
-      </c>
+        <v>0.9572000000000001</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr"/>
       <c r="Q44" s="6" t="inlineStr"/>
       <c r="R44" s="6" t="inlineStr"/>
       <c r="S44" s="6" t="inlineStr"/>
@@ -3559,7 +3425,6 @@
       <c r="U44" s="6" t="inlineStr"/>
       <c r="V44" s="6" t="inlineStr"/>
       <c r="W44" s="6" t="inlineStr"/>
-      <c r="X44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3606,14 +3471,12 @@
       <c r="L45" s="5" t="inlineStr"/>
       <c r="M45" s="5" t="inlineStr"/>
       <c r="N45" s="5" t="n">
-        <v>0.9547</v>
+        <v>0.9624</v>
       </c>
       <c r="O45" s="5" t="n">
-        <v>0.9624</v>
-      </c>
-      <c r="P45" s="5" t="n">
         <v>0.9611</v>
       </c>
+      <c r="P45" s="6" t="inlineStr"/>
       <c r="Q45" s="6" t="inlineStr"/>
       <c r="R45" s="6" t="inlineStr"/>
       <c r="S45" s="6" t="inlineStr"/>
@@ -3621,7 +3484,6 @@
       <c r="U45" s="6" t="inlineStr"/>
       <c r="V45" s="6" t="inlineStr"/>
       <c r="W45" s="6" t="inlineStr"/>
-      <c r="X45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3668,14 +3530,12 @@
       <c r="L46" s="5" t="inlineStr"/>
       <c r="M46" s="5" t="inlineStr"/>
       <c r="N46" s="5" t="n">
-        <v>0.8179</v>
+        <v>0.8456</v>
       </c>
       <c r="O46" s="5" t="n">
-        <v>0.8456</v>
-      </c>
-      <c r="P46" s="5" t="n">
-        <v>0.844</v>
-      </c>
+        <v>0.8476</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr"/>
       <c r="Q46" s="6" t="inlineStr"/>
       <c r="R46" s="6" t="inlineStr"/>
       <c r="S46" s="6" t="inlineStr"/>
@@ -3683,7 +3543,6 @@
       <c r="U46" s="6" t="inlineStr"/>
       <c r="V46" s="6" t="inlineStr"/>
       <c r="W46" s="6" t="inlineStr"/>
-      <c r="X46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3730,14 +3589,12 @@
       <c r="L47" s="5" t="inlineStr"/>
       <c r="M47" s="5" t="inlineStr"/>
       <c r="N47" s="5" t="n">
-        <v>0.9498</v>
+        <v>0.9601</v>
       </c>
       <c r="O47" s="5" t="n">
-        <v>0.9601</v>
-      </c>
-      <c r="P47" s="5" t="n">
-        <v>0.9605</v>
-      </c>
+        <v>0.9592000000000001</v>
+      </c>
+      <c r="P47" s="6" t="inlineStr"/>
       <c r="Q47" s="6" t="inlineStr"/>
       <c r="R47" s="6" t="inlineStr"/>
       <c r="S47" s="6" t="inlineStr"/>
@@ -3745,7 +3602,6 @@
       <c r="U47" s="6" t="inlineStr"/>
       <c r="V47" s="6" t="inlineStr"/>
       <c r="W47" s="6" t="inlineStr"/>
-      <c r="X47" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3758,7 +3614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W47"/>
+  <dimension ref="A1:V47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3783,7 +3639,6 @@
     <col width="14" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3799,105 +3654,100 @@
       </c>
       <c r="C1" s="7" t="inlineStr">
         <is>
-          <t>MLF_FY24-25</t>
+          <t>MLF_FY25-26</t>
         </is>
       </c>
       <c r="D1" s="7" t="inlineStr">
         <is>
-          <t>MLF_FY25-26</t>
+          <t>MLF_FY26-27</t>
         </is>
       </c>
       <c r="E1" s="7" t="inlineStr">
         <is>
-          <t>MLF_FY26-27 (Draft)</t>
+          <t>CURTAILMENT_ACTUAL_FY23-24</t>
         </is>
       </c>
       <c r="F1" s="7" t="inlineStr">
         <is>
-          <t>CURTAILMENT_ACTUAL_FY23-24</t>
+          <t>CURTAILMENT_ACTUAL_FY24-25</t>
         </is>
       </c>
       <c r="G1" s="7" t="inlineStr">
         <is>
-          <t>CURTAILMENT_ACTUAL_FY24-25</t>
+          <t>ELI_CURTAILMENT_NEAR</t>
         </is>
       </c>
       <c r="H1" s="7" t="inlineStr">
         <is>
-          <t>ELI_CURTAILMENT_NEAR</t>
+          <t>ELI_CURTAILMENT_MED</t>
         </is>
       </c>
       <c r="I1" s="7" t="inlineStr">
         <is>
-          <t>ELI_CURTAILMENT_MED</t>
+          <t>ISP_CURTAILMENT_FY1</t>
         </is>
       </c>
       <c r="J1" s="7" t="inlineStr">
         <is>
-          <t>ISP_CURTAILMENT_FY1</t>
+          <t>ISP_CURTAILMENT_FY1_LABEL</t>
         </is>
       </c>
       <c r="K1" s="7" t="inlineStr">
         <is>
-          <t>ISP_CURTAILMENT_FY1_LABEL</t>
+          <t>ISP_CURTAILMENT_FY2</t>
         </is>
       </c>
       <c r="L1" s="7" t="inlineStr">
         <is>
-          <t>ISP_CURTAILMENT_FY2</t>
+          <t>ISP_CURTAILMENT_FY2_LABEL</t>
         </is>
       </c>
       <c r="M1" s="7" t="inlineStr">
         <is>
-          <t>ISP_CURTAILMENT_FY2_LABEL</t>
+          <t>ISP_CURTAILMENT_FY3</t>
         </is>
       </c>
       <c r="N1" s="7" t="inlineStr">
         <is>
-          <t>ISP_CURTAILMENT_FY3</t>
+          <t>ISP_CURTAILMENT_FY3_LABEL</t>
         </is>
       </c>
       <c r="O1" s="7" t="inlineStr">
         <is>
-          <t>ISP_CURTAILMENT_FY3_LABEL</t>
+          <t>ISP_CURTAILMENT_AVG</t>
         </is>
       </c>
       <c r="P1" s="7" t="inlineStr">
         <is>
-          <t>ISP_CURTAILMENT_AVG</t>
+          <t>ISP_OFFLOADING_FY1</t>
         </is>
       </c>
       <c r="Q1" s="7" t="inlineStr">
         <is>
-          <t>ISP_OFFLOADING_FY1</t>
+          <t>ISP_OFFLOADING_FY1_LABEL</t>
         </is>
       </c>
       <c r="R1" s="7" t="inlineStr">
         <is>
-          <t>ISP_OFFLOADING_FY1_LABEL</t>
+          <t>ISP_OFFLOADING_FY2</t>
         </is>
       </c>
       <c r="S1" s="7" t="inlineStr">
         <is>
-          <t>ISP_OFFLOADING_FY2</t>
+          <t>ISP_OFFLOADING_FY2_LABEL</t>
         </is>
       </c>
       <c r="T1" s="7" t="inlineStr">
         <is>
-          <t>ISP_OFFLOADING_FY2_LABEL</t>
+          <t>ISP_OFFLOADING_FY3</t>
         </is>
       </c>
       <c r="U1" s="7" t="inlineStr">
         <is>
-          <t>ISP_OFFLOADING_FY3</t>
+          <t>ISP_OFFLOADING_FY3_LABEL</t>
         </is>
       </c>
       <c r="V1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY3_LABEL</t>
-        </is>
-      </c>
-      <c r="W1" s="7" t="inlineStr">
         <is>
           <t>ISP_OFFLOADING_AVG</t>
         </is>
@@ -3915,60 +3765,57 @@
         </is>
       </c>
       <c r="C2" s="5" t="n">
-        <v>1.0025</v>
+        <v>1.0037</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>1.0037</v>
+        <v>1.0033</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>1.0034</v>
+        <v>0.2903</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>0.2903</v>
-      </c>
-      <c r="G2" s="5" t="n">
         <v>0.256</v>
       </c>
+      <c r="G2" s="5" t="inlineStr"/>
       <c r="H2" s="5" t="inlineStr"/>
       <c r="I2" s="5" t="inlineStr"/>
-      <c r="J2" s="5" t="inlineStr"/>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="inlineStr"/>
-      <c r="M2" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N2" s="5" t="inlineStr"/>
-      <c r="O2" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr"/>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr"/>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr"/>
       <c r="P2" s="5" t="inlineStr"/>
-      <c r="Q2" s="5" t="inlineStr"/>
-      <c r="R2" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S2" s="5" t="inlineStr"/>
-      <c r="T2" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U2" s="5" t="inlineStr"/>
-      <c r="V2" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr"/>
+      <c r="U2" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
@@ -3982,56 +3829,53 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1.0025</v>
+        <v>1.0037</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1.0037</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>1.0034</v>
-      </c>
+        <v>1.0033</v>
+      </c>
+      <c r="E3" s="5" t="inlineStr"/>
       <c r="F3" s="5" t="inlineStr"/>
       <c r="G3" s="5" t="inlineStr"/>
       <c r="H3" s="5" t="inlineStr"/>
       <c r="I3" s="5" t="inlineStr"/>
-      <c r="J3" s="5" t="inlineStr"/>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="inlineStr"/>
-      <c r="M3" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N3" s="5" t="inlineStr"/>
-      <c r="O3" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr"/>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr"/>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr"/>
       <c r="P3" s="5" t="inlineStr"/>
-      <c r="Q3" s="5" t="inlineStr"/>
-      <c r="R3" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S3" s="5" t="inlineStr"/>
-      <c r="T3" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U3" s="5" t="inlineStr"/>
-      <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr"/>
+      <c r="U3" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
@@ -4045,56 +3889,53 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>1.0025</v>
+        <v>1.0037</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>1.0037</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>1.0034</v>
-      </c>
+        <v>1.0033</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr"/>
       <c r="F4" s="5" t="inlineStr"/>
       <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="inlineStr"/>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N4" s="5" t="inlineStr"/>
-      <c r="O4" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr"/>
       <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="5" t="inlineStr"/>
-      <c r="R4" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S4" s="5" t="inlineStr"/>
-      <c r="T4" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U4" s="5" t="inlineStr"/>
-      <c r="V4" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -4108,58 +3949,55 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1.0004</v>
+        <v>0.9999</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.9999</v>
-      </c>
-      <c r="E5" s="5" t="n">
         <v>1.0002</v>
       </c>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="n">
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="n">
         <v>0.1726</v>
       </c>
+      <c r="G5" s="5" t="inlineStr"/>
       <c r="H5" s="5" t="inlineStr"/>
       <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="inlineStr"/>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N5" s="5" t="inlineStr"/>
-      <c r="O5" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr"/>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr"/>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="inlineStr"/>
       <c r="P5" s="5" t="inlineStr"/>
-      <c r="Q5" s="5" t="inlineStr"/>
-      <c r="R5" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S5" s="5" t="inlineStr"/>
-      <c r="T5" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U5" s="5" t="inlineStr"/>
-      <c r="V5" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W5" s="5" t="inlineStr"/>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="inlineStr"/>
+      <c r="S5" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T5" s="5" t="inlineStr"/>
+      <c r="U5" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -4173,78 +4011,75 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.9565</v>
+        <v>0.9725</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0.9725</v>
+        <v>0.9703000000000001</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.9698</v>
+        <v>0.2073</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.2073</v>
+        <v>0.3235</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.3235</v>
+        <v>0.501077617843089</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0.501077617843089</v>
+        <v>0.212860651220515</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.212860651220515</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="5" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="R6" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S6" s="5" t="n">
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R6" s="5" t="n">
         <v>0.08</v>
       </c>
-      <c r="T6" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U6" s="5" t="n">
+      <c r="S6" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T6" s="5" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="V6" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W6" s="5" t="n">
+      <c r="U6" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V6" s="5" t="n">
         <v>0.07333333333333335</v>
       </c>
     </row>
@@ -4260,78 +4095,75 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.9565</v>
+        <v>0.9725</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.9725</v>
+        <v>0.9703000000000001</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.9698</v>
+        <v>0.1744</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.1744</v>
+        <v>0.2766</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.2766</v>
+        <v>0.501077617843089</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0.501077617843089</v>
+        <v>0.212860651220515</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0.212860651220515</v>
-      </c>
-      <c r="J7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="5" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="R7" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S7" s="5" t="n">
+      <c r="Q7" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R7" s="5" t="n">
         <v>0.08</v>
       </c>
-      <c r="T7" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U7" s="5" t="n">
+      <c r="S7" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T7" s="5" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="V7" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W7" s="5" t="n">
+      <c r="U7" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V7" s="5" t="n">
         <v>0.07333333333333335</v>
       </c>
     </row>
@@ -4347,56 +4179,53 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1.0025</v>
+        <v>1.0037</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>1.0037</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>1.0034</v>
-      </c>
+        <v>1.0033</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr"/>
       <c r="F8" s="5" t="inlineStr"/>
       <c r="G8" s="5" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="5" t="inlineStr"/>
-      <c r="J8" s="5" t="inlineStr"/>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="inlineStr"/>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N8" s="5" t="inlineStr"/>
-      <c r="O8" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O8" s="5" t="inlineStr"/>
       <c r="P8" s="5" t="inlineStr"/>
-      <c r="Q8" s="5" t="inlineStr"/>
-      <c r="R8" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S8" s="5" t="inlineStr"/>
-      <c r="T8" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U8" s="5" t="inlineStr"/>
-      <c r="V8" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W8" s="5" t="inlineStr"/>
+      <c r="Q8" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R8" s="5" t="inlineStr"/>
+      <c r="S8" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T8" s="5" t="inlineStr"/>
+      <c r="U8" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -4410,56 +4239,53 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1.0025</v>
+        <v>1.0037</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1.0037</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>1.0034</v>
-      </c>
+        <v>1.0033</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr"/>
       <c r="F9" s="5" t="inlineStr"/>
       <c r="G9" s="5" t="inlineStr"/>
       <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="5" t="inlineStr"/>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr"/>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N9" s="5" t="inlineStr"/>
-      <c r="O9" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="inlineStr"/>
       <c r="P9" s="5" t="inlineStr"/>
-      <c r="Q9" s="5" t="inlineStr"/>
-      <c r="R9" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S9" s="5" t="inlineStr"/>
-      <c r="T9" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U9" s="5" t="inlineStr"/>
-      <c r="V9" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W9" s="5" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R9" s="5" t="inlineStr"/>
+      <c r="S9" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T9" s="5" t="inlineStr"/>
+      <c r="U9" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -4473,64 +4299,61 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>1.0043</v>
+        <v>1.0024</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>1.0024</v>
+        <v>1.0022</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>1.0022</v>
+        <v>0.2225</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.2225</v>
+        <v>0.2415</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.2415</v>
+        <v>0.511388342191138</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0.511388342191138</v>
-      </c>
-      <c r="I10" s="5" t="n">
         <v>0.22265637813532</v>
       </c>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="inlineStr"/>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N10" s="5" t="inlineStr"/>
-      <c r="O10" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O10" s="5" t="inlineStr"/>
       <c r="P10" s="5" t="inlineStr"/>
-      <c r="Q10" s="5" t="inlineStr"/>
-      <c r="R10" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S10" s="5" t="inlineStr"/>
-      <c r="T10" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U10" s="5" t="inlineStr"/>
-      <c r="V10" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W10" s="5" t="inlineStr"/>
+      <c r="Q10" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R10" s="5" t="inlineStr"/>
+      <c r="S10" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T10" s="5" t="inlineStr"/>
+      <c r="U10" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -4544,78 +4367,75 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0.9926</v>
+        <v>1.0257</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1.0257</v>
+        <v>1.0134</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1.0132</v>
+        <v>0.2199</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.2199</v>
+        <v>0.2007</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.2007</v>
+        <v>0.510590381447813</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0.510590381447813</v>
+        <v>0.225784053085401</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.225784053085401</v>
-      </c>
-      <c r="J11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P11" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W11" s="5" t="n">
+      <c r="Q11" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V11" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4631,76 +4451,73 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0.9802</v>
+        <v>1.0252</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>1.0252</v>
+        <v>1.0137</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>1.0135</v>
-      </c>
-      <c r="F12" s="5" t="n">
         <v>0.2291</v>
       </c>
-      <c r="G12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="n">
+        <v>0.510590381447813</v>
+      </c>
       <c r="H12" s="5" t="n">
-        <v>0.510590381447813</v>
+        <v>0.225784053085401</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.225784053085401</v>
-      </c>
-      <c r="J12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O12" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P12" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W12" s="5" t="n">
+      <c r="Q12" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V12" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4716,76 +4533,73 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.9937</v>
+        <v>0.9932</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>0.9932</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>0.9955000000000001</v>
-      </c>
-      <c r="F13" s="5" t="inlineStr"/>
+        <v>0.9959</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="n">
+        <v>0.3012</v>
+      </c>
       <c r="G13" s="5" t="n">
-        <v>0.3012</v>
+        <v>0.510590381447813</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>0.510590381447813</v>
+        <v>0.225784053085401</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.225784053085401</v>
-      </c>
-      <c r="J13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O13" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="5" t="n">
         <v>0.16</v>
       </c>
-      <c r="R13" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S13" s="5" t="n">
+      <c r="Q13" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R13" s="5" t="n">
         <v>0.16</v>
       </c>
-      <c r="T13" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U13" s="5" t="n">
+      <c r="S13" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T13" s="5" t="n">
         <v>0.16</v>
       </c>
-      <c r="V13" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W13" s="5" t="n">
+      <c r="U13" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V13" s="5" t="n">
         <v>0.16</v>
       </c>
     </row>
@@ -4801,78 +4615,75 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0.9759</v>
+        <v>1.0146</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>1.0146</v>
+        <v>0.9540999999999999</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.966</v>
+        <v>0.1286</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.1286</v>
+        <v>0.2462</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.2462</v>
+        <v>0.65425629128861</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>0.65425629128861</v>
+        <v>0.512670422089759</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0.512670422089759</v>
-      </c>
-      <c r="J14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O14" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="5" t="n">
         <v>0.16</v>
       </c>
-      <c r="R14" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S14" s="5" t="n">
+      <c r="Q14" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R14" s="5" t="n">
         <v>0.16</v>
       </c>
-      <c r="T14" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U14" s="5" t="n">
+      <c r="S14" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T14" s="5" t="n">
         <v>0.16</v>
       </c>
-      <c r="V14" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W14" s="5" t="n">
+      <c r="U14" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V14" s="5" t="n">
         <v>0.16</v>
       </c>
     </row>
@@ -4888,78 +4699,75 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0.9766</v>
+        <v>1.003</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1.003</v>
+        <v>0.9664</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.9723000000000001</v>
+        <v>0.1131</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.1131</v>
+        <v>0.2411</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.2411</v>
+        <v>0.65425629128861</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>0.65425629128861</v>
+        <v>0.512670422089759</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.512670422089759</v>
-      </c>
-      <c r="J15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O15" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="5" t="n">
         <v>0.16</v>
       </c>
-      <c r="R15" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S15" s="5" t="n">
+      <c r="Q15" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R15" s="5" t="n">
         <v>0.16</v>
       </c>
-      <c r="T15" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U15" s="5" t="n">
+      <c r="S15" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T15" s="5" t="n">
         <v>0.16</v>
       </c>
-      <c r="V15" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W15" s="5" t="n">
+      <c r="U15" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V15" s="5" t="n">
         <v>0.16</v>
       </c>
     </row>
@@ -4975,78 +4783,75 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.9787</v>
+        <v>0.9897</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>0.9897</v>
+        <v>0.9741</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.9766</v>
+        <v>0.0897</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.0897</v>
+        <v>0.1273</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.1273</v>
+        <v>0.65425629128861</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>0.65425629128861</v>
+        <v>0.512670422089759</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.512670422089759</v>
-      </c>
-      <c r="J16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O16" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="5" t="n">
         <v>0.16</v>
       </c>
-      <c r="R16" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S16" s="5" t="n">
+      <c r="Q16" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R16" s="5" t="n">
         <v>0.16</v>
       </c>
-      <c r="T16" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U16" s="5" t="n">
+      <c r="S16" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T16" s="5" t="n">
         <v>0.16</v>
       </c>
-      <c r="V16" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W16" s="5" t="n">
+      <c r="U16" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V16" s="5" t="n">
         <v>0.16</v>
       </c>
     </row>
@@ -5062,78 +4867,75 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>0.9751</v>
+        <v>0.9837</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0.9837</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.9781</v>
+        <v>0.1184</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.1184</v>
+        <v>0.2031</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.2031</v>
+        <v>0.65425629128861</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>0.65425629128861</v>
+        <v>0.512670422089759</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>0.512670422089759</v>
-      </c>
-      <c r="J17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O17" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="5" t="n">
         <v>0.16</v>
       </c>
-      <c r="R17" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S17" s="5" t="n">
+      <c r="Q17" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R17" s="5" t="n">
         <v>0.16</v>
       </c>
-      <c r="T17" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U17" s="5" t="n">
+      <c r="S17" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T17" s="5" t="n">
         <v>0.16</v>
       </c>
-      <c r="V17" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W17" s="5" t="n">
+      <c r="U17" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V17" s="5" t="n">
         <v>0.16</v>
       </c>
     </row>
@@ -5149,78 +4951,75 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.9993</v>
+        <v>1.0127</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>1.0127</v>
+        <v>1.011</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>1.0106</v>
+        <v>0.2268</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.2268</v>
+        <v>0.2284</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.2284</v>
+        <v>0.510590381447813</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>0.510590381447813</v>
+        <v>0.225784053085401</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>0.225784053085401</v>
-      </c>
-      <c r="J18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O18" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P18" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W18" s="5" t="n">
+      <c r="Q18" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V18" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5236,78 +5035,75 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>0.9608</v>
+        <v>0.9735</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>0.9735</v>
+        <v>0.9709</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0.9709</v>
+        <v>0.1842</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.1842</v>
+        <v>0.3589</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.3589</v>
+        <v>0.501077617843089</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>0.501077617843089</v>
+        <v>0.212860651220515</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>0.212860651220515</v>
-      </c>
-      <c r="J19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O19" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="5" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="R19" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S19" s="5" t="n">
+      <c r="Q19" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R19" s="5" t="n">
         <v>0.08</v>
       </c>
-      <c r="T19" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U19" s="5" t="n">
+      <c r="S19" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T19" s="5" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="V19" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W19" s="5" t="n">
+      <c r="U19" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V19" s="5" t="n">
         <v>0.07333333333333335</v>
       </c>
     </row>
@@ -5323,64 +5119,61 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>1.0102</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>0.9945000000000001</v>
+        <v>0.9968</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.9963</v>
+        <v>0.1987</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.1987</v>
+        <v>0.2973</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.2973</v>
+        <v>0.511370986967519</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>0.511370986967519</v>
-      </c>
-      <c r="I20" s="5" t="n">
         <v>0.22945882760626</v>
       </c>
-      <c r="J20" s="5" t="inlineStr"/>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L20" s="5" t="inlineStr"/>
-      <c r="M20" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N20" s="5" t="inlineStr"/>
-      <c r="O20" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O20" s="5" t="inlineStr"/>
       <c r="P20" s="5" t="inlineStr"/>
-      <c r="Q20" s="5" t="inlineStr"/>
-      <c r="R20" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S20" s="5" t="inlineStr"/>
-      <c r="T20" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U20" s="5" t="inlineStr"/>
-      <c r="V20" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W20" s="5" t="inlineStr"/>
+      <c r="Q20" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R20" s="5" t="inlineStr"/>
+      <c r="S20" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T20" s="5" t="inlineStr"/>
+      <c r="U20" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
@@ -5394,64 +5187,61 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1.009</v>
+        <v>0.9952</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>0.9952</v>
+        <v>0.9978</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0.9967</v>
+        <v>0.2394</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.2394</v>
+        <v>0.3511</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.3511</v>
+        <v>0.511370986967519</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>0.511370986967519</v>
-      </c>
-      <c r="I21" s="5" t="n">
         <v>0.22945882760626</v>
       </c>
-      <c r="J21" s="5" t="inlineStr"/>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr"/>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N21" s="5" t="inlineStr"/>
-      <c r="O21" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O21" s="5" t="inlineStr"/>
       <c r="P21" s="5" t="inlineStr"/>
-      <c r="Q21" s="5" t="inlineStr"/>
-      <c r="R21" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S21" s="5" t="inlineStr"/>
-      <c r="T21" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U21" s="5" t="inlineStr"/>
-      <c r="V21" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W21" s="5" t="inlineStr"/>
+      <c r="Q21" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R21" s="5" t="inlineStr"/>
+      <c r="S21" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T21" s="5" t="inlineStr"/>
+      <c r="U21" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
@@ -5465,60 +5255,57 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.9755</v>
+        <v>0.9333</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>0.9333</v>
+        <v>0.9527</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.9458</v>
+        <v>0.1746</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.1746</v>
-      </c>
-      <c r="G22" s="5" t="n">
         <v>0.254</v>
       </c>
+      <c r="G22" s="5" t="inlineStr"/>
       <c r="H22" s="5" t="inlineStr"/>
       <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L22" s="5" t="inlineStr"/>
-      <c r="M22" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N22" s="5" t="inlineStr"/>
-      <c r="O22" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O22" s="5" t="inlineStr"/>
       <c r="P22" s="5" t="inlineStr"/>
-      <c r="Q22" s="5" t="inlineStr"/>
-      <c r="R22" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S22" s="5" t="inlineStr"/>
-      <c r="T22" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U22" s="5" t="inlineStr"/>
-      <c r="V22" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W22" s="5" t="inlineStr"/>
+      <c r="Q22" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R22" s="5" t="inlineStr"/>
+      <c r="S22" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T22" s="5" t="inlineStr"/>
+      <c r="U22" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -5532,60 +5319,57 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>0.9308999999999999</v>
+        <v>0.9467</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>0.9467</v>
+        <v>0.9417</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0.9408</v>
+        <v>0.1389</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.1389</v>
-      </c>
-      <c r="G23" s="5" t="n">
         <v>0.0515</v>
       </c>
+      <c r="G23" s="5" t="inlineStr"/>
       <c r="H23" s="5" t="inlineStr"/>
       <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr"/>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N23" s="5" t="inlineStr"/>
-      <c r="O23" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr"/>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O23" s="5" t="inlineStr"/>
       <c r="P23" s="5" t="inlineStr"/>
-      <c r="Q23" s="5" t="inlineStr"/>
-      <c r="R23" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S23" s="5" t="inlineStr"/>
-      <c r="T23" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U23" s="5" t="inlineStr"/>
-      <c r="V23" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W23" s="5" t="inlineStr"/>
+      <c r="Q23" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R23" s="5" t="inlineStr"/>
+      <c r="S23" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T23" s="5" t="inlineStr"/>
+      <c r="U23" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -5599,60 +5383,57 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>0.9486</v>
+        <v>0.9604</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>0.9604</v>
+        <v>0.9614</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0.9605</v>
+        <v>0.0134</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.0134</v>
-      </c>
-      <c r="G24" s="5" t="n">
         <v>0.0062</v>
       </c>
+      <c r="G24" s="5" t="inlineStr"/>
       <c r="H24" s="5" t="inlineStr"/>
       <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L24" s="5" t="inlineStr"/>
-      <c r="M24" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N24" s="5" t="inlineStr"/>
-      <c r="O24" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O24" s="5" t="inlineStr"/>
       <c r="P24" s="5" t="inlineStr"/>
-      <c r="Q24" s="5" t="inlineStr"/>
-      <c r="R24" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S24" s="5" t="inlineStr"/>
-      <c r="T24" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U24" s="5" t="inlineStr"/>
-      <c r="V24" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W24" s="5" t="inlineStr"/>
+      <c r="Q24" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R24" s="5" t="inlineStr"/>
+      <c r="S24" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T24" s="5" t="inlineStr"/>
+      <c r="U24" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -5666,58 +5447,55 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>0.9643</v>
+        <v>0.9697</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>0.9697</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>0.9711</v>
-      </c>
-      <c r="F25" s="5" t="inlineStr"/>
-      <c r="G25" s="5" t="n">
+        <v>0.9687</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="n">
         <v>0.176</v>
       </c>
+      <c r="G25" s="5" t="inlineStr"/>
       <c r="H25" s="5" t="inlineStr"/>
       <c r="I25" s="5" t="inlineStr"/>
-      <c r="J25" s="5" t="inlineStr"/>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr"/>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N25" s="5" t="inlineStr"/>
-      <c r="O25" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O25" s="5" t="inlineStr"/>
       <c r="P25" s="5" t="inlineStr"/>
-      <c r="Q25" s="5" t="inlineStr"/>
-      <c r="R25" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S25" s="5" t="inlineStr"/>
-      <c r="T25" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U25" s="5" t="inlineStr"/>
-      <c r="V25" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W25" s="5" t="inlineStr"/>
+      <c r="Q25" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R25" s="5" t="inlineStr"/>
+      <c r="S25" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T25" s="5" t="inlineStr"/>
+      <c r="U25" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
@@ -5731,56 +5509,53 @@
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>0.9641</v>
+        <v>0.9689</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>0.9689</v>
-      </c>
-      <c r="E26" s="5" t="n">
-        <v>0.971</v>
-      </c>
+        <v>0.9687</v>
+      </c>
+      <c r="E26" s="5" t="inlineStr"/>
       <c r="F26" s="5" t="inlineStr"/>
       <c r="G26" s="5" t="inlineStr"/>
       <c r="H26" s="5" t="inlineStr"/>
       <c r="I26" s="5" t="inlineStr"/>
-      <c r="J26" s="5" t="inlineStr"/>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L26" s="5" t="inlineStr"/>
-      <c r="M26" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N26" s="5" t="inlineStr"/>
-      <c r="O26" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O26" s="5" t="inlineStr"/>
       <c r="P26" s="5" t="inlineStr"/>
-      <c r="Q26" s="5" t="inlineStr"/>
-      <c r="R26" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S26" s="5" t="inlineStr"/>
-      <c r="T26" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U26" s="5" t="inlineStr"/>
-      <c r="V26" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W26" s="5" t="inlineStr"/>
+      <c r="Q26" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R26" s="5" t="inlineStr"/>
+      <c r="S26" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T26" s="5" t="inlineStr"/>
+      <c r="U26" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -5794,60 +5569,57 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>0.9565</v>
+        <v>0.9663</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>0.9663</v>
+        <v>0.9628</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>0.9635</v>
+        <v>0.0813</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>0.0813</v>
-      </c>
-      <c r="G27" s="5" t="n">
         <v>0.1169</v>
       </c>
+      <c r="G27" s="5" t="inlineStr"/>
       <c r="H27" s="5" t="inlineStr"/>
       <c r="I27" s="5" t="inlineStr"/>
-      <c r="J27" s="5" t="inlineStr"/>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr"/>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N27" s="5" t="inlineStr"/>
-      <c r="O27" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O27" s="5" t="inlineStr"/>
       <c r="P27" s="5" t="inlineStr"/>
-      <c r="Q27" s="5" t="inlineStr"/>
-      <c r="R27" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S27" s="5" t="inlineStr"/>
-      <c r="T27" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U27" s="5" t="inlineStr"/>
-      <c r="V27" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W27" s="5" t="inlineStr"/>
+      <c r="Q27" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R27" s="5" t="inlineStr"/>
+      <c r="S27" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T27" s="5" t="inlineStr"/>
+      <c r="U27" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -5861,60 +5633,57 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>0.9526</v>
+        <v>0.9608</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>0.9608</v>
+        <v>0.9606</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0.962</v>
+        <v>0.0914</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.0914</v>
-      </c>
-      <c r="G28" s="5" t="n">
         <v>0.1053</v>
       </c>
+      <c r="G28" s="5" t="inlineStr"/>
       <c r="H28" s="5" t="inlineStr"/>
       <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L28" s="5" t="inlineStr"/>
-      <c r="M28" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N28" s="5" t="inlineStr"/>
-      <c r="O28" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O28" s="5" t="inlineStr"/>
       <c r="P28" s="5" t="inlineStr"/>
-      <c r="Q28" s="5" t="inlineStr"/>
-      <c r="R28" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S28" s="5" t="inlineStr"/>
-      <c r="T28" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U28" s="5" t="inlineStr"/>
-      <c r="V28" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W28" s="5" t="inlineStr"/>
+      <c r="Q28" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R28" s="5" t="inlineStr"/>
+      <c r="S28" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T28" s="5" t="inlineStr"/>
+      <c r="U28" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
@@ -5928,60 +5697,57 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>0.9423</v>
+        <v>0.956</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>0.956</v>
+        <v>0.9533</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0.9538</v>
+        <v>0.0092</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0.0092</v>
-      </c>
-      <c r="G29" s="5" t="n">
         <v>0.0033</v>
       </c>
+      <c r="G29" s="5" t="inlineStr"/>
       <c r="H29" s="5" t="inlineStr"/>
       <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L29" s="5" t="inlineStr"/>
-      <c r="M29" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N29" s="5" t="inlineStr"/>
-      <c r="O29" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O29" s="5" t="inlineStr"/>
       <c r="P29" s="5" t="inlineStr"/>
-      <c r="Q29" s="5" t="inlineStr"/>
-      <c r="R29" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S29" s="5" t="inlineStr"/>
-      <c r="T29" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U29" s="5" t="inlineStr"/>
-      <c r="V29" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W29" s="5" t="inlineStr"/>
+      <c r="Q29" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R29" s="5" t="inlineStr"/>
+      <c r="S29" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T29" s="5" t="inlineStr"/>
+      <c r="U29" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -5995,60 +5761,57 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>0.9423</v>
+        <v>0.956</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>0.956</v>
+        <v>0.9533</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0.9538</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.008500000000000001</v>
-      </c>
-      <c r="G30" s="5" t="n">
         <v>0.0038</v>
       </c>
+      <c r="G30" s="5" t="inlineStr"/>
       <c r="H30" s="5" t="inlineStr"/>
       <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L30" s="5" t="inlineStr"/>
-      <c r="M30" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N30" s="5" t="inlineStr"/>
-      <c r="O30" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="inlineStr"/>
+      <c r="N30" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O30" s="5" t="inlineStr"/>
       <c r="P30" s="5" t="inlineStr"/>
-      <c r="Q30" s="5" t="inlineStr"/>
-      <c r="R30" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S30" s="5" t="inlineStr"/>
-      <c r="T30" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U30" s="5" t="inlineStr"/>
-      <c r="V30" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W30" s="5" t="inlineStr"/>
+      <c r="Q30" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R30" s="5" t="inlineStr"/>
+      <c r="S30" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T30" s="5" t="inlineStr"/>
+      <c r="U30" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
@@ -6062,60 +5825,57 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>0.9423</v>
+        <v>0.956</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>0.956</v>
+        <v>0.9533</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0.9538</v>
+        <v>0.0092</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>0.0092</v>
-      </c>
-      <c r="G31" s="5" t="n">
         <v>0.0027</v>
       </c>
+      <c r="G31" s="5" t="inlineStr"/>
       <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="5" t="inlineStr"/>
-      <c r="J31" s="5" t="inlineStr"/>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L31" s="5" t="inlineStr"/>
-      <c r="M31" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N31" s="5" t="inlineStr"/>
-      <c r="O31" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr"/>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O31" s="5" t="inlineStr"/>
       <c r="P31" s="5" t="inlineStr"/>
-      <c r="Q31" s="5" t="inlineStr"/>
-      <c r="R31" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S31" s="5" t="inlineStr"/>
-      <c r="T31" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U31" s="5" t="inlineStr"/>
-      <c r="V31" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W31" s="5" t="inlineStr"/>
+      <c r="Q31" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R31" s="5" t="inlineStr"/>
+      <c r="S31" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T31" s="5" t="inlineStr"/>
+      <c r="U31" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
@@ -6129,60 +5889,57 @@
         </is>
       </c>
       <c r="C32" s="5" t="n">
-        <v>0.9709</v>
+        <v>0.9297</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>0.9297</v>
+        <v>0.9468</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.1058</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>0.1058</v>
-      </c>
-      <c r="G32" s="5" t="n">
         <v>0.1941</v>
       </c>
+      <c r="G32" s="5" t="inlineStr"/>
       <c r="H32" s="5" t="inlineStr"/>
       <c r="I32" s="5" t="inlineStr"/>
-      <c r="J32" s="5" t="inlineStr"/>
-      <c r="K32" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L32" s="5" t="inlineStr"/>
-      <c r="M32" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N32" s="5" t="inlineStr"/>
-      <c r="O32" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr"/>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr"/>
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O32" s="5" t="inlineStr"/>
       <c r="P32" s="5" t="inlineStr"/>
-      <c r="Q32" s="5" t="inlineStr"/>
-      <c r="R32" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S32" s="5" t="inlineStr"/>
-      <c r="T32" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U32" s="5" t="inlineStr"/>
-      <c r="V32" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W32" s="5" t="inlineStr"/>
+      <c r="Q32" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R32" s="5" t="inlineStr"/>
+      <c r="S32" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T32" s="5" t="inlineStr"/>
+      <c r="U32" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
@@ -6196,60 +5953,57 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>0.9709</v>
+        <v>0.9297</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>0.9297</v>
+        <v>0.9468</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.1939</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>0.1939</v>
-      </c>
-      <c r="G33" s="5" t="n">
         <v>0.2514</v>
       </c>
+      <c r="G33" s="5" t="inlineStr"/>
       <c r="H33" s="5" t="inlineStr"/>
       <c r="I33" s="5" t="inlineStr"/>
-      <c r="J33" s="5" t="inlineStr"/>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L33" s="5" t="inlineStr"/>
-      <c r="M33" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N33" s="5" t="inlineStr"/>
-      <c r="O33" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr"/>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr"/>
+      <c r="N33" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O33" s="5" t="inlineStr"/>
       <c r="P33" s="5" t="inlineStr"/>
-      <c r="Q33" s="5" t="inlineStr"/>
-      <c r="R33" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S33" s="5" t="inlineStr"/>
-      <c r="T33" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U33" s="5" t="inlineStr"/>
-      <c r="V33" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W33" s="5" t="inlineStr"/>
+      <c r="Q33" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R33" s="5" t="inlineStr"/>
+      <c r="S33" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T33" s="5" t="inlineStr"/>
+      <c r="U33" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
@@ -6263,60 +6017,57 @@
         </is>
       </c>
       <c r="C34" s="5" t="n">
-        <v>0.9709</v>
+        <v>0.9297</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>0.9297</v>
+        <v>0.9468</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.1878</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.1878</v>
-      </c>
-      <c r="G34" s="5" t="n">
         <v>0.2535</v>
       </c>
+      <c r="G34" s="5" t="inlineStr"/>
       <c r="H34" s="5" t="inlineStr"/>
       <c r="I34" s="5" t="inlineStr"/>
-      <c r="J34" s="5" t="inlineStr"/>
-      <c r="K34" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L34" s="5" t="inlineStr"/>
-      <c r="M34" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N34" s="5" t="inlineStr"/>
-      <c r="O34" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr"/>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="inlineStr"/>
+      <c r="N34" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O34" s="5" t="inlineStr"/>
       <c r="P34" s="5" t="inlineStr"/>
-      <c r="Q34" s="5" t="inlineStr"/>
-      <c r="R34" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S34" s="5" t="inlineStr"/>
-      <c r="T34" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U34" s="5" t="inlineStr"/>
-      <c r="V34" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W34" s="5" t="inlineStr"/>
+      <c r="Q34" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R34" s="5" t="inlineStr"/>
+      <c r="S34" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T34" s="5" t="inlineStr"/>
+      <c r="U34" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
@@ -6330,60 +6081,57 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>0.9576</v>
+        <v>0.9689</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>0.9689</v>
+        <v>0.9661</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>0.09669999999999999</v>
-      </c>
-      <c r="G35" s="5" t="n">
         <v>0.1438</v>
       </c>
+      <c r="G35" s="5" t="inlineStr"/>
       <c r="H35" s="5" t="inlineStr"/>
       <c r="I35" s="5" t="inlineStr"/>
-      <c r="J35" s="5" t="inlineStr"/>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L35" s="5" t="inlineStr"/>
-      <c r="M35" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N35" s="5" t="inlineStr"/>
-      <c r="O35" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr"/>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr"/>
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O35" s="5" t="inlineStr"/>
       <c r="P35" s="5" t="inlineStr"/>
-      <c r="Q35" s="5" t="inlineStr"/>
-      <c r="R35" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S35" s="5" t="inlineStr"/>
-      <c r="T35" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U35" s="5" t="inlineStr"/>
-      <c r="V35" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W35" s="5" t="inlineStr"/>
+      <c r="Q35" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R35" s="5" t="inlineStr"/>
+      <c r="S35" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T35" s="5" t="inlineStr"/>
+      <c r="U35" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
@@ -6397,60 +6145,57 @@
         </is>
       </c>
       <c r="C36" s="5" t="n">
-        <v>0.9576</v>
+        <v>0.9689</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>0.9689</v>
+        <v>0.9661</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.1085</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0.1085</v>
-      </c>
-      <c r="G36" s="5" t="n">
         <v>0.1628</v>
       </c>
+      <c r="G36" s="5" t="inlineStr"/>
       <c r="H36" s="5" t="inlineStr"/>
       <c r="I36" s="5" t="inlineStr"/>
-      <c r="J36" s="5" t="inlineStr"/>
-      <c r="K36" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L36" s="5" t="inlineStr"/>
-      <c r="M36" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N36" s="5" t="inlineStr"/>
-      <c r="O36" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr"/>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="inlineStr"/>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O36" s="5" t="inlineStr"/>
       <c r="P36" s="5" t="inlineStr"/>
-      <c r="Q36" s="5" t="inlineStr"/>
-      <c r="R36" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S36" s="5" t="inlineStr"/>
-      <c r="T36" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U36" s="5" t="inlineStr"/>
-      <c r="V36" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W36" s="5" t="inlineStr"/>
+      <c r="Q36" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R36" s="5" t="inlineStr"/>
+      <c r="S36" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T36" s="5" t="inlineStr"/>
+      <c r="U36" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
@@ -6464,60 +6209,57 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>0.9162</v>
+        <v>0.9403</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>0.9403</v>
+        <v>0.9387</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0.9379</v>
+        <v>0.1885</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>0.1885</v>
-      </c>
-      <c r="G37" s="5" t="n">
         <v>0.287</v>
       </c>
+      <c r="G37" s="5" t="inlineStr"/>
       <c r="H37" s="5" t="inlineStr"/>
       <c r="I37" s="5" t="inlineStr"/>
-      <c r="J37" s="5" t="inlineStr"/>
-      <c r="K37" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L37" s="5" t="inlineStr"/>
-      <c r="M37" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N37" s="5" t="inlineStr"/>
-      <c r="O37" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr"/>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr"/>
+      <c r="N37" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O37" s="5" t="inlineStr"/>
       <c r="P37" s="5" t="inlineStr"/>
-      <c r="Q37" s="5" t="inlineStr"/>
-      <c r="R37" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S37" s="5" t="inlineStr"/>
-      <c r="T37" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U37" s="5" t="inlineStr"/>
-      <c r="V37" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W37" s="5" t="inlineStr"/>
+      <c r="Q37" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R37" s="5" t="inlineStr"/>
+      <c r="S37" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T37" s="5" t="inlineStr"/>
+      <c r="U37" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
@@ -6531,60 +6273,57 @@
         </is>
       </c>
       <c r="C38" s="5" t="n">
-        <v>0.9467</v>
+        <v>0.9579</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>0.9579</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>0.9583</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0.07389999999999999</v>
-      </c>
-      <c r="G38" s="5" t="n">
         <v>0.1193</v>
       </c>
+      <c r="G38" s="5" t="inlineStr"/>
       <c r="H38" s="5" t="inlineStr"/>
       <c r="I38" s="5" t="inlineStr"/>
-      <c r="J38" s="5" t="inlineStr"/>
-      <c r="K38" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L38" s="5" t="inlineStr"/>
-      <c r="M38" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N38" s="5" t="inlineStr"/>
-      <c r="O38" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr"/>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M38" s="5" t="inlineStr"/>
+      <c r="N38" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O38" s="5" t="inlineStr"/>
       <c r="P38" s="5" t="inlineStr"/>
-      <c r="Q38" s="5" t="inlineStr"/>
-      <c r="R38" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S38" s="5" t="inlineStr"/>
-      <c r="T38" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U38" s="5" t="inlineStr"/>
-      <c r="V38" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W38" s="5" t="inlineStr"/>
+      <c r="Q38" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R38" s="5" t="inlineStr"/>
+      <c r="S38" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T38" s="5" t="inlineStr"/>
+      <c r="U38" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
@@ -6598,60 +6337,57 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>0.9608</v>
+        <v>0.9735</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>0.9735</v>
+        <v>0.9709</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>0.9709</v>
+        <v>0.0914</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>0.0914</v>
-      </c>
-      <c r="G39" s="5" t="n">
         <v>0.1943</v>
       </c>
+      <c r="G39" s="5" t="inlineStr"/>
       <c r="H39" s="5" t="inlineStr"/>
       <c r="I39" s="5" t="inlineStr"/>
-      <c r="J39" s="5" t="inlineStr"/>
-      <c r="K39" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L39" s="5" t="inlineStr"/>
-      <c r="M39" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N39" s="5" t="inlineStr"/>
-      <c r="O39" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr"/>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr"/>
+      <c r="N39" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O39" s="5" t="inlineStr"/>
       <c r="P39" s="5" t="inlineStr"/>
-      <c r="Q39" s="5" t="inlineStr"/>
-      <c r="R39" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S39" s="5" t="inlineStr"/>
-      <c r="T39" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U39" s="5" t="inlineStr"/>
-      <c r="V39" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W39" s="5" t="inlineStr"/>
+      <c r="Q39" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R39" s="5" t="inlineStr"/>
+      <c r="S39" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T39" s="5" t="inlineStr"/>
+      <c r="U39" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
@@ -6665,60 +6401,57 @@
         </is>
       </c>
       <c r="C40" s="5" t="n">
-        <v>0.9613</v>
+        <v>0.9695</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>0.9695</v>
+        <v>0.9699</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>0.9694</v>
+        <v>0.0071</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>0.0071</v>
-      </c>
-      <c r="G40" s="5" t="n">
         <v>0.0037</v>
       </c>
+      <c r="G40" s="5" t="inlineStr"/>
       <c r="H40" s="5" t="inlineStr"/>
       <c r="I40" s="5" t="inlineStr"/>
-      <c r="J40" s="5" t="inlineStr"/>
-      <c r="K40" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L40" s="5" t="inlineStr"/>
-      <c r="M40" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N40" s="5" t="inlineStr"/>
-      <c r="O40" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr"/>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M40" s="5" t="inlineStr"/>
+      <c r="N40" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O40" s="5" t="inlineStr"/>
       <c r="P40" s="5" t="inlineStr"/>
-      <c r="Q40" s="5" t="inlineStr"/>
-      <c r="R40" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S40" s="5" t="inlineStr"/>
-      <c r="T40" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U40" s="5" t="inlineStr"/>
-      <c r="V40" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W40" s="5" t="inlineStr"/>
+      <c r="Q40" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R40" s="5" t="inlineStr"/>
+      <c r="S40" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T40" s="5" t="inlineStr"/>
+      <c r="U40" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
@@ -6732,60 +6465,57 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>0.9613</v>
+        <v>0.9695</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>0.9695</v>
+        <v>0.9699</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>0.9694</v>
+        <v>0.0101</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>0.0101</v>
-      </c>
-      <c r="G41" s="5" t="n">
         <v>0.0026</v>
       </c>
+      <c r="G41" s="5" t="inlineStr"/>
       <c r="H41" s="5" t="inlineStr"/>
       <c r="I41" s="5" t="inlineStr"/>
-      <c r="J41" s="5" t="inlineStr"/>
-      <c r="K41" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L41" s="5" t="inlineStr"/>
-      <c r="M41" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N41" s="5" t="inlineStr"/>
-      <c r="O41" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr"/>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr"/>
+      <c r="N41" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O41" s="5" t="inlineStr"/>
       <c r="P41" s="5" t="inlineStr"/>
-      <c r="Q41" s="5" t="inlineStr"/>
-      <c r="R41" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S41" s="5" t="inlineStr"/>
-      <c r="T41" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U41" s="5" t="inlineStr"/>
-      <c r="V41" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W41" s="5" t="inlineStr"/>
+      <c r="Q41" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R41" s="5" t="inlineStr"/>
+      <c r="S41" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T41" s="5" t="inlineStr"/>
+      <c r="U41" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
@@ -6799,60 +6529,57 @@
         </is>
       </c>
       <c r="C42" s="5" t="n">
-        <v>0.8932</v>
+        <v>0.9157</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>0.9157</v>
+        <v>0.9132</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0.9112</v>
+        <v>0.1075</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.1075</v>
-      </c>
-      <c r="G42" s="5" t="n">
         <v>0.1825</v>
       </c>
+      <c r="G42" s="5" t="inlineStr"/>
       <c r="H42" s="5" t="inlineStr"/>
       <c r="I42" s="5" t="inlineStr"/>
-      <c r="J42" s="5" t="inlineStr"/>
-      <c r="K42" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L42" s="5" t="inlineStr"/>
-      <c r="M42" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N42" s="5" t="inlineStr"/>
-      <c r="O42" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="inlineStr"/>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M42" s="5" t="inlineStr"/>
+      <c r="N42" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O42" s="5" t="inlineStr"/>
       <c r="P42" s="5" t="inlineStr"/>
-      <c r="Q42" s="5" t="inlineStr"/>
-      <c r="R42" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S42" s="5" t="inlineStr"/>
-      <c r="T42" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U42" s="5" t="inlineStr"/>
-      <c r="V42" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W42" s="5" t="inlineStr"/>
+      <c r="Q42" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R42" s="5" t="inlineStr"/>
+      <c r="S42" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T42" s="5" t="inlineStr"/>
+      <c r="U42" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
@@ -6866,60 +6593,57 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>1.0025</v>
+        <v>1.0037</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>1.0037</v>
+        <v>1.0033</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>1.0034</v>
+        <v>0</v>
       </c>
       <c r="F43" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G43" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="G43" s="5" t="inlineStr"/>
       <c r="H43" s="5" t="inlineStr"/>
       <c r="I43" s="5" t="inlineStr"/>
-      <c r="J43" s="5" t="inlineStr"/>
-      <c r="K43" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L43" s="5" t="inlineStr"/>
-      <c r="M43" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N43" s="5" t="inlineStr"/>
-      <c r="O43" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr"/>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr"/>
+      <c r="N43" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O43" s="5" t="inlineStr"/>
       <c r="P43" s="5" t="inlineStr"/>
-      <c r="Q43" s="5" t="inlineStr"/>
-      <c r="R43" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S43" s="5" t="inlineStr"/>
-      <c r="T43" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U43" s="5" t="inlineStr"/>
-      <c r="V43" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W43" s="5" t="inlineStr"/>
+      <c r="Q43" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R43" s="5" t="inlineStr"/>
+      <c r="S43" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T43" s="5" t="inlineStr"/>
+      <c r="U43" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
@@ -6933,60 +6657,57 @@
         </is>
       </c>
       <c r="C44" s="5" t="n">
-        <v>0.9467</v>
+        <v>0.9579</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>0.9579</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0.9583</v>
+        <v>0.1016</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.1016</v>
-      </c>
-      <c r="G44" s="5" t="n">
         <v>0.0847</v>
       </c>
+      <c r="G44" s="5" t="inlineStr"/>
       <c r="H44" s="5" t="inlineStr"/>
       <c r="I44" s="5" t="inlineStr"/>
-      <c r="J44" s="5" t="inlineStr"/>
-      <c r="K44" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L44" s="5" t="inlineStr"/>
-      <c r="M44" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N44" s="5" t="inlineStr"/>
-      <c r="O44" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="inlineStr"/>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M44" s="5" t="inlineStr"/>
+      <c r="N44" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O44" s="5" t="inlineStr"/>
       <c r="P44" s="5" t="inlineStr"/>
-      <c r="Q44" s="5" t="inlineStr"/>
-      <c r="R44" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S44" s="5" t="inlineStr"/>
-      <c r="T44" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U44" s="5" t="inlineStr"/>
-      <c r="V44" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W44" s="5" t="inlineStr"/>
+      <c r="Q44" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R44" s="5" t="inlineStr"/>
+      <c r="S44" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T44" s="5" t="inlineStr"/>
+      <c r="U44" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V44" s="5" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
@@ -7000,60 +6721,57 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>0.9547</v>
+        <v>0.9624</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>0.9624</v>
+        <v>0.9611</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>0.9611</v>
+        <v>0.0239</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>0.0239</v>
-      </c>
-      <c r="G45" s="5" t="n">
         <v>0.0203</v>
       </c>
+      <c r="G45" s="5" t="inlineStr"/>
       <c r="H45" s="5" t="inlineStr"/>
       <c r="I45" s="5" t="inlineStr"/>
-      <c r="J45" s="5" t="inlineStr"/>
-      <c r="K45" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L45" s="5" t="inlineStr"/>
-      <c r="M45" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N45" s="5" t="inlineStr"/>
-      <c r="O45" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr"/>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr"/>
+      <c r="N45" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O45" s="5" t="inlineStr"/>
       <c r="P45" s="5" t="inlineStr"/>
-      <c r="Q45" s="5" t="inlineStr"/>
-      <c r="R45" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S45" s="5" t="inlineStr"/>
-      <c r="T45" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U45" s="5" t="inlineStr"/>
-      <c r="V45" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W45" s="5" t="inlineStr"/>
+      <c r="Q45" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R45" s="5" t="inlineStr"/>
+      <c r="S45" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T45" s="5" t="inlineStr"/>
+      <c r="U45" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
@@ -7067,60 +6785,57 @@
         </is>
       </c>
       <c r="C46" s="5" t="n">
-        <v>0.8179</v>
+        <v>0.8456</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>0.8456</v>
+        <v>0.8476</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>0.844</v>
+        <v>0.0871</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.0871</v>
-      </c>
-      <c r="G46" s="5" t="n">
         <v>0.1598</v>
       </c>
+      <c r="G46" s="5" t="inlineStr"/>
       <c r="H46" s="5" t="inlineStr"/>
       <c r="I46" s="5" t="inlineStr"/>
-      <c r="J46" s="5" t="inlineStr"/>
-      <c r="K46" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L46" s="5" t="inlineStr"/>
-      <c r="M46" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N46" s="5" t="inlineStr"/>
-      <c r="O46" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="inlineStr"/>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M46" s="5" t="inlineStr"/>
+      <c r="N46" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O46" s="5" t="inlineStr"/>
       <c r="P46" s="5" t="inlineStr"/>
-      <c r="Q46" s="5" t="inlineStr"/>
-      <c r="R46" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S46" s="5" t="inlineStr"/>
-      <c r="T46" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U46" s="5" t="inlineStr"/>
-      <c r="V46" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W46" s="5" t="inlineStr"/>
+      <c r="Q46" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R46" s="5" t="inlineStr"/>
+      <c r="S46" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T46" s="5" t="inlineStr"/>
+      <c r="U46" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
@@ -7134,60 +6849,57 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>0.9498</v>
+        <v>0.9601</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>0.9601</v>
+        <v>0.9592000000000001</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0.9605</v>
+        <v>0.0941</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>0.0941</v>
-      </c>
-      <c r="G47" s="5" t="n">
         <v>0.0426</v>
       </c>
+      <c r="G47" s="5" t="inlineStr"/>
       <c r="H47" s="5" t="inlineStr"/>
       <c r="I47" s="5" t="inlineStr"/>
-      <c r="J47" s="5" t="inlineStr"/>
-      <c r="K47" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L47" s="5" t="inlineStr"/>
-      <c r="M47" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N47" s="5" t="inlineStr"/>
-      <c r="O47" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr"/>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr"/>
+      <c r="N47" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O47" s="5" t="inlineStr"/>
       <c r="P47" s="5" t="inlineStr"/>
-      <c r="Q47" s="5" t="inlineStr"/>
-      <c r="R47" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S47" s="5" t="inlineStr"/>
-      <c r="T47" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U47" s="5" t="inlineStr"/>
-      <c r="V47" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W47" s="5" t="inlineStr"/>
+      <c r="Q47" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R47" s="5" t="inlineStr"/>
+      <c r="S47" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T47" s="5" t="inlineStr"/>
+      <c r="U47" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V47" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C47">
@@ -7220,9 +6932,9 @@
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
         <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
         <color rgb="00F8696B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="0063BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
@@ -7430,18 +7142,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W2:W47">
-    <cfRule type="colorScale" priority="21">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/SA_curtailment.xlsx
+++ b/outputs/SA_curtailment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -67,7 +67,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -82,9 +82,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -456,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W47"/>
+  <dimension ref="A1:O47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -474,14 +471,6 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -560,46 +549,6 @@
           <t>FY26-27</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Curt FY1</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Curt FY2</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Curt FY3</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Curt Avg</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Offl FY1</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Offl FY2</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Offl FY3</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Offl Avg</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -651,14 +600,6 @@
       <c r="O2" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="P2" s="6" t="inlineStr"/>
-      <c r="Q2" s="6" t="inlineStr"/>
-      <c r="R2" s="6" t="inlineStr"/>
-      <c r="S2" s="6" t="inlineStr"/>
-      <c r="T2" s="6" t="inlineStr"/>
-      <c r="U2" s="6" t="inlineStr"/>
-      <c r="V2" s="6" t="inlineStr"/>
-      <c r="W2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -706,14 +647,6 @@
       <c r="O3" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="P3" s="6" t="inlineStr"/>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr"/>
-      <c r="V3" s="6" t="inlineStr"/>
-      <c r="W3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -761,14 +694,6 @@
       <c r="O4" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="P4" s="6" t="inlineStr"/>
-      <c r="Q4" s="6" t="inlineStr"/>
-      <c r="R4" s="6" t="inlineStr"/>
-      <c r="S4" s="6" t="inlineStr"/>
-      <c r="T4" s="6" t="inlineStr"/>
-      <c r="U4" s="6" t="inlineStr"/>
-      <c r="V4" s="6" t="inlineStr"/>
-      <c r="W4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -818,14 +743,6 @@
       <c r="O5" s="5" t="n">
         <v>1.0002</v>
       </c>
-      <c r="P5" s="6" t="inlineStr"/>
-      <c r="Q5" s="6" t="inlineStr"/>
-      <c r="R5" s="6" t="inlineStr"/>
-      <c r="S5" s="6" t="inlineStr"/>
-      <c r="T5" s="6" t="inlineStr"/>
-      <c r="U5" s="6" t="inlineStr"/>
-      <c r="V5" s="6" t="inlineStr"/>
-      <c r="W5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -887,30 +804,6 @@
       <c r="O6" s="5" t="n">
         <v>0.9703000000000001</v>
       </c>
-      <c r="P6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="U6" s="6" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="V6" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="W6" s="6" t="n">
-        <v>0.07333333333333335</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -971,30 +864,6 @@
       </c>
       <c r="O7" s="5" t="n">
         <v>0.9703000000000001</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="U7" s="6" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="V7" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="W7" s="6" t="n">
-        <v>0.07333333333333335</v>
       </c>
     </row>
     <row r="8">
@@ -1043,14 +912,6 @@
       <c r="O8" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="P8" s="6" t="inlineStr"/>
-      <c r="Q8" s="6" t="inlineStr"/>
-      <c r="R8" s="6" t="inlineStr"/>
-      <c r="S8" s="6" t="inlineStr"/>
-      <c r="T8" s="6" t="inlineStr"/>
-      <c r="U8" s="6" t="inlineStr"/>
-      <c r="V8" s="6" t="inlineStr"/>
-      <c r="W8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1098,14 +959,6 @@
       <c r="O9" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="P9" s="6" t="inlineStr"/>
-      <c r="Q9" s="6" t="inlineStr"/>
-      <c r="R9" s="6" t="inlineStr"/>
-      <c r="S9" s="6" t="inlineStr"/>
-      <c r="T9" s="6" t="inlineStr"/>
-      <c r="U9" s="6" t="inlineStr"/>
-      <c r="V9" s="6" t="inlineStr"/>
-      <c r="W9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1167,14 +1020,6 @@
       <c r="O10" s="5" t="n">
         <v>1.0022</v>
       </c>
-      <c r="P10" s="6" t="inlineStr"/>
-      <c r="Q10" s="6" t="inlineStr"/>
-      <c r="R10" s="6" t="inlineStr"/>
-      <c r="S10" s="6" t="inlineStr"/>
-      <c r="T10" s="6" t="inlineStr"/>
-      <c r="U10" s="6" t="inlineStr"/>
-      <c r="V10" s="6" t="inlineStr"/>
-      <c r="W10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1235,30 +1080,6 @@
       </c>
       <c r="O11" s="5" t="n">
         <v>1.0134</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" s="6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1319,30 +1140,6 @@
       <c r="O12" s="5" t="n">
         <v>1.0137</v>
       </c>
-      <c r="P12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" s="6" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1402,30 +1199,6 @@
       <c r="O13" s="5" t="n">
         <v>0.9959</v>
       </c>
-      <c r="P13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="U13" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="V13" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="W13" s="6" t="n">
-        <v>0.16</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1487,30 +1260,6 @@
       <c r="O14" s="5" t="n">
         <v>0.9540999999999999</v>
       </c>
-      <c r="P14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="U14" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="V14" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="W14" s="6" t="n">
-        <v>0.16</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1572,30 +1321,6 @@
       <c r="O15" s="5" t="n">
         <v>0.9664</v>
       </c>
-      <c r="P15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="U15" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="V15" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="W15" s="6" t="n">
-        <v>0.16</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1657,30 +1382,6 @@
       <c r="O16" s="5" t="n">
         <v>0.9741</v>
       </c>
-      <c r="P16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="U16" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="V16" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="W16" s="6" t="n">
-        <v>0.16</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1742,30 +1443,6 @@
       <c r="O17" s="5" t="n">
         <v>0.9772999999999999</v>
       </c>
-      <c r="P17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="U17" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="V17" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="W17" s="6" t="n">
-        <v>0.16</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1827,30 +1504,6 @@
       <c r="O18" s="5" t="n">
         <v>1.011</v>
       </c>
-      <c r="P18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" s="6" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1912,30 +1565,6 @@
       <c r="O19" s="5" t="n">
         <v>0.9709</v>
       </c>
-      <c r="P19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="U19" s="6" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="V19" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="W19" s="6" t="n">
-        <v>0.07333333333333335</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1997,14 +1626,6 @@
       <c r="O20" s="5" t="n">
         <v>0.9968</v>
       </c>
-      <c r="P20" s="6" t="inlineStr"/>
-      <c r="Q20" s="6" t="inlineStr"/>
-      <c r="R20" s="6" t="inlineStr"/>
-      <c r="S20" s="6" t="inlineStr"/>
-      <c r="T20" s="6" t="inlineStr"/>
-      <c r="U20" s="6" t="inlineStr"/>
-      <c r="V20" s="6" t="inlineStr"/>
-      <c r="W20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2066,14 +1687,6 @@
       <c r="O21" s="5" t="n">
         <v>0.9978</v>
       </c>
-      <c r="P21" s="6" t="inlineStr"/>
-      <c r="Q21" s="6" t="inlineStr"/>
-      <c r="R21" s="6" t="inlineStr"/>
-      <c r="S21" s="6" t="inlineStr"/>
-      <c r="T21" s="6" t="inlineStr"/>
-      <c r="U21" s="6" t="inlineStr"/>
-      <c r="V21" s="6" t="inlineStr"/>
-      <c r="W21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2125,14 +1738,6 @@
       <c r="O22" s="5" t="n">
         <v>0.9527</v>
       </c>
-      <c r="P22" s="6" t="inlineStr"/>
-      <c r="Q22" s="6" t="inlineStr"/>
-      <c r="R22" s="6" t="inlineStr"/>
-      <c r="S22" s="6" t="inlineStr"/>
-      <c r="T22" s="6" t="inlineStr"/>
-      <c r="U22" s="6" t="inlineStr"/>
-      <c r="V22" s="6" t="inlineStr"/>
-      <c r="W22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2184,14 +1789,6 @@
       <c r="O23" s="5" t="n">
         <v>0.9417</v>
       </c>
-      <c r="P23" s="6" t="inlineStr"/>
-      <c r="Q23" s="6" t="inlineStr"/>
-      <c r="R23" s="6" t="inlineStr"/>
-      <c r="S23" s="6" t="inlineStr"/>
-      <c r="T23" s="6" t="inlineStr"/>
-      <c r="U23" s="6" t="inlineStr"/>
-      <c r="V23" s="6" t="inlineStr"/>
-      <c r="W23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2243,14 +1840,6 @@
       <c r="O24" s="5" t="n">
         <v>0.9614</v>
       </c>
-      <c r="P24" s="6" t="inlineStr"/>
-      <c r="Q24" s="6" t="inlineStr"/>
-      <c r="R24" s="6" t="inlineStr"/>
-      <c r="S24" s="6" t="inlineStr"/>
-      <c r="T24" s="6" t="inlineStr"/>
-      <c r="U24" s="6" t="inlineStr"/>
-      <c r="V24" s="6" t="inlineStr"/>
-      <c r="W24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2300,14 +1889,6 @@
       <c r="O25" s="5" t="n">
         <v>0.9687</v>
       </c>
-      <c r="P25" s="6" t="inlineStr"/>
-      <c r="Q25" s="6" t="inlineStr"/>
-      <c r="R25" s="6" t="inlineStr"/>
-      <c r="S25" s="6" t="inlineStr"/>
-      <c r="T25" s="6" t="inlineStr"/>
-      <c r="U25" s="6" t="inlineStr"/>
-      <c r="V25" s="6" t="inlineStr"/>
-      <c r="W25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2355,14 +1936,6 @@
       <c r="O26" s="5" t="n">
         <v>0.9687</v>
       </c>
-      <c r="P26" s="6" t="inlineStr"/>
-      <c r="Q26" s="6" t="inlineStr"/>
-      <c r="R26" s="6" t="inlineStr"/>
-      <c r="S26" s="6" t="inlineStr"/>
-      <c r="T26" s="6" t="inlineStr"/>
-      <c r="U26" s="6" t="inlineStr"/>
-      <c r="V26" s="6" t="inlineStr"/>
-      <c r="W26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2414,14 +1987,6 @@
       <c r="O27" s="5" t="n">
         <v>0.9628</v>
       </c>
-      <c r="P27" s="6" t="inlineStr"/>
-      <c r="Q27" s="6" t="inlineStr"/>
-      <c r="R27" s="6" t="inlineStr"/>
-      <c r="S27" s="6" t="inlineStr"/>
-      <c r="T27" s="6" t="inlineStr"/>
-      <c r="U27" s="6" t="inlineStr"/>
-      <c r="V27" s="6" t="inlineStr"/>
-      <c r="W27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2473,14 +2038,6 @@
       <c r="O28" s="5" t="n">
         <v>0.9606</v>
       </c>
-      <c r="P28" s="6" t="inlineStr"/>
-      <c r="Q28" s="6" t="inlineStr"/>
-      <c r="R28" s="6" t="inlineStr"/>
-      <c r="S28" s="6" t="inlineStr"/>
-      <c r="T28" s="6" t="inlineStr"/>
-      <c r="U28" s="6" t="inlineStr"/>
-      <c r="V28" s="6" t="inlineStr"/>
-      <c r="W28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2532,14 +2089,6 @@
       <c r="O29" s="5" t="n">
         <v>0.9533</v>
       </c>
-      <c r="P29" s="6" t="inlineStr"/>
-      <c r="Q29" s="6" t="inlineStr"/>
-      <c r="R29" s="6" t="inlineStr"/>
-      <c r="S29" s="6" t="inlineStr"/>
-      <c r="T29" s="6" t="inlineStr"/>
-      <c r="U29" s="6" t="inlineStr"/>
-      <c r="V29" s="6" t="inlineStr"/>
-      <c r="W29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2591,14 +2140,6 @@
       <c r="O30" s="5" t="n">
         <v>0.9533</v>
       </c>
-      <c r="P30" s="6" t="inlineStr"/>
-      <c r="Q30" s="6" t="inlineStr"/>
-      <c r="R30" s="6" t="inlineStr"/>
-      <c r="S30" s="6" t="inlineStr"/>
-      <c r="T30" s="6" t="inlineStr"/>
-      <c r="U30" s="6" t="inlineStr"/>
-      <c r="V30" s="6" t="inlineStr"/>
-      <c r="W30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2650,14 +2191,6 @@
       <c r="O31" s="5" t="n">
         <v>0.9533</v>
       </c>
-      <c r="P31" s="6" t="inlineStr"/>
-      <c r="Q31" s="6" t="inlineStr"/>
-      <c r="R31" s="6" t="inlineStr"/>
-      <c r="S31" s="6" t="inlineStr"/>
-      <c r="T31" s="6" t="inlineStr"/>
-      <c r="U31" s="6" t="inlineStr"/>
-      <c r="V31" s="6" t="inlineStr"/>
-      <c r="W31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2709,14 +2242,6 @@
       <c r="O32" s="5" t="n">
         <v>0.9468</v>
       </c>
-      <c r="P32" s="6" t="inlineStr"/>
-      <c r="Q32" s="6" t="inlineStr"/>
-      <c r="R32" s="6" t="inlineStr"/>
-      <c r="S32" s="6" t="inlineStr"/>
-      <c r="T32" s="6" t="inlineStr"/>
-      <c r="U32" s="6" t="inlineStr"/>
-      <c r="V32" s="6" t="inlineStr"/>
-      <c r="W32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2768,14 +2293,6 @@
       <c r="O33" s="5" t="n">
         <v>0.9468</v>
       </c>
-      <c r="P33" s="6" t="inlineStr"/>
-      <c r="Q33" s="6" t="inlineStr"/>
-      <c r="R33" s="6" t="inlineStr"/>
-      <c r="S33" s="6" t="inlineStr"/>
-      <c r="T33" s="6" t="inlineStr"/>
-      <c r="U33" s="6" t="inlineStr"/>
-      <c r="V33" s="6" t="inlineStr"/>
-      <c r="W33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2827,14 +2344,6 @@
       <c r="O34" s="5" t="n">
         <v>0.9468</v>
       </c>
-      <c r="P34" s="6" t="inlineStr"/>
-      <c r="Q34" s="6" t="inlineStr"/>
-      <c r="R34" s="6" t="inlineStr"/>
-      <c r="S34" s="6" t="inlineStr"/>
-      <c r="T34" s="6" t="inlineStr"/>
-      <c r="U34" s="6" t="inlineStr"/>
-      <c r="V34" s="6" t="inlineStr"/>
-      <c r="W34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2886,14 +2395,6 @@
       <c r="O35" s="5" t="n">
         <v>0.9661</v>
       </c>
-      <c r="P35" s="6" t="inlineStr"/>
-      <c r="Q35" s="6" t="inlineStr"/>
-      <c r="R35" s="6" t="inlineStr"/>
-      <c r="S35" s="6" t="inlineStr"/>
-      <c r="T35" s="6" t="inlineStr"/>
-      <c r="U35" s="6" t="inlineStr"/>
-      <c r="V35" s="6" t="inlineStr"/>
-      <c r="W35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2945,14 +2446,6 @@
       <c r="O36" s="5" t="n">
         <v>0.9661</v>
       </c>
-      <c r="P36" s="6" t="inlineStr"/>
-      <c r="Q36" s="6" t="inlineStr"/>
-      <c r="R36" s="6" t="inlineStr"/>
-      <c r="S36" s="6" t="inlineStr"/>
-      <c r="T36" s="6" t="inlineStr"/>
-      <c r="U36" s="6" t="inlineStr"/>
-      <c r="V36" s="6" t="inlineStr"/>
-      <c r="W36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -3004,14 +2497,6 @@
       <c r="O37" s="5" t="n">
         <v>0.9387</v>
       </c>
-      <c r="P37" s="6" t="inlineStr"/>
-      <c r="Q37" s="6" t="inlineStr"/>
-      <c r="R37" s="6" t="inlineStr"/>
-      <c r="S37" s="6" t="inlineStr"/>
-      <c r="T37" s="6" t="inlineStr"/>
-      <c r="U37" s="6" t="inlineStr"/>
-      <c r="V37" s="6" t="inlineStr"/>
-      <c r="W37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3063,14 +2548,6 @@
       <c r="O38" s="5" t="n">
         <v>0.9572000000000001</v>
       </c>
-      <c r="P38" s="6" t="inlineStr"/>
-      <c r="Q38" s="6" t="inlineStr"/>
-      <c r="R38" s="6" t="inlineStr"/>
-      <c r="S38" s="6" t="inlineStr"/>
-      <c r="T38" s="6" t="inlineStr"/>
-      <c r="U38" s="6" t="inlineStr"/>
-      <c r="V38" s="6" t="inlineStr"/>
-      <c r="W38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3122,14 +2599,6 @@
       <c r="O39" s="5" t="n">
         <v>0.9709</v>
       </c>
-      <c r="P39" s="6" t="inlineStr"/>
-      <c r="Q39" s="6" t="inlineStr"/>
-      <c r="R39" s="6" t="inlineStr"/>
-      <c r="S39" s="6" t="inlineStr"/>
-      <c r="T39" s="6" t="inlineStr"/>
-      <c r="U39" s="6" t="inlineStr"/>
-      <c r="V39" s="6" t="inlineStr"/>
-      <c r="W39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3181,14 +2650,6 @@
       <c r="O40" s="5" t="n">
         <v>0.9699</v>
       </c>
-      <c r="P40" s="6" t="inlineStr"/>
-      <c r="Q40" s="6" t="inlineStr"/>
-      <c r="R40" s="6" t="inlineStr"/>
-      <c r="S40" s="6" t="inlineStr"/>
-      <c r="T40" s="6" t="inlineStr"/>
-      <c r="U40" s="6" t="inlineStr"/>
-      <c r="V40" s="6" t="inlineStr"/>
-      <c r="W40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3240,14 +2701,6 @@
       <c r="O41" s="5" t="n">
         <v>0.9699</v>
       </c>
-      <c r="P41" s="6" t="inlineStr"/>
-      <c r="Q41" s="6" t="inlineStr"/>
-      <c r="R41" s="6" t="inlineStr"/>
-      <c r="S41" s="6" t="inlineStr"/>
-      <c r="T41" s="6" t="inlineStr"/>
-      <c r="U41" s="6" t="inlineStr"/>
-      <c r="V41" s="6" t="inlineStr"/>
-      <c r="W41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3299,14 +2752,6 @@
       <c r="O42" s="5" t="n">
         <v>0.9132</v>
       </c>
-      <c r="P42" s="6" t="inlineStr"/>
-      <c r="Q42" s="6" t="inlineStr"/>
-      <c r="R42" s="6" t="inlineStr"/>
-      <c r="S42" s="6" t="inlineStr"/>
-      <c r="T42" s="6" t="inlineStr"/>
-      <c r="U42" s="6" t="inlineStr"/>
-      <c r="V42" s="6" t="inlineStr"/>
-      <c r="W42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3358,14 +2803,6 @@
       <c r="O43" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="P43" s="6" t="inlineStr"/>
-      <c r="Q43" s="6" t="inlineStr"/>
-      <c r="R43" s="6" t="inlineStr"/>
-      <c r="S43" s="6" t="inlineStr"/>
-      <c r="T43" s="6" t="inlineStr"/>
-      <c r="U43" s="6" t="inlineStr"/>
-      <c r="V43" s="6" t="inlineStr"/>
-      <c r="W43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3417,14 +2854,6 @@
       <c r="O44" s="5" t="n">
         <v>0.9572000000000001</v>
       </c>
-      <c r="P44" s="6" t="inlineStr"/>
-      <c r="Q44" s="6" t="inlineStr"/>
-      <c r="R44" s="6" t="inlineStr"/>
-      <c r="S44" s="6" t="inlineStr"/>
-      <c r="T44" s="6" t="inlineStr"/>
-      <c r="U44" s="6" t="inlineStr"/>
-      <c r="V44" s="6" t="inlineStr"/>
-      <c r="W44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3476,14 +2905,6 @@
       <c r="O45" s="5" t="n">
         <v>0.9611</v>
       </c>
-      <c r="P45" s="6" t="inlineStr"/>
-      <c r="Q45" s="6" t="inlineStr"/>
-      <c r="R45" s="6" t="inlineStr"/>
-      <c r="S45" s="6" t="inlineStr"/>
-      <c r="T45" s="6" t="inlineStr"/>
-      <c r="U45" s="6" t="inlineStr"/>
-      <c r="V45" s="6" t="inlineStr"/>
-      <c r="W45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3535,14 +2956,6 @@
       <c r="O46" s="5" t="n">
         <v>0.8476</v>
       </c>
-      <c r="P46" s="6" t="inlineStr"/>
-      <c r="Q46" s="6" t="inlineStr"/>
-      <c r="R46" s="6" t="inlineStr"/>
-      <c r="S46" s="6" t="inlineStr"/>
-      <c r="T46" s="6" t="inlineStr"/>
-      <c r="U46" s="6" t="inlineStr"/>
-      <c r="V46" s="6" t="inlineStr"/>
-      <c r="W46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3594,14 +3007,6 @@
       <c r="O47" s="5" t="n">
         <v>0.9592000000000001</v>
       </c>
-      <c r="P47" s="6" t="inlineStr"/>
-      <c r="Q47" s="6" t="inlineStr"/>
-      <c r="R47" s="6" t="inlineStr"/>
-      <c r="S47" s="6" t="inlineStr"/>
-      <c r="T47" s="6" t="inlineStr"/>
-      <c r="U47" s="6" t="inlineStr"/>
-      <c r="V47" s="6" t="inlineStr"/>
-      <c r="W47" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3614,7 +3019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V47"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3625,141 +3030,57 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>DUID</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Fuel</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>MLF_FY25-26</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>MLF_FY26-27</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>CURTAILMENT_ACTUAL_FY23-24</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>CURTAILMENT_ACTUAL_FY24-25</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>ELI_CURTAILMENT_NEAR</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>ELI_CURTAILMENT_MED</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY1</t>
-        </is>
-      </c>
-      <c r="J1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY1_LABEL</t>
-        </is>
-      </c>
-      <c r="K1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY2</t>
-        </is>
-      </c>
-      <c r="L1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY2_LABEL</t>
-        </is>
-      </c>
-      <c r="M1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY3</t>
-        </is>
-      </c>
-      <c r="N1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY3_LABEL</t>
-        </is>
-      </c>
-      <c r="O1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_AVG</t>
-        </is>
-      </c>
-      <c r="P1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY1</t>
-        </is>
-      </c>
-      <c r="Q1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY1_LABEL</t>
-        </is>
-      </c>
-      <c r="R1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY2</t>
-        </is>
-      </c>
-      <c r="S1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY2_LABEL</t>
-        </is>
-      </c>
-      <c r="T1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY3</t>
-        </is>
-      </c>
-      <c r="U1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY3_LABEL</t>
-        </is>
-      </c>
-      <c r="V1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_AVG</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>ADPPV1</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3778,52 +3099,14 @@
       </c>
       <c r="G2" s="5" t="inlineStr"/>
       <c r="H2" s="5" t="inlineStr"/>
-      <c r="I2" s="5" t="inlineStr"/>
-      <c r="J2" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K2" s="5" t="inlineStr"/>
-      <c r="L2" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M2" s="5" t="inlineStr"/>
-      <c r="N2" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O2" s="5" t="inlineStr"/>
-      <c r="P2" s="5" t="inlineStr"/>
-      <c r="Q2" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R2" s="5" t="inlineStr"/>
-      <c r="S2" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T2" s="5" t="inlineStr"/>
-      <c r="U2" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>ADPPV2</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3838,52 +3121,14 @@
       <c r="F3" s="5" t="inlineStr"/>
       <c r="G3" s="5" t="inlineStr"/>
       <c r="H3" s="5" t="inlineStr"/>
-      <c r="I3" s="5" t="inlineStr"/>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr"/>
-      <c r="L3" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M3" s="5" t="inlineStr"/>
-      <c r="N3" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O3" s="5" t="inlineStr"/>
-      <c r="P3" s="5" t="inlineStr"/>
-      <c r="Q3" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R3" s="5" t="inlineStr"/>
-      <c r="S3" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T3" s="5" t="inlineStr"/>
-      <c r="U3" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>ADPPV3</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3898,52 +3143,14 @@
       <c r="F4" s="5" t="inlineStr"/>
       <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr"/>
-      <c r="L4" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M4" s="5" t="inlineStr"/>
-      <c r="N4" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O4" s="5" t="inlineStr"/>
-      <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R4" s="5" t="inlineStr"/>
-      <c r="S4" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T4" s="5" t="inlineStr"/>
-      <c r="U4" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>BOWWPV1</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3960,52 +3167,14 @@
       </c>
       <c r="G5" s="5" t="inlineStr"/>
       <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr"/>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M5" s="5" t="inlineStr"/>
-      <c r="N5" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O5" s="5" t="inlineStr"/>
-      <c r="P5" s="5" t="inlineStr"/>
-      <c r="Q5" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R5" s="5" t="inlineStr"/>
-      <c r="S5" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T5" s="5" t="inlineStr"/>
-      <c r="U5" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>BNGSF1</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4028,68 +3197,14 @@
       <c r="H6" s="5" t="n">
         <v>0.212860651220515</v>
       </c>
-      <c r="I6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="Q6" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R6" s="5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="S6" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T6" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="U6" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V6" s="5" t="n">
-        <v>0.07333333333333335</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>BNGSF2</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4112,68 +3227,14 @@
       <c r="H7" s="5" t="n">
         <v>0.212860651220515</v>
       </c>
-      <c r="I7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="Q7" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R7" s="5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="S7" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T7" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="U7" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V7" s="5" t="n">
-        <v>0.07333333333333335</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>CBWWPV1</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4188,52 +3249,14 @@
       <c r="F8" s="5" t="inlineStr"/>
       <c r="G8" s="5" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr"/>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr"/>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M8" s="5" t="inlineStr"/>
-      <c r="N8" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O8" s="5" t="inlineStr"/>
-      <c r="P8" s="5" t="inlineStr"/>
-      <c r="Q8" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R8" s="5" t="inlineStr"/>
-      <c r="S8" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T8" s="5" t="inlineStr"/>
-      <c r="U8" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>CBWWPV2</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4248,52 +3271,14 @@
       <c r="F9" s="5" t="inlineStr"/>
       <c r="G9" s="5" t="inlineStr"/>
       <c r="H9" s="5" t="inlineStr"/>
-      <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr"/>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="inlineStr"/>
-      <c r="N9" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O9" s="5" t="inlineStr"/>
-      <c r="P9" s="5" t="inlineStr"/>
-      <c r="Q9" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R9" s="5" t="inlineStr"/>
-      <c r="S9" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T9" s="5" t="inlineStr"/>
-      <c r="U9" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>HVWWPV1</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4316,52 +3301,14 @@
       <c r="H10" s="5" t="n">
         <v>0.22265637813532</v>
       </c>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr"/>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M10" s="5" t="inlineStr"/>
-      <c r="N10" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O10" s="5" t="inlineStr"/>
-      <c r="P10" s="5" t="inlineStr"/>
-      <c r="Q10" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R10" s="5" t="inlineStr"/>
-      <c r="S10" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T10" s="5" t="inlineStr"/>
-      <c r="U10" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>MAPS2PV1</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4384,68 +3331,14 @@
       <c r="H11" s="5" t="n">
         <v>0.225784053085401</v>
       </c>
-      <c r="I11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V11" s="5" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>MAPS3PV1</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4466,68 +3359,14 @@
       <c r="H12" s="5" t="n">
         <v>0.225784053085401</v>
       </c>
-      <c r="I12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V12" s="5" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>MANNSF2</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4548,68 +3387,14 @@
       <c r="H13" s="5" t="n">
         <v>0.225784053085401</v>
       </c>
-      <c r="I13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="Q13" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R13" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="S13" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T13" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="U13" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V13" s="5" t="n">
-        <v>0.16</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>MWPS1PV1</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4632,68 +3417,14 @@
       <c r="H14" s="5" t="n">
         <v>0.512670422089759</v>
       </c>
-      <c r="I14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="Q14" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R14" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="S14" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T14" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="U14" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V14" s="5" t="n">
-        <v>0.16</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>MWPS2PV1</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4716,68 +3447,14 @@
       <c r="H15" s="5" t="n">
         <v>0.512670422089759</v>
       </c>
-      <c r="I15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="Q15" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R15" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="S15" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T15" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="U15" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V15" s="5" t="n">
-        <v>0.16</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>MWPS3PV1</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4800,68 +3477,14 @@
       <c r="H16" s="5" t="n">
         <v>0.512670422089759</v>
       </c>
-      <c r="I16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="Q16" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R16" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="S16" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T16" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="U16" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V16" s="5" t="n">
-        <v>0.16</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>MWPS4PV1</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4884,68 +3507,14 @@
       <c r="H17" s="5" t="n">
         <v>0.512670422089759</v>
       </c>
-      <c r="I17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="Q17" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R17" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="S17" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T17" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="U17" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V17" s="5" t="n">
-        <v>0.16</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>MBPS2PV1</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4968,68 +3537,14 @@
       <c r="H18" s="5" t="n">
         <v>0.225784053085401</v>
       </c>
-      <c r="I18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V18" s="5" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>PAREPS1</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5052,68 +3567,14 @@
       <c r="H19" s="5" t="n">
         <v>0.212860651220515</v>
       </c>
-      <c r="I19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="Q19" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R19" s="5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="S19" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T19" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="U19" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V19" s="5" t="n">
-        <v>0.07333333333333335</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>TB2SF1</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5136,52 +3597,14 @@
       <c r="H20" s="5" t="n">
         <v>0.22945882760626</v>
       </c>
-      <c r="I20" s="5" t="inlineStr"/>
-      <c r="J20" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K20" s="5" t="inlineStr"/>
-      <c r="L20" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M20" s="5" t="inlineStr"/>
-      <c r="N20" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O20" s="5" t="inlineStr"/>
-      <c r="P20" s="5" t="inlineStr"/>
-      <c r="Q20" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R20" s="5" t="inlineStr"/>
-      <c r="S20" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T20" s="5" t="inlineStr"/>
-      <c r="U20" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>TBSF1</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5204,52 +3627,14 @@
       <c r="H21" s="5" t="n">
         <v>0.22945882760626</v>
       </c>
-      <c r="I21" s="5" t="inlineStr"/>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr"/>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M21" s="5" t="inlineStr"/>
-      <c r="N21" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O21" s="5" t="inlineStr"/>
-      <c r="P21" s="5" t="inlineStr"/>
-      <c r="Q21" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R21" s="5" t="inlineStr"/>
-      <c r="S21" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T21" s="5" t="inlineStr"/>
-      <c r="U21" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>CNUNDAWF</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5268,52 +3653,14 @@
       </c>
       <c r="G22" s="5" t="inlineStr"/>
       <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="inlineStr"/>
-      <c r="L22" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M22" s="5" t="inlineStr"/>
-      <c r="N22" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O22" s="5" t="inlineStr"/>
-      <c r="P22" s="5" t="inlineStr"/>
-      <c r="Q22" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R22" s="5" t="inlineStr"/>
-      <c r="S22" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T22" s="5" t="inlineStr"/>
-      <c r="U22" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>CATHROCK</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5332,52 +3679,14 @@
       </c>
       <c r="G23" s="5" t="inlineStr"/>
       <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr"/>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr"/>
-      <c r="N23" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O23" s="5" t="inlineStr"/>
-      <c r="P23" s="5" t="inlineStr"/>
-      <c r="Q23" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R23" s="5" t="inlineStr"/>
-      <c r="S23" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T23" s="5" t="inlineStr"/>
-      <c r="U23" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>CLEMGPWF</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5396,52 +3705,14 @@
       </c>
       <c r="G24" s="5" t="inlineStr"/>
       <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K24" s="5" t="inlineStr"/>
-      <c r="L24" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M24" s="5" t="inlineStr"/>
-      <c r="N24" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O24" s="5" t="inlineStr"/>
-      <c r="P24" s="5" t="inlineStr"/>
-      <c r="Q24" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R24" s="5" t="inlineStr"/>
-      <c r="S24" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T24" s="5" t="inlineStr"/>
-      <c r="U24" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>GSWF1A</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5458,52 +3729,14 @@
       </c>
       <c r="G25" s="5" t="inlineStr"/>
       <c r="H25" s="5" t="inlineStr"/>
-      <c r="I25" s="5" t="inlineStr"/>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr"/>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr"/>
-      <c r="N25" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O25" s="5" t="inlineStr"/>
-      <c r="P25" s="5" t="inlineStr"/>
-      <c r="Q25" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R25" s="5" t="inlineStr"/>
-      <c r="S25" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T25" s="5" t="inlineStr"/>
-      <c r="U25" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>GSWF1B1</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5518,52 +3751,14 @@
       <c r="F26" s="5" t="inlineStr"/>
       <c r="G26" s="5" t="inlineStr"/>
       <c r="H26" s="5" t="inlineStr"/>
-      <c r="I26" s="5" t="inlineStr"/>
-      <c r="J26" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K26" s="5" t="inlineStr"/>
-      <c r="L26" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M26" s="5" t="inlineStr"/>
-      <c r="N26" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O26" s="5" t="inlineStr"/>
-      <c r="P26" s="5" t="inlineStr"/>
-      <c r="Q26" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R26" s="5" t="inlineStr"/>
-      <c r="S26" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T26" s="5" t="inlineStr"/>
-      <c r="U26" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>HALLWF1</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5582,52 +3777,14 @@
       </c>
       <c r="G27" s="5" t="inlineStr"/>
       <c r="H27" s="5" t="inlineStr"/>
-      <c r="I27" s="5" t="inlineStr"/>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr"/>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr"/>
-      <c r="N27" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O27" s="5" t="inlineStr"/>
-      <c r="P27" s="5" t="inlineStr"/>
-      <c r="Q27" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R27" s="5" t="inlineStr"/>
-      <c r="S27" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T27" s="5" t="inlineStr"/>
-      <c r="U27" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>HALLWF2</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5646,52 +3803,14 @@
       </c>
       <c r="G28" s="5" t="inlineStr"/>
       <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K28" s="5" t="inlineStr"/>
-      <c r="L28" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M28" s="5" t="inlineStr"/>
-      <c r="N28" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O28" s="5" t="inlineStr"/>
-      <c r="P28" s="5" t="inlineStr"/>
-      <c r="Q28" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R28" s="5" t="inlineStr"/>
-      <c r="S28" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T28" s="5" t="inlineStr"/>
-      <c r="U28" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>HDWF1</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5710,52 +3829,14 @@
       </c>
       <c r="G29" s="5" t="inlineStr"/>
       <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="inlineStr"/>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M29" s="5" t="inlineStr"/>
-      <c r="N29" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O29" s="5" t="inlineStr"/>
-      <c r="P29" s="5" t="inlineStr"/>
-      <c r="Q29" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R29" s="5" t="inlineStr"/>
-      <c r="S29" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T29" s="5" t="inlineStr"/>
-      <c r="U29" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>HDWF2</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5774,52 +3855,14 @@
       </c>
       <c r="G30" s="5" t="inlineStr"/>
       <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K30" s="5" t="inlineStr"/>
-      <c r="L30" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M30" s="5" t="inlineStr"/>
-      <c r="N30" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O30" s="5" t="inlineStr"/>
-      <c r="P30" s="5" t="inlineStr"/>
-      <c r="Q30" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R30" s="5" t="inlineStr"/>
-      <c r="S30" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T30" s="5" t="inlineStr"/>
-      <c r="U30" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>HDWF3</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5838,52 +3881,14 @@
       </c>
       <c r="G31" s="5" t="inlineStr"/>
       <c r="H31" s="5" t="inlineStr"/>
-      <c r="I31" s="5" t="inlineStr"/>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K31" s="5" t="inlineStr"/>
-      <c r="L31" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M31" s="5" t="inlineStr"/>
-      <c r="N31" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O31" s="5" t="inlineStr"/>
-      <c r="P31" s="5" t="inlineStr"/>
-      <c r="Q31" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R31" s="5" t="inlineStr"/>
-      <c r="S31" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T31" s="5" t="inlineStr"/>
-      <c r="U31" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>LKBONNY2</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5902,52 +3907,14 @@
       </c>
       <c r="G32" s="5" t="inlineStr"/>
       <c r="H32" s="5" t="inlineStr"/>
-      <c r="I32" s="5" t="inlineStr"/>
-      <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K32" s="5" t="inlineStr"/>
-      <c r="L32" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M32" s="5" t="inlineStr"/>
-      <c r="N32" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O32" s="5" t="inlineStr"/>
-      <c r="P32" s="5" t="inlineStr"/>
-      <c r="Q32" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R32" s="5" t="inlineStr"/>
-      <c r="S32" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T32" s="5" t="inlineStr"/>
-      <c r="U32" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>LKBONNY3</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5966,52 +3933,14 @@
       </c>
       <c r="G33" s="5" t="inlineStr"/>
       <c r="H33" s="5" t="inlineStr"/>
-      <c r="I33" s="5" t="inlineStr"/>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K33" s="5" t="inlineStr"/>
-      <c r="L33" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M33" s="5" t="inlineStr"/>
-      <c r="N33" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O33" s="5" t="inlineStr"/>
-      <c r="P33" s="5" t="inlineStr"/>
-      <c r="Q33" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R33" s="5" t="inlineStr"/>
-      <c r="S33" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T33" s="5" t="inlineStr"/>
-      <c r="U33" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>LKBONNY1</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6030,52 +3959,14 @@
       </c>
       <c r="G34" s="5" t="inlineStr"/>
       <c r="H34" s="5" t="inlineStr"/>
-      <c r="I34" s="5" t="inlineStr"/>
-      <c r="J34" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K34" s="5" t="inlineStr"/>
-      <c r="L34" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M34" s="5" t="inlineStr"/>
-      <c r="N34" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O34" s="5" t="inlineStr"/>
-      <c r="P34" s="5" t="inlineStr"/>
-      <c r="Q34" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R34" s="5" t="inlineStr"/>
-      <c r="S34" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T34" s="5" t="inlineStr"/>
-      <c r="U34" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>LGAPWF1</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6094,52 +3985,14 @@
       </c>
       <c r="G35" s="5" t="inlineStr"/>
       <c r="H35" s="5" t="inlineStr"/>
-      <c r="I35" s="5" t="inlineStr"/>
-      <c r="J35" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K35" s="5" t="inlineStr"/>
-      <c r="L35" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M35" s="5" t="inlineStr"/>
-      <c r="N35" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O35" s="5" t="inlineStr"/>
-      <c r="P35" s="5" t="inlineStr"/>
-      <c r="Q35" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R35" s="5" t="inlineStr"/>
-      <c r="S35" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T35" s="5" t="inlineStr"/>
-      <c r="U35" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>LGAPWF2</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6158,52 +4011,14 @@
       </c>
       <c r="G36" s="5" t="inlineStr"/>
       <c r="H36" s="5" t="inlineStr"/>
-      <c r="I36" s="5" t="inlineStr"/>
-      <c r="J36" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K36" s="5" t="inlineStr"/>
-      <c r="L36" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M36" s="5" t="inlineStr"/>
-      <c r="N36" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O36" s="5" t="inlineStr"/>
-      <c r="P36" s="5" t="inlineStr"/>
-      <c r="Q36" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R36" s="5" t="inlineStr"/>
-      <c r="S36" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T36" s="5" t="inlineStr"/>
-      <c r="U36" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>MTMILLAR</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6222,52 +4037,14 @@
       </c>
       <c r="G37" s="5" t="inlineStr"/>
       <c r="H37" s="5" t="inlineStr"/>
-      <c r="I37" s="5" t="inlineStr"/>
-      <c r="J37" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K37" s="5" t="inlineStr"/>
-      <c r="L37" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M37" s="5" t="inlineStr"/>
-      <c r="N37" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O37" s="5" t="inlineStr"/>
-      <c r="P37" s="5" t="inlineStr"/>
-      <c r="Q37" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R37" s="5" t="inlineStr"/>
-      <c r="S37" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T37" s="5" t="inlineStr"/>
-      <c r="U37" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>NBHWF1</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6286,52 +4063,14 @@
       </c>
       <c r="G38" s="5" t="inlineStr"/>
       <c r="H38" s="5" t="inlineStr"/>
-      <c r="I38" s="5" t="inlineStr"/>
-      <c r="J38" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K38" s="5" t="inlineStr"/>
-      <c r="L38" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M38" s="5" t="inlineStr"/>
-      <c r="N38" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O38" s="5" t="inlineStr"/>
-      <c r="P38" s="5" t="inlineStr"/>
-      <c r="Q38" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R38" s="5" t="inlineStr"/>
-      <c r="S38" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T38" s="5" t="inlineStr"/>
-      <c r="U38" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>PAREPW1</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6350,52 +4089,14 @@
       </c>
       <c r="G39" s="5" t="inlineStr"/>
       <c r="H39" s="5" t="inlineStr"/>
-      <c r="I39" s="5" t="inlineStr"/>
-      <c r="J39" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K39" s="5" t="inlineStr"/>
-      <c r="L39" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M39" s="5" t="inlineStr"/>
-      <c r="N39" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O39" s="5" t="inlineStr"/>
-      <c r="P39" s="5" t="inlineStr"/>
-      <c r="Q39" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R39" s="5" t="inlineStr"/>
-      <c r="S39" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T39" s="5" t="inlineStr"/>
-      <c r="U39" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>SNOWSTH1</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6414,52 +4115,14 @@
       </c>
       <c r="G40" s="5" t="inlineStr"/>
       <c r="H40" s="5" t="inlineStr"/>
-      <c r="I40" s="5" t="inlineStr"/>
-      <c r="J40" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K40" s="5" t="inlineStr"/>
-      <c r="L40" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M40" s="5" t="inlineStr"/>
-      <c r="N40" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O40" s="5" t="inlineStr"/>
-      <c r="P40" s="5" t="inlineStr"/>
-      <c r="Q40" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R40" s="5" t="inlineStr"/>
-      <c r="S40" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T40" s="5" t="inlineStr"/>
-      <c r="U40" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>SNOWNTH1</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6478,52 +4141,14 @@
       </c>
       <c r="G41" s="5" t="inlineStr"/>
       <c r="H41" s="5" t="inlineStr"/>
-      <c r="I41" s="5" t="inlineStr"/>
-      <c r="J41" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K41" s="5" t="inlineStr"/>
-      <c r="L41" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M41" s="5" t="inlineStr"/>
-      <c r="N41" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O41" s="5" t="inlineStr"/>
-      <c r="P41" s="5" t="inlineStr"/>
-      <c r="Q41" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R41" s="5" t="inlineStr"/>
-      <c r="S41" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T41" s="5" t="inlineStr"/>
-      <c r="U41" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>SNOWTWN1</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6542,52 +4167,14 @@
       </c>
       <c r="G42" s="5" t="inlineStr"/>
       <c r="H42" s="5" t="inlineStr"/>
-      <c r="I42" s="5" t="inlineStr"/>
-      <c r="J42" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K42" s="5" t="inlineStr"/>
-      <c r="L42" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M42" s="5" t="inlineStr"/>
-      <c r="N42" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O42" s="5" t="inlineStr"/>
-      <c r="P42" s="5" t="inlineStr"/>
-      <c r="Q42" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R42" s="5" t="inlineStr"/>
-      <c r="S42" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T42" s="5" t="inlineStr"/>
-      <c r="U42" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>STARHLWF</t>
         </is>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6606,52 +4193,14 @@
       </c>
       <c r="G43" s="5" t="inlineStr"/>
       <c r="H43" s="5" t="inlineStr"/>
-      <c r="I43" s="5" t="inlineStr"/>
-      <c r="J43" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K43" s="5" t="inlineStr"/>
-      <c r="L43" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M43" s="5" t="inlineStr"/>
-      <c r="N43" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O43" s="5" t="inlineStr"/>
-      <c r="P43" s="5" t="inlineStr"/>
-      <c r="Q43" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R43" s="5" t="inlineStr"/>
-      <c r="S43" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T43" s="5" t="inlineStr"/>
-      <c r="U43" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>BLUFF1</t>
         </is>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6670,52 +4219,14 @@
       </c>
       <c r="G44" s="5" t="inlineStr"/>
       <c r="H44" s="5" t="inlineStr"/>
-      <c r="I44" s="5" t="inlineStr"/>
-      <c r="J44" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K44" s="5" t="inlineStr"/>
-      <c r="L44" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M44" s="5" t="inlineStr"/>
-      <c r="N44" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O44" s="5" t="inlineStr"/>
-      <c r="P44" s="5" t="inlineStr"/>
-      <c r="Q44" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R44" s="5" t="inlineStr"/>
-      <c r="S44" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T44" s="5" t="inlineStr"/>
-      <c r="U44" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V44" s="5" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="inlineStr">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>WATERLWF</t>
         </is>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6734,52 +4245,14 @@
       </c>
       <c r="G45" s="5" t="inlineStr"/>
       <c r="H45" s="5" t="inlineStr"/>
-      <c r="I45" s="5" t="inlineStr"/>
-      <c r="J45" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K45" s="5" t="inlineStr"/>
-      <c r="L45" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M45" s="5" t="inlineStr"/>
-      <c r="N45" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O45" s="5" t="inlineStr"/>
-      <c r="P45" s="5" t="inlineStr"/>
-      <c r="Q45" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R45" s="5" t="inlineStr"/>
-      <c r="S45" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T45" s="5" t="inlineStr"/>
-      <c r="U45" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>WPWF</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6798,52 +4271,14 @@
       </c>
       <c r="G46" s="5" t="inlineStr"/>
       <c r="H46" s="5" t="inlineStr"/>
-      <c r="I46" s="5" t="inlineStr"/>
-      <c r="J46" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K46" s="5" t="inlineStr"/>
-      <c r="L46" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M46" s="5" t="inlineStr"/>
-      <c r="N46" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O46" s="5" t="inlineStr"/>
-      <c r="P46" s="5" t="inlineStr"/>
-      <c r="Q46" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R46" s="5" t="inlineStr"/>
-      <c r="S46" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T46" s="5" t="inlineStr"/>
-      <c r="U46" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="8" t="inlineStr">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>WGWF1</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6862,44 +4297,6 @@
       </c>
       <c r="G47" s="5" t="inlineStr"/>
       <c r="H47" s="5" t="inlineStr"/>
-      <c r="I47" s="5" t="inlineStr"/>
-      <c r="J47" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K47" s="5" t="inlineStr"/>
-      <c r="L47" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M47" s="5" t="inlineStr"/>
-      <c r="N47" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O47" s="5" t="inlineStr"/>
-      <c r="P47" s="5" t="inlineStr"/>
-      <c r="Q47" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R47" s="5" t="inlineStr"/>
-      <c r="S47" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T47" s="5" t="inlineStr"/>
-      <c r="U47" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V47" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C47">
@@ -6974,174 +4371,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I47">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J47">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K47">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L47">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M47">
-    <cfRule type="colorScale" priority="11">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N47">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O47">
-    <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P47">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q47">
-    <cfRule type="colorScale" priority="15">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R47">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S47">
-    <cfRule type="colorScale" priority="17">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T47">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U47">
-    <cfRule type="colorScale" priority="19">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V47">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/SA_curtailment.xlsx
+++ b/outputs/SA_curtailment.xlsx
@@ -67,7 +67,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -82,6 +82,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -453,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O47"/>
+  <dimension ref="A1:W47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -471,6 +474,14 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -549,6 +560,46 @@
           <t>FY26-27</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Curt FY1</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Curt FY2</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Curt FY3</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Curt Avg</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Offl FY1</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Offl FY2</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Offl FY3</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Offl Avg</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -600,6 +651,14 @@
       <c r="O2" s="5" t="n">
         <v>1.0033</v>
       </c>
+      <c r="P2" s="6" t="inlineStr"/>
+      <c r="Q2" s="6" t="inlineStr"/>
+      <c r="R2" s="6" t="inlineStr"/>
+      <c r="S2" s="6" t="inlineStr"/>
+      <c r="T2" s="6" t="inlineStr"/>
+      <c r="U2" s="6" t="inlineStr"/>
+      <c r="V2" s="6" t="inlineStr"/>
+      <c r="W2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -647,6 +706,14 @@
       <c r="O3" s="5" t="n">
         <v>1.0033</v>
       </c>
+      <c r="P3" s="6" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr"/>
+      <c r="R3" s="6" t="inlineStr"/>
+      <c r="S3" s="6" t="inlineStr"/>
+      <c r="T3" s="6" t="inlineStr"/>
+      <c r="U3" s="6" t="inlineStr"/>
+      <c r="V3" s="6" t="inlineStr"/>
+      <c r="W3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -694,6 +761,14 @@
       <c r="O4" s="5" t="n">
         <v>1.0033</v>
       </c>
+      <c r="P4" s="6" t="inlineStr"/>
+      <c r="Q4" s="6" t="inlineStr"/>
+      <c r="R4" s="6" t="inlineStr"/>
+      <c r="S4" s="6" t="inlineStr"/>
+      <c r="T4" s="6" t="inlineStr"/>
+      <c r="U4" s="6" t="inlineStr"/>
+      <c r="V4" s="6" t="inlineStr"/>
+      <c r="W4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -743,6 +818,14 @@
       <c r="O5" s="5" t="n">
         <v>1.0002</v>
       </c>
+      <c r="P5" s="6" t="inlineStr"/>
+      <c r="Q5" s="6" t="inlineStr"/>
+      <c r="R5" s="6" t="inlineStr"/>
+      <c r="S5" s="6" t="inlineStr"/>
+      <c r="T5" s="6" t="inlineStr"/>
+      <c r="U5" s="6" t="inlineStr"/>
+      <c r="V5" s="6" t="inlineStr"/>
+      <c r="W5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -804,6 +887,30 @@
       <c r="O6" s="5" t="n">
         <v>0.9703000000000001</v>
       </c>
+      <c r="P6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="U6" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="V6" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="W6" s="6" t="n">
+        <v>0.07333333333333335</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -864,6 +971,30 @@
       </c>
       <c r="O7" s="5" t="n">
         <v>0.9703000000000001</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="U7" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="V7" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="W7" s="6" t="n">
+        <v>0.07333333333333335</v>
       </c>
     </row>
     <row r="8">
@@ -912,6 +1043,14 @@
       <c r="O8" s="5" t="n">
         <v>1.0033</v>
       </c>
+      <c r="P8" s="6" t="inlineStr"/>
+      <c r="Q8" s="6" t="inlineStr"/>
+      <c r="R8" s="6" t="inlineStr"/>
+      <c r="S8" s="6" t="inlineStr"/>
+      <c r="T8" s="6" t="inlineStr"/>
+      <c r="U8" s="6" t="inlineStr"/>
+      <c r="V8" s="6" t="inlineStr"/>
+      <c r="W8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -959,6 +1098,14 @@
       <c r="O9" s="5" t="n">
         <v>1.0033</v>
       </c>
+      <c r="P9" s="6" t="inlineStr"/>
+      <c r="Q9" s="6" t="inlineStr"/>
+      <c r="R9" s="6" t="inlineStr"/>
+      <c r="S9" s="6" t="inlineStr"/>
+      <c r="T9" s="6" t="inlineStr"/>
+      <c r="U9" s="6" t="inlineStr"/>
+      <c r="V9" s="6" t="inlineStr"/>
+      <c r="W9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1020,6 +1167,14 @@
       <c r="O10" s="5" t="n">
         <v>1.0022</v>
       </c>
+      <c r="P10" s="6" t="inlineStr"/>
+      <c r="Q10" s="6" t="inlineStr"/>
+      <c r="R10" s="6" t="inlineStr"/>
+      <c r="S10" s="6" t="inlineStr"/>
+      <c r="T10" s="6" t="inlineStr"/>
+      <c r="U10" s="6" t="inlineStr"/>
+      <c r="V10" s="6" t="inlineStr"/>
+      <c r="W10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1080,6 +1235,30 @@
       </c>
       <c r="O11" s="5" t="n">
         <v>1.0134</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1140,6 +1319,30 @@
       <c r="O12" s="5" t="n">
         <v>1.0137</v>
       </c>
+      <c r="P12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1199,6 +1402,30 @@
       <c r="O13" s="5" t="n">
         <v>0.9959</v>
       </c>
+      <c r="P13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="U13" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="V13" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W13" s="6" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1260,6 +1487,30 @@
       <c r="O14" s="5" t="n">
         <v>0.9540999999999999</v>
       </c>
+      <c r="P14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="U14" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="V14" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W14" s="6" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1321,6 +1572,30 @@
       <c r="O15" s="5" t="n">
         <v>0.9664</v>
       </c>
+      <c r="P15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="U15" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="V15" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W15" s="6" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1382,6 +1657,30 @@
       <c r="O16" s="5" t="n">
         <v>0.9741</v>
       </c>
+      <c r="P16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="U16" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="V16" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W16" s="6" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1443,6 +1742,30 @@
       <c r="O17" s="5" t="n">
         <v>0.9772999999999999</v>
       </c>
+      <c r="P17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="U17" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="V17" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W17" s="6" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1504,6 +1827,30 @@
       <c r="O18" s="5" t="n">
         <v>1.011</v>
       </c>
+      <c r="P18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1565,6 +1912,30 @@
       <c r="O19" s="5" t="n">
         <v>0.9709</v>
       </c>
+      <c r="P19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="U19" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="V19" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="W19" s="6" t="n">
+        <v>0.07333333333333335</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1626,6 +1997,14 @@
       <c r="O20" s="5" t="n">
         <v>0.9968</v>
       </c>
+      <c r="P20" s="6" t="inlineStr"/>
+      <c r="Q20" s="6" t="inlineStr"/>
+      <c r="R20" s="6" t="inlineStr"/>
+      <c r="S20" s="6" t="inlineStr"/>
+      <c r="T20" s="6" t="inlineStr"/>
+      <c r="U20" s="6" t="inlineStr"/>
+      <c r="V20" s="6" t="inlineStr"/>
+      <c r="W20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1687,6 +2066,14 @@
       <c r="O21" s="5" t="n">
         <v>0.9978</v>
       </c>
+      <c r="P21" s="6" t="inlineStr"/>
+      <c r="Q21" s="6" t="inlineStr"/>
+      <c r="R21" s="6" t="inlineStr"/>
+      <c r="S21" s="6" t="inlineStr"/>
+      <c r="T21" s="6" t="inlineStr"/>
+      <c r="U21" s="6" t="inlineStr"/>
+      <c r="V21" s="6" t="inlineStr"/>
+      <c r="W21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1738,6 +2125,14 @@
       <c r="O22" s="5" t="n">
         <v>0.9527</v>
       </c>
+      <c r="P22" s="6" t="inlineStr"/>
+      <c r="Q22" s="6" t="inlineStr"/>
+      <c r="R22" s="6" t="inlineStr"/>
+      <c r="S22" s="6" t="inlineStr"/>
+      <c r="T22" s="6" t="inlineStr"/>
+      <c r="U22" s="6" t="inlineStr"/>
+      <c r="V22" s="6" t="inlineStr"/>
+      <c r="W22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1789,6 +2184,14 @@
       <c r="O23" s="5" t="n">
         <v>0.9417</v>
       </c>
+      <c r="P23" s="6" t="inlineStr"/>
+      <c r="Q23" s="6" t="inlineStr"/>
+      <c r="R23" s="6" t="inlineStr"/>
+      <c r="S23" s="6" t="inlineStr"/>
+      <c r="T23" s="6" t="inlineStr"/>
+      <c r="U23" s="6" t="inlineStr"/>
+      <c r="V23" s="6" t="inlineStr"/>
+      <c r="W23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1840,6 +2243,14 @@
       <c r="O24" s="5" t="n">
         <v>0.9614</v>
       </c>
+      <c r="P24" s="6" t="inlineStr"/>
+      <c r="Q24" s="6" t="inlineStr"/>
+      <c r="R24" s="6" t="inlineStr"/>
+      <c r="S24" s="6" t="inlineStr"/>
+      <c r="T24" s="6" t="inlineStr"/>
+      <c r="U24" s="6" t="inlineStr"/>
+      <c r="V24" s="6" t="inlineStr"/>
+      <c r="W24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1889,6 +2300,14 @@
       <c r="O25" s="5" t="n">
         <v>0.9687</v>
       </c>
+      <c r="P25" s="6" t="inlineStr"/>
+      <c r="Q25" s="6" t="inlineStr"/>
+      <c r="R25" s="6" t="inlineStr"/>
+      <c r="S25" s="6" t="inlineStr"/>
+      <c r="T25" s="6" t="inlineStr"/>
+      <c r="U25" s="6" t="inlineStr"/>
+      <c r="V25" s="6" t="inlineStr"/>
+      <c r="W25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1936,6 +2355,14 @@
       <c r="O26" s="5" t="n">
         <v>0.9687</v>
       </c>
+      <c r="P26" s="6" t="inlineStr"/>
+      <c r="Q26" s="6" t="inlineStr"/>
+      <c r="R26" s="6" t="inlineStr"/>
+      <c r="S26" s="6" t="inlineStr"/>
+      <c r="T26" s="6" t="inlineStr"/>
+      <c r="U26" s="6" t="inlineStr"/>
+      <c r="V26" s="6" t="inlineStr"/>
+      <c r="W26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1987,6 +2414,14 @@
       <c r="O27" s="5" t="n">
         <v>0.9628</v>
       </c>
+      <c r="P27" s="6" t="inlineStr"/>
+      <c r="Q27" s="6" t="inlineStr"/>
+      <c r="R27" s="6" t="inlineStr"/>
+      <c r="S27" s="6" t="inlineStr"/>
+      <c r="T27" s="6" t="inlineStr"/>
+      <c r="U27" s="6" t="inlineStr"/>
+      <c r="V27" s="6" t="inlineStr"/>
+      <c r="W27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2038,6 +2473,14 @@
       <c r="O28" s="5" t="n">
         <v>0.9606</v>
       </c>
+      <c r="P28" s="6" t="inlineStr"/>
+      <c r="Q28" s="6" t="inlineStr"/>
+      <c r="R28" s="6" t="inlineStr"/>
+      <c r="S28" s="6" t="inlineStr"/>
+      <c r="T28" s="6" t="inlineStr"/>
+      <c r="U28" s="6" t="inlineStr"/>
+      <c r="V28" s="6" t="inlineStr"/>
+      <c r="W28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2089,6 +2532,14 @@
       <c r="O29" s="5" t="n">
         <v>0.9533</v>
       </c>
+      <c r="P29" s="6" t="inlineStr"/>
+      <c r="Q29" s="6" t="inlineStr"/>
+      <c r="R29" s="6" t="inlineStr"/>
+      <c r="S29" s="6" t="inlineStr"/>
+      <c r="T29" s="6" t="inlineStr"/>
+      <c r="U29" s="6" t="inlineStr"/>
+      <c r="V29" s="6" t="inlineStr"/>
+      <c r="W29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2140,6 +2591,14 @@
       <c r="O30" s="5" t="n">
         <v>0.9533</v>
       </c>
+      <c r="P30" s="6" t="inlineStr"/>
+      <c r="Q30" s="6" t="inlineStr"/>
+      <c r="R30" s="6" t="inlineStr"/>
+      <c r="S30" s="6" t="inlineStr"/>
+      <c r="T30" s="6" t="inlineStr"/>
+      <c r="U30" s="6" t="inlineStr"/>
+      <c r="V30" s="6" t="inlineStr"/>
+      <c r="W30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2191,6 +2650,14 @@
       <c r="O31" s="5" t="n">
         <v>0.9533</v>
       </c>
+      <c r="P31" s="6" t="inlineStr"/>
+      <c r="Q31" s="6" t="inlineStr"/>
+      <c r="R31" s="6" t="inlineStr"/>
+      <c r="S31" s="6" t="inlineStr"/>
+      <c r="T31" s="6" t="inlineStr"/>
+      <c r="U31" s="6" t="inlineStr"/>
+      <c r="V31" s="6" t="inlineStr"/>
+      <c r="W31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2242,6 +2709,14 @@
       <c r="O32" s="5" t="n">
         <v>0.9468</v>
       </c>
+      <c r="P32" s="6" t="inlineStr"/>
+      <c r="Q32" s="6" t="inlineStr"/>
+      <c r="R32" s="6" t="inlineStr"/>
+      <c r="S32" s="6" t="inlineStr"/>
+      <c r="T32" s="6" t="inlineStr"/>
+      <c r="U32" s="6" t="inlineStr"/>
+      <c r="V32" s="6" t="inlineStr"/>
+      <c r="W32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2293,6 +2768,14 @@
       <c r="O33" s="5" t="n">
         <v>0.9468</v>
       </c>
+      <c r="P33" s="6" t="inlineStr"/>
+      <c r="Q33" s="6" t="inlineStr"/>
+      <c r="R33" s="6" t="inlineStr"/>
+      <c r="S33" s="6" t="inlineStr"/>
+      <c r="T33" s="6" t="inlineStr"/>
+      <c r="U33" s="6" t="inlineStr"/>
+      <c r="V33" s="6" t="inlineStr"/>
+      <c r="W33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2344,6 +2827,14 @@
       <c r="O34" s="5" t="n">
         <v>0.9468</v>
       </c>
+      <c r="P34" s="6" t="inlineStr"/>
+      <c r="Q34" s="6" t="inlineStr"/>
+      <c r="R34" s="6" t="inlineStr"/>
+      <c r="S34" s="6" t="inlineStr"/>
+      <c r="T34" s="6" t="inlineStr"/>
+      <c r="U34" s="6" t="inlineStr"/>
+      <c r="V34" s="6" t="inlineStr"/>
+      <c r="W34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2395,6 +2886,14 @@
       <c r="O35" s="5" t="n">
         <v>0.9661</v>
       </c>
+      <c r="P35" s="6" t="inlineStr"/>
+      <c r="Q35" s="6" t="inlineStr"/>
+      <c r="R35" s="6" t="inlineStr"/>
+      <c r="S35" s="6" t="inlineStr"/>
+      <c r="T35" s="6" t="inlineStr"/>
+      <c r="U35" s="6" t="inlineStr"/>
+      <c r="V35" s="6" t="inlineStr"/>
+      <c r="W35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2446,6 +2945,14 @@
       <c r="O36" s="5" t="n">
         <v>0.9661</v>
       </c>
+      <c r="P36" s="6" t="inlineStr"/>
+      <c r="Q36" s="6" t="inlineStr"/>
+      <c r="R36" s="6" t="inlineStr"/>
+      <c r="S36" s="6" t="inlineStr"/>
+      <c r="T36" s="6" t="inlineStr"/>
+      <c r="U36" s="6" t="inlineStr"/>
+      <c r="V36" s="6" t="inlineStr"/>
+      <c r="W36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2497,6 +3004,14 @@
       <c r="O37" s="5" t="n">
         <v>0.9387</v>
       </c>
+      <c r="P37" s="6" t="inlineStr"/>
+      <c r="Q37" s="6" t="inlineStr"/>
+      <c r="R37" s="6" t="inlineStr"/>
+      <c r="S37" s="6" t="inlineStr"/>
+      <c r="T37" s="6" t="inlineStr"/>
+      <c r="U37" s="6" t="inlineStr"/>
+      <c r="V37" s="6" t="inlineStr"/>
+      <c r="W37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2548,6 +3063,14 @@
       <c r="O38" s="5" t="n">
         <v>0.9572000000000001</v>
       </c>
+      <c r="P38" s="6" t="inlineStr"/>
+      <c r="Q38" s="6" t="inlineStr"/>
+      <c r="R38" s="6" t="inlineStr"/>
+      <c r="S38" s="6" t="inlineStr"/>
+      <c r="T38" s="6" t="inlineStr"/>
+      <c r="U38" s="6" t="inlineStr"/>
+      <c r="V38" s="6" t="inlineStr"/>
+      <c r="W38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2599,6 +3122,14 @@
       <c r="O39" s="5" t="n">
         <v>0.9709</v>
       </c>
+      <c r="P39" s="6" t="inlineStr"/>
+      <c r="Q39" s="6" t="inlineStr"/>
+      <c r="R39" s="6" t="inlineStr"/>
+      <c r="S39" s="6" t="inlineStr"/>
+      <c r="T39" s="6" t="inlineStr"/>
+      <c r="U39" s="6" t="inlineStr"/>
+      <c r="V39" s="6" t="inlineStr"/>
+      <c r="W39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2650,6 +3181,14 @@
       <c r="O40" s="5" t="n">
         <v>0.9699</v>
       </c>
+      <c r="P40" s="6" t="inlineStr"/>
+      <c r="Q40" s="6" t="inlineStr"/>
+      <c r="R40" s="6" t="inlineStr"/>
+      <c r="S40" s="6" t="inlineStr"/>
+      <c r="T40" s="6" t="inlineStr"/>
+      <c r="U40" s="6" t="inlineStr"/>
+      <c r="V40" s="6" t="inlineStr"/>
+      <c r="W40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2701,6 +3240,14 @@
       <c r="O41" s="5" t="n">
         <v>0.9699</v>
       </c>
+      <c r="P41" s="6" t="inlineStr"/>
+      <c r="Q41" s="6" t="inlineStr"/>
+      <c r="R41" s="6" t="inlineStr"/>
+      <c r="S41" s="6" t="inlineStr"/>
+      <c r="T41" s="6" t="inlineStr"/>
+      <c r="U41" s="6" t="inlineStr"/>
+      <c r="V41" s="6" t="inlineStr"/>
+      <c r="W41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2752,6 +3299,14 @@
       <c r="O42" s="5" t="n">
         <v>0.9132</v>
       </c>
+      <c r="P42" s="6" t="inlineStr"/>
+      <c r="Q42" s="6" t="inlineStr"/>
+      <c r="R42" s="6" t="inlineStr"/>
+      <c r="S42" s="6" t="inlineStr"/>
+      <c r="T42" s="6" t="inlineStr"/>
+      <c r="U42" s="6" t="inlineStr"/>
+      <c r="V42" s="6" t="inlineStr"/>
+      <c r="W42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2803,6 +3358,14 @@
       <c r="O43" s="5" t="n">
         <v>1.0033</v>
       </c>
+      <c r="P43" s="6" t="inlineStr"/>
+      <c r="Q43" s="6" t="inlineStr"/>
+      <c r="R43" s="6" t="inlineStr"/>
+      <c r="S43" s="6" t="inlineStr"/>
+      <c r="T43" s="6" t="inlineStr"/>
+      <c r="U43" s="6" t="inlineStr"/>
+      <c r="V43" s="6" t="inlineStr"/>
+      <c r="W43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2854,6 +3417,14 @@
       <c r="O44" s="5" t="n">
         <v>0.9572000000000001</v>
       </c>
+      <c r="P44" s="6" t="inlineStr"/>
+      <c r="Q44" s="6" t="inlineStr"/>
+      <c r="R44" s="6" t="inlineStr"/>
+      <c r="S44" s="6" t="inlineStr"/>
+      <c r="T44" s="6" t="inlineStr"/>
+      <c r="U44" s="6" t="inlineStr"/>
+      <c r="V44" s="6" t="inlineStr"/>
+      <c r="W44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2905,6 +3476,14 @@
       <c r="O45" s="5" t="n">
         <v>0.9611</v>
       </c>
+      <c r="P45" s="6" t="inlineStr"/>
+      <c r="Q45" s="6" t="inlineStr"/>
+      <c r="R45" s="6" t="inlineStr"/>
+      <c r="S45" s="6" t="inlineStr"/>
+      <c r="T45" s="6" t="inlineStr"/>
+      <c r="U45" s="6" t="inlineStr"/>
+      <c r="V45" s="6" t="inlineStr"/>
+      <c r="W45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2956,6 +3535,14 @@
       <c r="O46" s="5" t="n">
         <v>0.8476</v>
       </c>
+      <c r="P46" s="6" t="inlineStr"/>
+      <c r="Q46" s="6" t="inlineStr"/>
+      <c r="R46" s="6" t="inlineStr"/>
+      <c r="S46" s="6" t="inlineStr"/>
+      <c r="T46" s="6" t="inlineStr"/>
+      <c r="U46" s="6" t="inlineStr"/>
+      <c r="V46" s="6" t="inlineStr"/>
+      <c r="W46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3007,6 +3594,14 @@
       <c r="O47" s="5" t="n">
         <v>0.9592000000000001</v>
       </c>
+      <c r="P47" s="6" t="inlineStr"/>
+      <c r="Q47" s="6" t="inlineStr"/>
+      <c r="R47" s="6" t="inlineStr"/>
+      <c r="S47" s="6" t="inlineStr"/>
+      <c r="T47" s="6" t="inlineStr"/>
+      <c r="U47" s="6" t="inlineStr"/>
+      <c r="V47" s="6" t="inlineStr"/>
+      <c r="W47" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3019,7 +3614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:V47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3030,57 +3625,141 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>DUID</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Fuel</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>MLF_FY25-26</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>MLF_FY26-27</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>CURTAILMENT_ACTUAL_FY23-24</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>CURTAILMENT_ACTUAL_FY24-25</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>ELI_CURTAILMENT_NEAR</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>ELI_CURTAILMENT_MED</t>
         </is>
       </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY1</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY1_LABEL</t>
+        </is>
+      </c>
+      <c r="K1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY2</t>
+        </is>
+      </c>
+      <c r="L1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY2_LABEL</t>
+        </is>
+      </c>
+      <c r="M1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY3</t>
+        </is>
+      </c>
+      <c r="N1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY3_LABEL</t>
+        </is>
+      </c>
+      <c r="O1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_AVG</t>
+        </is>
+      </c>
+      <c r="P1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY1</t>
+        </is>
+      </c>
+      <c r="Q1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY1_LABEL</t>
+        </is>
+      </c>
+      <c r="R1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY2</t>
+        </is>
+      </c>
+      <c r="S1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY2_LABEL</t>
+        </is>
+      </c>
+      <c r="T1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY3</t>
+        </is>
+      </c>
+      <c r="U1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY3_LABEL</t>
+        </is>
+      </c>
+      <c r="V1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_AVG</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>ADPPV1</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3099,14 +3778,52 @@
       </c>
       <c r="G2" s="5" t="inlineStr"/>
       <c r="H2" s="5" t="inlineStr"/>
+      <c r="I2" s="5" t="inlineStr"/>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr"/>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr"/>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr"/>
+      <c r="U2" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>ADPPV2</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3121,14 +3838,52 @@
       <c r="F3" s="5" t="inlineStr"/>
       <c r="G3" s="5" t="inlineStr"/>
       <c r="H3" s="5" t="inlineStr"/>
+      <c r="I3" s="5" t="inlineStr"/>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr"/>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr"/>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr"/>
+      <c r="U3" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>ADPPV3</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3143,14 +3898,52 @@
       <c r="F4" s="5" t="inlineStr"/>
       <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>BOWWPV1</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3167,14 +3960,52 @@
       </c>
       <c r="G5" s="5" t="inlineStr"/>
       <c r="H5" s="5" t="inlineStr"/>
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr"/>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr"/>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="inlineStr"/>
+      <c r="P5" s="5" t="inlineStr"/>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="inlineStr"/>
+      <c r="S5" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T5" s="5" t="inlineStr"/>
+      <c r="U5" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>BNGSF1</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3197,14 +4028,68 @@
       <c r="H6" s="5" t="n">
         <v>0.212860651220515</v>
       </c>
+      <c r="I6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R6" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="S6" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T6" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="U6" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V6" s="5" t="n">
+        <v>0.07333333333333335</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>BNGSF2</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3227,14 +4112,68 @@
       <c r="H7" s="5" t="n">
         <v>0.212860651220515</v>
       </c>
+      <c r="I7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Q7" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R7" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="S7" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T7" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="U7" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V7" s="5" t="n">
+        <v>0.07333333333333335</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>CBWWPV1</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3249,14 +4188,52 @@
       <c r="F8" s="5" t="inlineStr"/>
       <c r="G8" s="5" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr"/>
+      <c r="Q8" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R8" s="5" t="inlineStr"/>
+      <c r="S8" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T8" s="5" t="inlineStr"/>
+      <c r="U8" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>CBWWPV2</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3271,14 +4248,52 @@
       <c r="F9" s="5" t="inlineStr"/>
       <c r="G9" s="5" t="inlineStr"/>
       <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R9" s="5" t="inlineStr"/>
+      <c r="S9" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T9" s="5" t="inlineStr"/>
+      <c r="U9" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>HVWWPV1</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3301,14 +4316,52 @@
       <c r="H10" s="5" t="n">
         <v>0.22265637813532</v>
       </c>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr"/>
+      <c r="Q10" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R10" s="5" t="inlineStr"/>
+      <c r="S10" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T10" s="5" t="inlineStr"/>
+      <c r="U10" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>MAPS2PV1</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3331,14 +4384,68 @@
       <c r="H11" s="5" t="n">
         <v>0.225784053085401</v>
       </c>
+      <c r="I11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V11" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>MAPS3PV1</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3359,14 +4466,68 @@
       <c r="H12" s="5" t="n">
         <v>0.225784053085401</v>
       </c>
+      <c r="I12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V12" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>MANNSF2</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3387,14 +4548,68 @@
       <c r="H13" s="5" t="n">
         <v>0.225784053085401</v>
       </c>
+      <c r="I13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Q13" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R13" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="S13" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T13" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="U13" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V13" s="5" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>MWPS1PV1</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3417,14 +4632,68 @@
       <c r="H14" s="5" t="n">
         <v>0.512670422089759</v>
       </c>
+      <c r="I14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Q14" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R14" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="S14" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T14" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="U14" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V14" s="5" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>MWPS2PV1</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3447,14 +4716,68 @@
       <c r="H15" s="5" t="n">
         <v>0.512670422089759</v>
       </c>
+      <c r="I15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Q15" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R15" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="S15" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T15" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="U15" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V15" s="5" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>MWPS3PV1</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3477,14 +4800,68 @@
       <c r="H16" s="5" t="n">
         <v>0.512670422089759</v>
       </c>
+      <c r="I16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Q16" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R16" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="S16" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T16" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="U16" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V16" s="5" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>MWPS4PV1</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3507,14 +4884,68 @@
       <c r="H17" s="5" t="n">
         <v>0.512670422089759</v>
       </c>
+      <c r="I17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Q17" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R17" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="S17" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T17" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="U17" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V17" s="5" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>MBPS2PV1</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3537,14 +4968,68 @@
       <c r="H18" s="5" t="n">
         <v>0.225784053085401</v>
       </c>
+      <c r="I18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V18" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>PAREPS1</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3567,14 +5052,68 @@
       <c r="H19" s="5" t="n">
         <v>0.212860651220515</v>
       </c>
+      <c r="I19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Q19" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R19" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="S19" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T19" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="U19" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V19" s="5" t="n">
+        <v>0.07333333333333335</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>TB2SF1</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3597,14 +5136,52 @@
       <c r="H20" s="5" t="n">
         <v>0.22945882760626</v>
       </c>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O20" s="5" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr"/>
+      <c r="Q20" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R20" s="5" t="inlineStr"/>
+      <c r="S20" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T20" s="5" t="inlineStr"/>
+      <c r="U20" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>TBSF1</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -3627,14 +5204,52 @@
       <c r="H21" s="5" t="n">
         <v>0.22945882760626</v>
       </c>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+      <c r="Q21" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R21" s="5" t="inlineStr"/>
+      <c r="S21" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T21" s="5" t="inlineStr"/>
+      <c r="U21" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>CNUNDAWF</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -3653,14 +5268,52 @@
       </c>
       <c r="G22" s="5" t="inlineStr"/>
       <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr"/>
+      <c r="Q22" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R22" s="5" t="inlineStr"/>
+      <c r="S22" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T22" s="5" t="inlineStr"/>
+      <c r="U22" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>CATHROCK</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -3679,14 +5332,52 @@
       </c>
       <c r="G23" s="5" t="inlineStr"/>
       <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr"/>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr"/>
+      <c r="Q23" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R23" s="5" t="inlineStr"/>
+      <c r="S23" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T23" s="5" t="inlineStr"/>
+      <c r="U23" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>CLEMGPWF</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -3705,14 +5396,52 @@
       </c>
       <c r="G24" s="5" t="inlineStr"/>
       <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O24" s="5" t="inlineStr"/>
+      <c r="P24" s="5" t="inlineStr"/>
+      <c r="Q24" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R24" s="5" t="inlineStr"/>
+      <c r="S24" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T24" s="5" t="inlineStr"/>
+      <c r="U24" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>GSWF1A</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -3729,14 +5458,52 @@
       </c>
       <c r="G25" s="5" t="inlineStr"/>
       <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O25" s="5" t="inlineStr"/>
+      <c r="P25" s="5" t="inlineStr"/>
+      <c r="Q25" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R25" s="5" t="inlineStr"/>
+      <c r="S25" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T25" s="5" t="inlineStr"/>
+      <c r="U25" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>GSWF1B1</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -3751,14 +5518,52 @@
       <c r="F26" s="5" t="inlineStr"/>
       <c r="G26" s="5" t="inlineStr"/>
       <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O26" s="5" t="inlineStr"/>
+      <c r="P26" s="5" t="inlineStr"/>
+      <c r="Q26" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R26" s="5" t="inlineStr"/>
+      <c r="S26" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T26" s="5" t="inlineStr"/>
+      <c r="U26" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>HALLWF1</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -3777,14 +5582,52 @@
       </c>
       <c r="G27" s="5" t="inlineStr"/>
       <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr"/>
+      <c r="Q27" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R27" s="5" t="inlineStr"/>
+      <c r="S27" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T27" s="5" t="inlineStr"/>
+      <c r="U27" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>HALLWF2</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -3803,14 +5646,52 @@
       </c>
       <c r="G28" s="5" t="inlineStr"/>
       <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O28" s="5" t="inlineStr"/>
+      <c r="P28" s="5" t="inlineStr"/>
+      <c r="Q28" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R28" s="5" t="inlineStr"/>
+      <c r="S28" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T28" s="5" t="inlineStr"/>
+      <c r="U28" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>HDWF1</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -3829,14 +5710,52 @@
       </c>
       <c r="G29" s="5" t="inlineStr"/>
       <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O29" s="5" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr"/>
+      <c r="Q29" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R29" s="5" t="inlineStr"/>
+      <c r="S29" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T29" s="5" t="inlineStr"/>
+      <c r="U29" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>HDWF2</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -3855,14 +5774,52 @@
       </c>
       <c r="G30" s="5" t="inlineStr"/>
       <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="inlineStr"/>
+      <c r="N30" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O30" s="5" t="inlineStr"/>
+      <c r="P30" s="5" t="inlineStr"/>
+      <c r="Q30" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R30" s="5" t="inlineStr"/>
+      <c r="S30" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T30" s="5" t="inlineStr"/>
+      <c r="U30" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>HDWF3</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -3881,14 +5838,52 @@
       </c>
       <c r="G31" s="5" t="inlineStr"/>
       <c r="H31" s="5" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr"/>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O31" s="5" t="inlineStr"/>
+      <c r="P31" s="5" t="inlineStr"/>
+      <c r="Q31" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R31" s="5" t="inlineStr"/>
+      <c r="S31" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T31" s="5" t="inlineStr"/>
+      <c r="U31" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>LKBONNY2</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -3907,14 +5902,52 @@
       </c>
       <c r="G32" s="5" t="inlineStr"/>
       <c r="H32" s="5" t="inlineStr"/>
+      <c r="I32" s="5" t="inlineStr"/>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr"/>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr"/>
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O32" s="5" t="inlineStr"/>
+      <c r="P32" s="5" t="inlineStr"/>
+      <c r="Q32" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R32" s="5" t="inlineStr"/>
+      <c r="S32" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T32" s="5" t="inlineStr"/>
+      <c r="U32" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>LKBONNY3</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -3933,14 +5966,52 @@
       </c>
       <c r="G33" s="5" t="inlineStr"/>
       <c r="H33" s="5" t="inlineStr"/>
+      <c r="I33" s="5" t="inlineStr"/>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr"/>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr"/>
+      <c r="N33" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O33" s="5" t="inlineStr"/>
+      <c r="P33" s="5" t="inlineStr"/>
+      <c r="Q33" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R33" s="5" t="inlineStr"/>
+      <c r="S33" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T33" s="5" t="inlineStr"/>
+      <c r="U33" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>LKBONNY1</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -3959,14 +6030,52 @@
       </c>
       <c r="G34" s="5" t="inlineStr"/>
       <c r="H34" s="5" t="inlineStr"/>
+      <c r="I34" s="5" t="inlineStr"/>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr"/>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="inlineStr"/>
+      <c r="N34" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O34" s="5" t="inlineStr"/>
+      <c r="P34" s="5" t="inlineStr"/>
+      <c r="Q34" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R34" s="5" t="inlineStr"/>
+      <c r="S34" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T34" s="5" t="inlineStr"/>
+      <c r="U34" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>LGAPWF1</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -3985,14 +6094,52 @@
       </c>
       <c r="G35" s="5" t="inlineStr"/>
       <c r="H35" s="5" t="inlineStr"/>
+      <c r="I35" s="5" t="inlineStr"/>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr"/>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr"/>
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O35" s="5" t="inlineStr"/>
+      <c r="P35" s="5" t="inlineStr"/>
+      <c r="Q35" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R35" s="5" t="inlineStr"/>
+      <c r="S35" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T35" s="5" t="inlineStr"/>
+      <c r="U35" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>LGAPWF2</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4011,14 +6158,52 @@
       </c>
       <c r="G36" s="5" t="inlineStr"/>
       <c r="H36" s="5" t="inlineStr"/>
+      <c r="I36" s="5" t="inlineStr"/>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr"/>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="inlineStr"/>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O36" s="5" t="inlineStr"/>
+      <c r="P36" s="5" t="inlineStr"/>
+      <c r="Q36" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R36" s="5" t="inlineStr"/>
+      <c r="S36" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T36" s="5" t="inlineStr"/>
+      <c r="U36" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>MTMILLAR</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4037,14 +6222,52 @@
       </c>
       <c r="G37" s="5" t="inlineStr"/>
       <c r="H37" s="5" t="inlineStr"/>
+      <c r="I37" s="5" t="inlineStr"/>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr"/>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr"/>
+      <c r="N37" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O37" s="5" t="inlineStr"/>
+      <c r="P37" s="5" t="inlineStr"/>
+      <c r="Q37" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R37" s="5" t="inlineStr"/>
+      <c r="S37" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T37" s="5" t="inlineStr"/>
+      <c r="U37" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>NBHWF1</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4063,14 +6286,52 @@
       </c>
       <c r="G38" s="5" t="inlineStr"/>
       <c r="H38" s="5" t="inlineStr"/>
+      <c r="I38" s="5" t="inlineStr"/>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr"/>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M38" s="5" t="inlineStr"/>
+      <c r="N38" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O38" s="5" t="inlineStr"/>
+      <c r="P38" s="5" t="inlineStr"/>
+      <c r="Q38" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R38" s="5" t="inlineStr"/>
+      <c r="S38" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T38" s="5" t="inlineStr"/>
+      <c r="U38" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="inlineStr">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>PAREPW1</t>
         </is>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4089,14 +6350,52 @@
       </c>
       <c r="G39" s="5" t="inlineStr"/>
       <c r="H39" s="5" t="inlineStr"/>
+      <c r="I39" s="5" t="inlineStr"/>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr"/>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr"/>
+      <c r="N39" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O39" s="5" t="inlineStr"/>
+      <c r="P39" s="5" t="inlineStr"/>
+      <c r="Q39" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R39" s="5" t="inlineStr"/>
+      <c r="S39" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T39" s="5" t="inlineStr"/>
+      <c r="U39" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="7" t="inlineStr">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>SNOWSTH1</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4115,14 +6414,52 @@
       </c>
       <c r="G40" s="5" t="inlineStr"/>
       <c r="H40" s="5" t="inlineStr"/>
+      <c r="I40" s="5" t="inlineStr"/>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr"/>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M40" s="5" t="inlineStr"/>
+      <c r="N40" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O40" s="5" t="inlineStr"/>
+      <c r="P40" s="5" t="inlineStr"/>
+      <c r="Q40" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R40" s="5" t="inlineStr"/>
+      <c r="S40" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T40" s="5" t="inlineStr"/>
+      <c r="U40" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="7" t="inlineStr">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>SNOWNTH1</t>
         </is>
       </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4141,14 +6478,52 @@
       </c>
       <c r="G41" s="5" t="inlineStr"/>
       <c r="H41" s="5" t="inlineStr"/>
+      <c r="I41" s="5" t="inlineStr"/>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr"/>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr"/>
+      <c r="N41" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O41" s="5" t="inlineStr"/>
+      <c r="P41" s="5" t="inlineStr"/>
+      <c r="Q41" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R41" s="5" t="inlineStr"/>
+      <c r="S41" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T41" s="5" t="inlineStr"/>
+      <c r="U41" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>SNOWTWN1</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4167,14 +6542,52 @@
       </c>
       <c r="G42" s="5" t="inlineStr"/>
       <c r="H42" s="5" t="inlineStr"/>
+      <c r="I42" s="5" t="inlineStr"/>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="inlineStr"/>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M42" s="5" t="inlineStr"/>
+      <c r="N42" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O42" s="5" t="inlineStr"/>
+      <c r="P42" s="5" t="inlineStr"/>
+      <c r="Q42" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R42" s="5" t="inlineStr"/>
+      <c r="S42" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T42" s="5" t="inlineStr"/>
+      <c r="U42" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="7" t="inlineStr">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>STARHLWF</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4193,14 +6606,52 @@
       </c>
       <c r="G43" s="5" t="inlineStr"/>
       <c r="H43" s="5" t="inlineStr"/>
+      <c r="I43" s="5" t="inlineStr"/>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr"/>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr"/>
+      <c r="N43" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O43" s="5" t="inlineStr"/>
+      <c r="P43" s="5" t="inlineStr"/>
+      <c r="Q43" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R43" s="5" t="inlineStr"/>
+      <c r="S43" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T43" s="5" t="inlineStr"/>
+      <c r="U43" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="7" t="inlineStr">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>BLUFF1</t>
         </is>
       </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="B44" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4219,14 +6670,52 @@
       </c>
       <c r="G44" s="5" t="inlineStr"/>
       <c r="H44" s="5" t="inlineStr"/>
+      <c r="I44" s="5" t="inlineStr"/>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="inlineStr"/>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M44" s="5" t="inlineStr"/>
+      <c r="N44" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O44" s="5" t="inlineStr"/>
+      <c r="P44" s="5" t="inlineStr"/>
+      <c r="Q44" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R44" s="5" t="inlineStr"/>
+      <c r="S44" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T44" s="5" t="inlineStr"/>
+      <c r="U44" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V44" s="5" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="7" t="inlineStr">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>WATERLWF</t>
         </is>
       </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4245,14 +6734,52 @@
       </c>
       <c r="G45" s="5" t="inlineStr"/>
       <c r="H45" s="5" t="inlineStr"/>
+      <c r="I45" s="5" t="inlineStr"/>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr"/>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr"/>
+      <c r="N45" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O45" s="5" t="inlineStr"/>
+      <c r="P45" s="5" t="inlineStr"/>
+      <c r="Q45" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R45" s="5" t="inlineStr"/>
+      <c r="S45" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T45" s="5" t="inlineStr"/>
+      <c r="U45" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="7" t="inlineStr">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>WPWF</t>
         </is>
       </c>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="B46" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4271,14 +6798,52 @@
       </c>
       <c r="G46" s="5" t="inlineStr"/>
       <c r="H46" s="5" t="inlineStr"/>
+      <c r="I46" s="5" t="inlineStr"/>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="inlineStr"/>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M46" s="5" t="inlineStr"/>
+      <c r="N46" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O46" s="5" t="inlineStr"/>
+      <c r="P46" s="5" t="inlineStr"/>
+      <c r="Q46" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R46" s="5" t="inlineStr"/>
+      <c r="S46" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T46" s="5" t="inlineStr"/>
+      <c r="U46" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="7" t="inlineStr">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>WGWF1</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -4297,6 +6862,44 @@
       </c>
       <c r="G47" s="5" t="inlineStr"/>
       <c r="H47" s="5" t="inlineStr"/>
+      <c r="I47" s="5" t="inlineStr"/>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr"/>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr"/>
+      <c r="N47" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O47" s="5" t="inlineStr"/>
+      <c r="P47" s="5" t="inlineStr"/>
+      <c r="Q47" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R47" s="5" t="inlineStr"/>
+      <c r="S47" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T47" s="5" t="inlineStr"/>
+      <c r="U47" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V47" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C47">
@@ -4371,6 +6974,174 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I47">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J47">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K47">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L47">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M47">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:N47">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O2:O47">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P47">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q2:Q47">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R47">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S2:S47">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T2:T47">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U2:U47">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V2:V47">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/SA_curtailment.xlsx
+++ b/outputs/SA_curtailment.xlsx
@@ -532,12 +532,12 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Actual FY23-24</t>
+          <t>Actual FY24-25</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Actual FY24-25</t>
+          <t>Actual FY25-26</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -638,11 +638,9 @@
       </c>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="5" t="n">
-        <v>0.2903</v>
-      </c>
-      <c r="K2" s="5" t="n">
         <v>0.256</v>
       </c>
+      <c r="K2" s="5" t="inlineStr"/>
       <c r="L2" s="5" t="inlineStr"/>
       <c r="M2" s="5" t="inlineStr"/>
       <c r="N2" s="5" t="n">
@@ -806,10 +804,10 @@
         <v>8.25</v>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="n">
+      <c r="J5" s="5" t="n">
         <v>0.1726</v>
       </c>
+      <c r="K5" s="5" t="inlineStr"/>
       <c r="L5" s="5" t="inlineStr"/>
       <c r="M5" s="5" t="inlineStr"/>
       <c r="N5" s="5" t="n">
@@ -870,11 +868,9 @@
         <v>132</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0.2073</v>
-      </c>
-      <c r="K6" s="5" t="n">
         <v>0.3235</v>
       </c>
+      <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="n">
         <v>0.501077617843089</v>
       </c>
@@ -955,11 +951,9 @@
         <v>132</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>0.1744</v>
-      </c>
-      <c r="K7" s="5" t="n">
         <v>0.2766</v>
       </c>
+      <c r="K7" s="5" t="inlineStr"/>
       <c r="L7" s="5" t="n">
         <v>0.501077617843089</v>
       </c>
@@ -1150,11 +1144,9 @@
         <v>66</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0.2225</v>
-      </c>
-      <c r="K10" s="5" t="n">
         <v>0.2415</v>
       </c>
+      <c r="K10" s="5" t="inlineStr"/>
       <c r="L10" s="5" t="n">
         <v>0.511388342191138</v>
       </c>
@@ -1219,11 +1211,9 @@
         <v>3.3</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>0.2199</v>
-      </c>
-      <c r="K11" s="5" t="n">
         <v>0.2007</v>
       </c>
+      <c r="K11" s="5" t="inlineStr"/>
       <c r="L11" s="5" t="n">
         <v>0.510590381447813</v>
       </c>
@@ -1303,9 +1293,7 @@
       <c r="I12" s="2" t="n">
         <v>3.3</v>
       </c>
-      <c r="J12" s="5" t="n">
-        <v>0.2291</v>
-      </c>
+      <c r="J12" s="5" t="inlineStr"/>
       <c r="K12" s="5" t="inlineStr"/>
       <c r="L12" s="5" t="n">
         <v>0.510590381447813</v>
@@ -1386,10 +1374,10 @@
       <c r="I13" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="J13" s="5" t="inlineStr"/>
-      <c r="K13" s="5" t="n">
+      <c r="J13" s="5" t="n">
         <v>0.3012</v>
       </c>
+      <c r="K13" s="5" t="inlineStr"/>
       <c r="L13" s="5" t="n">
         <v>0.510590381447813</v>
       </c>
@@ -1470,11 +1458,9 @@
         <v>3.3</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0.1286</v>
-      </c>
-      <c r="K14" s="5" t="n">
         <v>0.2462</v>
       </c>
+      <c r="K14" s="5" t="inlineStr"/>
       <c r="L14" s="5" t="n">
         <v>0.65425629128861</v>
       </c>
@@ -1555,11 +1541,9 @@
         <v>3.3</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>0.1131</v>
-      </c>
-      <c r="K15" s="5" t="n">
         <v>0.2411</v>
       </c>
+      <c r="K15" s="5" t="inlineStr"/>
       <c r="L15" s="5" t="n">
         <v>0.65425629128861</v>
       </c>
@@ -1640,11 +1624,9 @@
         <v>3.3</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0.0897</v>
-      </c>
-      <c r="K16" s="5" t="n">
         <v>0.1273</v>
       </c>
+      <c r="K16" s="5" t="inlineStr"/>
       <c r="L16" s="5" t="n">
         <v>0.65425629128861</v>
       </c>
@@ -1725,11 +1707,9 @@
         <v>3.3</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0.1184</v>
-      </c>
-      <c r="K17" s="5" t="n">
         <v>0.2031</v>
       </c>
+      <c r="K17" s="5" t="inlineStr"/>
       <c r="L17" s="5" t="n">
         <v>0.65425629128861</v>
       </c>
@@ -1810,11 +1790,9 @@
         <v>11</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>0.2268</v>
-      </c>
-      <c r="K18" s="5" t="n">
         <v>0.2284</v>
       </c>
+      <c r="K18" s="5" t="inlineStr"/>
       <c r="L18" s="5" t="n">
         <v>0.510590381447813</v>
       </c>
@@ -1895,11 +1873,9 @@
         <v>275</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>0.1842</v>
-      </c>
-      <c r="K19" s="5" t="n">
         <v>0.3589</v>
       </c>
+      <c r="K19" s="5" t="inlineStr"/>
       <c r="L19" s="5" t="n">
         <v>0.501077617843089</v>
       </c>
@@ -1980,11 +1956,9 @@
         <v>132</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>0.1987</v>
-      </c>
-      <c r="K20" s="5" t="n">
         <v>0.2973</v>
       </c>
+      <c r="K20" s="5" t="inlineStr"/>
       <c r="L20" s="5" t="n">
         <v>0.511370986967519</v>
       </c>
@@ -2049,11 +2023,9 @@
         <v>132</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>0.2394</v>
-      </c>
-      <c r="K21" s="5" t="n">
         <v>0.3511</v>
       </c>
+      <c r="K21" s="5" t="inlineStr"/>
       <c r="L21" s="5" t="n">
         <v>0.511370986967519</v>
       </c>
@@ -2112,11 +2084,9 @@
       </c>
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="5" t="n">
-        <v>0.1746</v>
-      </c>
-      <c r="K22" s="5" t="n">
         <v>0.254</v>
       </c>
+      <c r="K22" s="5" t="inlineStr"/>
       <c r="L22" s="5" t="inlineStr"/>
       <c r="M22" s="5" t="inlineStr"/>
       <c r="N22" s="5" t="n">
@@ -2171,11 +2141,9 @@
       </c>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="5" t="n">
-        <v>0.1389</v>
-      </c>
-      <c r="K23" s="5" t="n">
         <v>0.0515</v>
       </c>
+      <c r="K23" s="5" t="inlineStr"/>
       <c r="L23" s="5" t="inlineStr"/>
       <c r="M23" s="5" t="inlineStr"/>
       <c r="N23" s="5" t="n">
@@ -2230,11 +2198,9 @@
       </c>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="5" t="n">
-        <v>0.0134</v>
-      </c>
-      <c r="K24" s="5" t="n">
         <v>0.0062</v>
       </c>
+      <c r="K24" s="5" t="inlineStr"/>
       <c r="L24" s="5" t="inlineStr"/>
       <c r="M24" s="5" t="inlineStr"/>
       <c r="N24" s="5" t="n">
@@ -2288,10 +2254,10 @@
         <v>209</v>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="5" t="inlineStr"/>
-      <c r="K25" s="5" t="n">
+      <c r="J25" s="5" t="n">
         <v>0.176</v>
       </c>
+      <c r="K25" s="5" t="inlineStr"/>
       <c r="L25" s="5" t="inlineStr"/>
       <c r="M25" s="5" t="inlineStr"/>
       <c r="N25" s="5" t="n">
@@ -2401,11 +2367,9 @@
       </c>
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="5" t="n">
-        <v>0.0813</v>
-      </c>
-      <c r="K27" s="5" t="n">
         <v>0.1169</v>
       </c>
+      <c r="K27" s="5" t="inlineStr"/>
       <c r="L27" s="5" t="inlineStr"/>
       <c r="M27" s="5" t="inlineStr"/>
       <c r="N27" s="5" t="n">
@@ -2460,11 +2424,9 @@
       </c>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="5" t="n">
-        <v>0.0914</v>
-      </c>
-      <c r="K28" s="5" t="n">
         <v>0.1053</v>
       </c>
+      <c r="K28" s="5" t="inlineStr"/>
       <c r="L28" s="5" t="inlineStr"/>
       <c r="M28" s="5" t="inlineStr"/>
       <c r="N28" s="5" t="n">
@@ -2519,11 +2481,9 @@
       </c>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="5" t="n">
-        <v>0.0092</v>
-      </c>
-      <c r="K29" s="5" t="n">
         <v>0.0033</v>
       </c>
+      <c r="K29" s="5" t="inlineStr"/>
       <c r="L29" s="5" t="inlineStr"/>
       <c r="M29" s="5" t="inlineStr"/>
       <c r="N29" s="5" t="n">
@@ -2578,11 +2538,9 @@
       </c>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="5" t="n">
-        <v>0.008500000000000001</v>
-      </c>
-      <c r="K30" s="5" t="n">
         <v>0.0038</v>
       </c>
+      <c r="K30" s="5" t="inlineStr"/>
       <c r="L30" s="5" t="inlineStr"/>
       <c r="M30" s="5" t="inlineStr"/>
       <c r="N30" s="5" t="n">
@@ -2637,11 +2595,9 @@
       </c>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="5" t="n">
-        <v>0.0092</v>
-      </c>
-      <c r="K31" s="5" t="n">
         <v>0.0027</v>
       </c>
+      <c r="K31" s="5" t="inlineStr"/>
       <c r="L31" s="5" t="inlineStr"/>
       <c r="M31" s="5" t="inlineStr"/>
       <c r="N31" s="5" t="n">
@@ -2696,11 +2652,9 @@
       </c>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="5" t="n">
-        <v>0.1058</v>
-      </c>
-      <c r="K32" s="5" t="n">
         <v>0.1941</v>
       </c>
+      <c r="K32" s="5" t="inlineStr"/>
       <c r="L32" s="5" t="inlineStr"/>
       <c r="M32" s="5" t="inlineStr"/>
       <c r="N32" s="5" t="n">
@@ -2755,11 +2709,9 @@
       </c>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="5" t="n">
-        <v>0.1939</v>
-      </c>
-      <c r="K33" s="5" t="n">
         <v>0.2514</v>
       </c>
+      <c r="K33" s="5" t="inlineStr"/>
       <c r="L33" s="5" t="inlineStr"/>
       <c r="M33" s="5" t="inlineStr"/>
       <c r="N33" s="5" t="n">
@@ -2814,11 +2766,9 @@
       </c>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="5" t="n">
-        <v>0.1878</v>
-      </c>
-      <c r="K34" s="5" t="n">
         <v>0.2535</v>
       </c>
+      <c r="K34" s="5" t="inlineStr"/>
       <c r="L34" s="5" t="inlineStr"/>
       <c r="M34" s="5" t="inlineStr"/>
       <c r="N34" s="5" t="n">
@@ -2873,11 +2823,9 @@
       </c>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="5" t="n">
-        <v>0.09669999999999999</v>
-      </c>
-      <c r="K35" s="5" t="n">
         <v>0.1438</v>
       </c>
+      <c r="K35" s="5" t="inlineStr"/>
       <c r="L35" s="5" t="inlineStr"/>
       <c r="M35" s="5" t="inlineStr"/>
       <c r="N35" s="5" t="n">
@@ -2932,11 +2880,9 @@
       </c>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="5" t="n">
-        <v>0.1085</v>
-      </c>
-      <c r="K36" s="5" t="n">
         <v>0.1628</v>
       </c>
+      <c r="K36" s="5" t="inlineStr"/>
       <c r="L36" s="5" t="inlineStr"/>
       <c r="M36" s="5" t="inlineStr"/>
       <c r="N36" s="5" t="n">
@@ -2991,11 +2937,9 @@
       </c>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="5" t="n">
-        <v>0.1885</v>
-      </c>
-      <c r="K37" s="5" t="n">
         <v>0.287</v>
       </c>
+      <c r="K37" s="5" t="inlineStr"/>
       <c r="L37" s="5" t="inlineStr"/>
       <c r="M37" s="5" t="inlineStr"/>
       <c r="N37" s="5" t="n">
@@ -3050,11 +2994,9 @@
       </c>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="5" t="n">
-        <v>0.07389999999999999</v>
-      </c>
-      <c r="K38" s="5" t="n">
         <v>0.1193</v>
       </c>
+      <c r="K38" s="5" t="inlineStr"/>
       <c r="L38" s="5" t="inlineStr"/>
       <c r="M38" s="5" t="inlineStr"/>
       <c r="N38" s="5" t="n">
@@ -3109,11 +3051,9 @@
       </c>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="5" t="n">
-        <v>0.0914</v>
-      </c>
-      <c r="K39" s="5" t="n">
         <v>0.1943</v>
       </c>
+      <c r="K39" s="5" t="inlineStr"/>
       <c r="L39" s="5" t="inlineStr"/>
       <c r="M39" s="5" t="inlineStr"/>
       <c r="N39" s="5" t="n">
@@ -3168,11 +3108,9 @@
       </c>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="5" t="n">
-        <v>0.0071</v>
-      </c>
-      <c r="K40" s="5" t="n">
         <v>0.0037</v>
       </c>
+      <c r="K40" s="5" t="inlineStr"/>
       <c r="L40" s="5" t="inlineStr"/>
       <c r="M40" s="5" t="inlineStr"/>
       <c r="N40" s="5" t="n">
@@ -3227,11 +3165,9 @@
       </c>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="5" t="n">
-        <v>0.0101</v>
-      </c>
-      <c r="K41" s="5" t="n">
         <v>0.0026</v>
       </c>
+      <c r="K41" s="5" t="inlineStr"/>
       <c r="L41" s="5" t="inlineStr"/>
       <c r="M41" s="5" t="inlineStr"/>
       <c r="N41" s="5" t="n">
@@ -3286,11 +3222,9 @@
       </c>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="5" t="n">
-        <v>0.1075</v>
-      </c>
-      <c r="K42" s="5" t="n">
         <v>0.1825</v>
       </c>
+      <c r="K42" s="5" t="inlineStr"/>
       <c r="L42" s="5" t="inlineStr"/>
       <c r="M42" s="5" t="inlineStr"/>
       <c r="N42" s="5" t="n">
@@ -3347,9 +3281,7 @@
       <c r="J43" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K43" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="K43" s="5" t="inlineStr"/>
       <c r="L43" s="5" t="inlineStr"/>
       <c r="M43" s="5" t="inlineStr"/>
       <c r="N43" s="5" t="n">
@@ -3404,11 +3336,9 @@
       </c>
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="5" t="n">
-        <v>0.1016</v>
-      </c>
-      <c r="K44" s="5" t="n">
         <v>0.0847</v>
       </c>
+      <c r="K44" s="5" t="inlineStr"/>
       <c r="L44" s="5" t="inlineStr"/>
       <c r="M44" s="5" t="inlineStr"/>
       <c r="N44" s="5" t="n">
@@ -3463,11 +3393,9 @@
       </c>
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="5" t="n">
-        <v>0.0239</v>
-      </c>
-      <c r="K45" s="5" t="n">
         <v>0.0203</v>
       </c>
+      <c r="K45" s="5" t="inlineStr"/>
       <c r="L45" s="5" t="inlineStr"/>
       <c r="M45" s="5" t="inlineStr"/>
       <c r="N45" s="5" t="n">
@@ -3522,11 +3450,9 @@
       </c>
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="5" t="n">
-        <v>0.0871</v>
-      </c>
-      <c r="K46" s="5" t="n">
         <v>0.1598</v>
       </c>
+      <c r="K46" s="5" t="inlineStr"/>
       <c r="L46" s="5" t="inlineStr"/>
       <c r="M46" s="5" t="inlineStr"/>
       <c r="N46" s="5" t="n">
@@ -3581,11 +3507,9 @@
       </c>
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="5" t="n">
-        <v>0.0941</v>
-      </c>
-      <c r="K47" s="5" t="n">
         <v>0.0426</v>
       </c>
+      <c r="K47" s="5" t="inlineStr"/>
       <c r="L47" s="5" t="inlineStr"/>
       <c r="M47" s="5" t="inlineStr"/>
       <c r="N47" s="5" t="n">
@@ -3664,12 +3588,12 @@
       </c>
       <c r="E1" s="7" t="inlineStr">
         <is>
-          <t>CURTAILMENT_ACTUAL_FY23-24</t>
+          <t>CURTAILMENT_ACTUAL_FY24-25</t>
         </is>
       </c>
       <c r="F1" s="7" t="inlineStr">
         <is>
-          <t>CURTAILMENT_ACTUAL_FY24-25</t>
+          <t>CURTAILMENT_ACTUAL_FY25-26</t>
         </is>
       </c>
       <c r="G1" s="7" t="inlineStr">
@@ -3771,11 +3695,9 @@
         <v>1.0033</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.2903</v>
-      </c>
-      <c r="F2" s="5" t="n">
         <v>0.256</v>
       </c>
+      <c r="F2" s="5" t="inlineStr"/>
       <c r="G2" s="5" t="inlineStr"/>
       <c r="H2" s="5" t="inlineStr"/>
       <c r="I2" s="5" t="inlineStr"/>
@@ -3954,10 +3876,10 @@
       <c r="D5" s="5" t="n">
         <v>1.0002</v>
       </c>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="n">
+      <c r="E5" s="5" t="n">
         <v>0.1726</v>
       </c>
+      <c r="F5" s="5" t="inlineStr"/>
       <c r="G5" s="5" t="inlineStr"/>
       <c r="H5" s="5" t="inlineStr"/>
       <c r="I5" s="5" t="inlineStr"/>
@@ -4017,11 +3939,9 @@
         <v>0.9703000000000001</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.2073</v>
-      </c>
-      <c r="F6" s="5" t="n">
         <v>0.3235</v>
       </c>
+      <c r="F6" s="5" t="inlineStr"/>
       <c r="G6" s="5" t="n">
         <v>0.501077617843089</v>
       </c>
@@ -4101,11 +4021,9 @@
         <v>0.9703000000000001</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.1744</v>
-      </c>
-      <c r="F7" s="5" t="n">
         <v>0.2766</v>
       </c>
+      <c r="F7" s="5" t="inlineStr"/>
       <c r="G7" s="5" t="n">
         <v>0.501077617843089</v>
       </c>
@@ -4305,11 +4223,9 @@
         <v>1.0022</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.2225</v>
-      </c>
-      <c r="F10" s="5" t="n">
         <v>0.2415</v>
       </c>
+      <c r="F10" s="5" t="inlineStr"/>
       <c r="G10" s="5" t="n">
         <v>0.511388342191138</v>
       </c>
@@ -4373,11 +4289,9 @@
         <v>1.0134</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.2199</v>
-      </c>
-      <c r="F11" s="5" t="n">
         <v>0.2007</v>
       </c>
+      <c r="F11" s="5" t="inlineStr"/>
       <c r="G11" s="5" t="n">
         <v>0.510590381447813</v>
       </c>
@@ -4456,9 +4370,7 @@
       <c r="D12" s="5" t="n">
         <v>1.0137</v>
       </c>
-      <c r="E12" s="5" t="n">
-        <v>0.2291</v>
-      </c>
+      <c r="E12" s="5" t="inlineStr"/>
       <c r="F12" s="5" t="inlineStr"/>
       <c r="G12" s="5" t="n">
         <v>0.510590381447813</v>
@@ -4538,10 +4450,10 @@
       <c r="D13" s="5" t="n">
         <v>0.9959</v>
       </c>
-      <c r="E13" s="5" t="inlineStr"/>
-      <c r="F13" s="5" t="n">
+      <c r="E13" s="5" t="n">
         <v>0.3012</v>
       </c>
+      <c r="F13" s="5" t="inlineStr"/>
       <c r="G13" s="5" t="n">
         <v>0.510590381447813</v>
       </c>
@@ -4621,11 +4533,9 @@
         <v>0.9540999999999999</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.1286</v>
-      </c>
-      <c r="F14" s="5" t="n">
         <v>0.2462</v>
       </c>
+      <c r="F14" s="5" t="inlineStr"/>
       <c r="G14" s="5" t="n">
         <v>0.65425629128861</v>
       </c>
@@ -4705,11 +4615,9 @@
         <v>0.9664</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.1131</v>
-      </c>
-      <c r="F15" s="5" t="n">
         <v>0.2411</v>
       </c>
+      <c r="F15" s="5" t="inlineStr"/>
       <c r="G15" s="5" t="n">
         <v>0.65425629128861</v>
       </c>
@@ -4789,11 +4697,9 @@
         <v>0.9741</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.0897</v>
-      </c>
-      <c r="F16" s="5" t="n">
         <v>0.1273</v>
       </c>
+      <c r="F16" s="5" t="inlineStr"/>
       <c r="G16" s="5" t="n">
         <v>0.65425629128861</v>
       </c>
@@ -4873,11 +4779,9 @@
         <v>0.9772999999999999</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.1184</v>
-      </c>
-      <c r="F17" s="5" t="n">
         <v>0.2031</v>
       </c>
+      <c r="F17" s="5" t="inlineStr"/>
       <c r="G17" s="5" t="n">
         <v>0.65425629128861</v>
       </c>
@@ -4957,11 +4861,9 @@
         <v>1.011</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.2268</v>
-      </c>
-      <c r="F18" s="5" t="n">
         <v>0.2284</v>
       </c>
+      <c r="F18" s="5" t="inlineStr"/>
       <c r="G18" s="5" t="n">
         <v>0.510590381447813</v>
       </c>
@@ -5041,11 +4943,9 @@
         <v>0.9709</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0.1842</v>
-      </c>
-      <c r="F19" s="5" t="n">
         <v>0.3589</v>
       </c>
+      <c r="F19" s="5" t="inlineStr"/>
       <c r="G19" s="5" t="n">
         <v>0.501077617843089</v>
       </c>
@@ -5125,11 +5025,9 @@
         <v>0.9968</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.1987</v>
-      </c>
-      <c r="F20" s="5" t="n">
         <v>0.2973</v>
       </c>
+      <c r="F20" s="5" t="inlineStr"/>
       <c r="G20" s="5" t="n">
         <v>0.511370986967519</v>
       </c>
@@ -5193,11 +5091,9 @@
         <v>0.9978</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0.2394</v>
-      </c>
-      <c r="F21" s="5" t="n">
         <v>0.3511</v>
       </c>
+      <c r="F21" s="5" t="inlineStr"/>
       <c r="G21" s="5" t="n">
         <v>0.511370986967519</v>
       </c>
@@ -5261,11 +5157,9 @@
         <v>0.9527</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.1746</v>
-      </c>
-      <c r="F22" s="5" t="n">
         <v>0.254</v>
       </c>
+      <c r="F22" s="5" t="inlineStr"/>
       <c r="G22" s="5" t="inlineStr"/>
       <c r="H22" s="5" t="inlineStr"/>
       <c r="I22" s="5" t="inlineStr"/>
@@ -5325,11 +5219,9 @@
         <v>0.9417</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0.1389</v>
-      </c>
-      <c r="F23" s="5" t="n">
         <v>0.0515</v>
       </c>
+      <c r="F23" s="5" t="inlineStr"/>
       <c r="G23" s="5" t="inlineStr"/>
       <c r="H23" s="5" t="inlineStr"/>
       <c r="I23" s="5" t="inlineStr"/>
@@ -5389,11 +5281,9 @@
         <v>0.9614</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0.0134</v>
-      </c>
-      <c r="F24" s="5" t="n">
         <v>0.0062</v>
       </c>
+      <c r="F24" s="5" t="inlineStr"/>
       <c r="G24" s="5" t="inlineStr"/>
       <c r="H24" s="5" t="inlineStr"/>
       <c r="I24" s="5" t="inlineStr"/>
@@ -5452,10 +5342,10 @@
       <c r="D25" s="5" t="n">
         <v>0.9687</v>
       </c>
-      <c r="E25" s="5" t="inlineStr"/>
-      <c r="F25" s="5" t="n">
+      <c r="E25" s="5" t="n">
         <v>0.176</v>
       </c>
+      <c r="F25" s="5" t="inlineStr"/>
       <c r="G25" s="5" t="inlineStr"/>
       <c r="H25" s="5" t="inlineStr"/>
       <c r="I25" s="5" t="inlineStr"/>
@@ -5575,11 +5465,9 @@
         <v>0.9628</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>0.0813</v>
-      </c>
-      <c r="F27" s="5" t="n">
         <v>0.1169</v>
       </c>
+      <c r="F27" s="5" t="inlineStr"/>
       <c r="G27" s="5" t="inlineStr"/>
       <c r="H27" s="5" t="inlineStr"/>
       <c r="I27" s="5" t="inlineStr"/>
@@ -5639,11 +5527,9 @@
         <v>0.9606</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0.0914</v>
-      </c>
-      <c r="F28" s="5" t="n">
         <v>0.1053</v>
       </c>
+      <c r="F28" s="5" t="inlineStr"/>
       <c r="G28" s="5" t="inlineStr"/>
       <c r="H28" s="5" t="inlineStr"/>
       <c r="I28" s="5" t="inlineStr"/>
@@ -5703,11 +5589,9 @@
         <v>0.9533</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0.0092</v>
-      </c>
-      <c r="F29" s="5" t="n">
         <v>0.0033</v>
       </c>
+      <c r="F29" s="5" t="inlineStr"/>
       <c r="G29" s="5" t="inlineStr"/>
       <c r="H29" s="5" t="inlineStr"/>
       <c r="I29" s="5" t="inlineStr"/>
@@ -5767,11 +5651,9 @@
         <v>0.9533</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0.008500000000000001</v>
-      </c>
-      <c r="F30" s="5" t="n">
         <v>0.0038</v>
       </c>
+      <c r="F30" s="5" t="inlineStr"/>
       <c r="G30" s="5" t="inlineStr"/>
       <c r="H30" s="5" t="inlineStr"/>
       <c r="I30" s="5" t="inlineStr"/>
@@ -5831,11 +5713,9 @@
         <v>0.9533</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0.0092</v>
-      </c>
-      <c r="F31" s="5" t="n">
         <v>0.0027</v>
       </c>
+      <c r="F31" s="5" t="inlineStr"/>
       <c r="G31" s="5" t="inlineStr"/>
       <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="5" t="inlineStr"/>
@@ -5895,11 +5775,9 @@
         <v>0.9468</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>0.1058</v>
-      </c>
-      <c r="F32" s="5" t="n">
         <v>0.1941</v>
       </c>
+      <c r="F32" s="5" t="inlineStr"/>
       <c r="G32" s="5" t="inlineStr"/>
       <c r="H32" s="5" t="inlineStr"/>
       <c r="I32" s="5" t="inlineStr"/>
@@ -5959,11 +5837,9 @@
         <v>0.9468</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0.1939</v>
-      </c>
-      <c r="F33" s="5" t="n">
         <v>0.2514</v>
       </c>
+      <c r="F33" s="5" t="inlineStr"/>
       <c r="G33" s="5" t="inlineStr"/>
       <c r="H33" s="5" t="inlineStr"/>
       <c r="I33" s="5" t="inlineStr"/>
@@ -6023,11 +5899,9 @@
         <v>0.9468</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0.1878</v>
-      </c>
-      <c r="F34" s="5" t="n">
         <v>0.2535</v>
       </c>
+      <c r="F34" s="5" t="inlineStr"/>
       <c r="G34" s="5" t="inlineStr"/>
       <c r="H34" s="5" t="inlineStr"/>
       <c r="I34" s="5" t="inlineStr"/>
@@ -6087,11 +5961,9 @@
         <v>0.9661</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0.09669999999999999</v>
-      </c>
-      <c r="F35" s="5" t="n">
         <v>0.1438</v>
       </c>
+      <c r="F35" s="5" t="inlineStr"/>
       <c r="G35" s="5" t="inlineStr"/>
       <c r="H35" s="5" t="inlineStr"/>
       <c r="I35" s="5" t="inlineStr"/>
@@ -6151,11 +6023,9 @@
         <v>0.9661</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0.1085</v>
-      </c>
-      <c r="F36" s="5" t="n">
         <v>0.1628</v>
       </c>
+      <c r="F36" s="5" t="inlineStr"/>
       <c r="G36" s="5" t="inlineStr"/>
       <c r="H36" s="5" t="inlineStr"/>
       <c r="I36" s="5" t="inlineStr"/>
@@ -6215,11 +6085,9 @@
         <v>0.9387</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0.1885</v>
-      </c>
-      <c r="F37" s="5" t="n">
         <v>0.287</v>
       </c>
+      <c r="F37" s="5" t="inlineStr"/>
       <c r="G37" s="5" t="inlineStr"/>
       <c r="H37" s="5" t="inlineStr"/>
       <c r="I37" s="5" t="inlineStr"/>
@@ -6279,11 +6147,9 @@
         <v>0.9572000000000001</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>0.07389999999999999</v>
-      </c>
-      <c r="F38" s="5" t="n">
         <v>0.1193</v>
       </c>
+      <c r="F38" s="5" t="inlineStr"/>
       <c r="G38" s="5" t="inlineStr"/>
       <c r="H38" s="5" t="inlineStr"/>
       <c r="I38" s="5" t="inlineStr"/>
@@ -6343,11 +6209,9 @@
         <v>0.9709</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>0.0914</v>
-      </c>
-      <c r="F39" s="5" t="n">
         <v>0.1943</v>
       </c>
+      <c r="F39" s="5" t="inlineStr"/>
       <c r="G39" s="5" t="inlineStr"/>
       <c r="H39" s="5" t="inlineStr"/>
       <c r="I39" s="5" t="inlineStr"/>
@@ -6407,11 +6271,9 @@
         <v>0.9699</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>0.0071</v>
-      </c>
-      <c r="F40" s="5" t="n">
         <v>0.0037</v>
       </c>
+      <c r="F40" s="5" t="inlineStr"/>
       <c r="G40" s="5" t="inlineStr"/>
       <c r="H40" s="5" t="inlineStr"/>
       <c r="I40" s="5" t="inlineStr"/>
@@ -6471,11 +6333,9 @@
         <v>0.9699</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>0.0101</v>
-      </c>
-      <c r="F41" s="5" t="n">
         <v>0.0026</v>
       </c>
+      <c r="F41" s="5" t="inlineStr"/>
       <c r="G41" s="5" t="inlineStr"/>
       <c r="H41" s="5" t="inlineStr"/>
       <c r="I41" s="5" t="inlineStr"/>
@@ -6535,11 +6395,9 @@
         <v>0.9132</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0.1075</v>
-      </c>
-      <c r="F42" s="5" t="n">
         <v>0.1825</v>
       </c>
+      <c r="F42" s="5" t="inlineStr"/>
       <c r="G42" s="5" t="inlineStr"/>
       <c r="H42" s="5" t="inlineStr"/>
       <c r="I42" s="5" t="inlineStr"/>
@@ -6601,9 +6459,7 @@
       <c r="E43" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F43" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="F43" s="5" t="inlineStr"/>
       <c r="G43" s="5" t="inlineStr"/>
       <c r="H43" s="5" t="inlineStr"/>
       <c r="I43" s="5" t="inlineStr"/>
@@ -6663,11 +6519,9 @@
         <v>0.9572000000000001</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0.1016</v>
-      </c>
-      <c r="F44" s="5" t="n">
         <v>0.0847</v>
       </c>
+      <c r="F44" s="5" t="inlineStr"/>
       <c r="G44" s="5" t="inlineStr"/>
       <c r="H44" s="5" t="inlineStr"/>
       <c r="I44" s="5" t="inlineStr"/>
@@ -6727,11 +6581,9 @@
         <v>0.9611</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>0.0239</v>
-      </c>
-      <c r="F45" s="5" t="n">
         <v>0.0203</v>
       </c>
+      <c r="F45" s="5" t="inlineStr"/>
       <c r="G45" s="5" t="inlineStr"/>
       <c r="H45" s="5" t="inlineStr"/>
       <c r="I45" s="5" t="inlineStr"/>
@@ -6791,11 +6643,9 @@
         <v>0.8476</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>0.0871</v>
-      </c>
-      <c r="F46" s="5" t="n">
         <v>0.1598</v>
       </c>
+      <c r="F46" s="5" t="inlineStr"/>
       <c r="G46" s="5" t="inlineStr"/>
       <c r="H46" s="5" t="inlineStr"/>
       <c r="I46" s="5" t="inlineStr"/>
@@ -6855,11 +6705,9 @@
         <v>0.9592000000000001</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0.0941</v>
-      </c>
-      <c r="F47" s="5" t="n">
         <v>0.0426</v>
       </c>
+      <c r="F47" s="5" t="inlineStr"/>
       <c r="G47" s="5" t="inlineStr"/>
       <c r="H47" s="5" t="inlineStr"/>
       <c r="I47" s="5" t="inlineStr"/>

--- a/outputs/SA_curtailment.xlsx
+++ b/outputs/SA_curtailment.xlsx
@@ -807,7 +807,9 @@
       <c r="J5" s="5" t="n">
         <v>0.1726</v>
       </c>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="K5" s="5" t="n">
+        <v>0.1928</v>
+      </c>
       <c r="L5" s="5" t="inlineStr"/>
       <c r="M5" s="5" t="inlineStr"/>
       <c r="N5" s="5" t="n">
@@ -953,7 +955,9 @@
       <c r="J7" s="5" t="n">
         <v>0.2766</v>
       </c>
-      <c r="K7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="n">
+        <v>0.302</v>
+      </c>
       <c r="L7" s="5" t="n">
         <v>0.501077617843089</v>
       </c>
@@ -1146,7 +1150,9 @@
       <c r="J10" s="5" t="n">
         <v>0.2415</v>
       </c>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="n">
+        <v>0.2987</v>
+      </c>
       <c r="L10" s="5" t="n">
         <v>0.511388342191138</v>
       </c>
@@ -1377,7 +1383,9 @@
       <c r="J13" s="5" t="n">
         <v>0.3012</v>
       </c>
-      <c r="K13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="n">
+        <v>0.2557</v>
+      </c>
       <c r="L13" s="5" t="n">
         <v>0.510590381447813</v>
       </c>
@@ -1460,7 +1468,9 @@
       <c r="J14" s="5" t="n">
         <v>0.2462</v>
       </c>
-      <c r="K14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="n">
+        <v>0.3446</v>
+      </c>
       <c r="L14" s="5" t="n">
         <v>0.65425629128861</v>
       </c>
@@ -1543,7 +1553,9 @@
       <c r="J15" s="5" t="n">
         <v>0.2411</v>
       </c>
-      <c r="K15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="n">
+        <v>0.3571</v>
+      </c>
       <c r="L15" s="5" t="n">
         <v>0.65425629128861</v>
       </c>
@@ -1626,7 +1638,9 @@
       <c r="J16" s="5" t="n">
         <v>0.1273</v>
       </c>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="n">
+        <v>0.2429</v>
+      </c>
       <c r="L16" s="5" t="n">
         <v>0.65425629128861</v>
       </c>
@@ -1709,7 +1723,9 @@
       <c r="J17" s="5" t="n">
         <v>0.2031</v>
       </c>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="n">
+        <v>0.3023</v>
+      </c>
       <c r="L17" s="5" t="n">
         <v>0.65425629128861</v>
       </c>
@@ -1875,7 +1891,9 @@
       <c r="J19" s="5" t="n">
         <v>0.3589</v>
       </c>
-      <c r="K19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="n">
+        <v>0.4077</v>
+      </c>
       <c r="L19" s="5" t="n">
         <v>0.501077617843089</v>
       </c>
@@ -1958,7 +1976,9 @@
       <c r="J20" s="5" t="n">
         <v>0.2973</v>
       </c>
-      <c r="K20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="n">
+        <v>0.3825</v>
+      </c>
       <c r="L20" s="5" t="n">
         <v>0.511370986967519</v>
       </c>
@@ -2025,7 +2045,9 @@
       <c r="J21" s="5" t="n">
         <v>0.3511</v>
       </c>
-      <c r="K21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="n">
+        <v>0.4088</v>
+      </c>
       <c r="L21" s="5" t="n">
         <v>0.511370986967519</v>
       </c>
@@ -2086,7 +2108,9 @@
       <c r="J22" s="5" t="n">
         <v>0.254</v>
       </c>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="n">
+        <v>0.2722</v>
+      </c>
       <c r="L22" s="5" t="inlineStr"/>
       <c r="M22" s="5" t="inlineStr"/>
       <c r="N22" s="5" t="n">
@@ -2143,7 +2167,9 @@
       <c r="J23" s="5" t="n">
         <v>0.0515</v>
       </c>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="n">
+        <v>0.0373</v>
+      </c>
       <c r="L23" s="5" t="inlineStr"/>
       <c r="M23" s="5" t="inlineStr"/>
       <c r="N23" s="5" t="n">
@@ -2200,7 +2226,9 @@
       <c r="J24" s="5" t="n">
         <v>0.0062</v>
       </c>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="n">
+        <v>0.0175</v>
+      </c>
       <c r="L24" s="5" t="inlineStr"/>
       <c r="M24" s="5" t="inlineStr"/>
       <c r="N24" s="5" t="n">
@@ -2257,7 +2285,9 @@
       <c r="J25" s="5" t="n">
         <v>0.176</v>
       </c>
-      <c r="K25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="n">
+        <v>0.09</v>
+      </c>
       <c r="L25" s="5" t="inlineStr"/>
       <c r="M25" s="5" t="inlineStr"/>
       <c r="N25" s="5" t="n">
@@ -2312,7 +2342,9 @@
       </c>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="5" t="inlineStr"/>
-      <c r="K26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="n">
+        <v>0.2684</v>
+      </c>
       <c r="L26" s="5" t="inlineStr"/>
       <c r="M26" s="5" t="inlineStr"/>
       <c r="N26" s="5" t="n">
@@ -2369,7 +2401,9 @@
       <c r="J27" s="5" t="n">
         <v>0.1169</v>
       </c>
-      <c r="K27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="n">
+        <v>0.1842</v>
+      </c>
       <c r="L27" s="5" t="inlineStr"/>
       <c r="M27" s="5" t="inlineStr"/>
       <c r="N27" s="5" t="n">
@@ -2426,7 +2460,9 @@
       <c r="J28" s="5" t="n">
         <v>0.1053</v>
       </c>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="n">
+        <v>0.1829</v>
+      </c>
       <c r="L28" s="5" t="inlineStr"/>
       <c r="M28" s="5" t="inlineStr"/>
       <c r="N28" s="5" t="n">
@@ -2483,7 +2519,9 @@
       <c r="J29" s="5" t="n">
         <v>0.0033</v>
       </c>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="n">
+        <v>0.0016</v>
+      </c>
       <c r="L29" s="5" t="inlineStr"/>
       <c r="M29" s="5" t="inlineStr"/>
       <c r="N29" s="5" t="n">
@@ -2540,7 +2578,9 @@
       <c r="J30" s="5" t="n">
         <v>0.0038</v>
       </c>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="n">
+        <v>0.0011</v>
+      </c>
       <c r="L30" s="5" t="inlineStr"/>
       <c r="M30" s="5" t="inlineStr"/>
       <c r="N30" s="5" t="n">
@@ -2597,7 +2637,9 @@
       <c r="J31" s="5" t="n">
         <v>0.0027</v>
       </c>
-      <c r="K31" s="5" t="inlineStr"/>
+      <c r="K31" s="5" t="n">
+        <v>0.0015</v>
+      </c>
       <c r="L31" s="5" t="inlineStr"/>
       <c r="M31" s="5" t="inlineStr"/>
       <c r="N31" s="5" t="n">
@@ -2654,7 +2696,9 @@
       <c r="J32" s="5" t="n">
         <v>0.1941</v>
       </c>
-      <c r="K32" s="5" t="inlineStr"/>
+      <c r="K32" s="5" t="n">
+        <v>0.2447</v>
+      </c>
       <c r="L32" s="5" t="inlineStr"/>
       <c r="M32" s="5" t="inlineStr"/>
       <c r="N32" s="5" t="n">
@@ -2711,7 +2755,9 @@
       <c r="J33" s="5" t="n">
         <v>0.2514</v>
       </c>
-      <c r="K33" s="5" t="inlineStr"/>
+      <c r="K33" s="5" t="n">
+        <v>0.2681</v>
+      </c>
       <c r="L33" s="5" t="inlineStr"/>
       <c r="M33" s="5" t="inlineStr"/>
       <c r="N33" s="5" t="n">
@@ -2768,7 +2814,9 @@
       <c r="J34" s="5" t="n">
         <v>0.2535</v>
       </c>
-      <c r="K34" s="5" t="inlineStr"/>
+      <c r="K34" s="5" t="n">
+        <v>0.2928</v>
+      </c>
       <c r="L34" s="5" t="inlineStr"/>
       <c r="M34" s="5" t="inlineStr"/>
       <c r="N34" s="5" t="n">
@@ -2825,7 +2873,9 @@
       <c r="J35" s="5" t="n">
         <v>0.1438</v>
       </c>
-      <c r="K35" s="5" t="inlineStr"/>
+      <c r="K35" s="5" t="n">
+        <v>0.1687</v>
+      </c>
       <c r="L35" s="5" t="inlineStr"/>
       <c r="M35" s="5" t="inlineStr"/>
       <c r="N35" s="5" t="n">
@@ -2882,7 +2932,9 @@
       <c r="J36" s="5" t="n">
         <v>0.1628</v>
       </c>
-      <c r="K36" s="5" t="inlineStr"/>
+      <c r="K36" s="5" t="n">
+        <v>0.1911</v>
+      </c>
       <c r="L36" s="5" t="inlineStr"/>
       <c r="M36" s="5" t="inlineStr"/>
       <c r="N36" s="5" t="n">
@@ -2939,7 +2991,9 @@
       <c r="J37" s="5" t="n">
         <v>0.287</v>
       </c>
-      <c r="K37" s="5" t="inlineStr"/>
+      <c r="K37" s="5" t="n">
+        <v>0.1473</v>
+      </c>
       <c r="L37" s="5" t="inlineStr"/>
       <c r="M37" s="5" t="inlineStr"/>
       <c r="N37" s="5" t="n">
@@ -2996,7 +3050,9 @@
       <c r="J38" s="5" t="n">
         <v>0.1193</v>
       </c>
-      <c r="K38" s="5" t="inlineStr"/>
+      <c r="K38" s="5" t="n">
+        <v>0.1648</v>
+      </c>
       <c r="L38" s="5" t="inlineStr"/>
       <c r="M38" s="5" t="inlineStr"/>
       <c r="N38" s="5" t="n">
@@ -3053,7 +3109,9 @@
       <c r="J39" s="5" t="n">
         <v>0.1943</v>
       </c>
-      <c r="K39" s="5" t="inlineStr"/>
+      <c r="K39" s="5" t="n">
+        <v>0.2082</v>
+      </c>
       <c r="L39" s="5" t="inlineStr"/>
       <c r="M39" s="5" t="inlineStr"/>
       <c r="N39" s="5" t="n">
@@ -3110,7 +3168,9 @@
       <c r="J40" s="5" t="n">
         <v>0.0037</v>
       </c>
-      <c r="K40" s="5" t="inlineStr"/>
+      <c r="K40" s="5" t="n">
+        <v>0.0026</v>
+      </c>
       <c r="L40" s="5" t="inlineStr"/>
       <c r="M40" s="5" t="inlineStr"/>
       <c r="N40" s="5" t="n">
@@ -3167,7 +3227,9 @@
       <c r="J41" s="5" t="n">
         <v>0.0026</v>
       </c>
-      <c r="K41" s="5" t="inlineStr"/>
+      <c r="K41" s="5" t="n">
+        <v>0.0028</v>
+      </c>
       <c r="L41" s="5" t="inlineStr"/>
       <c r="M41" s="5" t="inlineStr"/>
       <c r="N41" s="5" t="n">
@@ -3224,7 +3286,9 @@
       <c r="J42" s="5" t="n">
         <v>0.1825</v>
       </c>
-      <c r="K42" s="5" t="inlineStr"/>
+      <c r="K42" s="5" t="n">
+        <v>0.2632</v>
+      </c>
       <c r="L42" s="5" t="inlineStr"/>
       <c r="M42" s="5" t="inlineStr"/>
       <c r="N42" s="5" t="n">
@@ -3281,7 +3345,9 @@
       <c r="J43" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K43" s="5" t="inlineStr"/>
+      <c r="K43" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="L43" s="5" t="inlineStr"/>
       <c r="M43" s="5" t="inlineStr"/>
       <c r="N43" s="5" t="n">
@@ -3338,7 +3404,9 @@
       <c r="J44" s="5" t="n">
         <v>0.0847</v>
       </c>
-      <c r="K44" s="5" t="inlineStr"/>
+      <c r="K44" s="5" t="n">
+        <v>0.1771</v>
+      </c>
       <c r="L44" s="5" t="inlineStr"/>
       <c r="M44" s="5" t="inlineStr"/>
       <c r="N44" s="5" t="n">
@@ -3395,7 +3463,9 @@
       <c r="J45" s="5" t="n">
         <v>0.0203</v>
       </c>
-      <c r="K45" s="5" t="inlineStr"/>
+      <c r="K45" s="5" t="n">
+        <v>0.0122</v>
+      </c>
       <c r="L45" s="5" t="inlineStr"/>
       <c r="M45" s="5" t="inlineStr"/>
       <c r="N45" s="5" t="n">
@@ -3452,7 +3522,9 @@
       <c r="J46" s="5" t="n">
         <v>0.1598</v>
       </c>
-      <c r="K46" s="5" t="inlineStr"/>
+      <c r="K46" s="5" t="n">
+        <v>0.1908</v>
+      </c>
       <c r="L46" s="5" t="inlineStr"/>
       <c r="M46" s="5" t="inlineStr"/>
       <c r="N46" s="5" t="n">
@@ -3509,7 +3581,9 @@
       <c r="J47" s="5" t="n">
         <v>0.0426</v>
       </c>
-      <c r="K47" s="5" t="inlineStr"/>
+      <c r="K47" s="5" t="n">
+        <v>0.0328</v>
+      </c>
       <c r="L47" s="5" t="inlineStr"/>
       <c r="M47" s="5" t="inlineStr"/>
       <c r="N47" s="5" t="n">
@@ -3879,7 +3953,9 @@
       <c r="E5" s="5" t="n">
         <v>0.1726</v>
       </c>
-      <c r="F5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="n">
+        <v>0.1928</v>
+      </c>
       <c r="G5" s="5" t="inlineStr"/>
       <c r="H5" s="5" t="inlineStr"/>
       <c r="I5" s="5" t="inlineStr"/>
@@ -4023,7 +4099,9 @@
       <c r="E7" s="5" t="n">
         <v>0.2766</v>
       </c>
-      <c r="F7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="n">
+        <v>0.302</v>
+      </c>
       <c r="G7" s="5" t="n">
         <v>0.501077617843089</v>
       </c>
@@ -4225,7 +4303,9 @@
       <c r="E10" s="5" t="n">
         <v>0.2415</v>
       </c>
-      <c r="F10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="n">
+        <v>0.2987</v>
+      </c>
       <c r="G10" s="5" t="n">
         <v>0.511388342191138</v>
       </c>
@@ -4453,7 +4533,9 @@
       <c r="E13" s="5" t="n">
         <v>0.3012</v>
       </c>
-      <c r="F13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="n">
+        <v>0.2557</v>
+      </c>
       <c r="G13" s="5" t="n">
         <v>0.510590381447813</v>
       </c>
@@ -4535,7 +4617,9 @@
       <c r="E14" s="5" t="n">
         <v>0.2462</v>
       </c>
-      <c r="F14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="n">
+        <v>0.3446</v>
+      </c>
       <c r="G14" s="5" t="n">
         <v>0.65425629128861</v>
       </c>
@@ -4617,7 +4701,9 @@
       <c r="E15" s="5" t="n">
         <v>0.2411</v>
       </c>
-      <c r="F15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="n">
+        <v>0.3571</v>
+      </c>
       <c r="G15" s="5" t="n">
         <v>0.65425629128861</v>
       </c>
@@ -4699,7 +4785,9 @@
       <c r="E16" s="5" t="n">
         <v>0.1273</v>
       </c>
-      <c r="F16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="n">
+        <v>0.2429</v>
+      </c>
       <c r="G16" s="5" t="n">
         <v>0.65425629128861</v>
       </c>
@@ -4781,7 +4869,9 @@
       <c r="E17" s="5" t="n">
         <v>0.2031</v>
       </c>
-      <c r="F17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="n">
+        <v>0.3023</v>
+      </c>
       <c r="G17" s="5" t="n">
         <v>0.65425629128861</v>
       </c>
@@ -4945,7 +5035,9 @@
       <c r="E19" s="5" t="n">
         <v>0.3589</v>
       </c>
-      <c r="F19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="n">
+        <v>0.4077</v>
+      </c>
       <c r="G19" s="5" t="n">
         <v>0.501077617843089</v>
       </c>
@@ -5027,7 +5119,9 @@
       <c r="E20" s="5" t="n">
         <v>0.2973</v>
       </c>
-      <c r="F20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="n">
+        <v>0.3825</v>
+      </c>
       <c r="G20" s="5" t="n">
         <v>0.511370986967519</v>
       </c>
@@ -5093,7 +5187,9 @@
       <c r="E21" s="5" t="n">
         <v>0.3511</v>
       </c>
-      <c r="F21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="n">
+        <v>0.4088</v>
+      </c>
       <c r="G21" s="5" t="n">
         <v>0.511370986967519</v>
       </c>
@@ -5159,7 +5255,9 @@
       <c r="E22" s="5" t="n">
         <v>0.254</v>
       </c>
-      <c r="F22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="n">
+        <v>0.2722</v>
+      </c>
       <c r="G22" s="5" t="inlineStr"/>
       <c r="H22" s="5" t="inlineStr"/>
       <c r="I22" s="5" t="inlineStr"/>
@@ -5221,7 +5319,9 @@
       <c r="E23" s="5" t="n">
         <v>0.0515</v>
       </c>
-      <c r="F23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="n">
+        <v>0.0373</v>
+      </c>
       <c r="G23" s="5" t="inlineStr"/>
       <c r="H23" s="5" t="inlineStr"/>
       <c r="I23" s="5" t="inlineStr"/>
@@ -5283,7 +5383,9 @@
       <c r="E24" s="5" t="n">
         <v>0.0062</v>
       </c>
-      <c r="F24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="n">
+        <v>0.0175</v>
+      </c>
       <c r="G24" s="5" t="inlineStr"/>
       <c r="H24" s="5" t="inlineStr"/>
       <c r="I24" s="5" t="inlineStr"/>
@@ -5345,7 +5447,9 @@
       <c r="E25" s="5" t="n">
         <v>0.176</v>
       </c>
-      <c r="F25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="n">
+        <v>0.09</v>
+      </c>
       <c r="G25" s="5" t="inlineStr"/>
       <c r="H25" s="5" t="inlineStr"/>
       <c r="I25" s="5" t="inlineStr"/>
@@ -5405,7 +5509,9 @@
         <v>0.9687</v>
       </c>
       <c r="E26" s="5" t="inlineStr"/>
-      <c r="F26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="n">
+        <v>0.2684</v>
+      </c>
       <c r="G26" s="5" t="inlineStr"/>
       <c r="H26" s="5" t="inlineStr"/>
       <c r="I26" s="5" t="inlineStr"/>
@@ -5467,7 +5573,9 @@
       <c r="E27" s="5" t="n">
         <v>0.1169</v>
       </c>
-      <c r="F27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="n">
+        <v>0.1842</v>
+      </c>
       <c r="G27" s="5" t="inlineStr"/>
       <c r="H27" s="5" t="inlineStr"/>
       <c r="I27" s="5" t="inlineStr"/>
@@ -5529,7 +5637,9 @@
       <c r="E28" s="5" t="n">
         <v>0.1053</v>
       </c>
-      <c r="F28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="n">
+        <v>0.1829</v>
+      </c>
       <c r="G28" s="5" t="inlineStr"/>
       <c r="H28" s="5" t="inlineStr"/>
       <c r="I28" s="5" t="inlineStr"/>
@@ -5591,7 +5701,9 @@
       <c r="E29" s="5" t="n">
         <v>0.0033</v>
       </c>
-      <c r="F29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="n">
+        <v>0.0016</v>
+      </c>
       <c r="G29" s="5" t="inlineStr"/>
       <c r="H29" s="5" t="inlineStr"/>
       <c r="I29" s="5" t="inlineStr"/>
@@ -5653,7 +5765,9 @@
       <c r="E30" s="5" t="n">
         <v>0.0038</v>
       </c>
-      <c r="F30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="n">
+        <v>0.0011</v>
+      </c>
       <c r="G30" s="5" t="inlineStr"/>
       <c r="H30" s="5" t="inlineStr"/>
       <c r="I30" s="5" t="inlineStr"/>
@@ -5715,7 +5829,9 @@
       <c r="E31" s="5" t="n">
         <v>0.0027</v>
       </c>
-      <c r="F31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="n">
+        <v>0.0015</v>
+      </c>
       <c r="G31" s="5" t="inlineStr"/>
       <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="5" t="inlineStr"/>
@@ -5777,7 +5893,9 @@
       <c r="E32" s="5" t="n">
         <v>0.1941</v>
       </c>
-      <c r="F32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="n">
+        <v>0.2447</v>
+      </c>
       <c r="G32" s="5" t="inlineStr"/>
       <c r="H32" s="5" t="inlineStr"/>
       <c r="I32" s="5" t="inlineStr"/>
@@ -5839,7 +5957,9 @@
       <c r="E33" s="5" t="n">
         <v>0.2514</v>
       </c>
-      <c r="F33" s="5" t="inlineStr"/>
+      <c r="F33" s="5" t="n">
+        <v>0.2681</v>
+      </c>
       <c r="G33" s="5" t="inlineStr"/>
       <c r="H33" s="5" t="inlineStr"/>
       <c r="I33" s="5" t="inlineStr"/>
@@ -5901,7 +6021,9 @@
       <c r="E34" s="5" t="n">
         <v>0.2535</v>
       </c>
-      <c r="F34" s="5" t="inlineStr"/>
+      <c r="F34" s="5" t="n">
+        <v>0.2928</v>
+      </c>
       <c r="G34" s="5" t="inlineStr"/>
       <c r="H34" s="5" t="inlineStr"/>
       <c r="I34" s="5" t="inlineStr"/>
@@ -5963,7 +6085,9 @@
       <c r="E35" s="5" t="n">
         <v>0.1438</v>
       </c>
-      <c r="F35" s="5" t="inlineStr"/>
+      <c r="F35" s="5" t="n">
+        <v>0.1687</v>
+      </c>
       <c r="G35" s="5" t="inlineStr"/>
       <c r="H35" s="5" t="inlineStr"/>
       <c r="I35" s="5" t="inlineStr"/>
@@ -6025,7 +6149,9 @@
       <c r="E36" s="5" t="n">
         <v>0.1628</v>
       </c>
-      <c r="F36" s="5" t="inlineStr"/>
+      <c r="F36" s="5" t="n">
+        <v>0.1911</v>
+      </c>
       <c r="G36" s="5" t="inlineStr"/>
       <c r="H36" s="5" t="inlineStr"/>
       <c r="I36" s="5" t="inlineStr"/>
@@ -6087,7 +6213,9 @@
       <c r="E37" s="5" t="n">
         <v>0.287</v>
       </c>
-      <c r="F37" s="5" t="inlineStr"/>
+      <c r="F37" s="5" t="n">
+        <v>0.1473</v>
+      </c>
       <c r="G37" s="5" t="inlineStr"/>
       <c r="H37" s="5" t="inlineStr"/>
       <c r="I37" s="5" t="inlineStr"/>
@@ -6149,7 +6277,9 @@
       <c r="E38" s="5" t="n">
         <v>0.1193</v>
       </c>
-      <c r="F38" s="5" t="inlineStr"/>
+      <c r="F38" s="5" t="n">
+        <v>0.1648</v>
+      </c>
       <c r="G38" s="5" t="inlineStr"/>
       <c r="H38" s="5" t="inlineStr"/>
       <c r="I38" s="5" t="inlineStr"/>
@@ -6211,7 +6341,9 @@
       <c r="E39" s="5" t="n">
         <v>0.1943</v>
       </c>
-      <c r="F39" s="5" t="inlineStr"/>
+      <c r="F39" s="5" t="n">
+        <v>0.2082</v>
+      </c>
       <c r="G39" s="5" t="inlineStr"/>
       <c r="H39" s="5" t="inlineStr"/>
       <c r="I39" s="5" t="inlineStr"/>
@@ -6273,7 +6405,9 @@
       <c r="E40" s="5" t="n">
         <v>0.0037</v>
       </c>
-      <c r="F40" s="5" t="inlineStr"/>
+      <c r="F40" s="5" t="n">
+        <v>0.0026</v>
+      </c>
       <c r="G40" s="5" t="inlineStr"/>
       <c r="H40" s="5" t="inlineStr"/>
       <c r="I40" s="5" t="inlineStr"/>
@@ -6335,7 +6469,9 @@
       <c r="E41" s="5" t="n">
         <v>0.0026</v>
       </c>
-      <c r="F41" s="5" t="inlineStr"/>
+      <c r="F41" s="5" t="n">
+        <v>0.0028</v>
+      </c>
       <c r="G41" s="5" t="inlineStr"/>
       <c r="H41" s="5" t="inlineStr"/>
       <c r="I41" s="5" t="inlineStr"/>
@@ -6397,7 +6533,9 @@
       <c r="E42" s="5" t="n">
         <v>0.1825</v>
       </c>
-      <c r="F42" s="5" t="inlineStr"/>
+      <c r="F42" s="5" t="n">
+        <v>0.2632</v>
+      </c>
       <c r="G42" s="5" t="inlineStr"/>
       <c r="H42" s="5" t="inlineStr"/>
       <c r="I42" s="5" t="inlineStr"/>
@@ -6459,7 +6597,9 @@
       <c r="E43" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F43" s="5" t="inlineStr"/>
+      <c r="F43" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="G43" s="5" t="inlineStr"/>
       <c r="H43" s="5" t="inlineStr"/>
       <c r="I43" s="5" t="inlineStr"/>
@@ -6521,7 +6661,9 @@
       <c r="E44" s="5" t="n">
         <v>0.0847</v>
       </c>
-      <c r="F44" s="5" t="inlineStr"/>
+      <c r="F44" s="5" t="n">
+        <v>0.1771</v>
+      </c>
       <c r="G44" s="5" t="inlineStr"/>
       <c r="H44" s="5" t="inlineStr"/>
       <c r="I44" s="5" t="inlineStr"/>
@@ -6583,7 +6725,9 @@
       <c r="E45" s="5" t="n">
         <v>0.0203</v>
       </c>
-      <c r="F45" s="5" t="inlineStr"/>
+      <c r="F45" s="5" t="n">
+        <v>0.0122</v>
+      </c>
       <c r="G45" s="5" t="inlineStr"/>
       <c r="H45" s="5" t="inlineStr"/>
       <c r="I45" s="5" t="inlineStr"/>
@@ -6645,7 +6789,9 @@
       <c r="E46" s="5" t="n">
         <v>0.1598</v>
       </c>
-      <c r="F46" s="5" t="inlineStr"/>
+      <c r="F46" s="5" t="n">
+        <v>0.1908</v>
+      </c>
       <c r="G46" s="5" t="inlineStr"/>
       <c r="H46" s="5" t="inlineStr"/>
       <c r="I46" s="5" t="inlineStr"/>
@@ -6707,7 +6853,9 @@
       <c r="E47" s="5" t="n">
         <v>0.0426</v>
       </c>
-      <c r="F47" s="5" t="inlineStr"/>
+      <c r="F47" s="5" t="n">
+        <v>0.0328</v>
+      </c>
       <c r="G47" s="5" t="inlineStr"/>
       <c r="H47" s="5" t="inlineStr"/>
       <c r="I47" s="5" t="inlineStr"/>
